--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71676</v>
+        <v>71916</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>86676</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>124813</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47694</v>
+        <v>47811</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>62694</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90279</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94739</v>
+        <v>95098</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>109739</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>158024</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>84665</v>
+        <v>79913</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>99665</v>
+        <v>94913</v>
       </c>
       <c r="G5">
-        <v>143518</v>
+        <v>136675</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7144</v>
+        <v>6869</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30510</v>
+        <v>30400</v>
       </c>
       <c r="G7">
-        <v>43934</v>
+        <v>43776</v>
       </c>
       <c r="H7">
-        <v>23366</v>
+        <v>23531</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>38650</v>
+        <v>38780</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>54775</v>
+        <v>54827</v>
       </c>
       <c r="G8">
-        <v>78876</v>
+        <v>78951</v>
       </c>
       <c r="H8">
-        <v>16125</v>
+        <v>16047</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56058</v>
+        <v>56270</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78400</v>
+        <v>78484</v>
       </c>
       <c r="G10">
-        <v>112896</v>
+        <v>113017</v>
       </c>
       <c r="H10">
-        <v>22342</v>
+        <v>22214</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>61222</v>
+        <v>61454</v>
       </c>
       <c r="E11">
         <v>111059</v>
       </c>
       <c r="F11">
-        <v>76222</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>109760</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82558</v>
+        <v>82823</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>99133</v>
+        <v>99183</v>
       </c>
       <c r="G12">
-        <v>142752</v>
+        <v>142824</v>
       </c>
       <c r="H12">
-        <v>16575</v>
+        <v>16360</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13401</v>
+        <v>13451</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40401</v>
+        <v>40451</v>
       </c>
       <c r="G13">
-        <v>58177</v>
+        <v>58249</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27118</v>
+        <v>27205</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45720</v>
+        <v>45755</v>
       </c>
       <c r="G15">
-        <v>65837</v>
+        <v>65887</v>
       </c>
       <c r="H15">
-        <v>18602</v>
+        <v>18550</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54268</v>
+        <v>26315</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>69268</v>
+        <v>53315</v>
       </c>
       <c r="G21">
-        <v>99746</v>
+        <v>76774</v>
       </c>
       <c r="H21">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21273</v>
+        <v>21354</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>39772</v>
+        <v>39805</v>
       </c>
       <c r="G27">
-        <v>57272</v>
+        <v>57319</v>
       </c>
       <c r="H27">
-        <v>18499</v>
+        <v>18451</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80261</v>
+        <v>80518</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>97179</v>
+        <v>96515</v>
       </c>
       <c r="G28">
-        <v>139938</v>
+        <v>138982</v>
       </c>
       <c r="H28">
-        <v>16918</v>
+        <v>15997</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>41849</v>
+        <v>39194</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>68849</v>
+        <v>66194</v>
       </c>
       <c r="G29">
-        <v>99143</v>
+        <v>95319</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>135733</v>
+        <v>136184</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>150733</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>217056</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72120</v>
+        <v>72393</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>99120</v>
+        <v>99393</v>
       </c>
       <c r="G31">
-        <v>142733</v>
+        <v>143126</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60335</v>
+        <v>60563</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80424</v>
+        <v>80545</v>
       </c>
       <c r="G32">
-        <v>115811</v>
+        <v>115985</v>
       </c>
       <c r="H32">
-        <v>20089</v>
+        <v>19982</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>35893</v>
+        <v>36014</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>62893</v>
+        <v>63014</v>
       </c>
       <c r="G33">
-        <v>90566</v>
+        <v>90740</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>84175</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>99175</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>142812</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48360</v>
+        <v>48543</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75360</v>
+        <v>75543</v>
       </c>
       <c r="G36">
-        <v>108518</v>
+        <v>108782</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35355</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>62355</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89791</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>101851</v>
+        <v>102237</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>128851</v>
+        <v>129237</v>
       </c>
       <c r="G38">
-        <v>185545</v>
+        <v>186101</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>98351</v>
+        <v>98723</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>117534</v>
+        <v>117682</v>
       </c>
       <c r="G39">
-        <v>169249</v>
+        <v>169462</v>
       </c>
       <c r="H39">
-        <v>19183</v>
+        <v>18959</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,19 +2177,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>103926</v>
+        <v>122144</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>130926</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>188533</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>133959</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>148959</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>214501</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>40931</v>
+        <v>35759</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>67931</v>
+        <v>62759</v>
       </c>
       <c r="G43">
-        <v>97821</v>
+        <v>90373</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>24631</v>
+        <v>23945</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>51631</v>
+        <v>50945</v>
       </c>
       <c r="G47">
-        <v>74349</v>
+        <v>73361</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36575</v>
+        <v>36713</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>51575</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>74268</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>26595</v>
+        <v>26680</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>41901</v>
+        <v>41935</v>
       </c>
       <c r="G51">
-        <v>60337</v>
+        <v>60386</v>
       </c>
       <c r="H51">
-        <v>15306</v>
+        <v>15255</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>51005</v>
+        <v>54044</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>66005</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>95047</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>53951</v>
+        <v>54124</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>68951</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>99289</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44653</v>
+        <v>44949</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>79653</v>
+        <v>79949</v>
       </c>
       <c r="G54">
-        <v>114700</v>
+        <v>115127</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>43512</v>
+        <v>43661</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>70512</v>
+        <v>70661</v>
       </c>
       <c r="G55">
-        <v>101537</v>
+        <v>101752</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>45287</v>
+        <v>45458</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>72287</v>
+        <v>72458</v>
       </c>
       <c r="G56">
-        <v>104093</v>
+        <v>104340</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62014</v>
+        <v>62217</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>88559</v>
+        <v>88640</v>
       </c>
       <c r="G57">
-        <v>127525</v>
+        <v>127642</v>
       </c>
       <c r="H57">
-        <v>26545</v>
+        <v>26423</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>18469</v>
+        <v>18492</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38720</v>
+        <v>38729</v>
       </c>
       <c r="G58">
-        <v>55757</v>
+        <v>55770</v>
       </c>
       <c r="H58">
-        <v>20251</v>
+        <v>20237</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6384</v>
+        <v>6408</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22987</v>
+        <v>22996</v>
       </c>
       <c r="G59">
-        <v>33101</v>
+        <v>33114</v>
       </c>
       <c r="H59">
-        <v>16603</v>
+        <v>16588</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24029</v>
+        <v>24120</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>48423</v>
+        <v>48520</v>
       </c>
       <c r="G60">
-        <v>69729</v>
+        <v>69869</v>
       </c>
       <c r="H60">
-        <v>24394</v>
+        <v>24400</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25423</v>
+        <v>25520</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>40423</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58209</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14177</v>
+        <v>14215</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41177</v>
+        <v>41215</v>
       </c>
       <c r="G63">
-        <v>59295</v>
+        <v>59350</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23111</v>
+        <v>23198</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>50111</v>
+        <v>50198</v>
       </c>
       <c r="G65">
-        <v>72160</v>
+        <v>72285</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>28496</v>
+        <v>29367</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60507</v>
+        <v>61551</v>
       </c>
       <c r="G66">
-        <v>87130</v>
+        <v>88633</v>
       </c>
       <c r="H66">
-        <v>32011</v>
+        <v>32184</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>19721</v>
+        <v>20765</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>46721</v>
+        <v>47765</v>
       </c>
       <c r="G67">
-        <v>67278</v>
+        <v>68782</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47837</v>
+        <v>48018</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>74837</v>
+        <v>75018</v>
       </c>
       <c r="G68">
-        <v>107765</v>
+        <v>108026</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>29098</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>56098</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>80781</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110088</v>
+        <v>110505</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>125088</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>180127</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50244</v>
+        <v>50435</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>76631</v>
+        <v>76707</v>
       </c>
       <c r="G71">
-        <v>110349</v>
+        <v>110458</v>
       </c>
       <c r="H71">
-        <v>26387</v>
+        <v>26272</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>8379</v>
+        <v>6821</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>23379</v>
+        <v>21821</v>
       </c>
       <c r="G73">
-        <v>33666</v>
+        <v>31422</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>70278</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85278</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>122800</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87738</v>
+        <v>88038</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>122106</v>
+        <v>122177</v>
       </c>
       <c r="G76">
-        <v>175833</v>
+        <v>175935</v>
       </c>
       <c r="H76">
-        <v>34368</v>
+        <v>34139</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>59891</v>
+        <v>60070</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>80490</v>
+        <v>80561</v>
       </c>
       <c r="G77">
-        <v>115906</v>
+        <v>116008</v>
       </c>
       <c r="H77">
-        <v>20599</v>
+        <v>20491</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,19 +3974,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>38174</v>
+        <v>35362</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>57363</v>
+        <v>56238</v>
       </c>
       <c r="G81">
-        <v>82603</v>
+        <v>80983</v>
       </c>
       <c r="H81">
-        <v>19189</v>
+        <v>20876</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86787</v>
+        <v>87068</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>101787</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>146573</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>50577</v>
+        <v>60754</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>67144</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>96687</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>16567</v>
+        <v>0</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>43386</v>
+        <v>32007</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>58386</v>
+        <v>47675</v>
       </c>
       <c r="G85">
-        <v>84076</v>
+        <v>68652</v>
       </c>
       <c r="H85">
-        <v>15000</v>
+        <v>15668</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8173</v>
+        <v>8204</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38567</v>
+        <v>38573</v>
       </c>
       <c r="G90">
-        <v>55536</v>
+        <v>55545</v>
       </c>
       <c r="H90">
-        <v>30394</v>
+        <v>30369</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3675</v>
+        <v>3689</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30567</v>
+        <v>30573</v>
       </c>
       <c r="G91">
-        <v>44016</v>
+        <v>44025</v>
       </c>
       <c r="H91">
-        <v>26892</v>
+        <v>26884</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9456</v>
+        <v>9492</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>24456</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35217</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>59796</v>
+        <v>60007</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>77461</v>
+        <v>77507</v>
       </c>
       <c r="G96">
-        <v>111544</v>
+        <v>111610</v>
       </c>
       <c r="H96">
-        <v>17665</v>
+        <v>17500</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34404</v>
+        <v>34519</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52245</v>
+        <v>52291</v>
       </c>
       <c r="G97">
-        <v>75233</v>
+        <v>75299</v>
       </c>
       <c r="H97">
-        <v>17841</v>
+        <v>17772</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>78931</v>
+        <v>79198</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>93931</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>135261</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>49785</v>
+        <v>42262</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>64785</v>
+        <v>60442</v>
       </c>
       <c r="G99">
-        <v>93290</v>
+        <v>87036</v>
       </c>
       <c r="H99">
-        <v>15000</v>
+        <v>18180</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,7 +4809,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>62869</v>
+        <v>63107</v>
       </c>
       <c r="E100">
         <v>107912</v>
@@ -4821,7 +4821,7 @@
         <v>116545</v>
       </c>
       <c r="H100">
-        <v>18065</v>
+        <v>17827</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63138</v>
+        <v>63377</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>78138</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>112519</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71343</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>86343</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>124334</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6146</v>
+        <v>6169</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33146</v>
+        <v>33169</v>
       </c>
       <c r="G109">
-        <v>47730</v>
+        <v>47763</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14446</v>
+        <v>14501</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>41446</v>
+        <v>41501</v>
       </c>
       <c r="G111">
-        <v>59682</v>
+        <v>59761</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,16 +5370,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48375</v>
+        <v>48527</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>75375</v>
+        <v>75527</v>
       </c>
       <c r="G113">
-        <v>108540</v>
+        <v>108759</v>
       </c>
       <c r="H113">
         <v>27000</v>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>98018</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>117400</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>169056</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>19382</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5541,19 +5541,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>176140</v>
       </c>
       <c r="E117">
         <v>185111</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>191140</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>275242</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>79976</v>
+        <v>80247</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>94976</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>136765</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>46744</v>
+        <v>49751</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>61744</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>88911</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>85504</v>
+        <v>102078</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>100504</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>144726</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>207092</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>148085</v>
       </c>
       <c r="F122">
-        <v>222092</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>319812</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>113224</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>148085</v>
       </c>
       <c r="F123">
-        <v>128224</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>184643</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>45968</v>
+        <v>46142</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>60968</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>87794</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35355</v>
+        <v>35489</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>50355</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72511</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63455</v>
+        <v>63695</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>81078</v>
+        <v>78695</v>
       </c>
       <c r="G126">
-        <v>116752</v>
+        <v>113321</v>
       </c>
       <c r="H126">
-        <v>17623</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>55503</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>81439</v>
       </c>
       <c r="F127">
-        <v>70503</v>
+        <v>0</v>
       </c>
       <c r="G127">
-        <v>101524</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>38665</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>92546</v>
       </c>
       <c r="F128">
-        <v>65450</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>94248</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>26785</v>
+        <v>0</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>37050</v>
+        <v>37174</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56913</v>
+        <v>56963</v>
       </c>
       <c r="G129">
-        <v>81955</v>
+        <v>82027</v>
       </c>
       <c r="H129">
-        <v>19863</v>
+        <v>19789</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12672</v>
+        <v>12720</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33146</v>
+        <v>33140</v>
       </c>
       <c r="G130">
-        <v>47730</v>
+        <v>47722</v>
       </c>
       <c r="H130">
-        <v>20474</v>
+        <v>20420</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4562</v>
+        <v>4547</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25146</v>
+        <v>25140</v>
       </c>
       <c r="G131">
-        <v>36210</v>
+        <v>36202</v>
       </c>
       <c r="H131">
-        <v>20584</v>
+        <v>20593</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27498</v>
+        <v>27602</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43649</v>
+        <v>43691</v>
       </c>
       <c r="G132">
-        <v>62855</v>
+        <v>62915</v>
       </c>
       <c r="H132">
-        <v>16151</v>
+        <v>16089</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>18279</v>
+        <v>17744</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36979</v>
+        <v>36765</v>
       </c>
       <c r="G135">
-        <v>53250</v>
+        <v>52942</v>
       </c>
       <c r="H135">
-        <v>18700</v>
+        <v>19021</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28464</v>
+        <v>28572</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46873</v>
+        <v>46916</v>
       </c>
       <c r="G137">
-        <v>67497</v>
+        <v>67559</v>
       </c>
       <c r="H137">
-        <v>18409</v>
+        <v>18344</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>29573</v>
+        <v>29479</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54948</v>
+        <v>54910</v>
       </c>
       <c r="G139">
-        <v>79125</v>
+        <v>79070</v>
       </c>
       <c r="H139">
-        <v>25375</v>
+        <v>25431</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,16 +6591,16 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58196</v>
+        <v>52661</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>73196</v>
+        <v>67661</v>
       </c>
       <c r="G141">
-        <v>105402</v>
+        <v>97432</v>
       </c>
       <c r="H141">
         <v>15000</v>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77347</v>
+        <v>77608</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>92347</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>132980</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>97131</v>
+        <v>97451</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>112131</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>161469</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>85932</v>
+        <v>88134</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>100932</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>145342</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>125817</v>
+        <v>126151</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>140817</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>202776</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38174</v>
+        <v>38303</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62916</v>
+        <v>62967</v>
       </c>
       <c r="G150">
-        <v>90599</v>
+        <v>90672</v>
       </c>
       <c r="H150">
-        <v>24742</v>
+        <v>24664</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,19 +7067,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>22825</v>
+        <v>22848</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>49825</v>
+        <v>57848</v>
       </c>
       <c r="G152">
-        <v>71748</v>
+        <v>83301</v>
       </c>
       <c r="H152">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>14525</v>
+        <v>29653</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>41525</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>59796</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48550</v>
+        <v>48718</v>
       </c>
       <c r="E154">
         <v>92546</v>
       </c>
       <c r="F154">
-        <v>67068</v>
+        <v>67133</v>
       </c>
       <c r="G154">
-        <v>96578</v>
+        <v>96672</v>
       </c>
       <c r="H154">
-        <v>18518</v>
+        <v>18415</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>40218</v>
+        <v>40354</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>58180</v>
+        <v>58235</v>
       </c>
       <c r="G155">
-        <v>83779</v>
+        <v>83858</v>
       </c>
       <c r="H155">
-        <v>17962</v>
+        <v>17881</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65736</v>
+        <v>65953</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80736</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>116260</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38792</v>
+        <v>38939</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65450</v>
+        <v>65614</v>
       </c>
       <c r="G158">
-        <v>94248</v>
+        <v>94484</v>
       </c>
       <c r="H158">
-        <v>26658</v>
+        <v>26675</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>41913</v>
+        <v>42056</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>56913</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>81955</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>17899</v>
+        <v>23707</v>
       </c>
       <c r="E161">
         <v>83290</v>
       </c>
       <c r="F161">
-        <v>44899</v>
+        <v>47966</v>
       </c>
       <c r="G161">
-        <v>64655</v>
+        <v>69071</v>
       </c>
       <c r="H161">
-        <v>27000</v>
+        <v>24259</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>54331</v>
+        <v>54521</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>69331</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>99837</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>76460</v>
+        <v>76718</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>91460</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>131702</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>41327</v>
+        <v>46110</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>61110</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>87998</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33882</v>
+        <v>33994</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>48882</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70390</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60208</v>
+        <v>60436</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>95436</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>137428</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>73846</v>
+        <v>74126</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>88846</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>127938</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,16 +7902,16 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15903</v>
+        <v>15391</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>30903</v>
+        <v>30391</v>
       </c>
       <c r="G171">
-        <v>44500</v>
+        <v>43763</v>
       </c>
       <c r="H171">
         <v>15000</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30207</v>
+        <v>30687</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51288</v>
+        <v>51480</v>
       </c>
       <c r="G173">
-        <v>73855</v>
+        <v>74131</v>
       </c>
       <c r="H173">
-        <v>21081</v>
+        <v>20793</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7714</v>
+        <v>7282</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37764</v>
+        <v>37778</v>
       </c>
       <c r="G174">
-        <v>54380</v>
+        <v>54400</v>
       </c>
       <c r="H174">
-        <v>30050</v>
+        <v>30496</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5259</v>
+        <v>5295</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29764</v>
+        <v>29778</v>
       </c>
       <c r="G175">
-        <v>42860</v>
+        <v>42880</v>
       </c>
       <c r="H175">
-        <v>24505</v>
+        <v>24483</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10280</v>
+        <v>10319</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>45201</v>
+        <v>43077</v>
       </c>
       <c r="G176">
-        <v>65089</v>
+        <v>62031</v>
       </c>
       <c r="H176">
-        <v>34921</v>
+        <v>32758</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>10201</v>
+        <v>8077</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>37201</v>
+        <v>35077</v>
       </c>
       <c r="G177">
-        <v>53569</v>
+        <v>50511</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21812</v>
+        <v>21878</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41800</v>
+        <v>41827</v>
       </c>
       <c r="G179">
-        <v>60192</v>
+        <v>60231</v>
       </c>
       <c r="H179">
-        <v>19988</v>
+        <v>19949</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45793</v>
+        <v>45983</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65111</v>
+        <v>65187</v>
       </c>
       <c r="G181">
-        <v>93760</v>
+        <v>93869</v>
       </c>
       <c r="H181">
-        <v>19318</v>
+        <v>19204</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67890</v>
+        <v>67957</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86178</v>
+        <v>86565</v>
       </c>
       <c r="G182">
-        <v>124096</v>
+        <v>124654</v>
       </c>
       <c r="H182">
-        <v>18288</v>
+        <v>18608</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>9789</v>
+        <v>10176</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>36789</v>
+        <v>37176</v>
       </c>
       <c r="G183">
-        <v>52976</v>
+        <v>53533</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60335</v>
+        <v>60563</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80110</v>
+        <v>80202</v>
       </c>
       <c r="G184">
-        <v>115358</v>
+        <v>115491</v>
       </c>
       <c r="H184">
-        <v>19775</v>
+        <v>19639</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45540</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>67529</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>97242</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>21989</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79659</v>
+        <v>79961</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>110593</v>
+        <v>104623</v>
       </c>
       <c r="G186">
-        <v>159254</v>
+        <v>150657</v>
       </c>
       <c r="H186">
-        <v>30934</v>
+        <v>24662</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81037</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>96168</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>138482</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15131</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>146694</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>157342</v>
       </c>
       <c r="F190">
-        <v>161694</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>232839</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>171674</v>
+        <v>172324</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>186674</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>268811</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>6748</v>
+        <v>7123</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>28190</v>
+        <v>27815</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11722</v>
+        <v>11766</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38722</v>
+        <v>38766</v>
       </c>
       <c r="G196">
-        <v>55760</v>
+        <v>55823</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,19 +9083,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>55979</v>
+        <v>54791</v>
       </c>
       <c r="E198">
         <v>92546</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>89791</v>
       </c>
       <c r="G198">
-        <v>0</v>
+        <v>129299</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74765</v>
+        <v>75016</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>89765</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129262</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>54616</v>
+        <v>59673</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>69616</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>100247</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36590</v>
+        <v>36729</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63590</v>
+        <v>63729</v>
       </c>
       <c r="G202">
-        <v>91570</v>
+        <v>91770</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27387</v>
+        <v>27491</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54387</v>
+        <v>54491</v>
       </c>
       <c r="G204">
-        <v>78317</v>
+        <v>78467</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101360</v>
+        <v>101744</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>116360</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>167558</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>65261</v>
+        <v>65317</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82638</v>
+        <v>82660</v>
       </c>
       <c r="G207">
-        <v>118999</v>
+        <v>119030</v>
       </c>
       <c r="H207">
-        <v>17377</v>
+        <v>17343</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144128</v>
+        <v>144674</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>179128</v>
+        <v>179674</v>
       </c>
       <c r="G208">
-        <v>257944</v>
+        <v>258731</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>146076</v>
+        <v>146455</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>161076</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>231949</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>186896</v>
+        <v>187604</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>201896</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>290730</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>187736</v>
+        <v>188240</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>202736</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>291940</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>286688</v>
+        <v>287774</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>301688</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>434431</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>223613</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>370241</v>
       </c>
       <c r="F213">
-        <v>239839</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>345368</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>16226</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,16 +9784,16 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34040</v>
+        <v>33994</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>69040</v>
+        <v>68994</v>
       </c>
       <c r="G214">
-        <v>99418</v>
+        <v>99351</v>
       </c>
       <c r="H214">
         <v>35000</v>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>52652</v>
+        <v>51850</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>67652</v>
+        <v>66850</v>
       </c>
       <c r="G215">
-        <v>97419</v>
+        <v>96264</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>24378</v>
+        <v>46142</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>39911</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>57472</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>15533</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>24378</v>
+        <v>67400</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>39911</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>57472</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>15533</v>
+        <v>0</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13036</v>
+        <v>13277</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>46484</v>
+        <v>46528</v>
       </c>
       <c r="G220">
-        <v>66937</v>
+        <v>67000</v>
       </c>
       <c r="H220">
-        <v>33448</v>
+        <v>33251</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11484</v>
+        <v>11528</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>38484</v>
+        <v>38528</v>
       </c>
       <c r="G221">
-        <v>55417</v>
+        <v>55480</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21653</v>
+        <v>21735</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>48653</v>
+        <v>48735</v>
       </c>
       <c r="G222">
-        <v>70060</v>
+        <v>70178</v>
       </c>
       <c r="H222">
         <v>27000</v>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16727</v>
+        <v>16806</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>45740</v>
+        <v>45780</v>
       </c>
       <c r="G224">
-        <v>65866</v>
+        <v>65923</v>
       </c>
       <c r="H224">
-        <v>29013</v>
+        <v>28974</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10740</v>
+        <v>10780</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>37740</v>
+        <v>37780</v>
       </c>
       <c r="G225">
-        <v>54346</v>
+        <v>54403</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26405</v>
+        <v>26505</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61405</v>
+        <v>61505</v>
       </c>
       <c r="G226">
-        <v>88423</v>
+        <v>88567</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38254</v>
+        <v>96529</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>65254</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>93966</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>34991</v>
+        <v>35107</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>69991</v>
+        <v>70107</v>
       </c>
       <c r="G228">
-        <v>100787</v>
+        <v>100954</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>98050</v>
+        <v>98421</v>
       </c>
       <c r="E229">
         <v>185111</v>
       </c>
       <c r="F229">
-        <v>117413</v>
+        <v>117562</v>
       </c>
       <c r="G229">
-        <v>169075</v>
+        <v>169289</v>
       </c>
       <c r="H229">
-        <v>19363</v>
+        <v>19141</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16188</v>
+        <v>16250</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42715</v>
+        <v>41368</v>
       </c>
       <c r="G230">
-        <v>61510</v>
+        <v>59570</v>
       </c>
       <c r="H230">
-        <v>26527</v>
+        <v>25118</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9520</v>
+        <v>6153</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>32905</v>
+        <v>31558</v>
       </c>
       <c r="G231">
-        <v>47383</v>
+        <v>45444</v>
       </c>
       <c r="H231">
-        <v>23385</v>
+        <v>25405</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23364</v>
+        <v>23453</v>
       </c>
       <c r="E233">
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>38364</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>55244</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41548</v>
+        <v>41706</v>
       </c>
       <c r="E235">
         <v>111059</v>
       </c>
       <c r="F235">
-        <v>65932</v>
+        <v>65995</v>
       </c>
       <c r="G235">
-        <v>94942</v>
+        <v>95033</v>
       </c>
       <c r="H235">
-        <v>24384</v>
+        <v>24289</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>86114</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>112639</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>162200</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>26525</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>25518</v>
+        <v>25186</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>60518</v>
+        <v>60186</v>
       </c>
       <c r="G238">
-        <v>87146</v>
+        <v>86668</v>
       </c>
       <c r="H238">
         <v>35000</v>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31775</v>
+        <v>31895</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>53359</v>
+        <v>53407</v>
       </c>
       <c r="G239">
-        <v>76837</v>
+        <v>76906</v>
       </c>
       <c r="H239">
-        <v>21584</v>
+        <v>21512</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46855</v>
+        <v>47016</v>
       </c>
       <c r="E240">
         <v>103654</v>
       </c>
       <c r="F240">
-        <v>77741</v>
+        <v>71451</v>
       </c>
       <c r="G240">
-        <v>111947</v>
+        <v>102889</v>
       </c>
       <c r="H240">
-        <v>30886</v>
+        <v>24435</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>85441</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>100441</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>144635</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>63978</v>
+        <v>64220</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79475</v>
+        <v>79711</v>
       </c>
       <c r="G244">
-        <v>114444</v>
+        <v>114784</v>
       </c>
       <c r="H244">
-        <v>15497</v>
+        <v>15491</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54109</v>
+        <v>54314</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>69109</v>
+        <v>0</v>
       </c>
       <c r="G245">
-        <v>99517</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75383</v>
+        <v>75668</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>90383</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>130152</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>86957</v>
       </c>
       <c r="E247">
         <v>98119</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>101957</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>146818</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>18264</v>
+        <v>18047</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>41810</v>
+        <v>42220</v>
       </c>
       <c r="G248">
-        <v>60206</v>
+        <v>60797</v>
       </c>
       <c r="H248">
-        <v>23546</v>
+        <v>24173</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>9979</v>
+        <v>11003</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>33810</v>
+        <v>34220</v>
       </c>
       <c r="G249">
-        <v>48686</v>
+        <v>49277</v>
       </c>
       <c r="H249">
-        <v>23831</v>
+        <v>23217</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>15534</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>42534</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>61249</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>21306</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>48306</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>69561</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9536</v>
+        <v>9572</v>
       </c>
       <c r="E256">
         <v>53688</v>
       </c>
       <c r="F256">
-        <v>34938</v>
+        <v>40266</v>
       </c>
       <c r="G256">
-        <v>50311</v>
+        <v>57983</v>
       </c>
       <c r="H256">
-        <v>25402</v>
+        <v>30694</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>15105</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>32980</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>47491</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>17875</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>11832</v>
+        <v>11877</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>38832</v>
+        <v>38877</v>
       </c>
       <c r="G258">
-        <v>55918</v>
+        <v>55983</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,7 +11814,7 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8823</v>
+        <v>8856</v>
       </c>
       <c r="E260">
         <v>53688</v>
@@ -11826,7 +11826,7 @@
         <v>57983</v>
       </c>
       <c r="H260">
-        <v>31443</v>
+        <v>31410</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>52620</v>
+        <v>52788</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>0</v>
+        <v>67788</v>
       </c>
       <c r="G261">
-        <v>0</v>
+        <v>97615</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>13100</v>
+        <v>14040</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>35400</v>
+        <v>39142</v>
       </c>
       <c r="G262">
-        <v>50976</v>
+        <v>56364</v>
       </c>
       <c r="H262">
-        <v>22300</v>
+        <v>25102</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>10510</v>
       </c>
       <c r="E263">
         <v>53688</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>31142</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>44844</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>20632</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,16 +11991,16 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18390</v>
+        <v>18333</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>53390</v>
+        <v>53333</v>
       </c>
       <c r="G264">
-        <v>76882</v>
+        <v>76800</v>
       </c>
       <c r="H264">
         <v>35000</v>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>73038</v>
+        <v>73315</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>88038</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>126775</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,7 +12078,7 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34262</v>
+        <v>34392</v>
       </c>
       <c r="E266">
         <v>72201</v>
@@ -12090,7 +12090,7 @@
         <v>77977</v>
       </c>
       <c r="H266">
-        <v>19889</v>
+        <v>19759</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>91777</v>
+        <v>92125</v>
       </c>
       <c r="E267">
         <v>72201</v>
       </c>
       <c r="F267">
-        <v>106777</v>
+        <v>0</v>
       </c>
       <c r="G267">
-        <v>153759</v>
+        <v>0</v>
       </c>
       <c r="H267">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10185</v>
+        <v>10271</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>25185</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>36266</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>11848</v>
+        <v>11989</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>38848</v>
+        <v>38989</v>
       </c>
       <c r="G270">
-        <v>55941</v>
+        <v>56144</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>61824</v>
+        <v>63266</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>76824</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>110627</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>41723</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>60955</v>
+        <v>0</v>
       </c>
       <c r="G273">
-        <v>87775</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>19232</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>72721</v>
+        <v>72536</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>106362</v>
+        <v>87536</v>
       </c>
       <c r="G274">
-        <v>153161</v>
+        <v>126052</v>
       </c>
       <c r="H274">
-        <v>33641</v>
+        <v>15000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>77489</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>111059</v>
       </c>
       <c r="F275">
-        <v>92489</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>133184</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,7 +12519,7 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11199</v>
+        <v>11241</v>
       </c>
       <c r="E276">
         <v>53688</v>
@@ -12531,7 +12531,7 @@
         <v>57983</v>
       </c>
       <c r="H276">
-        <v>29067</v>
+        <v>29025</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>39616</v>
+        <v>39766</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>54616</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>78647</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,7 +12608,7 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20038</v>
+        <v>20114</v>
       </c>
       <c r="E278">
         <v>72201</v>
@@ -12620,7 +12620,7 @@
         <v>77977</v>
       </c>
       <c r="H278">
-        <v>34113</v>
+        <v>34037</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>73418</v>
+        <v>73697</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>88418</v>
+        <v>0</v>
       </c>
       <c r="G279">
-        <v>127322</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11706</v>
+        <v>11750</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23232</v>
+        <v>23188</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,16 +12826,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17677</v>
+        <v>15598</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32677</v>
+        <v>30598</v>
       </c>
       <c r="G283">
-        <v>47055</v>
+        <v>44061</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>49848</v>
+        <v>50006</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>64848</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>93381</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58624</v>
+        <v>58814</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>73624</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>106019</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>40851</v>
+        <v>41006</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55851</v>
+        <v>0</v>
       </c>
       <c r="G288">
-        <v>80425</v>
+        <v>0</v>
       </c>
       <c r="H288">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23871</v>
+        <v>23914</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39367</v>
+        <v>39384</v>
       </c>
       <c r="G289">
-        <v>56688</v>
+        <v>56713</v>
       </c>
       <c r="H289">
-        <v>15496</v>
+        <v>15470</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>35703</v>
+        <v>35839</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>50703</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>73012</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23617</v>
+        <v>23691</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39266</v>
+        <v>39295</v>
       </c>
       <c r="G293">
-        <v>56543</v>
+        <v>56585</v>
       </c>
       <c r="H293">
-        <v>15649</v>
+        <v>15604</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>88643</v>
       </c>
       <c r="E294">
         <v>68480</v>
       </c>
       <c r="F294">
-        <v>0</v>
+        <v>103643</v>
       </c>
       <c r="G294">
-        <v>0</v>
+        <v>149246</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>25946</v>
+        <v>26092</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>43086</v>
+        <v>43144</v>
       </c>
       <c r="G295">
-        <v>62044</v>
+        <v>62127</v>
       </c>
       <c r="H295">
-        <v>17140</v>
+        <v>17052</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62394</v>
+        <v>62630</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>77394</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>111447</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74274</v>
+        <v>74555</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>89274</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>128555</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>67969</v>
+        <v>68227</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>87577</v>
+        <v>88414</v>
       </c>
       <c r="G300">
-        <v>126111</v>
+        <v>127316</v>
       </c>
       <c r="H300">
-        <v>19608</v>
+        <v>20187</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>31537</v>
+        <v>33629</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>54708</v>
+        <v>55545</v>
       </c>
       <c r="G301">
-        <v>78780</v>
+        <v>79985</v>
       </c>
       <c r="H301">
-        <v>23171</v>
+        <v>21916</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>10740</v>
+        <v>10780</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>37740</v>
+        <v>37780</v>
       </c>
       <c r="G303">
-        <v>54346</v>
+        <v>54403</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>173496</v>
+        <v>174153</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>188496</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>271434</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104417</v>
+        <v>0</v>
       </c>
       <c r="E305">
         <v>166598</v>
       </c>
       <c r="F305">
-        <v>119417</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>171960</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>49848</v>
+        <v>50037</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>79908</v>
+        <v>79971</v>
       </c>
       <c r="G306">
-        <v>115068</v>
+        <v>115158</v>
       </c>
       <c r="H306">
-        <v>30060</v>
+        <v>29934</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50292</v>
+        <v>50451</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69430</v>
+        <v>69493</v>
       </c>
       <c r="G307">
-        <v>99979</v>
+        <v>100070</v>
       </c>
       <c r="H307">
-        <v>19138</v>
+        <v>19042</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>68983</v>
+        <v>69245</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>28196</v>
+        <v>27934</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77584</v>
+        <v>77878</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>92584</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>133321</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24504</v>
+        <v>24597</v>
       </c>
       <c r="E310">
         <v>55520</v>
@@ -14026,7 +14026,7 @@
         <v>59962</v>
       </c>
       <c r="H310">
-        <v>17136</v>
+        <v>17043</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,16 +14058,16 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>22461</v>
+        <v>22324</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>37461</v>
+        <v>37324</v>
       </c>
       <c r="G311">
-        <v>53944</v>
+        <v>53747</v>
       </c>
       <c r="H311">
         <v>15000</v>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>65831</v>
+        <v>67337</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>89877</v>
+        <v>82337</v>
       </c>
       <c r="G312">
-        <v>129423</v>
+        <v>118565</v>
       </c>
       <c r="H312">
-        <v>24046</v>
+        <v>15000</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63154</v>
+        <v>0</v>
       </c>
       <c r="E313">
         <v>83309</v>
       </c>
       <c r="F313">
-        <v>78154</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>112542</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20877</v>
+        <v>20940</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>35877</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>51663</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32298</v>
+        <v>32420</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>49500</v>
+        <v>62798</v>
       </c>
       <c r="G316">
-        <v>71280</v>
+        <v>90429</v>
       </c>
       <c r="H316">
-        <v>17202</v>
+        <v>30378</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26500</v>
+        <v>39607</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>41500</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>59760</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16141</v>
+        <v>15820</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>17169</v>
+        <v>17490</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29352</v>
+        <v>29351</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44352</v>
+        <v>44351</v>
       </c>
       <c r="G319">
-        <v>63867</v>
+        <v>63865</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>47029</v>
+        <v>0</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>68124</v>
+        <v>0</v>
       </c>
       <c r="G321">
-        <v>98099</v>
+        <v>0</v>
       </c>
       <c r="H321">
-        <v>21095</v>
+        <v>0</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58608</v>
+        <v>58830</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>90551</v>
+        <v>73830</v>
       </c>
       <c r="G324">
-        <v>130393</v>
+        <v>106315</v>
       </c>
       <c r="H324">
-        <v>31943</v>
+        <v>15000</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>63740</v>
+        <v>0</v>
       </c>
       <c r="E325">
         <v>74033</v>
       </c>
       <c r="F325">
-        <v>78740</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>113386</v>
+        <v>0</v>
       </c>
       <c r="H325">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9377</v>
+        <v>9413</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>35014</v>
+        <v>35028</v>
       </c>
       <c r="G327">
-        <v>50420</v>
+        <v>50440</v>
       </c>
       <c r="H327">
-        <v>25637</v>
+        <v>25615</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>17045</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>38081</v>
       </c>
       <c r="G329">
-        <v>0</v>
+        <v>54837</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>21036</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20703</v>
+        <v>20781</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47703</v>
+        <v>47781</v>
       </c>
       <c r="G330">
-        <v>68692</v>
+        <v>68805</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43544</v>
+        <v>43709</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>70544</v>
+        <v>70709</v>
       </c>
       <c r="G332">
-        <v>101583</v>
+        <v>101821</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,19 +15067,19 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32741</v>
+        <v>32961</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>67741</v>
+        <v>59961</v>
       </c>
       <c r="G334">
-        <v>97547</v>
+        <v>86344</v>
       </c>
       <c r="H334">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I334" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49231</v>
+        <v>0</v>
       </c>
       <c r="E335">
         <v>111059</v>
       </c>
       <c r="F335">
-        <v>69005</v>
+        <v>0</v>
       </c>
       <c r="G335">
-        <v>99367</v>
+        <v>0</v>
       </c>
       <c r="H335">
-        <v>19774</v>
+        <v>0</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188464</v>
+        <v>189099</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>203464</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>292988</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>143811</v>
+        <v>0</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>158811</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>228688</v>
+        <v>0</v>
       </c>
       <c r="H337">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>62378</v>
+        <v>59991</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89259</v>
+        <v>86991</v>
       </c>
       <c r="G338">
-        <v>128533</v>
+        <v>125267</v>
       </c>
       <c r="H338">
-        <v>26881</v>
+        <v>27000</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>47267</v>
+        <v>0</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>74267</v>
+        <v>0</v>
       </c>
       <c r="G339">
-        <v>106944</v>
+        <v>0</v>
       </c>
       <c r="H339">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>109581</v>
+        <v>109996</v>
       </c>
       <c r="E341">
         <v>185111</v>
       </c>
       <c r="F341">
-        <v>124581</v>
+        <v>0</v>
       </c>
       <c r="G341">
-        <v>179397</v>
+        <v>0</v>
       </c>
       <c r="H341">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>103673</v>
+        <v>0</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>138673</v>
+        <v>0</v>
       </c>
       <c r="G342">
-        <v>199689</v>
+        <v>0</v>
       </c>
       <c r="H342">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>143827</v>
+        <v>144372</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>158827</v>
+        <v>0</v>
       </c>
       <c r="G343">
-        <v>228711</v>
+        <v>0</v>
       </c>
       <c r="H343">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71916</v>
+        <v>71601</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86601</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>124705</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47811</v>
+        <v>47650</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>62650</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90216</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95098</v>
+        <v>94667</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>109667</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>157920</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>79913</v>
+        <v>79575</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>94913</v>
+        <v>94575</v>
       </c>
       <c r="G5">
-        <v>136675</v>
+        <v>136188</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>6869</v>
+        <v>6613</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30400</v>
+        <v>30298</v>
       </c>
       <c r="G7">
-        <v>43776</v>
+        <v>43629</v>
       </c>
       <c r="H7">
-        <v>23531</v>
+        <v>23685</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>38780</v>
+        <v>35832</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>54827</v>
+        <v>53648</v>
       </c>
       <c r="G8">
-        <v>78951</v>
+        <v>77253</v>
       </c>
       <c r="H8">
-        <v>16047</v>
+        <v>17816</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56270</v>
+        <v>55987</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78484</v>
+        <v>78371</v>
       </c>
       <c r="G10">
-        <v>113017</v>
+        <v>112854</v>
       </c>
       <c r="H10">
-        <v>22214</v>
+        <v>22384</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,7 +903,7 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>61454</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>111059</v>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82823</v>
+        <v>82470</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>99183</v>
+        <v>99116</v>
       </c>
       <c r="G12">
-        <v>142824</v>
+        <v>142727</v>
       </c>
       <c r="H12">
-        <v>16360</v>
+        <v>16646</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13451</v>
+        <v>13384</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40451</v>
+        <v>40384</v>
       </c>
       <c r="G13">
-        <v>58249</v>
+        <v>58153</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27205</v>
+        <v>27084</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45755</v>
+        <v>45706</v>
       </c>
       <c r="G15">
-        <v>65887</v>
+        <v>65817</v>
       </c>
       <c r="H15">
-        <v>18550</v>
+        <v>18622</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,16 +1336,16 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>26315</v>
+        <v>26198</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>53315</v>
+        <v>53198</v>
       </c>
       <c r="G21">
-        <v>76774</v>
+        <v>76605</v>
       </c>
       <c r="H21">
         <v>27000</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21354</v>
+        <v>21262</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>39805</v>
+        <v>39768</v>
       </c>
       <c r="G27">
-        <v>57319</v>
+        <v>57266</v>
       </c>
       <c r="H27">
-        <v>18451</v>
+        <v>18506</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80518</v>
+        <v>80065</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96515</v>
+        <v>96349</v>
       </c>
       <c r="G28">
-        <v>138982</v>
+        <v>138743</v>
       </c>
       <c r="H28">
-        <v>15997</v>
+        <v>16284</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>39194</v>
+        <v>39028</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>66194</v>
+        <v>66028</v>
       </c>
       <c r="G29">
-        <v>95319</v>
+        <v>95080</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>136184</v>
+        <v>135609</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>150609</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>216877</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,19 +1776,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72393</v>
+        <v>97499</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>99393</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>143126</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60563</v>
+        <v>60986</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80545</v>
+        <v>80395</v>
       </c>
       <c r="G32">
-        <v>115985</v>
+        <v>115769</v>
       </c>
       <c r="H32">
-        <v>19982</v>
+        <v>19409</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36014</v>
+        <v>35864</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63014</v>
+        <v>62864</v>
       </c>
       <c r="G33">
-        <v>90740</v>
+        <v>90524</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>84175</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>99175</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>142812</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,19 +2000,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48543</v>
+        <v>61745</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75543</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>108782</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>102237</v>
+        <v>101754</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>129237</v>
+        <v>128754</v>
       </c>
       <c r="G38">
-        <v>186101</v>
+        <v>185406</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>98723</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>117682</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>169462</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>18959</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,19 +2177,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>122144</v>
+        <v>123396</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>150396</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>216570</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>35759</v>
+        <v>33190</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>62759</v>
+        <v>60190</v>
       </c>
       <c r="G43">
-        <v>90373</v>
+        <v>86674</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>79132</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>106132</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>152830</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>23945</v>
+        <v>24126</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>50945</v>
+        <v>51126</v>
       </c>
       <c r="G47">
-        <v>73361</v>
+        <v>73621</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36713</v>
+        <v>38949</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>53949</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>77687</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>26680</v>
+        <v>23999</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>41935</v>
+        <v>40863</v>
       </c>
       <c r="G51">
-        <v>60386</v>
+        <v>58843</v>
       </c>
       <c r="H51">
-        <v>15255</v>
+        <v>16864</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54044</v>
+        <v>58629</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>73629</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>106026</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>54124</v>
+        <v>53930</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>68930</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>99259</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44949</v>
+        <v>44755</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>79949</v>
+        <v>79755</v>
       </c>
       <c r="G54">
-        <v>115127</v>
+        <v>114847</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>43661</v>
+        <v>43473</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>70661</v>
+        <v>70473</v>
       </c>
       <c r="G55">
-        <v>101752</v>
+        <v>101481</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>45458</v>
+        <v>50719</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>72458</v>
+        <v>77719</v>
       </c>
       <c r="G56">
-        <v>104340</v>
+        <v>111915</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62217</v>
+        <v>61951</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>88640</v>
+        <v>88533</v>
       </c>
       <c r="G57">
-        <v>127642</v>
+        <v>127488</v>
       </c>
       <c r="H57">
-        <v>26423</v>
+        <v>26582</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>18492</v>
+        <v>18130</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38729</v>
+        <v>38716</v>
       </c>
       <c r="G58">
-        <v>55770</v>
+        <v>55751</v>
       </c>
       <c r="H58">
-        <v>20237</v>
+        <v>20586</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6408</v>
+        <v>6375</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22996</v>
+        <v>22983</v>
       </c>
       <c r="G59">
-        <v>33114</v>
+        <v>33096</v>
       </c>
       <c r="H59">
-        <v>16588</v>
+        <v>16608</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24120</v>
+        <v>23999</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>48520</v>
+        <v>48391</v>
       </c>
       <c r="G60">
-        <v>69869</v>
+        <v>69683</v>
       </c>
       <c r="H60">
-        <v>24400</v>
+        <v>24392</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25520</v>
+        <v>25391</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40391</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58163</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14215</v>
+        <v>14159</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41215</v>
+        <v>41159</v>
       </c>
       <c r="G63">
-        <v>59350</v>
+        <v>59269</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23198</v>
+        <v>23097</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>50198</v>
+        <v>50097</v>
       </c>
       <c r="G65">
-        <v>72285</v>
+        <v>72140</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>29367</v>
+        <v>29188</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>61551</v>
+        <v>61463</v>
       </c>
       <c r="G66">
-        <v>88633</v>
+        <v>88507</v>
       </c>
       <c r="H66">
-        <v>32184</v>
+        <v>32275</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20765</v>
+        <v>20677</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47765</v>
+        <v>47677</v>
       </c>
       <c r="G67">
-        <v>68782</v>
+        <v>68655</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48018</v>
+        <v>47792</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75018</v>
+        <v>74792</v>
       </c>
       <c r="G68">
-        <v>108026</v>
+        <v>107700</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110505</v>
+        <v>109996</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>124996</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>179994</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50435</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>76707</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>110458</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>26272</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6821</v>
+        <v>6787</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21821</v>
+        <v>21787</v>
       </c>
       <c r="G73">
-        <v>31422</v>
+        <v>31373</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70278</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>85278</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>122800</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88038</v>
+        <v>87659</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>122177</v>
+        <v>122075</v>
       </c>
       <c r="G76">
-        <v>175935</v>
+        <v>175788</v>
       </c>
       <c r="H76">
-        <v>34139</v>
+        <v>34416</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>60070</v>
+        <v>59815</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>80561</v>
+        <v>80459</v>
       </c>
       <c r="G77">
-        <v>116008</v>
+        <v>115861</v>
       </c>
       <c r="H77">
-        <v>20491</v>
+        <v>20644</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,19 +3974,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>35362</v>
+        <v>27558</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>56238</v>
+        <v>53116</v>
       </c>
       <c r="G81">
-        <v>80983</v>
+        <v>76487</v>
       </c>
       <c r="H81">
-        <v>20876</v>
+        <v>25558</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87068</v>
+        <v>86709</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>101709</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>146461</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>60754</v>
+        <v>50545</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>65545</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>94385</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32007</v>
+        <v>28634</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>47675</v>
+        <v>46326</v>
       </c>
       <c r="G85">
-        <v>68652</v>
+        <v>66709</v>
       </c>
       <c r="H85">
-        <v>15668</v>
+        <v>17692</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8204</v>
+        <v>8163</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38573</v>
+        <v>38565</v>
       </c>
       <c r="G90">
-        <v>55545</v>
+        <v>55534</v>
       </c>
       <c r="H90">
-        <v>30369</v>
+        <v>30402</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3689</v>
+        <v>3670</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30573</v>
+        <v>30565</v>
       </c>
       <c r="G91">
-        <v>44025</v>
+        <v>44014</v>
       </c>
       <c r="H91">
-        <v>26884</v>
+        <v>26895</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9492</v>
+        <v>9445</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24445</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35201</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>60007</v>
+        <v>59721</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>77507</v>
+        <v>77450</v>
       </c>
       <c r="G96">
-        <v>111610</v>
+        <v>111528</v>
       </c>
       <c r="H96">
-        <v>17500</v>
+        <v>17729</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34519</v>
+        <v>34377</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52291</v>
+        <v>52234</v>
       </c>
       <c r="G97">
-        <v>75299</v>
+        <v>75217</v>
       </c>
       <c r="H97">
-        <v>17772</v>
+        <v>17857</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79198</v>
+        <v>78847</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>93847</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>135140</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>42262</v>
+        <v>43679</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>60442</v>
+        <v>61009</v>
       </c>
       <c r="G99">
-        <v>87036</v>
+        <v>87853</v>
       </c>
       <c r="H99">
-        <v>18180</v>
+        <v>17330</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>63107</v>
+        <v>60369</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>80934</v>
+        <v>78708</v>
       </c>
       <c r="G100">
-        <v>116545</v>
+        <v>113340</v>
       </c>
       <c r="H100">
-        <v>17827</v>
+        <v>18339</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,7 +4855,7 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63377</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>107912</v>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6169</v>
+        <v>6138</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33169</v>
+        <v>33138</v>
       </c>
       <c r="G109">
-        <v>47763</v>
+        <v>47719</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14501</v>
+        <v>14428</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>41501</v>
+        <v>41428</v>
       </c>
       <c r="G111">
-        <v>59761</v>
+        <v>59656</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,16 +5370,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48527</v>
+        <v>48330</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>75527</v>
+        <v>75330</v>
       </c>
       <c r="G113">
-        <v>108759</v>
+        <v>108475</v>
       </c>
       <c r="H113">
         <v>27000</v>
@@ -5541,19 +5541,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>176140</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>185111</v>
       </c>
       <c r="F117">
-        <v>191140</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>275242</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80247</v>
+        <v>79907</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>94907</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>136666</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>49751</v>
+        <v>46637</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>61637</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>88757</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102078</v>
+        <v>101644</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>116644</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>167967</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>206926</v>
       </c>
       <c r="E122">
         <v>148085</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>221926</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>319573</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46142</v>
+        <v>45941</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>60941</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>87755</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35489</v>
+        <v>35405</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50405</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72583</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,16 +5935,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63695</v>
+        <v>63391</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>78695</v>
+        <v>78391</v>
       </c>
       <c r="G126">
-        <v>113321</v>
+        <v>112883</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>37174</v>
+        <v>37019</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56963</v>
+        <v>56901</v>
       </c>
       <c r="G129">
-        <v>82027</v>
+        <v>81937</v>
       </c>
       <c r="H129">
-        <v>19789</v>
+        <v>19882</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12720</v>
+        <v>12672</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33140</v>
+        <v>33310</v>
       </c>
       <c r="G130">
-        <v>47722</v>
+        <v>47966</v>
       </c>
       <c r="H130">
-        <v>20420</v>
+        <v>20638</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4547</v>
+        <v>6075</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25140</v>
+        <v>25751</v>
       </c>
       <c r="G131">
-        <v>36202</v>
+        <v>37081</v>
       </c>
       <c r="H131">
-        <v>20593</v>
+        <v>19676</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27602</v>
+        <v>27479</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43691</v>
+        <v>43642</v>
       </c>
       <c r="G132">
-        <v>62915</v>
+        <v>62844</v>
       </c>
       <c r="H132">
-        <v>16089</v>
+        <v>16163</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17744</v>
+        <v>17355</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36765</v>
+        <v>36610</v>
       </c>
       <c r="G135">
-        <v>52942</v>
+        <v>52718</v>
       </c>
       <c r="H135">
-        <v>19021</v>
+        <v>19255</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28572</v>
+        <v>27638</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46916</v>
+        <v>46542</v>
       </c>
       <c r="G137">
-        <v>67559</v>
+        <v>67020</v>
       </c>
       <c r="H137">
-        <v>18344</v>
+        <v>18904</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>29479</v>
+        <v>27653</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54910</v>
+        <v>54180</v>
       </c>
       <c r="G139">
-        <v>79070</v>
+        <v>78019</v>
       </c>
       <c r="H139">
-        <v>25431</v>
+        <v>26527</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>52661</v>
+        <v>57933</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>67661</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>97432</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77608</v>
+        <v>77265</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>92265</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>132862</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>97451</v>
+        <v>97040</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>112040</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>161338</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>88134</v>
+        <v>87754</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>102754</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>147966</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>126151</v>
+        <v>125611</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>140611</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>202480</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38303</v>
+        <v>38142</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62967</v>
+        <v>62903</v>
       </c>
       <c r="G150">
-        <v>90672</v>
+        <v>90580</v>
       </c>
       <c r="H150">
-        <v>24664</v>
+        <v>24761</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>22848</v>
+        <v>23050</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>57848</v>
+        <v>58050</v>
       </c>
       <c r="G152">
-        <v>83301</v>
+        <v>83592</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29653</v>
+        <v>29536</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>53907</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>77626</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>24371</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48718</v>
+        <v>48504</v>
       </c>
       <c r="E154">
         <v>92546</v>
       </c>
       <c r="F154">
-        <v>67133</v>
+        <v>67064</v>
       </c>
       <c r="G154">
-        <v>96672</v>
+        <v>96572</v>
       </c>
       <c r="H154">
-        <v>18415</v>
+        <v>18560</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>40354</v>
+        <v>40183</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>58235</v>
+        <v>58166</v>
       </c>
       <c r="G155">
-        <v>83858</v>
+        <v>83759</v>
       </c>
       <c r="H155">
-        <v>17881</v>
+        <v>17983</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65953</v>
+        <v>65194</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80194</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>115479</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38939</v>
+        <v>38743</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65614</v>
+        <v>65425</v>
       </c>
       <c r="G158">
-        <v>94484</v>
+        <v>94212</v>
       </c>
       <c r="H158">
-        <v>26675</v>
+        <v>26682</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42056</v>
+        <v>41891</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>56891</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>81923</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>83290</v>
+        <v>55520</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>23707</v>
+        <v>23619</v>
       </c>
       <c r="E161">
-        <v>83290</v>
+        <v>55520</v>
       </c>
       <c r="F161">
-        <v>47966</v>
+        <v>38619</v>
       </c>
       <c r="G161">
-        <v>69071</v>
+        <v>55611</v>
       </c>
       <c r="H161">
-        <v>24259</v>
+        <v>15000</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>54521</v>
+        <v>54278</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>69278</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>99760</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>76718</v>
+        <v>76395</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>91395</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>131609</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>46110</v>
+        <v>51557</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>61110</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>87998</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33994</v>
+        <v>33855</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>48855</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70351</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60436</v>
+        <v>60148</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>95436</v>
+        <v>75148</v>
       </c>
       <c r="G168">
-        <v>137428</v>
+        <v>108213</v>
       </c>
       <c r="H168">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,7 +7815,7 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74126</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>74033</v>
@@ -7902,16 +7902,16 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15391</v>
+        <v>14934</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>30391</v>
+        <v>29934</v>
       </c>
       <c r="G171">
-        <v>43763</v>
+        <v>43105</v>
       </c>
       <c r="H171">
         <v>15000</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30687</v>
+        <v>31150</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51480</v>
+        <v>51665</v>
       </c>
       <c r="G173">
-        <v>74131</v>
+        <v>74398</v>
       </c>
       <c r="H173">
-        <v>20793</v>
+        <v>20515</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7282</v>
+        <v>7467</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37778</v>
+        <v>37761</v>
       </c>
       <c r="G174">
-        <v>54400</v>
+        <v>54376</v>
       </c>
       <c r="H174">
-        <v>30496</v>
+        <v>30294</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5295</v>
+        <v>5252</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29778</v>
+        <v>29761</v>
       </c>
       <c r="G175">
-        <v>42880</v>
+        <v>42856</v>
       </c>
       <c r="H175">
-        <v>24483</v>
+        <v>24509</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10319</v>
+        <v>10283</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>43077</v>
+        <v>44856</v>
       </c>
       <c r="G176">
-        <v>62031</v>
+        <v>64593</v>
       </c>
       <c r="H176">
-        <v>32758</v>
+        <v>34573</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>8077</v>
+        <v>9856</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>35077</v>
+        <v>36856</v>
       </c>
       <c r="G177">
-        <v>50511</v>
+        <v>53073</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21878</v>
+        <v>21784</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41827</v>
+        <v>41789</v>
       </c>
       <c r="G179">
-        <v>60231</v>
+        <v>60176</v>
       </c>
       <c r="H179">
-        <v>19949</v>
+        <v>20005</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45983</v>
+        <v>45783</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65187</v>
+        <v>65107</v>
       </c>
       <c r="G181">
-        <v>93869</v>
+        <v>93754</v>
       </c>
       <c r="H181">
-        <v>19204</v>
+        <v>19324</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67957</v>
+        <v>67615</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86565</v>
+        <v>86514</v>
       </c>
       <c r="G182">
-        <v>124654</v>
+        <v>124580</v>
       </c>
       <c r="H182">
-        <v>18608</v>
+        <v>18899</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10176</v>
+        <v>10125</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37176</v>
+        <v>37125</v>
       </c>
       <c r="G183">
-        <v>53533</v>
+        <v>53460</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60563</v>
+        <v>72345</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80202</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>115491</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>19639</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79961</v>
+        <v>89082</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>104623</v>
+        <v>108271</v>
       </c>
       <c r="G186">
-        <v>150657</v>
+        <v>155910</v>
       </c>
       <c r="H186">
-        <v>24662</v>
+        <v>19189</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8823,7 +8823,7 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>172324</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>185111</v>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7123</v>
+        <v>6739</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>27815</v>
+        <v>28199</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11766</v>
+        <v>11707</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38766</v>
+        <v>38707</v>
       </c>
       <c r="G196">
-        <v>55823</v>
+        <v>55738</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,16 +9083,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>54791</v>
+        <v>54563</v>
       </c>
       <c r="E198">
         <v>92546</v>
       </c>
       <c r="F198">
-        <v>89791</v>
+        <v>89563</v>
       </c>
       <c r="G198">
-        <v>129299</v>
+        <v>128971</v>
       </c>
       <c r="H198">
         <v>35000</v>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75016</v>
+        <v>74702</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>89702</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>129171</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>59673</v>
+        <v>59420</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>74420</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>107165</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,19 +9259,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36729</v>
+        <v>55133</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63729</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>91770</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27491</v>
+        <v>27369</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54491</v>
+        <v>54369</v>
       </c>
       <c r="G204">
-        <v>78467</v>
+        <v>78291</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101744</v>
+        <v>101232</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>116232</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>167374</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>65317</v>
+        <v>64862</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82660</v>
+        <v>82478</v>
       </c>
       <c r="G207">
-        <v>119030</v>
+        <v>118768</v>
       </c>
       <c r="H207">
-        <v>17343</v>
+        <v>17616</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144674</v>
+        <v>143946</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>179674</v>
+        <v>178946</v>
       </c>
       <c r="G208">
-        <v>258731</v>
+        <v>257682</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>146455</v>
+        <v>145829</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>160829</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>231594</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187604</v>
+        <v>186660</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>201660</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>290390</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>188240</v>
+        <v>158880</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>173880</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>250387</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>287774</v>
+        <v>286326</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>301326</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>433909</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,16 +9784,16 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>33994</v>
+        <v>34345</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>68994</v>
+        <v>69345</v>
       </c>
       <c r="G214">
-        <v>99351</v>
+        <v>99857</v>
       </c>
       <c r="H214">
         <v>35000</v>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>51850</v>
+        <v>51589</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>66850</v>
+        <v>66589</v>
       </c>
       <c r="G215">
-        <v>96264</v>
+        <v>95888</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>46142</v>
+        <v>45941</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>60941</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>87755</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67400</v>
+        <v>16358</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>36703</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>52852</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>20345</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13277</v>
+        <v>13226</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>46528</v>
+        <v>46470</v>
       </c>
       <c r="G220">
-        <v>67000</v>
+        <v>66917</v>
       </c>
       <c r="H220">
-        <v>33251</v>
+        <v>33244</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11528</v>
+        <v>11470</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>38528</v>
+        <v>38470</v>
       </c>
       <c r="G221">
-        <v>55480</v>
+        <v>55397</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21735</v>
+        <v>21610</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>48735</v>
+        <v>48610</v>
       </c>
       <c r="G222">
-        <v>70178</v>
+        <v>69998</v>
       </c>
       <c r="H222">
         <v>27000</v>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16806</v>
+        <v>16326</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>45780</v>
+        <v>45726</v>
       </c>
       <c r="G224">
-        <v>65923</v>
+        <v>65845</v>
       </c>
       <c r="H224">
-        <v>28974</v>
+        <v>29400</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10780</v>
+        <v>10726</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>37780</v>
+        <v>37726</v>
       </c>
       <c r="G225">
-        <v>54403</v>
+        <v>54325</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26505</v>
+        <v>26372</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61505</v>
+        <v>61372</v>
       </c>
       <c r="G226">
-        <v>88567</v>
+        <v>88376</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>96529</v>
+        <v>96122</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>111122</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>160016</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,19 +10406,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35107</v>
+        <v>34962</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>70107</v>
+        <v>61962</v>
       </c>
       <c r="G228">
-        <v>100954</v>
+        <v>89225</v>
       </c>
       <c r="H228">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>98421</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>185111</v>
       </c>
       <c r="F229">
-        <v>117562</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>169289</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>19141</v>
+        <v>0</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16250</v>
+        <v>16136</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>41368</v>
+        <v>41356</v>
       </c>
       <c r="G230">
-        <v>59570</v>
+        <v>59553</v>
       </c>
       <c r="H230">
-        <v>25118</v>
+        <v>25220</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>6153</v>
+        <v>6122</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>31558</v>
+        <v>31546</v>
       </c>
       <c r="G231">
-        <v>45444</v>
+        <v>45426</v>
       </c>
       <c r="H231">
-        <v>25405</v>
+        <v>25424</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23453</v>
+        <v>23335</v>
       </c>
       <c r="E233">
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>38335</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>55202</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41706</v>
+        <v>41496</v>
       </c>
       <c r="E235">
         <v>111059</v>
       </c>
       <c r="F235">
-        <v>65995</v>
+        <v>65911</v>
       </c>
       <c r="G235">
-        <v>95033</v>
+        <v>94912</v>
       </c>
       <c r="H235">
-        <v>24289</v>
+        <v>24415</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>86114</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>112639</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>162200</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>26525</v>
+        <v>0</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>25186</v>
+        <v>25043</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>60186</v>
+        <v>60043</v>
       </c>
       <c r="G238">
-        <v>86668</v>
+        <v>86462</v>
       </c>
       <c r="H238">
         <v>35000</v>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31895</v>
+        <v>31735</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>53407</v>
+        <v>53343</v>
       </c>
       <c r="G239">
-        <v>76906</v>
+        <v>76814</v>
       </c>
       <c r="H239">
-        <v>21512</v>
+        <v>21608</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47016</v>
+        <v>46811</v>
       </c>
       <c r="E240">
         <v>103654</v>
       </c>
       <c r="F240">
-        <v>71451</v>
+        <v>77741</v>
       </c>
       <c r="G240">
-        <v>102889</v>
+        <v>111947</v>
       </c>
       <c r="H240">
-        <v>24435</v>
+        <v>30930</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>85333</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>100333</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>144480</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64220</v>
+        <v>63929</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79711</v>
+        <v>79397</v>
       </c>
       <c r="G244">
-        <v>114784</v>
+        <v>114332</v>
       </c>
       <c r="H244">
-        <v>15491</v>
+        <v>15468</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54314</v>
+        <v>54041</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>0</v>
+        <v>69041</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>99419</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75668</v>
+        <v>75287</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>90287</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>130013</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>86957</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>98119</v>
       </c>
       <c r="F247">
-        <v>101957</v>
+        <v>0</v>
       </c>
       <c r="G247">
-        <v>146818</v>
+        <v>0</v>
       </c>
       <c r="H247">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>18047</v>
+        <v>17655</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42220</v>
+        <v>42204</v>
       </c>
       <c r="G248">
-        <v>60797</v>
+        <v>60774</v>
       </c>
       <c r="H248">
-        <v>24173</v>
+        <v>24549</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11003</v>
+        <v>10963</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34220</v>
+        <v>34204</v>
       </c>
       <c r="G249">
-        <v>49277</v>
+        <v>49254</v>
       </c>
       <c r="H249">
-        <v>23217</v>
+        <v>23241</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>15534</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>42534</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>61249</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11596,16 +11596,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>21306</v>
+        <v>20867</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>48306</v>
+        <v>47867</v>
       </c>
       <c r="G255">
-        <v>69561</v>
+        <v>68928</v>
       </c>
       <c r="H255">
         <v>27000</v>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9572</v>
+        <v>9508</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>57983</v>
       </c>
       <c r="H256">
-        <v>30694</v>
+        <v>30758</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>15105</v>
+        <v>14823</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>32980</v>
+        <v>32867</v>
       </c>
       <c r="G257">
-        <v>47491</v>
+        <v>47328</v>
       </c>
       <c r="H257">
-        <v>17875</v>
+        <v>18044</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>11877</v>
+        <v>11818</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>38877</v>
+        <v>38818</v>
       </c>
       <c r="G258">
-        <v>55983</v>
+        <v>55898</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,7 +11814,7 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8856</v>
+        <v>8828</v>
       </c>
       <c r="E260">
         <v>53688</v>
@@ -11826,7 +11826,7 @@
         <v>57983</v>
       </c>
       <c r="H260">
-        <v>31410</v>
+        <v>31438</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,16 +11859,16 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>52788</v>
+        <v>52554</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>67788</v>
+        <v>67554</v>
       </c>
       <c r="G261">
-        <v>97615</v>
+        <v>97278</v>
       </c>
       <c r="H261">
         <v>15000</v>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>14040</v>
+        <v>13827</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>39142</v>
+        <v>39121</v>
       </c>
       <c r="G262">
-        <v>56364</v>
+        <v>56334</v>
       </c>
       <c r="H262">
-        <v>25102</v>
+        <v>25294</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10510</v>
+        <v>10457</v>
       </c>
       <c r="E263">
         <v>53688</v>
       </c>
       <c r="F263">
-        <v>31142</v>
+        <v>31121</v>
       </c>
       <c r="G263">
-        <v>44844</v>
+        <v>44814</v>
       </c>
       <c r="H263">
-        <v>20632</v>
+        <v>20664</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18333</v>
+        <v>17940</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>53333</v>
+        <v>44940</v>
       </c>
       <c r="G264">
-        <v>76800</v>
+        <v>64714</v>
       </c>
       <c r="H264">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,7 +12035,7 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>73315</v>
+        <v>0</v>
       </c>
       <c r="E265">
         <v>72201</v>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34392</v>
+        <v>34234</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>54151</v>
+        <v>52184</v>
       </c>
       <c r="G266">
-        <v>77977</v>
+        <v>75145</v>
       </c>
       <c r="H266">
-        <v>19759</v>
+        <v>17950</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,7 +12123,7 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>92125</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>72201</v>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10271</v>
+        <v>10220</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>25220</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>36317</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>11989</v>
+        <v>11818</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>38989</v>
+        <v>38818</v>
       </c>
       <c r="G270">
-        <v>56144</v>
+        <v>55898</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>63266</v>
+        <v>61255</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>76255</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>109807</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,16 +12430,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>72536</v>
+        <v>71079</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>87536</v>
+        <v>86079</v>
       </c>
       <c r="G274">
-        <v>126052</v>
+        <v>123954</v>
       </c>
       <c r="H274">
         <v>15000</v>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11241</v>
+        <v>11201</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>40266</v>
+        <v>34938</v>
       </c>
       <c r="G276">
-        <v>57983</v>
+        <v>50311</v>
       </c>
       <c r="H276">
-        <v>29025</v>
+        <v>23737</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,7 +12565,7 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>39766</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>53688</v>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20114</v>
+        <v>19965</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>54151</v>
+        <v>46477</v>
       </c>
       <c r="G278">
-        <v>77977</v>
+        <v>66927</v>
       </c>
       <c r="H278">
-        <v>34037</v>
+        <v>26512</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,7 +12654,7 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>73697</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>72201</v>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11750</v>
+        <v>11691</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23188</v>
+        <v>23247</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>15598</v>
+        <v>17655</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>30598</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>44061</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50006</v>
+        <v>49786</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>64786</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>93292</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58814</v>
+        <v>58566</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>73566</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>105935</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>41006</v>
+        <v>40800</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>0</v>
+        <v>55800</v>
       </c>
       <c r="G288">
-        <v>0</v>
+        <v>80352</v>
       </c>
       <c r="H288">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23914</v>
+        <v>23809</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39384</v>
+        <v>39342</v>
       </c>
       <c r="G289">
-        <v>56713</v>
+        <v>56652</v>
       </c>
       <c r="H289">
-        <v>15470</v>
+        <v>15533</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>35839</v>
+        <v>35674</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>50674</v>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>72971</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23691</v>
+        <v>23588</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39295</v>
+        <v>39254</v>
       </c>
       <c r="G293">
-        <v>56585</v>
+        <v>56526</v>
       </c>
       <c r="H293">
-        <v>15604</v>
+        <v>15666</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>88643</v>
+        <v>0</v>
       </c>
       <c r="E294">
         <v>68480</v>
       </c>
       <c r="F294">
-        <v>103643</v>
+        <v>0</v>
       </c>
       <c r="G294">
-        <v>149246</v>
+        <v>0</v>
       </c>
       <c r="H294">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>26092</v>
+        <v>0</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>43144</v>
+        <v>0</v>
       </c>
       <c r="G295">
-        <v>62127</v>
+        <v>0</v>
       </c>
       <c r="H295">
-        <v>17052</v>
+        <v>0</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62630</v>
+        <v>62315</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>77315</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>111334</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74555</v>
+        <v>74180</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>89180</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>128419</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>68227</v>
+        <v>67915</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>88414</v>
+        <v>89270</v>
       </c>
       <c r="G300">
-        <v>127316</v>
+        <v>128549</v>
       </c>
       <c r="H300">
-        <v>20187</v>
+        <v>21355</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33629</v>
+        <v>35769</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>55545</v>
+        <v>56401</v>
       </c>
       <c r="G301">
-        <v>79985</v>
+        <v>81217</v>
       </c>
       <c r="H301">
-        <v>21916</v>
+        <v>20632</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>10780</v>
+        <v>12102</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>37780</v>
+        <v>39102</v>
       </c>
       <c r="G303">
-        <v>54403</v>
+        <v>56307</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174153</v>
+        <v>173371</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>188371</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>271254</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50037</v>
+        <v>49817</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>79971</v>
+        <v>79888</v>
       </c>
       <c r="G306">
-        <v>115158</v>
+        <v>115039</v>
       </c>
       <c r="H306">
-        <v>29934</v>
+        <v>30071</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50451</v>
+        <v>50244</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69493</v>
+        <v>69410</v>
       </c>
       <c r="G307">
-        <v>100070</v>
+        <v>99950</v>
       </c>
       <c r="H307">
-        <v>19042</v>
+        <v>19166</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69245</v>
+        <v>68944</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>27934</v>
+        <v>28235</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77878</v>
+        <v>105282</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>120282</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>173206</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24597</v>
+        <v>24426</v>
       </c>
       <c r="E310">
         <v>55520</v>
       </c>
       <c r="F310">
-        <v>41640</v>
+        <v>40754</v>
       </c>
       <c r="G310">
-        <v>59962</v>
+        <v>58686</v>
       </c>
       <c r="H310">
-        <v>17043</v>
+        <v>16328</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>22324</v>
+        <v>0</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>37324</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>53747</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,16 +14101,16 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>67337</v>
+        <v>67235</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>82337</v>
+        <v>82235</v>
       </c>
       <c r="G312">
-        <v>118565</v>
+        <v>118418</v>
       </c>
       <c r="H312">
         <v>15000</v>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20940</v>
+        <v>20851</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>35851</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>51625</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32420</v>
+        <v>32257</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>62798</v>
+        <v>62605</v>
       </c>
       <c r="G316">
-        <v>90429</v>
+        <v>90151</v>
       </c>
       <c r="H316">
-        <v>30378</v>
+        <v>30348</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39607</v>
+        <v>39439</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>54439</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>78392</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>15820</v>
+        <v>12118</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>17490</v>
+        <v>21192</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29351</v>
+        <v>29220</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44351</v>
+        <v>44220</v>
       </c>
       <c r="G319">
-        <v>63865</v>
+        <v>63677</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>46970</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>0</v>
+        <v>68101</v>
       </c>
       <c r="G321">
-        <v>0</v>
+        <v>98065</v>
       </c>
       <c r="H321">
-        <v>0</v>
+        <v>21131</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58830</v>
+        <v>0</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>73830</v>
+        <v>0</v>
       </c>
       <c r="G324">
-        <v>106315</v>
+        <v>0</v>
       </c>
       <c r="H324">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9413</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>35028</v>
+        <v>0</v>
       </c>
       <c r="G327">
-        <v>50440</v>
+        <v>0</v>
       </c>
       <c r="H327">
-        <v>25615</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>17045</v>
+        <v>16959</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>38081</v>
+        <v>38047</v>
       </c>
       <c r="G329">
-        <v>54837</v>
+        <v>54788</v>
       </c>
       <c r="H329">
-        <v>21036</v>
+        <v>21088</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20781</v>
+        <v>20693</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47781</v>
+        <v>47693</v>
       </c>
       <c r="G330">
-        <v>68805</v>
+        <v>68678</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,19 +14979,19 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43709</v>
+        <v>43505</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>70709</v>
+        <v>78505</v>
       </c>
       <c r="G332">
-        <v>101821</v>
+        <v>113047</v>
       </c>
       <c r="H332">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I332" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>0</v>
+        <v>83023</v>
       </c>
       <c r="E333">
         <v>111059</v>
       </c>
       <c r="F333">
-        <v>0</v>
+        <v>98023</v>
       </c>
       <c r="G333">
-        <v>0</v>
+        <v>141153</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32961</v>
+        <v>32985</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>59961</v>
+        <v>59985</v>
       </c>
       <c r="G334">
-        <v>86344</v>
+        <v>86378</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>189099</v>
+        <v>188385</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>203385</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>292874</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>143630</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>158630</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>228427</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,16 +15243,16 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>59991</v>
+        <v>59721</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>86991</v>
+        <v>86721</v>
       </c>
       <c r="G338">
-        <v>125267</v>
+        <v>124878</v>
       </c>
       <c r="H338">
         <v>27000</v>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>41686</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>0</v>
+        <v>68686</v>
       </c>
       <c r="G339">
-        <v>0</v>
+        <v>98908</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15372,7 +15372,7 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>109996</v>
+        <v>0</v>
       </c>
       <c r="E341">
         <v>185111</v>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>103542</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>0</v>
+        <v>138542</v>
       </c>
       <c r="G342">
-        <v>0</v>
+        <v>199500</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>144372</v>
+        <v>143646</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>158646</v>
       </c>
       <c r="G343">
-        <v>0</v>
+        <v>228450</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71601</v>
+        <v>71694</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>86601</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>124705</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47650</v>
+        <v>47712</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>62650</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90216</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94667</v>
+        <v>94758</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>109667</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>157920</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>94575</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>136188</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>6613</v>
+        <v>6474</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30298</v>
+        <v>30242</v>
       </c>
       <c r="G7">
-        <v>43629</v>
+        <v>43548</v>
       </c>
       <c r="H7">
-        <v>23685</v>
+        <v>23768</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35832</v>
+        <v>38673</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>53648</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>77253</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>17816</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>55987</v>
+        <v>56323</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78371</v>
+        <v>78506</v>
       </c>
       <c r="G10">
-        <v>112854</v>
+        <v>113049</v>
       </c>
       <c r="H10">
-        <v>22384</v>
+        <v>22183</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82470</v>
+        <v>82585</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>99116</v>
+        <v>99140</v>
       </c>
       <c r="G12">
-        <v>142727</v>
+        <v>142762</v>
       </c>
       <c r="H12">
-        <v>16646</v>
+        <v>16555</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13384</v>
+        <v>13408</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40384</v>
+        <v>40408</v>
       </c>
       <c r="G13">
-        <v>58153</v>
+        <v>58188</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27084</v>
+        <v>27117</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45706</v>
+        <v>45719</v>
       </c>
       <c r="G15">
-        <v>65817</v>
+        <v>65835</v>
       </c>
       <c r="H15">
-        <v>18622</v>
+        <v>18602</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,16 +1336,16 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>26198</v>
+        <v>26230</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>53198</v>
+        <v>53230</v>
       </c>
       <c r="G21">
-        <v>76605</v>
+        <v>76651</v>
       </c>
       <c r="H21">
         <v>27000</v>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>95629</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>110629</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>159306</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21262</v>
+        <v>21291</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>39768</v>
+        <v>39779</v>
       </c>
       <c r="G27">
-        <v>57266</v>
+        <v>57282</v>
       </c>
       <c r="H27">
-        <v>18506</v>
+        <v>18488</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80065</v>
+        <v>80163</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96349</v>
+        <v>96389</v>
       </c>
       <c r="G28">
-        <v>138743</v>
+        <v>138800</v>
       </c>
       <c r="H28">
-        <v>16284</v>
+        <v>16226</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>39028</v>
+        <v>39068</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>66028</v>
+        <v>66068</v>
       </c>
       <c r="G29">
-        <v>95080</v>
+        <v>95138</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>135609</v>
+        <v>135774</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>150609</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>216877</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,19 +1776,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>97499</v>
+        <v>79942</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>106942</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>153996</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60986</v>
+        <v>59315</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80395</v>
+        <v>80433</v>
       </c>
       <c r="G32">
-        <v>115769</v>
+        <v>115824</v>
       </c>
       <c r="H32">
-        <v>19409</v>
+        <v>21118</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>35864</v>
+        <v>35902</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>62864</v>
+        <v>62902</v>
       </c>
       <c r="G33">
-        <v>90524</v>
+        <v>90579</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>83646</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>98646</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>142050</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,19 +2000,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>61745</v>
+        <v>61832</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>88832</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>127918</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35333</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62333</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>89760</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>101754</v>
+        <v>101866</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>128754</v>
+        <v>128866</v>
       </c>
       <c r="G38">
-        <v>185406</v>
+        <v>185567</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2177,19 +2177,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>123396</v>
+        <v>173703</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>150396</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>216570</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>33190</v>
+        <v>33211</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>60190</v>
+        <v>60211</v>
       </c>
       <c r="G43">
-        <v>86674</v>
+        <v>86704</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,16 +2393,16 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>79132</v>
+        <v>81714</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>106132</v>
+        <v>108714</v>
       </c>
       <c r="G45">
-        <v>152830</v>
+        <v>156548</v>
       </c>
       <c r="H45">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>24126</v>
+        <v>23777</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>51126</v>
+        <v>50777</v>
       </c>
       <c r="G47">
-        <v>73621</v>
+        <v>73119</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>38949</v>
+        <v>36551</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>53949</v>
+        <v>53961</v>
       </c>
       <c r="G50">
-        <v>77687</v>
+        <v>77704</v>
       </c>
       <c r="H50">
-        <v>15000</v>
+        <v>17410</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>23999</v>
+        <v>24030</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>40863</v>
+        <v>40875</v>
       </c>
       <c r="G51">
-        <v>58843</v>
+        <v>58860</v>
       </c>
       <c r="H51">
-        <v>16864</v>
+        <v>16845</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,16 +2698,16 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>58629</v>
+        <v>50973</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>73629</v>
+        <v>65973</v>
       </c>
       <c r="G52">
-        <v>106026</v>
+        <v>95001</v>
       </c>
       <c r="H52">
         <v>15000</v>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>53930</v>
+        <v>53996</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>68930</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>99259</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44755</v>
+        <v>44688</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>79755</v>
+        <v>79688</v>
       </c>
       <c r="G54">
-        <v>114847</v>
+        <v>114751</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>43473</v>
+        <v>43533</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>70473</v>
+        <v>70533</v>
       </c>
       <c r="G55">
-        <v>101481</v>
+        <v>101568</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>50719</v>
+        <v>45258</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>77719</v>
+        <v>72258</v>
       </c>
       <c r="G56">
-        <v>111915</v>
+        <v>104052</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>61951</v>
+        <v>62022</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>88533</v>
+        <v>88562</v>
       </c>
       <c r="G57">
-        <v>127488</v>
+        <v>127529</v>
       </c>
       <c r="H57">
-        <v>26582</v>
+        <v>26540</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>18130</v>
+        <v>17540</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38716</v>
+        <v>38724</v>
       </c>
       <c r="G58">
-        <v>55751</v>
+        <v>55763</v>
       </c>
       <c r="H58">
-        <v>20586</v>
+        <v>21184</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6375</v>
+        <v>6395</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22983</v>
+        <v>22991</v>
       </c>
       <c r="G59">
-        <v>33096</v>
+        <v>33107</v>
       </c>
       <c r="H59">
-        <v>16608</v>
+        <v>16596</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>23999</v>
+        <v>24030</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>48391</v>
+        <v>48407</v>
       </c>
       <c r="G60">
-        <v>69683</v>
+        <v>69706</v>
       </c>
       <c r="H60">
-        <v>24392</v>
+        <v>24377</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25391</v>
+        <v>25407</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>40391</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58163</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14159</v>
+        <v>14184</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41159</v>
+        <v>41184</v>
       </c>
       <c r="G63">
-        <v>59269</v>
+        <v>59305</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23097</v>
+        <v>23128</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>50097</v>
+        <v>50128</v>
       </c>
       <c r="G65">
-        <v>72140</v>
+        <v>72184</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>29188</v>
+        <v>29254</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>61463</v>
+        <v>61476</v>
       </c>
       <c r="G66">
-        <v>88507</v>
+        <v>88525</v>
       </c>
       <c r="H66">
-        <v>32275</v>
+        <v>32222</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20677</v>
+        <v>20690</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47677</v>
+        <v>47690</v>
       </c>
       <c r="G67">
-        <v>68655</v>
+        <v>68674</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47792</v>
+        <v>47838</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>74792</v>
+        <v>74838</v>
       </c>
       <c r="G68">
-        <v>107700</v>
+        <v>107767</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>28336</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>55336</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>79684</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>109996</v>
+        <v>110113</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>124996</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>179994</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>52334</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>77467</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>111552</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>25133</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6787</v>
+        <v>6791</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21787</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>31373</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87659</v>
+        <v>87762</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>122075</v>
+        <v>122110</v>
       </c>
       <c r="G76">
-        <v>175788</v>
+        <v>175838</v>
       </c>
       <c r="H76">
-        <v>34416</v>
+        <v>34348</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>59815</v>
+        <v>59901</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>80459</v>
+        <v>80494</v>
       </c>
       <c r="G77">
-        <v>115861</v>
+        <v>115911</v>
       </c>
       <c r="H77">
-        <v>20644</v>
+        <v>20593</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,19 +3974,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>27558</v>
+        <v>23175</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>53116</v>
+        <v>50175</v>
       </c>
       <c r="G81">
-        <v>76487</v>
+        <v>72252</v>
       </c>
       <c r="H81">
-        <v>25558</v>
+        <v>27000</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86709</v>
+        <v>86812</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>101709</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>146461</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>50545</v>
+        <v>50498</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>65545</v>
+        <v>66135</v>
       </c>
       <c r="G84">
-        <v>94385</v>
+        <v>95234</v>
       </c>
       <c r="H84">
-        <v>15000</v>
+        <v>15637</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>28634</v>
+        <v>30109</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>46326</v>
+        <v>46916</v>
       </c>
       <c r="G85">
-        <v>66709</v>
+        <v>67559</v>
       </c>
       <c r="H85">
-        <v>17692</v>
+        <v>16807</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8163</v>
+        <v>8168</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38565</v>
+        <v>38572</v>
       </c>
       <c r="G90">
-        <v>55534</v>
+        <v>55544</v>
       </c>
       <c r="H90">
-        <v>30402</v>
+        <v>30404</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3670</v>
+        <v>3688</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30565</v>
+        <v>30572</v>
       </c>
       <c r="G91">
-        <v>44014</v>
+        <v>44024</v>
       </c>
       <c r="H91">
-        <v>26895</v>
+        <v>26884</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9445</v>
+        <v>9466</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>24445</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35201</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>59721</v>
+        <v>59822</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>77450</v>
+        <v>77465</v>
       </c>
       <c r="G96">
-        <v>111528</v>
+        <v>111550</v>
       </c>
       <c r="H96">
-        <v>17729</v>
+        <v>17643</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34377</v>
+        <v>34414</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52234</v>
+        <v>52249</v>
       </c>
       <c r="G97">
-        <v>75217</v>
+        <v>75239</v>
       </c>
       <c r="H97">
-        <v>17857</v>
+        <v>17835</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>78847</v>
+        <v>78944</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>93847</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>135140</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>43679</v>
+        <v>42076</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>61009</v>
+        <v>60368</v>
       </c>
       <c r="G99">
-        <v>87853</v>
+        <v>86930</v>
       </c>
       <c r="H99">
-        <v>17330</v>
+        <v>18292</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60369</v>
+        <v>60439</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>78708</v>
+        <v>80934</v>
       </c>
       <c r="G100">
-        <v>113340</v>
+        <v>116545</v>
       </c>
       <c r="H100">
-        <v>18339</v>
+        <v>20495</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>63098</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>78098</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>112461</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>71298</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>86298</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>124269</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>76744</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>103744</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>149391</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33138</v>
+        <v>33142</v>
       </c>
       <c r="G109">
-        <v>47719</v>
+        <v>47724</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14428</v>
+        <v>14453</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>41428</v>
+        <v>41453</v>
       </c>
       <c r="G111">
-        <v>59656</v>
+        <v>59692</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,16 +5370,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48330</v>
+        <v>48392</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>75330</v>
+        <v>75392</v>
       </c>
       <c r="G113">
-        <v>108475</v>
+        <v>108564</v>
       </c>
       <c r="H113">
         <v>27000</v>
@@ -5541,19 +5541,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>175365</v>
       </c>
       <c r="E117">
         <v>185111</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>190365</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>274126</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>79907</v>
+        <v>80005</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>94907</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>136666</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>46637</v>
+        <v>46699</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>61637</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>88757</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,16 +5716,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>101644</v>
+        <v>87762</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>116644</v>
+        <v>102762</v>
       </c>
       <c r="G121">
-        <v>167967</v>
+        <v>147977</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>206926</v>
+        <v>207136</v>
       </c>
       <c r="E122">
         <v>148085</v>
       </c>
       <c r="F122">
-        <v>221926</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>319573</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>113153</v>
       </c>
       <c r="E123">
         <v>148085</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>128153</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>184540</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>45941</v>
+        <v>45986</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>60941</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>87755</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,16 +5891,16 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35405</v>
+        <v>35333</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>50405</v>
+        <v>50333</v>
       </c>
       <c r="G125">
-        <v>72583</v>
+        <v>72480</v>
       </c>
       <c r="H125">
         <v>15000</v>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63391</v>
+        <v>63462</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>78391</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>112883</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>55468</v>
       </c>
       <c r="E127">
         <v>81439</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>70468</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>101474</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>37019</v>
+        <v>37058</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56901</v>
+        <v>56916</v>
       </c>
       <c r="G129">
-        <v>81937</v>
+        <v>81959</v>
       </c>
       <c r="H129">
-        <v>19882</v>
+        <v>19858</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12672</v>
+        <v>12680</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33310</v>
+        <v>33132</v>
       </c>
       <c r="G130">
-        <v>47966</v>
+        <v>47710</v>
       </c>
       <c r="H130">
-        <v>20638</v>
+        <v>20452</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>6075</v>
+        <v>4527</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25751</v>
+        <v>25132</v>
       </c>
       <c r="G131">
-        <v>37081</v>
+        <v>36190</v>
       </c>
       <c r="H131">
-        <v>19676</v>
+        <v>20605</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27479</v>
+        <v>27513</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43642</v>
+        <v>43655</v>
       </c>
       <c r="G132">
-        <v>62844</v>
+        <v>62863</v>
       </c>
       <c r="H132">
-        <v>16163</v>
+        <v>16142</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17355</v>
+        <v>17286</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36610</v>
+        <v>36582</v>
       </c>
       <c r="G135">
-        <v>52718</v>
+        <v>52678</v>
       </c>
       <c r="H135">
-        <v>19255</v>
+        <v>19296</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>27638</v>
+        <v>27671</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46542</v>
+        <v>46555</v>
       </c>
       <c r="G137">
-        <v>67020</v>
+        <v>67039</v>
       </c>
       <c r="H137">
-        <v>18904</v>
+        <v>18884</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27653</v>
+        <v>27592</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54180</v>
+        <v>54155</v>
       </c>
       <c r="G139">
-        <v>78019</v>
+        <v>77983</v>
       </c>
       <c r="H139">
-        <v>26527</v>
+        <v>26563</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>57933</v>
+        <v>52429</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>67429</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>97098</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77265</v>
+        <v>77361</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>92265</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>132862</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,16 +6763,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>97040</v>
+        <v>87619</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>112040</v>
+        <v>102619</v>
       </c>
       <c r="G145">
-        <v>161338</v>
+        <v>147771</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>87754</v>
+        <v>87872</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>102754</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>147966</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>125611</v>
+        <v>125912</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>140611</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>202480</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38142</v>
+        <v>38182</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62903</v>
+        <v>62919</v>
       </c>
       <c r="G150">
-        <v>90580</v>
+        <v>90603</v>
       </c>
       <c r="H150">
-        <v>24761</v>
+        <v>24737</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,19 +7067,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>23050</v>
+        <v>23159</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>58050</v>
+        <v>50159</v>
       </c>
       <c r="G152">
-        <v>83592</v>
+        <v>72229</v>
       </c>
       <c r="H152">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29536</v>
+        <v>14516</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>53907</v>
+        <v>41516</v>
       </c>
       <c r="G153">
-        <v>77626</v>
+        <v>59783</v>
       </c>
       <c r="H153">
-        <v>24371</v>
+        <v>27000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48504</v>
+        <v>48566</v>
       </c>
       <c r="E154">
         <v>92546</v>
       </c>
       <c r="F154">
-        <v>67064</v>
+        <v>67081</v>
       </c>
       <c r="G154">
-        <v>96572</v>
+        <v>96597</v>
       </c>
       <c r="H154">
-        <v>18560</v>
+        <v>18515</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>40183</v>
+        <v>40224</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>58166</v>
+        <v>58183</v>
       </c>
       <c r="G155">
-        <v>83759</v>
+        <v>83784</v>
       </c>
       <c r="H155">
-        <v>17983</v>
+        <v>17959</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65194</v>
+        <v>65267</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80194</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>115479</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38743</v>
+        <v>38768</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65425</v>
+        <v>65493</v>
       </c>
       <c r="G158">
-        <v>94212</v>
+        <v>94310</v>
       </c>
       <c r="H158">
-        <v>26682</v>
+        <v>26725</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>41891</v>
+        <v>41950</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>56891</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>81923</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>23619</v>
+        <v>20231</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>38619</v>
+        <v>35745</v>
       </c>
       <c r="G161">
-        <v>55611</v>
+        <v>51473</v>
       </c>
       <c r="H161">
-        <v>15000</v>
+        <v>15514</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>54278</v>
+        <v>54344</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>69278</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>99760</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,16 +7635,16 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>76395</v>
+        <v>70380</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>91395</v>
+        <v>85380</v>
       </c>
       <c r="G165">
-        <v>131609</v>
+        <v>122947</v>
       </c>
       <c r="H165">
         <v>15000</v>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>51557</v>
+        <v>51590</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>66590</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>95890</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33855</v>
+        <v>33892</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>48855</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70351</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60148</v>
+        <v>60201</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>75148</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>108213</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>14934</v>
+        <v>14975</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>29934</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>43105</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31150</v>
+        <v>30235</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51665</v>
+        <v>51299</v>
       </c>
       <c r="G173">
-        <v>74398</v>
+        <v>73871</v>
       </c>
       <c r="H173">
-        <v>20515</v>
+        <v>21064</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7467</v>
+        <v>7868</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37761</v>
+        <v>37775</v>
       </c>
       <c r="G174">
-        <v>54376</v>
+        <v>54396</v>
       </c>
       <c r="H174">
-        <v>30294</v>
+        <v>29907</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5252</v>
+        <v>5287</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29761</v>
+        <v>29775</v>
       </c>
       <c r="G175">
-        <v>42856</v>
+        <v>42876</v>
       </c>
       <c r="H175">
-        <v>24509</v>
+        <v>24488</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10283</v>
+        <v>10290</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>44856</v>
+        <v>42519</v>
       </c>
       <c r="G176">
-        <v>64593</v>
+        <v>61227</v>
       </c>
       <c r="H176">
-        <v>34573</v>
+        <v>32229</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>9856</v>
+        <v>7519</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>36856</v>
+        <v>34519</v>
       </c>
       <c r="G177">
-        <v>53073</v>
+        <v>49707</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21784</v>
+        <v>21814</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41789</v>
+        <v>41801</v>
       </c>
       <c r="G179">
-        <v>60176</v>
+        <v>60193</v>
       </c>
       <c r="H179">
-        <v>20005</v>
+        <v>19987</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45783</v>
+        <v>45860</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65107</v>
+        <v>65137</v>
       </c>
       <c r="G181">
-        <v>93754</v>
+        <v>93797</v>
       </c>
       <c r="H181">
-        <v>19324</v>
+        <v>19277</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67615</v>
+        <v>67673</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86514</v>
+        <v>86758</v>
       </c>
       <c r="G182">
-        <v>124580</v>
+        <v>124932</v>
       </c>
       <c r="H182">
-        <v>18899</v>
+        <v>19085</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10125</v>
+        <v>10369</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37125</v>
+        <v>37369</v>
       </c>
       <c r="G183">
-        <v>53460</v>
+        <v>53811</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>72345</v>
+        <v>60296</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>80095</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>115337</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>19799</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>89082</v>
+        <v>79609</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>108271</v>
+        <v>110569</v>
       </c>
       <c r="G186">
-        <v>155910</v>
+        <v>159219</v>
       </c>
       <c r="H186">
-        <v>19189</v>
+        <v>30960</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>80986</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>96147</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>138452</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>15161</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>171724</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>186724</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>268883</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>6739</v>
+        <v>6886</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>28199</v>
+        <v>28052</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11707</v>
+        <v>11714</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38707</v>
+        <v>38714</v>
       </c>
       <c r="G196">
-        <v>55738</v>
+        <v>55748</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,19 +9083,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>54563</v>
+        <v>51495</v>
       </c>
       <c r="E198">
         <v>92546</v>
       </c>
       <c r="F198">
-        <v>89563</v>
+        <v>69410</v>
       </c>
       <c r="G198">
-        <v>128971</v>
+        <v>99950</v>
       </c>
       <c r="H198">
-        <v>35000</v>
+        <v>17915</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74702</v>
+        <v>74797</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>89702</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129171</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,16 +9172,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>59420</v>
+        <v>54629</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>74420</v>
+        <v>69629</v>
       </c>
       <c r="G200">
-        <v>107165</v>
+        <v>100266</v>
       </c>
       <c r="H200">
         <v>15000</v>
@@ -9259,19 +9259,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>55133</v>
+        <v>36599</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>63599</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>91583</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
@@ -9348,19 +9348,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27369</v>
+        <v>49564</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54369</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>78291</v>
+        <v>0</v>
       </c>
       <c r="H204">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101232</v>
+        <v>101296</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>116232</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>167374</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>64862</v>
+        <v>64808</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82478</v>
+        <v>82456</v>
       </c>
       <c r="G207">
-        <v>118768</v>
+        <v>118737</v>
       </c>
       <c r="H207">
-        <v>17616</v>
+        <v>17648</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>143946</v>
+        <v>144037</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>178946</v>
+        <v>179037</v>
       </c>
       <c r="G208">
-        <v>257682</v>
+        <v>257813</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145829</v>
+        <v>146222</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>160829</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>231594</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>186660</v>
+        <v>186778</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>201660</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>290390</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>158880</v>
+        <v>158981</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>173880</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>250387</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>286326</v>
+        <v>286507</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>301326</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>433909</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>223472</v>
       </c>
       <c r="E213">
         <v>370241</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>239783</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>345288</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>16311</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34345</v>
+        <v>34636</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>69345</v>
+        <v>62197</v>
       </c>
       <c r="G214">
-        <v>99857</v>
+        <v>89564</v>
       </c>
       <c r="H214">
-        <v>35000</v>
+        <v>27561</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>51589</v>
+        <v>39084</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>66589</v>
+        <v>54084</v>
       </c>
       <c r="G215">
-        <v>95888</v>
+        <v>77881</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45941</v>
+        <v>16368</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>60941</v>
+        <v>36707</v>
       </c>
       <c r="G216">
-        <v>87755</v>
+        <v>52858</v>
       </c>
       <c r="H216">
-        <v>15000</v>
+        <v>20339</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16358</v>
+        <v>67167</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>36703</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>52852</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>20345</v>
+        <v>0</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13226</v>
+        <v>12791</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>46470</v>
+        <v>46477</v>
       </c>
       <c r="G220">
-        <v>66917</v>
+        <v>66927</v>
       </c>
       <c r="H220">
-        <v>33244</v>
+        <v>33686</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11470</v>
+        <v>11477</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>38470</v>
+        <v>38477</v>
       </c>
       <c r="G221">
-        <v>55397</v>
+        <v>55407</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21610</v>
+        <v>26895</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>48610</v>
+        <v>53895</v>
       </c>
       <c r="G222">
-        <v>69998</v>
+        <v>77609</v>
       </c>
       <c r="H222">
         <v>27000</v>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16326</v>
+        <v>16305</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>45726</v>
+        <v>45733</v>
       </c>
       <c r="G224">
-        <v>65845</v>
+        <v>65856</v>
       </c>
       <c r="H224">
-        <v>29400</v>
+        <v>29428</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10726</v>
+        <v>10733</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>37726</v>
+        <v>37733</v>
       </c>
       <c r="G225">
-        <v>54325</v>
+        <v>54336</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26372</v>
+        <v>26404</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61372</v>
+        <v>61404</v>
       </c>
       <c r="G226">
-        <v>88376</v>
+        <v>88422</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>96122</v>
+        <v>96310</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>111122</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>160016</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,19 +10406,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>34962</v>
+        <v>35000</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>61962</v>
+        <v>70000</v>
       </c>
       <c r="G228">
-        <v>89225</v>
+        <v>100800</v>
       </c>
       <c r="H228">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>97988</v>
       </c>
       <c r="E229">
         <v>185111</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>117388</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>169039</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16136</v>
+        <v>16194</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>41356</v>
+        <v>41357</v>
       </c>
       <c r="G230">
-        <v>59553</v>
+        <v>59554</v>
       </c>
       <c r="H230">
-        <v>25220</v>
+        <v>25163</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>31546</v>
+        <v>31547</v>
       </c>
       <c r="G231">
-        <v>45426</v>
+        <v>45428</v>
       </c>
       <c r="H231">
-        <v>25424</v>
+        <v>25421</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23335</v>
+        <v>23349</v>
       </c>
       <c r="E233">
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>38335</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>55202</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41496</v>
+        <v>0</v>
       </c>
       <c r="E235">
         <v>111059</v>
       </c>
       <c r="F235">
-        <v>65911</v>
+        <v>0</v>
       </c>
       <c r="G235">
-        <v>94912</v>
+        <v>0</v>
       </c>
       <c r="H235">
-        <v>24415</v>
+        <v>0</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>85688</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>112468</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>161954</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>26780</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>25043</v>
+        <v>25059</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>60043</v>
+        <v>60059</v>
       </c>
       <c r="G238">
-        <v>86462</v>
+        <v>86485</v>
       </c>
       <c r="H238">
         <v>35000</v>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31735</v>
+        <v>31755</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>53343</v>
+        <v>53351</v>
       </c>
       <c r="G239">
-        <v>76814</v>
+        <v>76825</v>
       </c>
       <c r="H239">
-        <v>21608</v>
+        <v>21596</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,7 +10931,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46811</v>
+        <v>46873</v>
       </c>
       <c r="E240">
         <v>103654</v>
@@ -10943,7 +10943,7 @@
         <v>111947</v>
       </c>
       <c r="H240">
-        <v>30930</v>
+        <v>30868</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>85333</v>
+        <v>85387</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>100333</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>144480</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>110224</v>
       </c>
       <c r="E243">
         <v>133275</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>125224</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>180323</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>63929</v>
+        <v>64001</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79397</v>
+        <v>79001</v>
       </c>
       <c r="G244">
-        <v>114332</v>
+        <v>113761</v>
       </c>
       <c r="H244">
-        <v>15468</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54041</v>
+        <v>0</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>69041</v>
+        <v>0</v>
       </c>
       <c r="G245">
-        <v>99419</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75287</v>
+        <v>75335</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>90287</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>130013</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17655</v>
+        <v>18347</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42204</v>
+        <v>42207</v>
       </c>
       <c r="G248">
-        <v>60774</v>
+        <v>60778</v>
       </c>
       <c r="H248">
-        <v>24549</v>
+        <v>23860</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>10963</v>
+        <v>10970</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34204</v>
+        <v>34207</v>
       </c>
       <c r="G249">
-        <v>49254</v>
+        <v>49258</v>
       </c>
       <c r="H249">
-        <v>23241</v>
+        <v>23237</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>15466</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>42466</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>61151</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11596,16 +11596,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>20867</v>
+        <v>20880</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>47867</v>
+        <v>47880</v>
       </c>
       <c r="G255">
-        <v>68928</v>
+        <v>68947</v>
       </c>
       <c r="H255">
         <v>27000</v>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9508</v>
+        <v>9514</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>57983</v>
       </c>
       <c r="H256">
-        <v>30758</v>
+        <v>30752</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14823</v>
+        <v>14833</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>32867</v>
+        <v>32871</v>
       </c>
       <c r="G257">
-        <v>47328</v>
+        <v>47334</v>
       </c>
       <c r="H257">
-        <v>18044</v>
+        <v>18038</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>11818</v>
+        <v>12126</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>38818</v>
+        <v>39126</v>
       </c>
       <c r="G258">
-        <v>55898</v>
+        <v>56341</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,7 +11814,7 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8828</v>
+        <v>8833</v>
       </c>
       <c r="E260">
         <v>53688</v>
@@ -11826,7 +11826,7 @@
         <v>57983</v>
       </c>
       <c r="H260">
-        <v>31438</v>
+        <v>31433</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>52554</v>
+        <v>16511</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>67554</v>
+        <v>33543</v>
       </c>
       <c r="G261">
-        <v>97278</v>
+        <v>48302</v>
       </c>
       <c r="H261">
-        <v>15000</v>
+        <v>17032</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>13827</v>
+        <v>13550</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>39121</v>
+        <v>39124</v>
       </c>
       <c r="G262">
-        <v>56334</v>
+        <v>56339</v>
       </c>
       <c r="H262">
-        <v>25294</v>
+        <v>25574</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10457</v>
+        <v>10464</v>
       </c>
       <c r="E263">
         <v>53688</v>
       </c>
       <c r="F263">
-        <v>31121</v>
+        <v>31124</v>
       </c>
       <c r="G263">
-        <v>44814</v>
+        <v>44819</v>
       </c>
       <c r="H263">
-        <v>20664</v>
+        <v>20660</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>17940</v>
+        <v>17888</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>44940</v>
+        <v>50567</v>
       </c>
       <c r="G264">
-        <v>64714</v>
+        <v>72816</v>
       </c>
       <c r="H264">
-        <v>27000</v>
+        <v>32679</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>21022</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>42567</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>61296</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>21545</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34234</v>
+        <v>34256</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>52184</v>
+        <v>54151</v>
       </c>
       <c r="G266">
-        <v>75145</v>
+        <v>77977</v>
       </c>
       <c r="H266">
-        <v>17950</v>
+        <v>19895</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>30821</v>
       </c>
       <c r="E267">
         <v>72201</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>46487</v>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>66941</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>15666</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10220</v>
+        <v>10147</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>25220</v>
+        <v>39511</v>
       </c>
       <c r="G268">
-        <v>36317</v>
+        <v>56896</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>29364</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,19 +12211,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>16511</v>
       </c>
       <c r="E269">
         <v>27770</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>31511</v>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>45376</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>11818</v>
+        <v>11873</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>38818</v>
+        <v>38873</v>
       </c>
       <c r="G270">
-        <v>55898</v>
+        <v>55977</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>61255</v>
+        <v>61088</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>76255</v>
+        <v>76088</v>
       </c>
       <c r="G272">
-        <v>109807</v>
+        <v>109567</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>41696</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>0</v>
+        <v>60945</v>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>87761</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>19249</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,16 +12430,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>71079</v>
+        <v>71013</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>86079</v>
+        <v>86013</v>
       </c>
       <c r="G274">
-        <v>123954</v>
+        <v>123859</v>
       </c>
       <c r="H274">
         <v>15000</v>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11201</v>
+        <v>11208</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>34938</v>
+        <v>40266</v>
       </c>
       <c r="G276">
-        <v>50311</v>
+        <v>57983</v>
       </c>
       <c r="H276">
-        <v>23737</v>
+        <v>29058</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>14326</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>32669</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>47043</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>18343</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>19965</v>
+        <v>19977</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>46477</v>
+        <v>46481</v>
       </c>
       <c r="G278">
-        <v>66927</v>
+        <v>66933</v>
       </c>
       <c r="H278">
-        <v>26512</v>
+        <v>26504</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11691</v>
+        <v>11714</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23247</v>
+        <v>23224</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17655</v>
+        <v>17682</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>32682</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>47062</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>49786</v>
+        <v>49849</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>64786</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>93292</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58566</v>
+        <v>58634</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>73566</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>105935</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>40800</v>
+        <v>36219</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55800</v>
+        <v>55813</v>
       </c>
       <c r="G288">
-        <v>80352</v>
+        <v>80371</v>
       </c>
       <c r="H288">
-        <v>15000</v>
+        <v>19594</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23809</v>
+        <v>23840</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39342</v>
+        <v>39355</v>
       </c>
       <c r="G289">
-        <v>56652</v>
+        <v>56671</v>
       </c>
       <c r="H289">
-        <v>15533</v>
+        <v>15515</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>35674</v>
+        <v>35712</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>50674</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>72971</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23588</v>
+        <v>23618</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39254</v>
+        <v>39266</v>
       </c>
       <c r="G293">
-        <v>56526</v>
+        <v>56543</v>
       </c>
       <c r="H293">
-        <v>15666</v>
+        <v>15648</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>51147</v>
       </c>
       <c r="E294">
         <v>68480</v>
       </c>
       <c r="F294">
-        <v>0</v>
+        <v>66147</v>
       </c>
       <c r="G294">
-        <v>0</v>
+        <v>95252</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>25977</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>0</v>
+        <v>43098</v>
       </c>
       <c r="G295">
-        <v>0</v>
+        <v>62061</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>17121</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62315</v>
+        <v>62354</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>77315</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>111334</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74180</v>
+        <v>74227</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>89180</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>128419</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>67915</v>
+        <v>67531</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>89270</v>
+        <v>89133</v>
       </c>
       <c r="G300">
-        <v>128549</v>
+        <v>128352</v>
       </c>
       <c r="H300">
-        <v>21355</v>
+        <v>21602</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>35769</v>
+        <v>35428</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>56401</v>
+        <v>56264</v>
       </c>
       <c r="G301">
-        <v>81217</v>
+        <v>81020</v>
       </c>
       <c r="H301">
-        <v>20632</v>
+        <v>20836</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12102</v>
+        <v>10733</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>39102</v>
+        <v>37733</v>
       </c>
       <c r="G303">
-        <v>56307</v>
+        <v>54336</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>173371</v>
+        <v>188171</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>188371</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>271254</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>104351</v>
       </c>
       <c r="E305">
         <v>166598</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>119351</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>171865</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>49817</v>
+        <v>49865</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>79888</v>
+        <v>79914</v>
       </c>
       <c r="G306">
-        <v>115039</v>
+        <v>115076</v>
       </c>
       <c r="H306">
-        <v>30071</v>
+        <v>30049</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50244</v>
+        <v>50308</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69410</v>
+        <v>69436</v>
       </c>
       <c r="G307">
-        <v>99950</v>
+        <v>99988</v>
       </c>
       <c r="H307">
-        <v>19166</v>
+        <v>19128</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>68944</v>
+        <v>69003</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>28235</v>
+        <v>28176</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,16 +13970,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>105282</v>
+        <v>77535</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>120282</v>
+        <v>92535</v>
       </c>
       <c r="G309">
-        <v>173206</v>
+        <v>133250</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24426</v>
+        <v>23824</v>
       </c>
       <c r="E310">
         <v>55520</v>
       </c>
       <c r="F310">
-        <v>40754</v>
+        <v>41640</v>
       </c>
       <c r="G310">
-        <v>58686</v>
+        <v>59962</v>
       </c>
       <c r="H310">
-        <v>16328</v>
+        <v>17816</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>21671</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>36671</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>52806</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,16 +14101,16 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>67235</v>
+        <v>65821</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>82235</v>
+        <v>80821</v>
       </c>
       <c r="G312">
-        <v>118418</v>
+        <v>116382</v>
       </c>
       <c r="H312">
         <v>15000</v>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20851</v>
+        <v>20880</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>35851</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>51625</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32257</v>
+        <v>32277</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>62605</v>
+        <v>62670</v>
       </c>
       <c r="G316">
-        <v>90151</v>
+        <v>90245</v>
       </c>
       <c r="H316">
-        <v>30348</v>
+        <v>30393</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39439</v>
+        <v>39496</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>54439</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>78392</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>12118</v>
+        <v>15751</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>21192</v>
+        <v>17559</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29220</v>
+        <v>29254</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44220</v>
+        <v>0</v>
       </c>
       <c r="G319">
-        <v>63677</v>
+        <v>0</v>
       </c>
       <c r="H319">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>46970</v>
+        <v>46999</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>68101</v>
+        <v>68112</v>
       </c>
       <c r="G321">
-        <v>98065</v>
+        <v>98081</v>
       </c>
       <c r="H321">
-        <v>21131</v>
+        <v>21113</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>58603</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>0</v>
+        <v>73603</v>
       </c>
       <c r="G324">
-        <v>0</v>
+        <v>105988</v>
       </c>
       <c r="H324">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>16959</v>
+        <v>0</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>38047</v>
+        <v>0</v>
       </c>
       <c r="G329">
-        <v>54788</v>
+        <v>0</v>
       </c>
       <c r="H329">
-        <v>21088</v>
+        <v>0</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20693</v>
+        <v>20706</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47693</v>
+        <v>47706</v>
       </c>
       <c r="G330">
-        <v>68678</v>
+        <v>68697</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43505</v>
+        <v>43548</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>78505</v>
+        <v>78548</v>
       </c>
       <c r="G332">
-        <v>113047</v>
+        <v>113109</v>
       </c>
       <c r="H332">
         <v>35000</v>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>83023</v>
+        <v>83076</v>
       </c>
       <c r="E333">
         <v>111059</v>
       </c>
       <c r="F333">
-        <v>98023</v>
+        <v>0</v>
       </c>
       <c r="G333">
-        <v>141153</v>
+        <v>0</v>
       </c>
       <c r="H333">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32985</v>
+        <v>32721</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>59985</v>
+        <v>59721</v>
       </c>
       <c r="G334">
-        <v>86378</v>
+        <v>85998</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188385</v>
+        <v>188614</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>203385</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>292874</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>143630</v>
+        <v>143721</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>158630</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>228427</v>
+        <v>0</v>
       </c>
       <c r="H337">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,16 +15243,16 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>59721</v>
+        <v>59790</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>86721</v>
+        <v>86790</v>
       </c>
       <c r="G338">
-        <v>124878</v>
+        <v>124978</v>
       </c>
       <c r="H338">
         <v>27000</v>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>41686</v>
+        <v>0</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>68686</v>
+        <v>0</v>
       </c>
       <c r="G339">
-        <v>98908</v>
+        <v>0</v>
       </c>
       <c r="H339">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>103542</v>
+        <v>103607</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>138542</v>
+        <v>130607</v>
       </c>
       <c r="G342">
-        <v>199500</v>
+        <v>188074</v>
       </c>
       <c r="H342">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>143646</v>
+        <v>0</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>158646</v>
+        <v>0</v>
       </c>
       <c r="G343">
-        <v>228450</v>
+        <v>0</v>
       </c>
       <c r="H343">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71694</v>
+        <v>71583</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86583</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>124680</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47712</v>
+        <v>47632</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>62632</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90190</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94758</v>
+        <v>94363</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>109363</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>157483</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>79577</v>
+        <v>72865</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>87865</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>126526</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>6474</v>
+        <v>6237</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30242</v>
+        <v>30148</v>
       </c>
       <c r="G7">
-        <v>43548</v>
+        <v>43413</v>
       </c>
       <c r="H7">
-        <v>23768</v>
+        <v>23911</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>38673</v>
+        <v>38609</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>55525</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>79956</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>16916</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>37422</v>
       </c>
       <c r="E9">
         <v>74033</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>52422</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>75488</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56323</v>
+        <v>56022</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78506</v>
+        <v>78385</v>
       </c>
       <c r="G10">
-        <v>113049</v>
+        <v>112874</v>
       </c>
       <c r="H10">
-        <v>22183</v>
+        <v>22363</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82585</v>
+        <v>82443</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>99140</v>
+        <v>99108</v>
       </c>
       <c r="G12">
-        <v>142762</v>
+        <v>142716</v>
       </c>
       <c r="H12">
-        <v>16555</v>
+        <v>16665</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13408</v>
+        <v>13376</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40408</v>
+        <v>40376</v>
       </c>
       <c r="G13">
-        <v>58188</v>
+        <v>58141</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27117</v>
+        <v>27069</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45719</v>
+        <v>45700</v>
       </c>
       <c r="G15">
-        <v>65835</v>
+        <v>65808</v>
       </c>
       <c r="H15">
-        <v>18602</v>
+        <v>18631</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,16 +1336,16 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>26230</v>
+        <v>26199</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>53230</v>
+        <v>53199</v>
       </c>
       <c r="G21">
-        <v>76651</v>
+        <v>76607</v>
       </c>
       <c r="H21">
         <v>27000</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21291</v>
+        <v>21101</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>39779</v>
+        <v>39703</v>
       </c>
       <c r="G27">
-        <v>57282</v>
+        <v>57172</v>
       </c>
       <c r="H27">
-        <v>18488</v>
+        <v>18602</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80163</v>
+        <v>80036</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96389</v>
+        <v>96326</v>
       </c>
       <c r="G28">
-        <v>138800</v>
+        <v>138709</v>
       </c>
       <c r="H28">
-        <v>16226</v>
+        <v>16290</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>39068</v>
+        <v>39005</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>66068</v>
+        <v>66005</v>
       </c>
       <c r="G29">
-        <v>95138</v>
+        <v>95047</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>135774</v>
+        <v>135552</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>150552</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>216795</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>79942</v>
+        <v>71441</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>106942</v>
+        <v>98441</v>
       </c>
       <c r="G31">
-        <v>153996</v>
+        <v>141755</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1826,13 +1826,13 @@
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80433</v>
+        <v>80370</v>
       </c>
       <c r="G32">
-        <v>115824</v>
+        <v>115733</v>
       </c>
       <c r="H32">
-        <v>21118</v>
+        <v>21055</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>35902</v>
+        <v>35839</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>62902</v>
+        <v>62839</v>
       </c>
       <c r="G33">
-        <v>90579</v>
+        <v>90488</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,16 +1956,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>83646</v>
+        <v>80654</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>98646</v>
+        <v>95654</v>
       </c>
       <c r="G35">
-        <v>142050</v>
+        <v>137742</v>
       </c>
       <c r="H35">
         <v>15000</v>
@@ -2000,19 +2000,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>61832</v>
+        <v>49247</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>88832</v>
+        <v>84247</v>
       </c>
       <c r="G36">
-        <v>127918</v>
+        <v>121316</v>
       </c>
       <c r="H36">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>101866</v>
+        <v>67895</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>128866</v>
+        <v>94895</v>
       </c>
       <c r="G38">
-        <v>185567</v>
+        <v>136649</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>98288</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>117508</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>169212</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>19220</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,19 +2177,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>173703</v>
+        <v>87603</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>114603</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>165028</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>133874</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>148874</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>214379</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2393,16 +2393,16 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>81714</v>
+        <v>79182</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>108714</v>
+        <v>106182</v>
       </c>
       <c r="G45">
-        <v>156548</v>
+        <v>152902</v>
       </c>
       <c r="H45">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>23777</v>
+        <v>23381</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>50777</v>
+        <v>50381</v>
       </c>
       <c r="G47">
-        <v>73119</v>
+        <v>72549</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2614,13 +2614,13 @@
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>53961</v>
+        <v>53942</v>
       </c>
       <c r="G50">
-        <v>77704</v>
+        <v>77676</v>
       </c>
       <c r="H50">
-        <v>17410</v>
+        <v>17391</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>24030</v>
+        <v>23982</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>40875</v>
+        <v>40856</v>
       </c>
       <c r="G51">
-        <v>58860</v>
+        <v>58833</v>
       </c>
       <c r="H51">
-        <v>16845</v>
+        <v>16874</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>50973</v>
+        <v>53806</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>65973</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>95001</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>53996</v>
+        <v>58745</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>73745</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>106193</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>43533</v>
+        <v>43453</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>70533</v>
+        <v>70453</v>
       </c>
       <c r="G55">
-        <v>101568</v>
+        <v>101452</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>45258</v>
+        <v>50767</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>72258</v>
+        <v>77767</v>
       </c>
       <c r="G56">
-        <v>104052</v>
+        <v>111984</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62022</v>
+        <v>61927</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>88562</v>
+        <v>88524</v>
       </c>
       <c r="G57">
-        <v>127529</v>
+        <v>127475</v>
       </c>
       <c r="H57">
-        <v>26540</v>
+        <v>26597</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>17540</v>
+        <v>17318</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38724</v>
+        <v>38642</v>
       </c>
       <c r="G58">
-        <v>55763</v>
+        <v>55644</v>
       </c>
       <c r="H58">
-        <v>21184</v>
+        <v>21324</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6395</v>
+        <v>6190</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22991</v>
+        <v>22909</v>
       </c>
       <c r="G59">
-        <v>33107</v>
+        <v>32989</v>
       </c>
       <c r="H59">
-        <v>16596</v>
+        <v>16719</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3108,13 +3108,13 @@
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40407</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58186</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14184</v>
+        <v>13392</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41184</v>
+        <v>40392</v>
       </c>
       <c r="G63">
-        <v>59305</v>
+        <v>58164</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23128</v>
+        <v>23080</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>50128</v>
+        <v>50080</v>
       </c>
       <c r="G65">
-        <v>72184</v>
+        <v>72115</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>29254</v>
+        <v>28035</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>61476</v>
+        <v>61444</v>
       </c>
       <c r="G66">
-        <v>88525</v>
+        <v>88479</v>
       </c>
       <c r="H66">
-        <v>32222</v>
+        <v>33409</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20690</v>
+        <v>20658</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47690</v>
+        <v>47658</v>
       </c>
       <c r="G67">
-        <v>68674</v>
+        <v>68628</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>28336</v>
+        <v>28051</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>55336</v>
+        <v>55051</v>
       </c>
       <c r="G69">
-        <v>79684</v>
+        <v>79273</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110113</v>
+        <v>110098</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>125098</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>180141</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6791</v>
+        <v>6775</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>21775</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>31356</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>69969</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>84969</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>122355</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87762</v>
+        <v>87619</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>122110</v>
+        <v>122065</v>
       </c>
       <c r="G76">
-        <v>175838</v>
+        <v>175774</v>
       </c>
       <c r="H76">
-        <v>34348</v>
+        <v>34446</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>59901</v>
+        <v>59790</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>80494</v>
+        <v>80449</v>
       </c>
       <c r="G77">
-        <v>115911</v>
+        <v>115847</v>
       </c>
       <c r="H77">
-        <v>20593</v>
+        <v>20659</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23175</v>
+        <v>23143</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>50175</v>
+        <v>50143</v>
       </c>
       <c r="G81">
-        <v>72252</v>
+        <v>72206</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86812</v>
+        <v>86669</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>101669</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>146403</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>50498</v>
+        <v>50482</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>66135</v>
+        <v>65482</v>
       </c>
       <c r="G84">
-        <v>95234</v>
+        <v>94294</v>
       </c>
       <c r="H84">
-        <v>15637</v>
+        <v>15000</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>30109</v>
+        <v>26943</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>46916</v>
+        <v>45650</v>
       </c>
       <c r="G85">
-        <v>67559</v>
+        <v>65736</v>
       </c>
       <c r="H85">
-        <v>16807</v>
+        <v>18707</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4373,13 +4373,13 @@
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38572</v>
+        <v>38566</v>
       </c>
       <c r="G90">
-        <v>55544</v>
+        <v>55535</v>
       </c>
       <c r="H90">
-        <v>30404</v>
+        <v>30398</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3688</v>
+        <v>3673</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30572</v>
+        <v>30566</v>
       </c>
       <c r="G91">
-        <v>44024</v>
+        <v>44015</v>
       </c>
       <c r="H91">
-        <v>26884</v>
+        <v>26893</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9466</v>
+        <v>9451</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24451</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35209</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>59822</v>
+        <v>63462</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>77465</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>111550</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>17643</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34414</v>
+        <v>34351</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52249</v>
+        <v>52224</v>
       </c>
       <c r="G97">
-        <v>75239</v>
+        <v>75203</v>
       </c>
       <c r="H97">
-        <v>17835</v>
+        <v>17873</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>78944</v>
+        <v>78818</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>93818</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>135098</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,7 +4809,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60439</v>
+        <v>60296</v>
       </c>
       <c r="E100">
         <v>107912</v>
@@ -4821,7 +4821,7 @@
         <v>116545</v>
       </c>
       <c r="H100">
-        <v>20495</v>
+        <v>20638</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5112,16 +5112,16 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>76744</v>
+        <v>74623</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>103744</v>
+        <v>101623</v>
       </c>
       <c r="G107">
-        <v>149391</v>
+        <v>146337</v>
       </c>
       <c r="H107">
         <v>27000</v>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6142</v>
+        <v>5778</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33142</v>
+        <v>32778</v>
       </c>
       <c r="G109">
-        <v>47724</v>
+        <v>47200</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14453</v>
+        <v>14437</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>41453</v>
+        <v>41437</v>
       </c>
       <c r="G111">
-        <v>59692</v>
+        <v>59669</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,16 +5370,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48392</v>
+        <v>48313</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>75392</v>
+        <v>75313</v>
       </c>
       <c r="G113">
-        <v>108564</v>
+        <v>108451</v>
       </c>
       <c r="H113">
         <v>27000</v>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>99080</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>117825</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>169668</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>18745</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5541,16 +5541,16 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>175365</v>
+        <v>166627</v>
       </c>
       <c r="E117">
         <v>185111</v>
       </c>
       <c r="F117">
-        <v>190365</v>
+        <v>181627</v>
       </c>
       <c r="G117">
-        <v>274126</v>
+        <v>261543</v>
       </c>
       <c r="H117">
         <v>15000</v>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80005</v>
+        <v>79862</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>94862</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>136601</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>46699</v>
+        <v>46619</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>61619</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>88731</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,16 +5716,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>87762</v>
+        <v>85450</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>102762</v>
+        <v>100450</v>
       </c>
       <c r="G121">
-        <v>147977</v>
+        <v>144648</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>207136</v>
+        <v>207120</v>
       </c>
       <c r="E122">
         <v>148085</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>222120</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>319853</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>113153</v>
+        <v>113929</v>
       </c>
       <c r="E123">
         <v>148085</v>
       </c>
       <c r="F123">
-        <v>128153</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>184540</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5852,13 +5852,13 @@
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>60986</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>87820</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5941,13 +5941,13 @@
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>81038</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>116695</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>17576</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>38673</v>
       </c>
       <c r="E128">
         <v>92546</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>65395</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>94169</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>26722</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>37058</v>
+        <v>36931</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56916</v>
+        <v>56865</v>
       </c>
       <c r="G129">
-        <v>81959</v>
+        <v>81886</v>
       </c>
       <c r="H129">
-        <v>19858</v>
+        <v>19934</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17286</v>
+        <v>17255</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36582</v>
+        <v>36570</v>
       </c>
       <c r="G135">
-        <v>52678</v>
+        <v>52661</v>
       </c>
       <c r="H135">
-        <v>19296</v>
+        <v>19315</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>27671</v>
+        <v>28447</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46555</v>
+        <v>46866</v>
       </c>
       <c r="G137">
-        <v>67039</v>
+        <v>67487</v>
       </c>
       <c r="H137">
-        <v>18884</v>
+        <v>18419</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27592</v>
+        <v>28842</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54155</v>
+        <v>54655</v>
       </c>
       <c r="G139">
-        <v>77983</v>
+        <v>78703</v>
       </c>
       <c r="H139">
-        <v>26563</v>
+        <v>25813</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77361</v>
+        <v>77235</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>92235</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>132818</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,16 +6763,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87619</v>
+        <v>86764</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>102619</v>
+        <v>101764</v>
       </c>
       <c r="G145">
-        <v>147771</v>
+        <v>146540</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>87872</v>
+        <v>85878</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>100878</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>145264</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>125912</v>
+        <v>121875</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>136875</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>197100</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38182</v>
+        <v>38119</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62919</v>
+        <v>62894</v>
       </c>
       <c r="G150">
-        <v>90603</v>
+        <v>90567</v>
       </c>
       <c r="H150">
-        <v>24737</v>
+        <v>24775</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,19 +7067,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>23159</v>
+        <v>22985</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>50159</v>
+        <v>53784</v>
       </c>
       <c r="G152">
-        <v>72229</v>
+        <v>77449</v>
       </c>
       <c r="H152">
-        <v>27000</v>
+        <v>30799</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7111,16 +7111,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>14516</v>
+        <v>18141</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>41516</v>
+        <v>45141</v>
       </c>
       <c r="G153">
-        <v>59783</v>
+        <v>65003</v>
       </c>
       <c r="H153">
         <v>27000</v>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48566</v>
+        <v>48487</v>
       </c>
       <c r="E154">
         <v>92546</v>
       </c>
       <c r="F154">
-        <v>67081</v>
+        <v>67055</v>
       </c>
       <c r="G154">
-        <v>96597</v>
+        <v>96559</v>
       </c>
       <c r="H154">
-        <v>18515</v>
+        <v>18568</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>40224</v>
+        <v>40161</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>58183</v>
+        <v>58157</v>
       </c>
       <c r="G155">
-        <v>83784</v>
+        <v>83746</v>
       </c>
       <c r="H155">
-        <v>17959</v>
+        <v>17996</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65267</v>
+        <v>65156</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80156</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>115425</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7338,13 +7338,13 @@
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65493</v>
+        <v>65401</v>
       </c>
       <c r="G158">
-        <v>94310</v>
+        <v>94177</v>
       </c>
       <c r="H158">
-        <v>26725</v>
+        <v>26633</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>41950</v>
+        <v>41870</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>56870</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>81893</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20231</v>
+        <v>17872</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>35745</v>
+        <v>34802</v>
       </c>
       <c r="G161">
-        <v>51473</v>
+        <v>50115</v>
       </c>
       <c r="H161">
-        <v>15514</v>
+        <v>16930</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>54344</v>
+        <v>54265</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>69265</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>99742</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33892</v>
+        <v>33845</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>48845</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70337</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60201</v>
+        <v>33449</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>55525</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>79956</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>22076</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>73799</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>88799</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>127871</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>14975</v>
+        <v>15688</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>30688</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>44191</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30235</v>
+        <v>31153</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51299</v>
+        <v>51666</v>
       </c>
       <c r="G173">
-        <v>73871</v>
+        <v>74399</v>
       </c>
       <c r="H173">
-        <v>21064</v>
+        <v>20513</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7868</v>
+        <v>7361</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37775</v>
+        <v>37756</v>
       </c>
       <c r="G174">
-        <v>54396</v>
+        <v>54369</v>
       </c>
       <c r="H174">
-        <v>29907</v>
+        <v>30395</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5287</v>
+        <v>5240</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29775</v>
+        <v>29756</v>
       </c>
       <c r="G175">
-        <v>42876</v>
+        <v>42849</v>
       </c>
       <c r="H175">
-        <v>24488</v>
+        <v>24516</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8128,13 +8128,13 @@
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>42519</v>
+        <v>42408</v>
       </c>
       <c r="G176">
-        <v>61227</v>
+        <v>61068</v>
       </c>
       <c r="H176">
-        <v>32229</v>
+        <v>32118</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7519</v>
+        <v>7408</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>34519</v>
+        <v>34408</v>
       </c>
       <c r="G177">
-        <v>49707</v>
+        <v>49548</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,19 +8212,19 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>48756</v>
       </c>
       <c r="E178">
         <v>69424</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>63756</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>91809</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I178" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21814</v>
+        <v>21782</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41801</v>
+        <v>41788</v>
       </c>
       <c r="G179">
-        <v>60193</v>
+        <v>60175</v>
       </c>
       <c r="H179">
-        <v>19987</v>
+        <v>20006</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45860</v>
+        <v>45796</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65137</v>
+        <v>65112</v>
       </c>
       <c r="G181">
-        <v>93797</v>
+        <v>93761</v>
       </c>
       <c r="H181">
-        <v>19277</v>
+        <v>19316</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8393,13 +8393,13 @@
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86758</v>
+        <v>86552</v>
       </c>
       <c r="G182">
-        <v>124932</v>
+        <v>124635</v>
       </c>
       <c r="H182">
-        <v>19085</v>
+        <v>18879</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10369</v>
+        <v>10163</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37369</v>
+        <v>37163</v>
       </c>
       <c r="G183">
-        <v>53811</v>
+        <v>53515</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>45511</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>67517</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>97224</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>22006</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>6886</v>
+        <v>6823</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>28052</v>
+        <v>28115</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74797</v>
+        <v>74670</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>89670</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>129125</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,16 +9172,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>54629</v>
+        <v>54534</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>69629</v>
+        <v>69534</v>
       </c>
       <c r="G200">
-        <v>100266</v>
+        <v>100129</v>
       </c>
       <c r="H200">
         <v>15000</v>
@@ -9348,19 +9348,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>49564</v>
+        <v>27402</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>54402</v>
       </c>
       <c r="G204">
-        <v>0</v>
+        <v>78339</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
@@ -9443,13 +9443,13 @@
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>116296</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>167466</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>64808</v>
+        <v>64523</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82456</v>
+        <v>82342</v>
       </c>
       <c r="G207">
-        <v>118737</v>
+        <v>118572</v>
       </c>
       <c r="H207">
-        <v>17648</v>
+        <v>17819</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>146222</v>
+        <v>145984</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>160984</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>231817</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9617,13 +9617,13 @@
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>201778</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>290560</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9660,13 +9660,13 @@
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>173981</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>250533</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9704,13 +9704,13 @@
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>301507</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>434170</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>223472</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>370241</v>
       </c>
       <c r="F213">
-        <v>239783</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>345288</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>16311</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,7 +9784,7 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34636</v>
+        <v>34351</v>
       </c>
       <c r="E214">
         <v>53688</v>
@@ -9796,7 +9796,7 @@
         <v>89564</v>
       </c>
       <c r="H214">
-        <v>27561</v>
+        <v>27846</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67167</v>
+        <v>67151</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>82151</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>118297</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,7 +10048,7 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12791</v>
+        <v>13044</v>
       </c>
       <c r="E220">
         <v>74033</v>
@@ -10060,7 +10060,7 @@
         <v>66927</v>
       </c>
       <c r="H220">
-        <v>33686</v>
+        <v>33433</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10232,13 +10232,13 @@
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>45733</v>
+        <v>46952</v>
       </c>
       <c r="G224">
-        <v>65856</v>
+        <v>67611</v>
       </c>
       <c r="H224">
-        <v>29428</v>
+        <v>30647</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10733</v>
+        <v>11952</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>37733</v>
+        <v>38952</v>
       </c>
       <c r="G225">
-        <v>54336</v>
+        <v>56091</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>96310</v>
+        <v>96041</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>111041</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>159899</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35000</v>
+        <v>34937</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>70000</v>
+        <v>69937</v>
       </c>
       <c r="G228">
-        <v>100800</v>
+        <v>100709</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10495,7 +10495,7 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16194</v>
+        <v>16147</v>
       </c>
       <c r="E230">
         <v>59223</v>
@@ -10507,7 +10507,7 @@
         <v>59554</v>
       </c>
       <c r="H230">
-        <v>25163</v>
+        <v>25210</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,13 +10634,13 @@
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>38349</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>55223</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10931,7 +10931,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46873</v>
+        <v>46793</v>
       </c>
       <c r="E240">
         <v>103654</v>
@@ -10943,7 +10943,7 @@
         <v>111947</v>
       </c>
       <c r="H240">
-        <v>30868</v>
+        <v>30948</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10983,13 +10983,13 @@
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>100387</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>144557</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>110224</v>
+        <v>0</v>
       </c>
       <c r="E243">
         <v>133275</v>
       </c>
       <c r="F243">
-        <v>125224</v>
+        <v>0</v>
       </c>
       <c r="G243">
-        <v>180323</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64001</v>
+        <v>63985</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79001</v>
+        <v>79436</v>
       </c>
       <c r="G244">
-        <v>113761</v>
+        <v>114388</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>15451</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>54075</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>0</v>
+        <v>69075</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>99468</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11205,13 +11205,13 @@
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>90335</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>130082</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11295,13 +11295,13 @@
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42207</v>
+        <v>42200</v>
       </c>
       <c r="G248">
-        <v>60778</v>
+        <v>60768</v>
       </c>
       <c r="H248">
-        <v>23860</v>
+        <v>23853</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>10970</v>
+        <v>10954</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34207</v>
+        <v>34200</v>
       </c>
       <c r="G249">
-        <v>49258</v>
+        <v>49248</v>
       </c>
       <c r="H249">
-        <v>23237</v>
+        <v>23246</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>5176</v>
       </c>
       <c r="E250">
         <v>74033</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>50400</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>29824</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11596,16 +11596,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>20880</v>
+        <v>20563</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>47880</v>
+        <v>47563</v>
       </c>
       <c r="G255">
-        <v>68947</v>
+        <v>68491</v>
       </c>
       <c r="H255">
         <v>27000</v>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12126</v>
+        <v>12205</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39126</v>
+        <v>39205</v>
       </c>
       <c r="G258">
-        <v>56341</v>
+        <v>56455</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11903,7 +11903,7 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>13550</v>
+        <v>12886</v>
       </c>
       <c r="E262">
         <v>53688</v>
@@ -11915,7 +11915,7 @@
         <v>56339</v>
       </c>
       <c r="H262">
-        <v>25574</v>
+        <v>26238</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>17888</v>
+        <v>18442</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>50567</v>
+        <v>51796</v>
       </c>
       <c r="G264">
-        <v>72816</v>
+        <v>74586</v>
       </c>
       <c r="H264">
-        <v>32679</v>
+        <v>33354</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>21022</v>
+        <v>24093</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>42567</v>
+        <v>43796</v>
       </c>
       <c r="G265">
-        <v>61296</v>
+        <v>63066</v>
       </c>
       <c r="H265">
-        <v>21545</v>
+        <v>19703</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12166,7 +12166,7 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10147</v>
+        <v>10115</v>
       </c>
       <c r="E268">
         <v>27770</v>
@@ -12178,7 +12178,7 @@
         <v>56896</v>
       </c>
       <c r="H268">
-        <v>29364</v>
+        <v>29396</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>11873</v>
+        <v>11857</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>38873</v>
+        <v>38857</v>
       </c>
       <c r="G270">
-        <v>55977</v>
+        <v>55954</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>61088</v>
+        <v>60771</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>76088</v>
+        <v>75771</v>
       </c>
       <c r="G272">
-        <v>109567</v>
+        <v>109110</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>41696</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>60945</v>
+        <v>0</v>
       </c>
       <c r="G273">
-        <v>87761</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>19249</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>71013</v>
+        <v>70364</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>86013</v>
+        <v>105364</v>
       </c>
       <c r="G274">
-        <v>123859</v>
+        <v>151724</v>
       </c>
       <c r="H274">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>77440</v>
       </c>
       <c r="E275">
         <v>111059</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>92440</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>133114</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12614,13 +12614,13 @@
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>46481</v>
+        <v>51796</v>
       </c>
       <c r="G278">
-        <v>66933</v>
+        <v>74586</v>
       </c>
       <c r="H278">
-        <v>26504</v>
+        <v>31819</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>24093</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>43796</v>
       </c>
       <c r="G279">
-        <v>0</v>
+        <v>63066</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>19703</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11714</v>
+        <v>11698</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23224</v>
+        <v>23240</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,16 +12826,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17682</v>
+        <v>17650</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32682</v>
+        <v>32650</v>
       </c>
       <c r="G283">
-        <v>47062</v>
+        <v>47016</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>49849</v>
+        <v>49754</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>64754</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>93246</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58634</v>
+        <v>58571</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>73571</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>105942</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>36219</v>
+        <v>34905</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55813</v>
+        <v>55838</v>
       </c>
       <c r="G288">
-        <v>80371</v>
+        <v>80407</v>
       </c>
       <c r="H288">
-        <v>19594</v>
+        <v>20933</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23840</v>
+        <v>23903</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39355</v>
+        <v>39380</v>
       </c>
       <c r="G289">
-        <v>56671</v>
+        <v>56707</v>
       </c>
       <c r="H289">
-        <v>15515</v>
+        <v>15477</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13227,13 +13227,13 @@
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>50712</v>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>73025</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23618</v>
+        <v>23587</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39266</v>
+        <v>39254</v>
       </c>
       <c r="G293">
-        <v>56543</v>
+        <v>56526</v>
       </c>
       <c r="H293">
-        <v>15648</v>
+        <v>15667</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,7 +13310,7 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>51147</v>
+        <v>49437</v>
       </c>
       <c r="E294">
         <v>68480</v>
@@ -13322,7 +13322,7 @@
         <v>95252</v>
       </c>
       <c r="H294">
-        <v>15000</v>
+        <v>16710</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13405,13 +13405,13 @@
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>77354</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>111390</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13492,13 +13492,13 @@
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>89227</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>128487</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>67531</v>
+        <v>67990</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>89133</v>
+        <v>88386</v>
       </c>
       <c r="G300">
-        <v>128352</v>
+        <v>127276</v>
       </c>
       <c r="H300">
-        <v>21602</v>
+        <v>20396</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>35428</v>
+        <v>33560</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>56264</v>
+        <v>55517</v>
       </c>
       <c r="G301">
-        <v>81020</v>
+        <v>79944</v>
       </c>
       <c r="H301">
-        <v>20836</v>
+        <v>21957</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>188171</v>
+        <v>173513</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>188513</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>271459</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13841,13 +13841,13 @@
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>79914</v>
+        <v>79876</v>
       </c>
       <c r="G306">
-        <v>115076</v>
+        <v>115021</v>
       </c>
       <c r="H306">
-        <v>30049</v>
+        <v>30011</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50308</v>
+        <v>50213</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69436</v>
+        <v>69398</v>
       </c>
       <c r="G307">
-        <v>99988</v>
+        <v>99933</v>
       </c>
       <c r="H307">
-        <v>19128</v>
+        <v>19185</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>23824</v>
+        <v>24457</v>
       </c>
       <c r="E310">
         <v>55520</v>
@@ -14026,7 +14026,7 @@
         <v>59962</v>
       </c>
       <c r="H310">
-        <v>17816</v>
+        <v>17183</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,16 +14058,16 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>21671</v>
+        <v>21418</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>36671</v>
+        <v>36418</v>
       </c>
       <c r="G311">
-        <v>52806</v>
+        <v>52442</v>
       </c>
       <c r="H311">
         <v>15000</v>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>65821</v>
+        <v>65789</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>80821</v>
+        <v>89831</v>
       </c>
       <c r="G312">
-        <v>116382</v>
+        <v>129357</v>
       </c>
       <c r="H312">
-        <v>15000</v>
+        <v>24042</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>63114</v>
       </c>
       <c r="E313">
         <v>83309</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>78114</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>112484</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20880</v>
+        <v>20737</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>35737</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>51461</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14282,13 +14282,13 @@
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>62670</v>
+        <v>49484</v>
       </c>
       <c r="G316">
-        <v>90245</v>
+        <v>71257</v>
       </c>
       <c r="H316">
-        <v>30393</v>
+        <v>17207</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39496</v>
+        <v>26484</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>41484</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>59737</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>15751</v>
+        <v>15703</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>17559</v>
+        <v>17607</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29254</v>
+        <v>29206</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>0</v>
+        <v>44206</v>
       </c>
       <c r="G319">
-        <v>0</v>
+        <v>63657</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58603</v>
+        <v>58571</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>73603</v>
+        <v>90505</v>
       </c>
       <c r="G324">
-        <v>105988</v>
+        <v>130327</v>
       </c>
       <c r="H324">
-        <v>15000</v>
+        <v>31934</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>63700</v>
       </c>
       <c r="E325">
         <v>74033</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>78700</v>
       </c>
       <c r="G325">
-        <v>0</v>
+        <v>113328</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>9371</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>35011</v>
       </c>
       <c r="G327">
-        <v>0</v>
+        <v>50416</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>25640</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20706</v>
+        <v>20674</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47706</v>
+        <v>47674</v>
       </c>
       <c r="G330">
-        <v>68697</v>
+        <v>68651</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,19 +14979,19 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43548</v>
+        <v>51511</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>78548</v>
+        <v>83294</v>
       </c>
       <c r="G332">
-        <v>113109</v>
+        <v>119943</v>
       </c>
       <c r="H332">
-        <v>35000</v>
+        <v>31783</v>
       </c>
       <c r="I332" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15030,13 +15030,13 @@
         <v>111059</v>
       </c>
       <c r="F333">
-        <v>0</v>
+        <v>98076</v>
       </c>
       <c r="G333">
-        <v>0</v>
+        <v>141229</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,19 +15067,19 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32721</v>
+        <v>31723</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>59721</v>
+        <v>66723</v>
       </c>
       <c r="G334">
-        <v>85998</v>
+        <v>96081</v>
       </c>
       <c r="H334">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I334" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>49200</v>
       </c>
       <c r="E335">
         <v>111059</v>
       </c>
       <c r="F335">
-        <v>0</v>
+        <v>68993</v>
       </c>
       <c r="G335">
-        <v>0</v>
+        <v>99350</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>19793</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188614</v>
+        <v>188187</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>203187</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>292589</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15205,13 +15205,13 @@
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>158721</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>228558</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,16 +15243,16 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>59790</v>
+        <v>59774</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>86790</v>
+        <v>86774</v>
       </c>
       <c r="G338">
-        <v>124978</v>
+        <v>124955</v>
       </c>
       <c r="H338">
         <v>27000</v>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>109512</v>
       </c>
       <c r="E341">
         <v>185111</v>
       </c>
       <c r="F341">
-        <v>0</v>
+        <v>124512</v>
       </c>
       <c r="G341">
-        <v>0</v>
+        <v>179297</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15421,13 +15421,13 @@
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>130607</v>
+        <v>138607</v>
       </c>
       <c r="G342">
-        <v>188074</v>
+        <v>199594</v>
       </c>
       <c r="H342">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>143736</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>158736</v>
       </c>
       <c r="G343">
-        <v>0</v>
+        <v>228580</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71583</v>
+        <v>71814</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>86583</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>124680</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47632</v>
+        <v>47739</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>62632</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90190</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94363</v>
+        <v>94541</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>109363</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>157483</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>72865</v>
+        <v>73004</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>87865</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>126526</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>6237</v>
+        <v>7153</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30148</v>
+        <v>30514</v>
       </c>
       <c r="G7">
-        <v>43413</v>
+        <v>43940</v>
       </c>
       <c r="H7">
-        <v>23911</v>
+        <v>23361</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>38609</v>
+        <v>38730</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55525</v>
+        <v>54807</v>
       </c>
       <c r="G8">
-        <v>79956</v>
+        <v>78922</v>
       </c>
       <c r="H8">
-        <v>16916</v>
+        <v>16077</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>37422</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>74033</v>
       </c>
       <c r="F9">
-        <v>52422</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>75488</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56022</v>
+        <v>56129</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78385</v>
+        <v>78428</v>
       </c>
       <c r="G10">
-        <v>112874</v>
+        <v>112936</v>
       </c>
       <c r="H10">
-        <v>22363</v>
+        <v>22299</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>74716</v>
       </c>
       <c r="E11">
         <v>111059</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>89716</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>129191</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82443</v>
+        <v>82710</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>99108</v>
+        <v>98341</v>
       </c>
       <c r="G12">
-        <v>142716</v>
+        <v>141611</v>
       </c>
       <c r="H12">
-        <v>16665</v>
+        <v>15631</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13376</v>
+        <v>12609</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40376</v>
+        <v>39609</v>
       </c>
       <c r="G13">
-        <v>58141</v>
+        <v>57037</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27069</v>
+        <v>27168</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45700</v>
+        <v>45740</v>
       </c>
       <c r="G15">
-        <v>65808</v>
+        <v>65866</v>
       </c>
       <c r="H15">
-        <v>18631</v>
+        <v>18572</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>26199</v>
+        <v>54368</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>53199</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>76607</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>95629</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>110629</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>159306</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21101</v>
+        <v>21316</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>39703</v>
+        <v>39789</v>
       </c>
       <c r="G27">
-        <v>57172</v>
+        <v>57296</v>
       </c>
       <c r="H27">
-        <v>18602</v>
+        <v>18473</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80036</v>
+        <v>80283</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96326</v>
+        <v>96448</v>
       </c>
       <c r="G28">
-        <v>138709</v>
+        <v>138885</v>
       </c>
       <c r="H28">
-        <v>16290</v>
+        <v>16165</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>39005</v>
+        <v>39127</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>66005</v>
+        <v>66127</v>
       </c>
       <c r="G29">
-        <v>95047</v>
+        <v>95223</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>135552</v>
+        <v>135984</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>150552</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>216795</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>71441</v>
+        <v>79697</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>98441</v>
+        <v>106697</v>
       </c>
       <c r="G31">
-        <v>141755</v>
+        <v>153644</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>59315</v>
+        <v>60411</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80370</v>
+        <v>80486</v>
       </c>
       <c r="G32">
-        <v>115733</v>
+        <v>115900</v>
       </c>
       <c r="H32">
-        <v>21055</v>
+        <v>20075</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>35839</v>
+        <v>35955</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>62839</v>
+        <v>62955</v>
       </c>
       <c r="G33">
-        <v>90488</v>
+        <v>90655</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>80654</v>
+        <v>80807</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>95654</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>137742</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,19 +2000,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>49247</v>
+        <v>49166</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>84247</v>
+        <v>76166</v>
       </c>
       <c r="G36">
-        <v>121316</v>
+        <v>109679</v>
       </c>
       <c r="H36">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35333</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>62333</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89760</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>67895</v>
+        <v>67802</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>94895</v>
+        <v>94802</v>
       </c>
       <c r="G38">
-        <v>136649</v>
+        <v>136515</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>98288</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>117508</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>169212</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>19220</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87603</v>
+        <v>87182</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>114603</v>
+        <v>114182</v>
       </c>
       <c r="G40">
-        <v>165028</v>
+        <v>164422</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>133874</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>148874</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>214379</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>33211</v>
+        <v>33274</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>60211</v>
+        <v>60274</v>
       </c>
       <c r="G43">
-        <v>86704</v>
+        <v>86795</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>79182</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>106182</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>152902</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>23381</v>
+        <v>23108</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>50381</v>
+        <v>50108</v>
       </c>
       <c r="G47">
-        <v>72549</v>
+        <v>72156</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36551</v>
+        <v>36621</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>53942</v>
+        <v>53973</v>
       </c>
       <c r="G50">
-        <v>77676</v>
+        <v>77721</v>
       </c>
       <c r="H50">
-        <v>17391</v>
+        <v>17352</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>23982</v>
+        <v>24060</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>40856</v>
+        <v>40887</v>
       </c>
       <c r="G51">
-        <v>58833</v>
+        <v>58877</v>
       </c>
       <c r="H51">
-        <v>16874</v>
+        <v>16827</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>53806</v>
+        <v>53908</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>68908</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>99228</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>58745</v>
+        <v>58856</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>73745</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>106193</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44688</v>
+        <v>44773</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>79688</v>
+        <v>79773</v>
       </c>
       <c r="G54">
-        <v>114751</v>
+        <v>114873</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>43453</v>
+        <v>43599</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>70453</v>
+        <v>70599</v>
       </c>
       <c r="G55">
-        <v>101452</v>
+        <v>101663</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>50767</v>
+        <v>50863</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>77767</v>
+        <v>77863</v>
       </c>
       <c r="G56">
-        <v>111984</v>
+        <v>112123</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>61927</v>
+        <v>62124</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>88524</v>
+        <v>88603</v>
       </c>
       <c r="G57">
-        <v>127475</v>
+        <v>127588</v>
       </c>
       <c r="H57">
-        <v>26597</v>
+        <v>26479</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>17318</v>
+        <v>17129</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38642</v>
+        <v>38653</v>
       </c>
       <c r="G58">
-        <v>55644</v>
+        <v>55660</v>
       </c>
       <c r="H58">
-        <v>21324</v>
+        <v>21524</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6190</v>
+        <v>6217</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22909</v>
+        <v>22920</v>
       </c>
       <c r="G59">
-        <v>32989</v>
+        <v>33005</v>
       </c>
       <c r="H59">
-        <v>16719</v>
+        <v>16703</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24030</v>
+        <v>24075</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>48407</v>
+        <v>48455</v>
       </c>
       <c r="G60">
-        <v>69706</v>
+        <v>69775</v>
       </c>
       <c r="H60">
-        <v>24377</v>
+        <v>24380</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25407</v>
+        <v>25455</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>40407</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58186</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13392</v>
+        <v>13418</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>40392</v>
+        <v>40418</v>
       </c>
       <c r="G63">
-        <v>58164</v>
+        <v>58202</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23080</v>
+        <v>23156</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>50080</v>
+        <v>50156</v>
       </c>
       <c r="G65">
-        <v>72115</v>
+        <v>72225</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>28035</v>
+        <v>29309</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>61444</v>
+        <v>61515</v>
       </c>
       <c r="G66">
-        <v>88479</v>
+        <v>88582</v>
       </c>
       <c r="H66">
-        <v>33409</v>
+        <v>32206</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20658</v>
+        <v>20729</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47658</v>
+        <v>47729</v>
       </c>
       <c r="G67">
-        <v>68628</v>
+        <v>68730</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47838</v>
+        <v>47929</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>74838</v>
+        <v>74929</v>
       </c>
       <c r="G68">
-        <v>107767</v>
+        <v>107898</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>28051</v>
+        <v>27866</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>55051</v>
+        <v>54866</v>
       </c>
       <c r="G69">
-        <v>79273</v>
+        <v>79007</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110098</v>
+        <v>110306</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>125098</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>180141</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52334</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>77467</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>111552</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>25133</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6775</v>
+        <v>6804</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21775</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>31356</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>69969</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>84969</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>122355</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87619</v>
+        <v>87912</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>122065</v>
+        <v>122142</v>
       </c>
       <c r="G76">
-        <v>175774</v>
+        <v>175884</v>
       </c>
       <c r="H76">
-        <v>34446</v>
+        <v>34230</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>59790</v>
+        <v>59983</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>80449</v>
+        <v>80526</v>
       </c>
       <c r="G77">
-        <v>115847</v>
+        <v>115957</v>
       </c>
       <c r="H77">
-        <v>20659</v>
+        <v>20543</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23143</v>
+        <v>23219</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>50143</v>
+        <v>50219</v>
       </c>
       <c r="G81">
-        <v>72206</v>
+        <v>72315</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86669</v>
+        <v>86945</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>101669</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>146403</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>50482</v>
+        <v>49737</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>65482</v>
+        <v>66714</v>
       </c>
       <c r="G84">
-        <v>94294</v>
+        <v>96068</v>
       </c>
       <c r="H84">
-        <v>15000</v>
+        <v>16977</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>26943</v>
+        <v>30023</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>45650</v>
+        <v>46882</v>
       </c>
       <c r="G85">
-        <v>65736</v>
+        <v>67510</v>
       </c>
       <c r="H85">
-        <v>18707</v>
+        <v>16859</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8168</v>
+        <v>8184</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38566</v>
+        <v>38575</v>
       </c>
       <c r="G90">
-        <v>55535</v>
+        <v>55548</v>
       </c>
       <c r="H90">
-        <v>30398</v>
+        <v>30391</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3673</v>
+        <v>3695</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30566</v>
+        <v>30575</v>
       </c>
       <c r="G91">
-        <v>44015</v>
+        <v>44028</v>
       </c>
       <c r="H91">
-        <v>26893</v>
+        <v>26880</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9451</v>
+        <v>9484</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>24451</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35209</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63462</v>
+        <v>63599</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>78599</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>113183</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34351</v>
+        <v>34464</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52224</v>
+        <v>52269</v>
       </c>
       <c r="G97">
-        <v>75203</v>
+        <v>75267</v>
       </c>
       <c r="H97">
-        <v>17873</v>
+        <v>17805</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>78818</v>
+        <v>79078</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>93818</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>135098</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>42076</v>
+        <v>43789</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>60368</v>
+        <v>61053</v>
       </c>
       <c r="G99">
-        <v>86930</v>
+        <v>87916</v>
       </c>
       <c r="H99">
-        <v>18292</v>
+        <v>17264</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60296</v>
+        <v>60490</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>80934</v>
+        <v>78756</v>
       </c>
       <c r="G100">
-        <v>116545</v>
+        <v>113409</v>
       </c>
       <c r="H100">
-        <v>20638</v>
+        <v>18266</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63098</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>78098</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>112461</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71298</v>
+        <v>71433</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>86298</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>124269</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>74623</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>101623</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>146337</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>5778</v>
+        <v>5313</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>32778</v>
+        <v>32313</v>
       </c>
       <c r="G109">
-        <v>47200</v>
+        <v>46531</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14437</v>
+        <v>14480</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>41437</v>
+        <v>41480</v>
       </c>
       <c r="G111">
-        <v>59669</v>
+        <v>59731</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,16 +5370,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48313</v>
+        <v>48468</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>75313</v>
+        <v>75468</v>
       </c>
       <c r="G113">
-        <v>108451</v>
+        <v>108674</v>
       </c>
       <c r="H113">
         <v>27000</v>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>99080</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>117825</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>169668</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>18745</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5541,19 +5541,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>166627</v>
+        <v>166942</v>
       </c>
       <c r="E117">
         <v>185111</v>
       </c>
       <c r="F117">
-        <v>181627</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>261543</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>79862</v>
+        <v>80125</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>94862</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>136601</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>46619</v>
+        <v>49626</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>61619</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>88731</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>85450</v>
+        <v>101916</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>100450</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>144648</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>207120</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>148085</v>
       </c>
       <c r="F122">
-        <v>222120</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>319853</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,7 +5803,7 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>113929</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>148085</v>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>45986</v>
+        <v>46073</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>60986</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>87820</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35333</v>
+        <v>35479</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>50333</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72480</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63462</v>
+        <v>63583</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>81038</v>
+        <v>78583</v>
       </c>
       <c r="G126">
-        <v>116695</v>
+        <v>113160</v>
       </c>
       <c r="H126">
-        <v>17576</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>55468</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>81439</v>
       </c>
       <c r="F127">
-        <v>70468</v>
+        <v>0</v>
       </c>
       <c r="G127">
-        <v>101474</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>38673</v>
+        <v>38746</v>
       </c>
       <c r="E128">
         <v>92546</v>
       </c>
       <c r="F128">
-        <v>65395</v>
+        <v>65450</v>
       </c>
       <c r="G128">
-        <v>94169</v>
+        <v>94248</v>
       </c>
       <c r="H128">
-        <v>26722</v>
+        <v>26704</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36931</v>
+        <v>37049</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56865</v>
+        <v>56913</v>
       </c>
       <c r="G129">
-        <v>81886</v>
+        <v>81955</v>
       </c>
       <c r="H129">
-        <v>19934</v>
+        <v>19864</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12680</v>
+        <v>12704</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33132</v>
+        <v>33310</v>
       </c>
       <c r="G130">
-        <v>47710</v>
+        <v>47966</v>
       </c>
       <c r="H130">
-        <v>20452</v>
+        <v>20606</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4527</v>
+        <v>6090</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25132</v>
+        <v>25757</v>
       </c>
       <c r="G131">
-        <v>36190</v>
+        <v>37090</v>
       </c>
       <c r="H131">
-        <v>20605</v>
+        <v>19667</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27513</v>
+        <v>27628</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43655</v>
+        <v>43701</v>
       </c>
       <c r="G132">
-        <v>62863</v>
+        <v>62929</v>
       </c>
       <c r="H132">
-        <v>16142</v>
+        <v>16073</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17255</v>
+        <v>17303</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36570</v>
+        <v>36589</v>
       </c>
       <c r="G135">
-        <v>52661</v>
+        <v>52688</v>
       </c>
       <c r="H135">
-        <v>19315</v>
+        <v>19286</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28447</v>
+        <v>28500</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46866</v>
+        <v>46887</v>
       </c>
       <c r="G137">
-        <v>67487</v>
+        <v>67517</v>
       </c>
       <c r="H137">
-        <v>18419</v>
+        <v>18387</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>28842</v>
+        <v>28802</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54655</v>
+        <v>54639</v>
       </c>
       <c r="G139">
-        <v>78703</v>
+        <v>78680</v>
       </c>
       <c r="H139">
-        <v>25813</v>
+        <v>25837</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>52429</v>
+        <v>58095</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>67429</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>97098</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77235</v>
+        <v>77492</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>92235</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>132818</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>86764</v>
+        <v>87040</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>101764</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>146540</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>85878</v>
+        <v>88039</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>100878</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>145264</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>121875</v>
+        <v>122106</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>136875</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>197100</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38119</v>
+        <v>38238</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62894</v>
+        <v>62941</v>
       </c>
       <c r="G150">
-        <v>90567</v>
+        <v>90635</v>
       </c>
       <c r="H150">
-        <v>24775</v>
+        <v>24703</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,19 +7067,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>22985</v>
+        <v>22870</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>53784</v>
+        <v>57870</v>
       </c>
       <c r="G152">
-        <v>77449</v>
+        <v>83333</v>
       </c>
       <c r="H152">
-        <v>30799</v>
+        <v>35000</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>18141</v>
+        <v>29611</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>45141</v>
+        <v>53937</v>
       </c>
       <c r="G153">
-        <v>65003</v>
+        <v>77669</v>
       </c>
       <c r="H153">
-        <v>27000</v>
+        <v>24326</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48487</v>
+        <v>48643</v>
       </c>
       <c r="E154">
         <v>92546</v>
       </c>
       <c r="F154">
-        <v>67055</v>
+        <v>69410</v>
       </c>
       <c r="G154">
-        <v>96559</v>
+        <v>99950</v>
       </c>
       <c r="H154">
-        <v>18568</v>
+        <v>20767</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>40161</v>
+        <v>55573</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>58157</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>83746</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>17996</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65156</v>
+        <v>65375</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80156</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>115425</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38768</v>
+        <v>42743</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65401</v>
+        <v>65565</v>
       </c>
       <c r="G158">
-        <v>94177</v>
+        <v>94414</v>
       </c>
       <c r="H158">
-        <v>26633</v>
+        <v>22822</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>41870</v>
+        <v>42013</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>56870</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>81893</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>17872</v>
+        <v>20063</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>34802</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>50115</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>16930</v>
+        <v>0</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>54265</v>
+        <v>54432</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>69265</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>99742</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70380</v>
+        <v>76604</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>85380</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>122947</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>51590</v>
+        <v>58634</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>66590</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>95890</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33845</v>
+        <v>33956</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>48845</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70337</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>33449</v>
+        <v>33512</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>55525</v>
+        <v>52720</v>
       </c>
       <c r="G168">
-        <v>79956</v>
+        <v>75917</v>
       </c>
       <c r="H168">
-        <v>22076</v>
+        <v>19208</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>73799</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>88799</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>127871</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15688</v>
+        <v>16479</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>30688</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>44191</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31153</v>
+        <v>30562</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51666</v>
+        <v>51430</v>
       </c>
       <c r="G173">
-        <v>74399</v>
+        <v>74059</v>
       </c>
       <c r="H173">
-        <v>20513</v>
+        <v>20868</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7361</v>
+        <v>7692</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37756</v>
+        <v>37772</v>
       </c>
       <c r="G174">
-        <v>54369</v>
+        <v>54392</v>
       </c>
       <c r="H174">
-        <v>30395</v>
+        <v>30080</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5240</v>
+        <v>5281</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29756</v>
+        <v>29772</v>
       </c>
       <c r="G175">
-        <v>42849</v>
+        <v>42872</v>
       </c>
       <c r="H175">
-        <v>24516</v>
+        <v>24491</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10290</v>
+        <v>10309</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>42408</v>
+        <v>42422</v>
       </c>
       <c r="G176">
-        <v>61068</v>
+        <v>61088</v>
       </c>
       <c r="H176">
-        <v>32118</v>
+        <v>32113</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7408</v>
+        <v>7422</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>34408</v>
+        <v>34422</v>
       </c>
       <c r="G177">
-        <v>49548</v>
+        <v>49568</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,19 +8212,19 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>48756</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>69424</v>
       </c>
       <c r="F178">
-        <v>63756</v>
+        <v>0</v>
       </c>
       <c r="G178">
-        <v>91809</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I178" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21782</v>
+        <v>21855</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41788</v>
+        <v>41818</v>
       </c>
       <c r="G179">
-        <v>60175</v>
+        <v>60218</v>
       </c>
       <c r="H179">
-        <v>20006</v>
+        <v>19963</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45796</v>
+        <v>45931</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65112</v>
+        <v>65166</v>
       </c>
       <c r="G181">
-        <v>93761</v>
+        <v>93839</v>
       </c>
       <c r="H181">
-        <v>19316</v>
+        <v>19235</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67673</v>
+        <v>67802</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86552</v>
+        <v>86746</v>
       </c>
       <c r="G182">
-        <v>124635</v>
+        <v>124914</v>
       </c>
       <c r="H182">
-        <v>18879</v>
+        <v>18944</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10163</v>
+        <v>10357</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37163</v>
+        <v>37357</v>
       </c>
       <c r="G183">
-        <v>53515</v>
+        <v>53794</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60296</v>
+        <v>60411</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80095</v>
+        <v>80141</v>
       </c>
       <c r="G184">
-        <v>115337</v>
+        <v>115403</v>
       </c>
       <c r="H184">
-        <v>19799</v>
+        <v>19730</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45511</v>
+        <v>45598</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>67517</v>
+        <v>67552</v>
       </c>
       <c r="G185">
-        <v>97224</v>
+        <v>97275</v>
       </c>
       <c r="H185">
-        <v>22006</v>
+        <v>21954</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79609</v>
+        <v>79760</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>110569</v>
+        <v>104542</v>
       </c>
       <c r="G186">
-        <v>159219</v>
+        <v>150540</v>
       </c>
       <c r="H186">
-        <v>30960</v>
+        <v>24782</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>80986</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>96147</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>138452</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15161</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>146864</v>
       </c>
       <c r="E190">
         <v>157342</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>161864</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>233084</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>171724</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>186724</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>268883</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>6823</v>
+        <v>7058</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>28115</v>
+        <v>27880</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11714</v>
+        <v>11736</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38714</v>
+        <v>38736</v>
       </c>
       <c r="G196">
-        <v>55748</v>
+        <v>55780</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51495</v>
+        <v>51593</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17915</v>
+        <v>17817</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74670</v>
+        <v>74907</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>89670</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129125</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>54534</v>
+        <v>54717</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>69534</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>100129</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36599</v>
+        <v>36668</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63599</v>
+        <v>63668</v>
       </c>
       <c r="G202">
-        <v>91583</v>
+        <v>91682</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27402</v>
+        <v>27454</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54402</v>
+        <v>54454</v>
       </c>
       <c r="G204">
-        <v>78339</v>
+        <v>78414</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101296</v>
+        <v>101488</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>116296</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>167466</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>64523</v>
+        <v>64518</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82342</v>
+        <v>82340</v>
       </c>
       <c r="G207">
-        <v>118572</v>
+        <v>118570</v>
       </c>
       <c r="H207">
-        <v>17819</v>
+        <v>17822</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144037</v>
+        <v>144310</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>179037</v>
+        <v>179310</v>
       </c>
       <c r="G208">
-        <v>257813</v>
+        <v>258206</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145984</v>
+        <v>146166</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>160984</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>231817</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>186778</v>
+        <v>187132</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>201778</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>290560</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>158981</v>
+        <v>159282</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>173981</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>250533</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>286507</v>
+        <v>287050</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>301507</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>434170</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34351</v>
+        <v>34511</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>62197</v>
+        <v>60654</v>
       </c>
       <c r="G214">
-        <v>89564</v>
+        <v>87342</v>
       </c>
       <c r="H214">
-        <v>27846</v>
+        <v>26143</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>39084</v>
+        <v>37541</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>54084</v>
+        <v>52541</v>
       </c>
       <c r="G215">
-        <v>77881</v>
+        <v>75659</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>16368</v>
+        <v>16399</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>36707</v>
+        <v>36719</v>
       </c>
       <c r="G216">
-        <v>52858</v>
+        <v>52875</v>
       </c>
       <c r="H216">
-        <v>20339</v>
+        <v>20320</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67151</v>
+        <v>16399</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>82151</v>
+        <v>36719</v>
       </c>
       <c r="G218">
-        <v>118297</v>
+        <v>52875</v>
       </c>
       <c r="H218">
-        <v>15000</v>
+        <v>20320</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13044</v>
+        <v>13259</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>46477</v>
+        <v>46499</v>
       </c>
       <c r="G220">
-        <v>66927</v>
+        <v>66959</v>
       </c>
       <c r="H220">
-        <v>33433</v>
+        <v>33240</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11477</v>
+        <v>11499</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>38477</v>
+        <v>38499</v>
       </c>
       <c r="G221">
-        <v>55407</v>
+        <v>55439</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>26895</v>
+        <v>25598</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>53895</v>
+        <v>52598</v>
       </c>
       <c r="G222">
-        <v>77609</v>
+        <v>75741</v>
       </c>
       <c r="H222">
         <v>27000</v>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16305</v>
+        <v>16479</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46952</v>
+        <v>45753</v>
       </c>
       <c r="G224">
-        <v>67611</v>
+        <v>65884</v>
       </c>
       <c r="H224">
-        <v>30647</v>
+        <v>29274</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11952</v>
+        <v>10753</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38952</v>
+        <v>37753</v>
       </c>
       <c r="G225">
-        <v>56091</v>
+        <v>54364</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26404</v>
+        <v>26454</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61404</v>
+        <v>61454</v>
       </c>
       <c r="G226">
-        <v>88422</v>
+        <v>88494</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>96041</v>
+        <v>38302</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>111041</v>
+        <v>65302</v>
       </c>
       <c r="G227">
-        <v>159899</v>
+        <v>94035</v>
       </c>
       <c r="H227">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>34937</v>
+        <v>35051</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>69937</v>
+        <v>70051</v>
       </c>
       <c r="G228">
-        <v>100709</v>
+        <v>100873</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>97988</v>
+        <v>98173</v>
       </c>
       <c r="E229">
         <v>185111</v>
       </c>
       <c r="F229">
-        <v>117388</v>
+        <v>117462</v>
       </c>
       <c r="G229">
-        <v>169039</v>
+        <v>169145</v>
       </c>
       <c r="H229">
-        <v>19400</v>
+        <v>19289</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16147</v>
+        <v>16193</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>41357</v>
+        <v>41362</v>
       </c>
       <c r="G230">
-        <v>59554</v>
+        <v>59561</v>
       </c>
       <c r="H230">
-        <v>25210</v>
+        <v>25169</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>6126</v>
+        <v>6138</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>31547</v>
+        <v>31552</v>
       </c>
       <c r="G231">
-        <v>45428</v>
+        <v>45435</v>
       </c>
       <c r="H231">
-        <v>25421</v>
+        <v>25414</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23349</v>
+        <v>23394</v>
       </c>
       <c r="E233">
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>38349</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>55223</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>85688</v>
+        <v>85850</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>112468</v>
+        <v>112533</v>
       </c>
       <c r="G237">
-        <v>161954</v>
+        <v>162048</v>
       </c>
       <c r="H237">
-        <v>26780</v>
+        <v>26683</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>25059</v>
+        <v>25598</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>60059</v>
+        <v>60598</v>
       </c>
       <c r="G238">
-        <v>86485</v>
+        <v>87261</v>
       </c>
       <c r="H238">
         <v>35000</v>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31755</v>
+        <v>31815</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>53351</v>
+        <v>53375</v>
       </c>
       <c r="G239">
-        <v>76825</v>
+        <v>76860</v>
       </c>
       <c r="H239">
-        <v>21596</v>
+        <v>21560</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,7 +10931,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46793</v>
+        <v>46946</v>
       </c>
       <c r="E240">
         <v>103654</v>
@@ -10943,7 +10943,7 @@
         <v>111947</v>
       </c>
       <c r="H240">
-        <v>30948</v>
+        <v>30795</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>85387</v>
+        <v>85549</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>100387</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>144557</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>110433</v>
       </c>
       <c r="E243">
         <v>133275</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>125433</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>180624</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>63985</v>
+        <v>64122</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79436</v>
+        <v>79555</v>
       </c>
       <c r="G244">
-        <v>114388</v>
+        <v>114559</v>
       </c>
       <c r="H244">
-        <v>15451</v>
+        <v>15433</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54075</v>
+        <v>54178</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>69075</v>
+        <v>0</v>
       </c>
       <c r="G245">
-        <v>99468</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75335</v>
+        <v>75478</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>90335</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>130082</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>79522</v>
       </c>
       <c r="E247">
         <v>98119</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>94522</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>136112</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>18347</v>
+        <v>18382</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42200</v>
+        <v>42215</v>
       </c>
       <c r="G248">
-        <v>60768</v>
+        <v>60790</v>
       </c>
       <c r="H248">
-        <v>23853</v>
+        <v>23833</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>10954</v>
+        <v>10991</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34200</v>
+        <v>34215</v>
       </c>
       <c r="G249">
-        <v>49248</v>
+        <v>49270</v>
       </c>
       <c r="H249">
-        <v>23246</v>
+        <v>23224</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>5176</v>
+        <v>30895</v>
       </c>
       <c r="E250">
         <v>74033</v>
       </c>
       <c r="F250">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="G250">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>29824</v>
+        <v>0</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>15466</v>
+        <v>15495</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>42466</v>
+        <v>42495</v>
       </c>
       <c r="G253">
-        <v>61151</v>
+        <v>61193</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>20563</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>47563</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>68491</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9514</v>
+        <v>9532</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>57983</v>
       </c>
       <c r="H256">
-        <v>30752</v>
+        <v>30734</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14833</v>
+        <v>14861</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>32871</v>
+        <v>32883</v>
       </c>
       <c r="G257">
-        <v>47334</v>
+        <v>47352</v>
       </c>
       <c r="H257">
-        <v>18038</v>
+        <v>18022</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12205</v>
+        <v>12228</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39205</v>
+        <v>39228</v>
       </c>
       <c r="G258">
-        <v>56455</v>
+        <v>56488</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,7 +11814,7 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8833</v>
+        <v>8850</v>
       </c>
       <c r="E260">
         <v>53688</v>
@@ -11826,7 +11826,7 @@
         <v>57983</v>
       </c>
       <c r="H260">
-        <v>31433</v>
+        <v>31416</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>16511</v>
+        <v>16542</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>33543</v>
+        <v>33555</v>
       </c>
       <c r="G261">
-        <v>48302</v>
+        <v>48319</v>
       </c>
       <c r="H261">
-        <v>17032</v>
+        <v>17013</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12886</v>
+        <v>12910</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>39124</v>
+        <v>39131</v>
       </c>
       <c r="G262">
-        <v>56339</v>
+        <v>56349</v>
       </c>
       <c r="H262">
-        <v>26238</v>
+        <v>26221</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10464</v>
+        <v>10483</v>
       </c>
       <c r="E263">
         <v>53688</v>
       </c>
       <c r="F263">
-        <v>31124</v>
+        <v>31131</v>
       </c>
       <c r="G263">
-        <v>44819</v>
+        <v>44829</v>
       </c>
       <c r="H263">
-        <v>20660</v>
+        <v>20648</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18442</v>
+        <v>18271</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>51796</v>
+        <v>51814</v>
       </c>
       <c r="G264">
-        <v>74586</v>
+        <v>74612</v>
       </c>
       <c r="H264">
-        <v>33354</v>
+        <v>33543</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24093</v>
+        <v>24139</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>43796</v>
+        <v>43814</v>
       </c>
       <c r="G265">
-        <v>63066</v>
+        <v>63092</v>
       </c>
       <c r="H265">
-        <v>19703</v>
+        <v>19675</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,7 +12078,7 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34256</v>
+        <v>34321</v>
       </c>
       <c r="E266">
         <v>72201</v>
@@ -12090,7 +12090,7 @@
         <v>77977</v>
       </c>
       <c r="H266">
-        <v>19895</v>
+        <v>19830</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>30821</v>
+        <v>30879</v>
       </c>
       <c r="E267">
         <v>72201</v>
       </c>
       <c r="F267">
-        <v>46487</v>
+        <v>46510</v>
       </c>
       <c r="G267">
-        <v>66941</v>
+        <v>66974</v>
       </c>
       <c r="H267">
-        <v>15666</v>
+        <v>15631</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10115</v>
+        <v>10182</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>39511</v>
+        <v>39542</v>
       </c>
       <c r="G268">
-        <v>56896</v>
+        <v>56940</v>
       </c>
       <c r="H268">
-        <v>29396</v>
+        <v>29360</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,19 +12211,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>16511</v>
+        <v>16542</v>
       </c>
       <c r="E269">
         <v>27770</v>
       </c>
       <c r="F269">
-        <v>31511</v>
+        <v>0</v>
       </c>
       <c r="G269">
-        <v>45376</v>
+        <v>0</v>
       </c>
       <c r="H269">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>11857</v>
+        <v>12054</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>38857</v>
+        <v>39054</v>
       </c>
       <c r="G270">
-        <v>55954</v>
+        <v>56238</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>60771</v>
+        <v>60633</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>75771</v>
+        <v>75633</v>
       </c>
       <c r="G272">
-        <v>109110</v>
+        <v>108912</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>40300</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>0</v>
+        <v>60386</v>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>86956</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>20086</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>70364</v>
+        <v>74510</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>105364</v>
+        <v>106475</v>
       </c>
       <c r="G274">
-        <v>151724</v>
+        <v>153324</v>
       </c>
       <c r="H274">
-        <v>35000</v>
+        <v>31965</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>77440</v>
+        <v>77587</v>
       </c>
       <c r="E275">
         <v>111059</v>
       </c>
       <c r="F275">
-        <v>92440</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>133114</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,7 +12519,7 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11208</v>
+        <v>11229</v>
       </c>
       <c r="E276">
         <v>53688</v>
@@ -12531,7 +12531,7 @@
         <v>57983</v>
       </c>
       <c r="H276">
-        <v>29058</v>
+        <v>29037</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>14326</v>
+        <v>14353</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>32669</v>
+        <v>32679</v>
       </c>
       <c r="G277">
-        <v>47043</v>
+        <v>47058</v>
       </c>
       <c r="H277">
-        <v>18343</v>
+        <v>18326</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>19977</v>
+        <v>20015</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>51796</v>
+        <v>51814</v>
       </c>
       <c r="G278">
-        <v>74586</v>
+        <v>74612</v>
       </c>
       <c r="H278">
-        <v>31819</v>
+        <v>31799</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24093</v>
+        <v>24139</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>43796</v>
+        <v>43814</v>
       </c>
       <c r="G279">
-        <v>63066</v>
+        <v>63092</v>
       </c>
       <c r="H279">
-        <v>19703</v>
+        <v>19675</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11698</v>
+        <v>11721</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23240</v>
+        <v>23217</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17650</v>
+        <v>17700</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32650</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>47016</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>49754</v>
+        <v>49959</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>64754</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>93246</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58571</v>
+        <v>58745</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>73571</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>105942</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>34905</v>
+        <v>35146</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55838</v>
+        <v>55869</v>
       </c>
       <c r="G288">
-        <v>80407</v>
+        <v>80451</v>
       </c>
       <c r="H288">
-        <v>20933</v>
+        <v>20723</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23903</v>
+        <v>23980</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39380</v>
+        <v>39411</v>
       </c>
       <c r="G289">
-        <v>56707</v>
+        <v>56752</v>
       </c>
       <c r="H289">
-        <v>15477</v>
+        <v>15431</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>35712</v>
+        <v>46850</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>50712</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>73025</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23587</v>
+        <v>23663</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39254</v>
+        <v>39284</v>
       </c>
       <c r="G293">
-        <v>56526</v>
+        <v>56569</v>
       </c>
       <c r="H293">
-        <v>15667</v>
+        <v>15621</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>49437</v>
+        <v>49753</v>
       </c>
       <c r="E294">
         <v>68480</v>
       </c>
       <c r="F294">
-        <v>66147</v>
+        <v>66167</v>
       </c>
       <c r="G294">
-        <v>95252</v>
+        <v>95280</v>
       </c>
       <c r="H294">
-        <v>16710</v>
+        <v>16414</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>25977</v>
+        <v>26026</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>43098</v>
+        <v>43118</v>
       </c>
       <c r="G295">
-        <v>62061</v>
+        <v>62090</v>
       </c>
       <c r="H295">
-        <v>17121</v>
+        <v>17092</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62354</v>
+        <v>62473</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>77354</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>111390</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74227</v>
+        <v>74368</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>89227</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>128487</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>67990</v>
+        <v>69229</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>88386</v>
+        <v>88411</v>
       </c>
       <c r="G300">
-        <v>127276</v>
+        <v>127312</v>
       </c>
       <c r="H300">
-        <v>20396</v>
+        <v>19182</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33560</v>
+        <v>33623</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>55517</v>
+        <v>55542</v>
       </c>
       <c r="G301">
-        <v>79944</v>
+        <v>79980</v>
       </c>
       <c r="H301">
-        <v>21957</v>
+        <v>21919</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>10733</v>
+        <v>10753</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>37733</v>
+        <v>37753</v>
       </c>
       <c r="G303">
-        <v>54336</v>
+        <v>54364</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>173513</v>
+        <v>188512</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>188513</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>271459</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104351</v>
+        <v>104549</v>
       </c>
       <c r="E305">
         <v>166598</v>
       </c>
       <c r="F305">
-        <v>119351</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>171865</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>49865</v>
+        <v>49959</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>79876</v>
+        <v>79939</v>
       </c>
       <c r="G306">
-        <v>115021</v>
+        <v>115112</v>
       </c>
       <c r="H306">
-        <v>30011</v>
+        <v>29980</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50213</v>
+        <v>50371</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69398</v>
+        <v>69461</v>
       </c>
       <c r="G307">
-        <v>99933</v>
+        <v>100024</v>
       </c>
       <c r="H307">
-        <v>19185</v>
+        <v>19090</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69003</v>
+        <v>69134</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>28176</v>
+        <v>28045</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77535</v>
+        <v>77682</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>92535</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>133250</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24457</v>
+        <v>24567</v>
       </c>
       <c r="E310">
         <v>55520</v>
@@ -14026,7 +14026,7 @@
         <v>59962</v>
       </c>
       <c r="H310">
-        <v>17183</v>
+        <v>17073</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>21418</v>
+        <v>22934</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>36418</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>52442</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>65789</v>
+        <v>65946</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>89831</v>
+        <v>89969</v>
       </c>
       <c r="G312">
-        <v>129357</v>
+        <v>129555</v>
       </c>
       <c r="H312">
-        <v>24042</v>
+        <v>24023</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63114</v>
+        <v>63234</v>
       </c>
       <c r="E313">
         <v>83309</v>
       </c>
       <c r="F313">
-        <v>78114</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>112484</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20737</v>
+        <v>20808</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>35737</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>51461</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32277</v>
+        <v>32339</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>49484</v>
+        <v>49534</v>
       </c>
       <c r="G316">
-        <v>71257</v>
+        <v>71329</v>
       </c>
       <c r="H316">
-        <v>17207</v>
+        <v>17195</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26484</v>
+        <v>26534</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>41484</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>59737</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>15703</v>
+        <v>15686</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>17607</v>
+        <v>17624</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29206</v>
+        <v>29484</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44206</v>
+        <v>0</v>
       </c>
       <c r="G319">
-        <v>63657</v>
+        <v>0</v>
       </c>
       <c r="H319">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>46999</v>
+        <v>47088</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>68112</v>
+        <v>68148</v>
       </c>
       <c r="G321">
-        <v>98081</v>
+        <v>98133</v>
       </c>
       <c r="H321">
-        <v>21113</v>
+        <v>21060</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58571</v>
+        <v>58698</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>90505</v>
+        <v>90644</v>
       </c>
       <c r="G324">
-        <v>130327</v>
+        <v>130527</v>
       </c>
       <c r="H324">
-        <v>31934</v>
+        <v>31946</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>63700</v>
+        <v>63821</v>
       </c>
       <c r="E325">
         <v>74033</v>
       </c>
       <c r="F325">
-        <v>78700</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>113328</v>
+        <v>0</v>
       </c>
       <c r="H325">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9371</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>35011</v>
+        <v>0</v>
       </c>
       <c r="G327">
-        <v>50416</v>
+        <v>0</v>
       </c>
       <c r="H327">
-        <v>25640</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>17002</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>38064</v>
       </c>
       <c r="G329">
-        <v>0</v>
+        <v>54812</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>21062</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20674</v>
+        <v>20856</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47674</v>
+        <v>47856</v>
       </c>
       <c r="G330">
-        <v>68651</v>
+        <v>68913</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,19 +14979,19 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>51511</v>
+        <v>43631</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>83294</v>
+        <v>78631</v>
       </c>
       <c r="G332">
-        <v>119943</v>
+        <v>113229</v>
       </c>
       <c r="H332">
-        <v>31783</v>
+        <v>35000</v>
       </c>
       <c r="I332" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>83076</v>
+        <v>83233</v>
       </c>
       <c r="E333">
         <v>111059</v>
       </c>
       <c r="F333">
-        <v>98076</v>
+        <v>0</v>
       </c>
       <c r="G333">
-        <v>141229</v>
+        <v>0</v>
       </c>
       <c r="H333">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>31723</v>
+        <v>31720</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>66723</v>
+        <v>66720</v>
       </c>
       <c r="G334">
-        <v>96081</v>
+        <v>96077</v>
       </c>
       <c r="H334">
         <v>35000</v>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49200</v>
+        <v>49293</v>
       </c>
       <c r="E335">
         <v>111059</v>
       </c>
       <c r="F335">
-        <v>68993</v>
+        <v>69030</v>
       </c>
       <c r="G335">
-        <v>99350</v>
+        <v>99403</v>
       </c>
       <c r="H335">
-        <v>19793</v>
+        <v>19737</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188187</v>
+        <v>188797</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>203187</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>292589</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>143721</v>
+        <v>143993</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>158721</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>228558</v>
+        <v>0</v>
       </c>
       <c r="H337">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,16 +15243,16 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>59774</v>
+        <v>59887</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>86774</v>
+        <v>86887</v>
       </c>
       <c r="G338">
-        <v>124955</v>
+        <v>125117</v>
       </c>
       <c r="H338">
         <v>27000</v>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>41791</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>0</v>
+        <v>68791</v>
       </c>
       <c r="G339">
-        <v>0</v>
+        <v>99059</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>109512</v>
+        <v>109719</v>
       </c>
       <c r="E341">
         <v>185111</v>
       </c>
       <c r="F341">
-        <v>124512</v>
+        <v>0</v>
       </c>
       <c r="G341">
-        <v>179297</v>
+        <v>0</v>
       </c>
       <c r="H341">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,16 +15415,16 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>103607</v>
+        <v>103804</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>138607</v>
+        <v>138804</v>
       </c>
       <c r="G342">
-        <v>199594</v>
+        <v>199878</v>
       </c>
       <c r="H342">
         <v>35000</v>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>143736</v>
+        <v>144009</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>158736</v>
+        <v>0</v>
       </c>
       <c r="G343">
-        <v>228580</v>
+        <v>0</v>
       </c>
       <c r="H343">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71814</v>
+        <v>71970</v>
       </c>
       <c r="E2">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86970</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>125237</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47739</v>
+        <v>47848</v>
       </c>
       <c r="E3">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>62848</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90501</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94541</v>
+        <v>94680</v>
       </c>
       <c r="E4">
-        <v>85141</v>
+        <v>85420</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>109680</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>157939</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>73004</v>
+        <v>70669</v>
       </c>
       <c r="E5">
-        <v>85141</v>
+        <v>85420</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>85669</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>123363</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7153</v>
+        <v>7173</v>
       </c>
       <c r="E7">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F7">
-        <v>30514</v>
+        <v>30593</v>
       </c>
       <c r="G7">
-        <v>43940</v>
+        <v>44054</v>
       </c>
       <c r="H7">
-        <v>23361</v>
+        <v>23420</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>38730</v>
+        <v>38707</v>
       </c>
       <c r="E8">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F8">
-        <v>54807</v>
+        <v>55706</v>
       </c>
       <c r="G8">
-        <v>78922</v>
+        <v>80217</v>
       </c>
       <c r="H8">
-        <v>16077</v>
+        <v>16999</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>37533</v>
       </c>
       <c r="E9">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>52533</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>75648</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56129</v>
+        <v>56164</v>
       </c>
       <c r="E10">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F10">
-        <v>78428</v>
+        <v>78606</v>
       </c>
       <c r="G10">
-        <v>112936</v>
+        <v>113193</v>
       </c>
       <c r="H10">
-        <v>22299</v>
+        <v>22442</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>74716</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F11">
-        <v>89716</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>129191</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82710</v>
+        <v>82889</v>
       </c>
       <c r="E12">
-        <v>83290</v>
+        <v>83562</v>
       </c>
       <c r="F12">
-        <v>98341</v>
+        <v>99190</v>
       </c>
       <c r="G12">
-        <v>141611</v>
+        <v>142834</v>
       </c>
       <c r="H12">
-        <v>15631</v>
+        <v>16301</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>12609</v>
+        <v>13458</v>
       </c>
       <c r="E13">
-        <v>83290</v>
+        <v>83562</v>
       </c>
       <c r="F13">
-        <v>39609</v>
+        <v>40458</v>
       </c>
       <c r="G13">
-        <v>57037</v>
+        <v>58260</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27168</v>
+        <v>27217</v>
       </c>
       <c r="E15">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F15">
-        <v>45740</v>
+        <v>45854</v>
       </c>
       <c r="G15">
-        <v>65866</v>
+        <v>66030</v>
       </c>
       <c r="H15">
-        <v>18572</v>
+        <v>18637</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>88844</v>
+        <v>89134</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>88844</v>
+        <v>89134</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>133275</v>
+        <v>133711</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>133275</v>
+        <v>133711</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>103654</v>
+        <v>103993</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54368</v>
+        <v>49229</v>
       </c>
       <c r="E21">
-        <v>103654</v>
+        <v>103993</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>66249</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>95399</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>17020</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>133275</v>
+        <v>133711</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>95807</v>
       </c>
       <c r="E23">
-        <v>133275</v>
+        <v>133711</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>110807</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>159562</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>162896</v>
+        <v>163428</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>162896</v>
+        <v>163428</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21316</v>
+        <v>21361</v>
       </c>
       <c r="E27">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F27">
-        <v>39789</v>
+        <v>39890</v>
       </c>
       <c r="G27">
-        <v>57296</v>
+        <v>57442</v>
       </c>
       <c r="H27">
-        <v>18473</v>
+        <v>18529</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80283</v>
+        <v>80477</v>
       </c>
       <c r="E28">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F28">
-        <v>96448</v>
+        <v>96689</v>
       </c>
       <c r="G28">
-        <v>138885</v>
+        <v>139232</v>
       </c>
       <c r="H28">
-        <v>16165</v>
+        <v>16212</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>39127</v>
+        <v>38247</v>
       </c>
       <c r="E29">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F29">
-        <v>66127</v>
+        <v>65247</v>
       </c>
       <c r="G29">
-        <v>95223</v>
+        <v>93956</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>135984</v>
+        <v>136292</v>
       </c>
       <c r="E30">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>151292</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>217860</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>79697</v>
+        <v>72796</v>
       </c>
       <c r="E31">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F31">
-        <v>106697</v>
+        <v>99796</v>
       </c>
       <c r="G31">
-        <v>153644</v>
+        <v>143706</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60411</v>
+        <v>60449</v>
       </c>
       <c r="E32">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F32">
-        <v>80486</v>
+        <v>80889</v>
       </c>
       <c r="G32">
-        <v>115900</v>
+        <v>116480</v>
       </c>
       <c r="H32">
-        <v>20075</v>
+        <v>20440</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>35955</v>
+        <v>36358</v>
       </c>
       <c r="E33">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F33">
-        <v>62955</v>
+        <v>63358</v>
       </c>
       <c r="G33">
-        <v>90655</v>
+        <v>91236</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1956,10 +1956,10 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>80807</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>49166</v>
+        <v>49260</v>
       </c>
       <c r="E36">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F36">
-        <v>76166</v>
+        <v>76260</v>
       </c>
       <c r="G36">
-        <v>109679</v>
+        <v>109814</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35406</v>
       </c>
       <c r="E37">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62406</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>89865</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>67802</v>
+        <v>67701</v>
       </c>
       <c r="E38">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F38">
-        <v>94802</v>
+        <v>94701</v>
       </c>
       <c r="G38">
-        <v>136515</v>
+        <v>136369</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>98473</v>
       </c>
       <c r="E39">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>117818</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>169658</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>19345</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87182</v>
+        <v>87825</v>
       </c>
       <c r="E40">
-        <v>240650</v>
+        <v>241437</v>
       </c>
       <c r="F40">
-        <v>114182</v>
+        <v>114825</v>
       </c>
       <c r="G40">
-        <v>164422</v>
+        <v>165348</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>33274</v>
+        <v>33502</v>
       </c>
       <c r="E43">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F43">
-        <v>60274</v>
+        <v>60502</v>
       </c>
       <c r="G43">
-        <v>86795</v>
+        <v>87123</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>74367</v>
       </c>
       <c r="E45">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>101367</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>145968</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>23108</v>
+        <v>22837</v>
       </c>
       <c r="E47">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F47">
-        <v>50108</v>
+        <v>49837</v>
       </c>
       <c r="G47">
-        <v>72156</v>
+        <v>71765</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36621</v>
+        <v>36644</v>
       </c>
       <c r="E50">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F50">
-        <v>53973</v>
+        <v>54081</v>
       </c>
       <c r="G50">
-        <v>77721</v>
+        <v>77877</v>
       </c>
       <c r="H50">
-        <v>17352</v>
+        <v>17437</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>24060</v>
+        <v>24122</v>
       </c>
       <c r="E51">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F51">
-        <v>40887</v>
+        <v>40995</v>
       </c>
       <c r="G51">
-        <v>58877</v>
+        <v>59033</v>
       </c>
       <c r="H51">
-        <v>16827</v>
+        <v>16873</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,16 +2698,16 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>53908</v>
+        <v>51070</v>
       </c>
       <c r="E52">
-        <v>77736</v>
+        <v>77990</v>
       </c>
       <c r="F52">
-        <v>68908</v>
+        <v>66070</v>
       </c>
       <c r="G52">
-        <v>99228</v>
+        <v>95141</v>
       </c>
       <c r="H52">
         <v>15000</v>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>58856</v>
+        <v>67955</v>
       </c>
       <c r="E53">
-        <v>77736</v>
+        <v>77990</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>82955</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>119455</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44773</v>
+        <v>44849</v>
       </c>
       <c r="E54">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F54">
-        <v>79773</v>
+        <v>79849</v>
       </c>
       <c r="G54">
-        <v>114873</v>
+        <v>114983</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>43599</v>
+        <v>44690</v>
       </c>
       <c r="E55">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F55">
-        <v>70599</v>
+        <v>71690</v>
       </c>
       <c r="G55">
-        <v>101663</v>
+        <v>103234</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>50863</v>
+        <v>50927</v>
       </c>
       <c r="E56">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F56">
-        <v>77863</v>
+        <v>77927</v>
       </c>
       <c r="G56">
-        <v>112123</v>
+        <v>112215</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62124</v>
+        <v>65956</v>
       </c>
       <c r="E57">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F57">
-        <v>88603</v>
+        <v>90324</v>
       </c>
       <c r="G57">
-        <v>127588</v>
+        <v>130067</v>
       </c>
       <c r="H57">
-        <v>26479</v>
+        <v>24368</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>17129</v>
+        <v>16949</v>
       </c>
       <c r="E58">
-        <v>37007</v>
+        <v>37128</v>
       </c>
       <c r="F58">
-        <v>38653</v>
+        <v>38701</v>
       </c>
       <c r="G58">
-        <v>55660</v>
+        <v>55729</v>
       </c>
       <c r="H58">
-        <v>21524</v>
+        <v>21752</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="E59">
-        <v>37007</v>
+        <v>37128</v>
       </c>
       <c r="F59">
-        <v>22920</v>
+        <v>22968</v>
       </c>
       <c r="G59">
-        <v>33005</v>
+        <v>33074</v>
       </c>
       <c r="H59">
-        <v>16703</v>
+        <v>16747</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,10 +3057,10 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24075</v>
+        <v>24107</v>
       </c>
       <c r="E60">
-        <v>49967</v>
+        <v>50130</v>
       </c>
       <c r="F60">
         <v>48455</v>
@@ -3069,7 +3069,7 @@
         <v>69775</v>
       </c>
       <c r="H60">
-        <v>24380</v>
+        <v>24348</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3105,16 +3105,16 @@
         <v>25455</v>
       </c>
       <c r="E61">
-        <v>49967</v>
+        <v>50130</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40455</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58255</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>83290</v>
+        <v>83562</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13418</v>
+        <v>14235</v>
       </c>
       <c r="E63">
-        <v>83290</v>
+        <v>83562</v>
       </c>
       <c r="F63">
-        <v>40418</v>
+        <v>41235</v>
       </c>
       <c r="G63">
-        <v>58202</v>
+        <v>59378</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>124926</v>
+        <v>125334</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23156</v>
+        <v>23218</v>
       </c>
       <c r="E65">
-        <v>124926</v>
+        <v>125334</v>
       </c>
       <c r="F65">
-        <v>50156</v>
+        <v>50218</v>
       </c>
       <c r="G65">
-        <v>72225</v>
+        <v>72314</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>29309</v>
+        <v>25820</v>
       </c>
       <c r="E66">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F66">
-        <v>61515</v>
+        <v>60820</v>
       </c>
       <c r="G66">
-        <v>88582</v>
+        <v>87581</v>
       </c>
       <c r="H66">
-        <v>32206</v>
+        <v>35000</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20729</v>
+        <v>20774</v>
       </c>
       <c r="E67">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F67">
-        <v>47729</v>
+        <v>47774</v>
       </c>
       <c r="G67">
-        <v>68730</v>
+        <v>68795</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47929</v>
+        <v>47991</v>
       </c>
       <c r="E68">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F68">
-        <v>74929</v>
+        <v>74991</v>
       </c>
       <c r="G68">
-        <v>107898</v>
+        <v>107987</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27866</v>
+        <v>27598</v>
       </c>
       <c r="E69">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F69">
-        <v>54866</v>
+        <v>54598</v>
       </c>
       <c r="G69">
-        <v>79007</v>
+        <v>78621</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110306</v>
+        <v>110471</v>
       </c>
       <c r="E70">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>125471</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>180678</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>27751</v>
+        <v>27842</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6804</v>
+        <v>6824</v>
       </c>
       <c r="E73">
-        <v>27751</v>
+        <v>27842</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>21824</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>31427</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>97175</v>
+        <v>97492</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>97175</v>
+        <v>97492</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87912</v>
+        <v>91030</v>
       </c>
       <c r="E76">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F76">
-        <v>122142</v>
+        <v>122373</v>
       </c>
       <c r="G76">
-        <v>175884</v>
+        <v>176217</v>
       </c>
       <c r="H76">
-        <v>34230</v>
+        <v>31343</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>59983</v>
+        <v>60147</v>
       </c>
       <c r="E77">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F77">
-        <v>80526</v>
+        <v>80757</v>
       </c>
       <c r="G77">
-        <v>115957</v>
+        <v>116290</v>
       </c>
       <c r="H77">
-        <v>20543</v>
+        <v>20610</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23219</v>
+        <v>23265</v>
       </c>
       <c r="E81">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F81">
-        <v>50219</v>
+        <v>50265</v>
       </c>
       <c r="G81">
-        <v>72315</v>
+        <v>72382</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86945</v>
+        <v>87142</v>
       </c>
       <c r="E83">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>102142</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>147084</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>49737</v>
+        <v>49499</v>
       </c>
       <c r="E84">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F84">
-        <v>66714</v>
+        <v>68968</v>
       </c>
       <c r="G84">
-        <v>96068</v>
+        <v>99314</v>
       </c>
       <c r="H84">
-        <v>16977</v>
+        <v>19469</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>30023</v>
+        <v>34136</v>
       </c>
       <c r="E85">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F85">
-        <v>46882</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>67510</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>16859</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8184</v>
+        <v>8189</v>
       </c>
       <c r="E90">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F90">
-        <v>38575</v>
+        <v>38652</v>
       </c>
       <c r="G90">
-        <v>55548</v>
+        <v>55659</v>
       </c>
       <c r="H90">
-        <v>30391</v>
+        <v>30463</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3695</v>
+        <v>3698</v>
       </c>
       <c r="E91">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F91">
-        <v>30575</v>
+        <v>30652</v>
       </c>
       <c r="G91">
-        <v>44028</v>
+        <v>44139</v>
       </c>
       <c r="H91">
-        <v>26880</v>
+        <v>26954</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>27751</v>
+        <v>27842</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9484</v>
+        <v>9506</v>
       </c>
       <c r="E93">
-        <v>27751</v>
+        <v>27842</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24506</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35289</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4546,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>35156</v>
+        <v>35271</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>35156</v>
+        <v>35271</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63599</v>
+        <v>63670</v>
       </c>
       <c r="E96">
-        <v>83290</v>
+        <v>83562</v>
       </c>
       <c r="F96">
-        <v>78599</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>113183</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34464</v>
+        <v>34549</v>
       </c>
       <c r="E97">
-        <v>83290</v>
+        <v>83562</v>
       </c>
       <c r="F97">
-        <v>52269</v>
+        <v>52409</v>
       </c>
       <c r="G97">
-        <v>75267</v>
+        <v>75469</v>
       </c>
       <c r="H97">
-        <v>17805</v>
+        <v>17860</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79078</v>
+        <v>79255</v>
       </c>
       <c r="E98">
-        <v>96249</v>
+        <v>96564</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>94255</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>135727</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>43789</v>
+        <v>42151</v>
       </c>
       <c r="E99">
-        <v>96249</v>
+        <v>96564</v>
       </c>
       <c r="F99">
-        <v>61053</v>
+        <v>60521</v>
       </c>
       <c r="G99">
-        <v>87916</v>
+        <v>87150</v>
       </c>
       <c r="H99">
-        <v>17264</v>
+        <v>18370</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60490</v>
+        <v>60623</v>
       </c>
       <c r="E100">
-        <v>107912</v>
+        <v>108265</v>
       </c>
       <c r="F100">
-        <v>78756</v>
+        <v>78969</v>
       </c>
       <c r="G100">
-        <v>113409</v>
+        <v>113715</v>
       </c>
       <c r="H100">
-        <v>18266</v>
+        <v>18346</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4858,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>107912</v>
+        <v>108265</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>138829</v>
+        <v>139283</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>138829</v>
+        <v>139283</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5027,10 +5027,10 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71433</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>74764</v>
       </c>
       <c r="E107">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>101764</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>146540</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>5313</v>
+        <v>4872</v>
       </c>
       <c r="E109">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F109">
-        <v>32313</v>
+        <v>31872</v>
       </c>
       <c r="G109">
-        <v>46531</v>
+        <v>45896</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5244,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>166598</v>
+        <v>167143</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14480</v>
+        <v>15077</v>
       </c>
       <c r="E111">
-        <v>166598</v>
+        <v>167143</v>
       </c>
       <c r="F111">
-        <v>41480</v>
+        <v>42077</v>
       </c>
       <c r="G111">
-        <v>59731</v>
+        <v>60591</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48468</v>
+        <v>51165</v>
       </c>
       <c r="E113">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F113">
-        <v>75468</v>
+        <v>77164</v>
       </c>
       <c r="G113">
-        <v>108674</v>
+        <v>111116</v>
       </c>
       <c r="H113">
-        <v>27000</v>
+        <v>25999</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>96823</v>
       </c>
       <c r="E115">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>117158</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>168708</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>20335</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>166942</v>
+        <v>0</v>
       </c>
       <c r="E117">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80125</v>
+        <v>83349</v>
       </c>
       <c r="E118">
-        <v>88844</v>
+        <v>89134</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>98349</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>141623</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>49626</v>
+        <v>50102</v>
       </c>
       <c r="E119">
-        <v>88844</v>
+        <v>89134</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>65102</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>93747</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5676,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>118465</v>
+        <v>118852</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>101916</v>
+        <v>85603</v>
       </c>
       <c r="E121">
-        <v>118465</v>
+        <v>118852</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>100603</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>144868</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46073</v>
+        <v>46134</v>
       </c>
       <c r="E124">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>61134</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>88033</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35479</v>
+        <v>35565</v>
       </c>
       <c r="E125">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50565</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72814</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63583</v>
+        <v>63670</v>
       </c>
       <c r="E126">
-        <v>81439</v>
+        <v>81705</v>
       </c>
       <c r="F126">
-        <v>78583</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>113160</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>81439</v>
+        <v>81705</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>38746</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F128">
-        <v>65450</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>94248</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>26704</v>
+        <v>0</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>37049</v>
+        <v>36977</v>
       </c>
       <c r="E129">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F129">
-        <v>56913</v>
+        <v>57002</v>
       </c>
       <c r="G129">
-        <v>81955</v>
+        <v>82083</v>
       </c>
       <c r="H129">
-        <v>19864</v>
+        <v>20025</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12704</v>
+        <v>12712</v>
       </c>
       <c r="E130">
-        <v>44413</v>
+        <v>44558</v>
       </c>
       <c r="F130">
-        <v>33310</v>
+        <v>33419</v>
       </c>
       <c r="G130">
-        <v>47966</v>
+        <v>48123</v>
       </c>
       <c r="H130">
-        <v>20606</v>
+        <v>20707</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>6090</v>
+        <v>5824</v>
       </c>
       <c r="E131">
-        <v>44413</v>
+        <v>44558</v>
       </c>
       <c r="F131">
-        <v>25757</v>
+        <v>25707</v>
       </c>
       <c r="G131">
-        <v>37090</v>
+        <v>37018</v>
       </c>
       <c r="H131">
-        <v>19667</v>
+        <v>19883</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27628</v>
+        <v>27677</v>
       </c>
       <c r="E132">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F132">
-        <v>43701</v>
+        <v>43809</v>
       </c>
       <c r="G132">
-        <v>62929</v>
+        <v>63085</v>
       </c>
       <c r="H132">
-        <v>16073</v>
+        <v>16132</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -6292,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>60686</v>
+        <v>60884</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17303</v>
+        <v>17330</v>
       </c>
       <c r="E135">
-        <v>60686</v>
+        <v>60884</v>
       </c>
       <c r="F135">
-        <v>36589</v>
+        <v>36677</v>
       </c>
       <c r="G135">
-        <v>52688</v>
+        <v>52815</v>
       </c>
       <c r="H135">
-        <v>19286</v>
+        <v>19347</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6379,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>75607</v>
+        <v>75854</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28500</v>
+        <v>29233</v>
       </c>
       <c r="E137">
-        <v>75607</v>
+        <v>75854</v>
       </c>
       <c r="F137">
-        <v>46887</v>
+        <v>47276</v>
       </c>
       <c r="G137">
-        <v>67517</v>
+        <v>68077</v>
       </c>
       <c r="H137">
-        <v>18387</v>
+        <v>18043</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>95175</v>
+        <v>95486</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>28802</v>
+        <v>28677</v>
       </c>
       <c r="E139">
-        <v>95175</v>
+        <v>95486</v>
       </c>
       <c r="F139">
-        <v>54639</v>
+        <v>54710</v>
       </c>
       <c r="G139">
-        <v>78680</v>
+        <v>78782</v>
       </c>
       <c r="H139">
-        <v>25837</v>
+        <v>26033</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>90695</v>
+        <v>90992</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58095</v>
+        <v>58211</v>
       </c>
       <c r="E141">
-        <v>90695</v>
+        <v>90992</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>73211</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>105424</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77492</v>
+        <v>77668</v>
       </c>
       <c r="E143">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>92668</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>133442</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>155491</v>
+        <v>155999</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87040</v>
+        <v>87237</v>
       </c>
       <c r="E145">
-        <v>155491</v>
+        <v>155999</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>102237</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>147221</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>90695</v>
+        <v>90992</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>88039</v>
+        <v>86047</v>
       </c>
       <c r="E147">
-        <v>90695</v>
+        <v>90992</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>101047</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>145508</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6896,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122106</v>
+        <v>122088</v>
       </c>
       <c r="E149">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>137088</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>197407</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38238</v>
+        <v>38326</v>
       </c>
       <c r="E150">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F150">
-        <v>62941</v>
+        <v>63113</v>
       </c>
       <c r="G150">
-        <v>90635</v>
+        <v>90883</v>
       </c>
       <c r="H150">
-        <v>24703</v>
+        <v>24787</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -7067,19 +7067,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>22870</v>
+        <v>22694</v>
       </c>
       <c r="E152">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F152">
-        <v>57870</v>
+        <v>53171</v>
       </c>
       <c r="G152">
-        <v>83333</v>
+        <v>76566</v>
       </c>
       <c r="H152">
-        <v>35000</v>
+        <v>30477</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29611</v>
+        <v>18171</v>
       </c>
       <c r="E153">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F153">
-        <v>53937</v>
+        <v>45171</v>
       </c>
       <c r="G153">
-        <v>77669</v>
+        <v>65046</v>
       </c>
       <c r="H153">
-        <v>24326</v>
+        <v>27000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48643</v>
+        <v>48753</v>
       </c>
       <c r="E154">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F154">
-        <v>69410</v>
+        <v>69637</v>
       </c>
       <c r="G154">
-        <v>99950</v>
+        <v>100277</v>
       </c>
       <c r="H154">
-        <v>20767</v>
+        <v>20884</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>55573</v>
+        <v>76128</v>
       </c>
       <c r="E155">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>91128</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>131224</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65375</v>
+        <v>65527</v>
       </c>
       <c r="E156">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80527</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>115959</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7292,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>42743</v>
+        <v>38866</v>
       </c>
       <c r="E158">
-        <v>62926</v>
+        <v>63131</v>
       </c>
       <c r="F158">
-        <v>65565</v>
+        <v>65668</v>
       </c>
       <c r="G158">
-        <v>94414</v>
+        <v>94562</v>
       </c>
       <c r="H158">
-        <v>22822</v>
+        <v>26802</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42013</v>
+        <v>42103</v>
       </c>
       <c r="E159">
-        <v>62926</v>
+        <v>63131</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>57103</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>82228</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20063</v>
+        <v>17901</v>
       </c>
       <c r="E161">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>34884</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>50233</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>16983</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7510,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>54432</v>
+        <v>56164</v>
       </c>
       <c r="E163">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>71164</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>102476</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>76604</v>
+        <v>70495</v>
       </c>
       <c r="E165">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>85495</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>123113</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>58634</v>
+        <v>53942</v>
       </c>
       <c r="E166">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>68942</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>99276</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33956</v>
+        <v>34025</v>
       </c>
       <c r="E167">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>49025</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70596</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>33512</v>
+        <v>33454</v>
       </c>
       <c r="E168">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F168">
-        <v>52720</v>
+        <v>55706</v>
       </c>
       <c r="G168">
-        <v>75917</v>
+        <v>80217</v>
       </c>
       <c r="H168">
-        <v>19208</v>
+        <v>22252</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>73938</v>
       </c>
       <c r="E169">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>88938</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>128071</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7861,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>27751</v>
+        <v>27842</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>16479</v>
+        <v>16203</v>
       </c>
       <c r="E171">
-        <v>27751</v>
+        <v>27842</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>31203</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>44932</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>85141</v>
+        <v>85420</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30562</v>
+        <v>29915</v>
       </c>
       <c r="E173">
-        <v>85141</v>
+        <v>85420</v>
       </c>
       <c r="F173">
-        <v>51430</v>
+        <v>51280</v>
       </c>
       <c r="G173">
-        <v>74059</v>
+        <v>73843</v>
       </c>
       <c r="H173">
-        <v>20868</v>
+        <v>21365</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7692</v>
+        <v>7253</v>
       </c>
       <c r="E174">
-        <v>55539</v>
+        <v>55721</v>
       </c>
       <c r="F174">
-        <v>37772</v>
+        <v>37839</v>
       </c>
       <c r="G174">
-        <v>54392</v>
+        <v>54488</v>
       </c>
       <c r="H174">
-        <v>30080</v>
+        <v>30586</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5281</v>
+        <v>5269</v>
       </c>
       <c r="E175">
-        <v>55539</v>
+        <v>55721</v>
       </c>
       <c r="F175">
-        <v>29772</v>
+        <v>29839</v>
       </c>
       <c r="G175">
-        <v>42872</v>
+        <v>42968</v>
       </c>
       <c r="H175">
-        <v>24491</v>
+        <v>24570</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10309</v>
+        <v>10316</v>
       </c>
       <c r="E176">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F176">
-        <v>42422</v>
+        <v>42411</v>
       </c>
       <c r="G176">
-        <v>61088</v>
+        <v>61072</v>
       </c>
       <c r="H176">
-        <v>32113</v>
+        <v>32095</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7422</v>
+        <v>7411</v>
       </c>
       <c r="E177">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F177">
-        <v>34422</v>
+        <v>34411</v>
       </c>
       <c r="G177">
-        <v>49568</v>
+        <v>49552</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,19 +8212,19 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>48927</v>
       </c>
       <c r="E178">
-        <v>69424</v>
+        <v>69651</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>63927</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>92055</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I178" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21855</v>
+        <v>21901</v>
       </c>
       <c r="E179">
-        <v>69424</v>
+        <v>69651</v>
       </c>
       <c r="F179">
-        <v>41818</v>
+        <v>41924</v>
       </c>
       <c r="G179">
-        <v>60218</v>
+        <v>60371</v>
       </c>
       <c r="H179">
-        <v>19963</v>
+        <v>20023</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>104598</v>
+        <v>104940</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45931</v>
+        <v>46039</v>
       </c>
       <c r="E181">
-        <v>104598</v>
+        <v>104940</v>
       </c>
       <c r="F181">
-        <v>65166</v>
+        <v>65342</v>
       </c>
       <c r="G181">
-        <v>93839</v>
+        <v>94092</v>
       </c>
       <c r="H181">
-        <v>19235</v>
+        <v>19303</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67802</v>
+        <v>67892</v>
       </c>
       <c r="E182">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F182">
-        <v>86746</v>
+        <v>86784</v>
       </c>
       <c r="G182">
-        <v>124914</v>
+        <v>124969</v>
       </c>
       <c r="H182">
-        <v>18944</v>
+        <v>18892</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10357</v>
+        <v>10395</v>
       </c>
       <c r="E183">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F183">
-        <v>37357</v>
+        <v>37395</v>
       </c>
       <c r="G183">
-        <v>53794</v>
+        <v>53849</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60411</v>
+        <v>60449</v>
       </c>
       <c r="E184">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F184">
-        <v>80141</v>
+        <v>80320</v>
       </c>
       <c r="G184">
-        <v>115403</v>
+        <v>115661</v>
       </c>
       <c r="H184">
-        <v>19730</v>
+        <v>19871</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45598</v>
+        <v>45595</v>
       </c>
       <c r="E185">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F185">
-        <v>67552</v>
+        <v>67692</v>
       </c>
       <c r="G185">
-        <v>97275</v>
+        <v>97476</v>
       </c>
       <c r="H185">
-        <v>21954</v>
+        <v>22097</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79760</v>
+        <v>79810</v>
       </c>
       <c r="E186">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F186">
-        <v>104542</v>
+        <v>110859</v>
       </c>
       <c r="G186">
-        <v>150540</v>
+        <v>159637</v>
       </c>
       <c r="H186">
-        <v>24782</v>
+        <v>31049</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>81143</v>
       </c>
       <c r="E187">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>96399</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>138815</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>15256</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="E188">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="E189">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -8738,16 +8738,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>146864</v>
+        <v>146845</v>
       </c>
       <c r="E190">
-        <v>157342</v>
+        <v>157856</v>
       </c>
       <c r="F190">
-        <v>161864</v>
+        <v>161845</v>
       </c>
       <c r="G190">
-        <v>233084</v>
+        <v>233057</v>
       </c>
       <c r="H190">
         <v>15000</v>
@@ -8784,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="E191">
-        <v>157342</v>
+        <v>157856</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>172047</v>
       </c>
       <c r="E192">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>187047</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>269348</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8869,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -8908,19 +8908,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7058</v>
+        <v>6903</v>
       </c>
       <c r="E194">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F194">
-        <v>34938</v>
+        <v>35000</v>
       </c>
       <c r="G194">
-        <v>50311</v>
+        <v>50400</v>
       </c>
       <c r="H194">
-        <v>27880</v>
+        <v>28097</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8956,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="E195">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11736</v>
+        <v>11760</v>
       </c>
       <c r="E196">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F196">
-        <v>38736</v>
+        <v>38760</v>
       </c>
       <c r="G196">
-        <v>55780</v>
+        <v>55814</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9044,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="E197">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -9083,19 +9083,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51593</v>
+        <v>51673</v>
       </c>
       <c r="E198">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F198">
-        <v>69410</v>
+        <v>69637</v>
       </c>
       <c r="G198">
-        <v>99950</v>
+        <v>100277</v>
       </c>
       <c r="H198">
-        <v>17817</v>
+        <v>17964</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74907</v>
+        <v>75081</v>
       </c>
       <c r="E199">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>90081</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>129717</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>54717</v>
+        <v>57576</v>
       </c>
       <c r="E200">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>72576</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>104509</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="E201">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -9259,19 +9259,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36668</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F202">
-        <v>63668</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>91682</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
@@ -9308,7 +9308,7 @@
         <v>0</v>
       </c>
       <c r="E203">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27454</v>
+        <v>27487</v>
       </c>
       <c r="E204">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F204">
-        <v>54454</v>
+        <v>54487</v>
       </c>
       <c r="G204">
-        <v>78414</v>
+        <v>78461</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9397,7 +9397,7 @@
         <v>0</v>
       </c>
       <c r="E205">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101488</v>
+        <v>101552</v>
       </c>
       <c r="E206">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>116552</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>167835</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>64518</v>
+        <v>63480</v>
       </c>
       <c r="E207">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F207">
-        <v>82340</v>
+        <v>82090</v>
       </c>
       <c r="G207">
-        <v>118570</v>
+        <v>118210</v>
       </c>
       <c r="H207">
-        <v>17822</v>
+        <v>18610</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144310</v>
+        <v>144401</v>
       </c>
       <c r="E208">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F208">
-        <v>179310</v>
+        <v>179401</v>
       </c>
       <c r="G208">
-        <v>258206</v>
+        <v>258337</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>146166</v>
+        <v>146036</v>
       </c>
       <c r="E209">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>161036</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>231892</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187132</v>
+        <v>187250</v>
       </c>
       <c r="E210">
-        <v>240650</v>
+        <v>241437</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>202250</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>291240</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>159282</v>
+        <v>159271</v>
       </c>
       <c r="E211">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>174271</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>250950</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>287050</v>
+        <v>287231</v>
       </c>
       <c r="E212">
-        <v>370241</v>
+        <v>371451</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>302231</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>435213</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>223894</v>
       </c>
       <c r="E213">
-        <v>370241</v>
+        <v>371451</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>240423</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>346209</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>16529</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34511</v>
+        <v>34787</v>
       </c>
       <c r="E214">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F214">
-        <v>60654</v>
+        <v>60646</v>
       </c>
       <c r="G214">
-        <v>87342</v>
+        <v>87330</v>
       </c>
       <c r="H214">
-        <v>26143</v>
+        <v>25859</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>37541</v>
+        <v>37533</v>
       </c>
       <c r="E215">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F215">
-        <v>52541</v>
+        <v>52533</v>
       </c>
       <c r="G215">
-        <v>75659</v>
+        <v>75648</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>16399</v>
+        <v>16410</v>
       </c>
       <c r="E216">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F216">
-        <v>36719</v>
+        <v>36802</v>
       </c>
       <c r="G216">
-        <v>52875</v>
+        <v>52995</v>
       </c>
       <c r="H216">
-        <v>20320</v>
+        <v>20392</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16399</v>
+        <v>16410</v>
       </c>
       <c r="E218">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F218">
-        <v>36719</v>
+        <v>36802</v>
       </c>
       <c r="G218">
-        <v>52875</v>
+        <v>52995</v>
       </c>
       <c r="H218">
-        <v>20320</v>
+        <v>20392</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10008,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="E219">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13259</v>
+        <v>13585</v>
       </c>
       <c r="E220">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F220">
-        <v>46499</v>
+        <v>46506</v>
       </c>
       <c r="G220">
-        <v>66959</v>
+        <v>66969</v>
       </c>
       <c r="H220">
-        <v>33240</v>
+        <v>32921</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11499</v>
+        <v>11506</v>
       </c>
       <c r="E221">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F221">
-        <v>38499</v>
+        <v>38506</v>
       </c>
       <c r="G221">
-        <v>55439</v>
+        <v>55449</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>25598</v>
+        <v>21758</v>
       </c>
       <c r="E222">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F222">
-        <v>52598</v>
+        <v>48758</v>
       </c>
       <c r="G222">
-        <v>75741</v>
+        <v>70212</v>
       </c>
       <c r="H222">
         <v>27000</v>
@@ -10186,7 +10186,7 @@
         <v>0</v>
       </c>
       <c r="E223">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F223">
         <v>0</v>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16479</v>
+        <v>16521</v>
       </c>
       <c r="E224">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F224">
-        <v>45753</v>
+        <v>45760</v>
       </c>
       <c r="G224">
-        <v>65884</v>
+        <v>65894</v>
       </c>
       <c r="H224">
-        <v>29274</v>
+        <v>29239</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10753</v>
+        <v>10760</v>
       </c>
       <c r="E225">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F225">
-        <v>37753</v>
+        <v>37760</v>
       </c>
       <c r="G225">
-        <v>54364</v>
+        <v>54374</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26454</v>
+        <v>26487</v>
       </c>
       <c r="E226">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F226">
-        <v>61454</v>
+        <v>61487</v>
       </c>
       <c r="G226">
-        <v>88494</v>
+        <v>88541</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,16 +10362,16 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38302</v>
+        <v>38294</v>
       </c>
       <c r="E227">
-        <v>148085</v>
+        <v>148569</v>
       </c>
       <c r="F227">
-        <v>65302</v>
+        <v>65294</v>
       </c>
       <c r="G227">
-        <v>94035</v>
+        <v>94023</v>
       </c>
       <c r="H227">
         <v>27000</v>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35051</v>
+        <v>35136</v>
       </c>
       <c r="E228">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F228">
-        <v>70051</v>
+        <v>70136</v>
       </c>
       <c r="G228">
-        <v>100873</v>
+        <v>100996</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>98173</v>
+        <v>98156</v>
       </c>
       <c r="E229">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F229">
-        <v>117462</v>
+        <v>117691</v>
       </c>
       <c r="G229">
-        <v>169145</v>
+        <v>169475</v>
       </c>
       <c r="H229">
-        <v>19289</v>
+        <v>19535</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16193</v>
+        <v>16124</v>
       </c>
       <c r="E230">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F230">
-        <v>41362</v>
+        <v>42055</v>
       </c>
       <c r="G230">
-        <v>59561</v>
+        <v>60559</v>
       </c>
       <c r="H230">
-        <v>25169</v>
+        <v>25931</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>6138</v>
+        <v>7681</v>
       </c>
       <c r="E231">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F231">
-        <v>31552</v>
+        <v>32245</v>
       </c>
       <c r="G231">
-        <v>45435</v>
+        <v>46433</v>
       </c>
       <c r="H231">
-        <v>25414</v>
+        <v>24564</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10588,7 +10588,7 @@
         <v>0</v>
       </c>
       <c r="E232">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F232">
         <v>0</v>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23394</v>
+        <v>23392</v>
       </c>
       <c r="E233">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>38392</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>55284</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="E234">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -10760,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="E236">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F236">
         <v>0</v>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>85850</v>
+        <v>85841</v>
       </c>
       <c r="E237">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F237">
-        <v>112533</v>
+        <v>112765</v>
       </c>
       <c r="G237">
-        <v>162048</v>
+        <v>162382</v>
       </c>
       <c r="H237">
-        <v>26683</v>
+        <v>26924</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>25598</v>
+        <v>26630</v>
       </c>
       <c r="E238">
-        <v>88844</v>
+        <v>89134</v>
       </c>
       <c r="F238">
-        <v>60598</v>
+        <v>61514</v>
       </c>
       <c r="G238">
-        <v>87261</v>
+        <v>88580</v>
       </c>
       <c r="H238">
-        <v>35000</v>
+        <v>34884</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31815</v>
+        <v>31819</v>
       </c>
       <c r="E239">
-        <v>88844</v>
+        <v>89134</v>
       </c>
       <c r="F239">
-        <v>53375</v>
+        <v>53490</v>
       </c>
       <c r="G239">
-        <v>76860</v>
+        <v>77026</v>
       </c>
       <c r="H239">
-        <v>21560</v>
+        <v>21671</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46946</v>
+        <v>47055</v>
       </c>
       <c r="E240">
-        <v>103654</v>
+        <v>103993</v>
       </c>
       <c r="F240">
-        <v>77741</v>
+        <v>71619</v>
       </c>
       <c r="G240">
-        <v>111947</v>
+        <v>103131</v>
       </c>
       <c r="H240">
-        <v>30795</v>
+        <v>24564</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,10 +10977,10 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>85549</v>
+        <v>0</v>
       </c>
       <c r="E241">
-        <v>103654</v>
+        <v>103993</v>
       </c>
       <c r="F241">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="E242">
-        <v>133275</v>
+        <v>133711</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -11066,16 +11066,16 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>110433</v>
+        <v>110423</v>
       </c>
       <c r="E243">
-        <v>133275</v>
+        <v>133711</v>
       </c>
       <c r="F243">
-        <v>125433</v>
+        <v>125423</v>
       </c>
       <c r="G243">
-        <v>180624</v>
+        <v>180609</v>
       </c>
       <c r="H243">
         <v>15000</v>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64122</v>
+        <v>64210</v>
       </c>
       <c r="E244">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F244">
-        <v>79555</v>
+        <v>79210</v>
       </c>
       <c r="G244">
-        <v>114559</v>
+        <v>114062</v>
       </c>
       <c r="H244">
-        <v>15433</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,10 +11155,10 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54178</v>
+        <v>0</v>
       </c>
       <c r="E245">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75478</v>
+        <v>75525</v>
       </c>
       <c r="E246">
-        <v>98119</v>
+        <v>98440</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>108685</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>156506</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>33160</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,16 +11245,16 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>79522</v>
+        <v>79509</v>
       </c>
       <c r="E247">
-        <v>98119</v>
+        <v>98440</v>
       </c>
       <c r="F247">
-        <v>94522</v>
+        <v>94509</v>
       </c>
       <c r="G247">
-        <v>136112</v>
+        <v>136093</v>
       </c>
       <c r="H247">
         <v>15000</v>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>18382</v>
+        <v>18393</v>
       </c>
       <c r="E248">
-        <v>61074</v>
+        <v>61274</v>
       </c>
       <c r="F248">
-        <v>42215</v>
+        <v>42302</v>
       </c>
       <c r="G248">
-        <v>60790</v>
+        <v>60915</v>
       </c>
       <c r="H248">
-        <v>23833</v>
+        <v>23909</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>10991</v>
+        <v>11014</v>
       </c>
       <c r="E249">
-        <v>61074</v>
+        <v>61274</v>
       </c>
       <c r="F249">
-        <v>34215</v>
+        <v>34302</v>
       </c>
       <c r="G249">
-        <v>49270</v>
+        <v>49395</v>
       </c>
       <c r="H249">
-        <v>23224</v>
+        <v>23288</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,10 +11379,10 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>30895</v>
+        <v>0</v>
       </c>
       <c r="E250">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F250">
         <v>0</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F251">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="E252">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F252">
         <v>0</v>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>15495</v>
+        <v>15489</v>
       </c>
       <c r="E253">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F253">
-        <v>42495</v>
+        <v>42489</v>
       </c>
       <c r="G253">
-        <v>61193</v>
+        <v>61184</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11557,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="E254">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F254">
         <v>0</v>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>22583</v>
       </c>
       <c r="E255">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>49583</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>71400</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9532</v>
+        <v>9506</v>
       </c>
       <c r="E256">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F256">
-        <v>40266</v>
+        <v>35000</v>
       </c>
       <c r="G256">
-        <v>57983</v>
+        <v>50400</v>
       </c>
       <c r="H256">
-        <v>30734</v>
+        <v>25494</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14861</v>
+        <v>0</v>
       </c>
       <c r="E257">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F257">
-        <v>32883</v>
+        <v>0</v>
       </c>
       <c r="G257">
-        <v>47352</v>
+        <v>0</v>
       </c>
       <c r="H257">
-        <v>18022</v>
+        <v>0</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12228</v>
+        <v>12299</v>
       </c>
       <c r="E258">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F258">
-        <v>39228</v>
+        <v>39299</v>
       </c>
       <c r="G258">
-        <v>56488</v>
+        <v>56591</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11775,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="E259">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F259">
         <v>0</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8850</v>
+        <v>8855</v>
       </c>
       <c r="E260">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F260">
-        <v>40266</v>
+        <v>39457</v>
       </c>
       <c r="G260">
-        <v>57983</v>
+        <v>56818</v>
       </c>
       <c r="H260">
-        <v>31416</v>
+        <v>30602</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>16542</v>
+        <v>11125</v>
       </c>
       <c r="E261">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F261">
-        <v>33555</v>
+        <v>31457</v>
       </c>
       <c r="G261">
-        <v>48319</v>
+        <v>45298</v>
       </c>
       <c r="H261">
-        <v>17013</v>
+        <v>20332</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12910</v>
+        <v>12617</v>
       </c>
       <c r="E262">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F262">
-        <v>39131</v>
+        <v>39203</v>
       </c>
       <c r="G262">
-        <v>56349</v>
+        <v>56452</v>
       </c>
       <c r="H262">
-        <v>26221</v>
+        <v>26586</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10483</v>
+        <v>10490</v>
       </c>
       <c r="E263">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F263">
-        <v>31131</v>
+        <v>31203</v>
       </c>
       <c r="G263">
-        <v>44829</v>
+        <v>44932</v>
       </c>
       <c r="H263">
-        <v>20648</v>
+        <v>20713</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18271</v>
+        <v>18092</v>
       </c>
       <c r="E264">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F264">
-        <v>51814</v>
+        <v>51906</v>
       </c>
       <c r="G264">
-        <v>74612</v>
+        <v>74745</v>
       </c>
       <c r="H264">
-        <v>33543</v>
+        <v>33814</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24139</v>
+        <v>24138</v>
       </c>
       <c r="E265">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F265">
-        <v>43814</v>
+        <v>43906</v>
       </c>
       <c r="G265">
-        <v>63092</v>
+        <v>63225</v>
       </c>
       <c r="H265">
-        <v>19675</v>
+        <v>19768</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34321</v>
+        <v>34374</v>
       </c>
       <c r="E266">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F266">
-        <v>54151</v>
+        <v>54328</v>
       </c>
       <c r="G266">
-        <v>77977</v>
+        <v>78232</v>
       </c>
       <c r="H266">
-        <v>19830</v>
+        <v>19954</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>30879</v>
+        <v>30883</v>
       </c>
       <c r="E267">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F267">
-        <v>46510</v>
+        <v>46604</v>
       </c>
       <c r="G267">
-        <v>66974</v>
+        <v>67110</v>
       </c>
       <c r="H267">
-        <v>15631</v>
+        <v>15721</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10182</v>
+        <v>10189</v>
       </c>
       <c r="E268">
-        <v>27770</v>
+        <v>27860</v>
       </c>
       <c r="F268">
-        <v>39542</v>
+        <v>39537</v>
       </c>
       <c r="G268">
-        <v>56940</v>
+        <v>56933</v>
       </c>
       <c r="H268">
-        <v>29360</v>
+        <v>29348</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,19 +12211,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>16542</v>
+        <v>16537</v>
       </c>
       <c r="E269">
-        <v>27770</v>
+        <v>27860</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>31537</v>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>45413</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12054</v>
+        <v>12172</v>
       </c>
       <c r="E270">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F270">
-        <v>39054</v>
+        <v>39172</v>
       </c>
       <c r="G270">
-        <v>56238</v>
+        <v>56408</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12302,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="E271">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F271">
         <v>0</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>60633</v>
+        <v>63210</v>
       </c>
       <c r="E272">
-        <v>98119</v>
+        <v>98440</v>
       </c>
       <c r="F272">
-        <v>75633</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>108912</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>40300</v>
+        <v>40294</v>
       </c>
       <c r="E273">
-        <v>98119</v>
+        <v>98440</v>
       </c>
       <c r="F273">
-        <v>60386</v>
+        <v>60509</v>
       </c>
       <c r="G273">
-        <v>86956</v>
+        <v>87133</v>
       </c>
       <c r="H273">
-        <v>20086</v>
+        <v>20215</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>74510</v>
+        <v>73304</v>
       </c>
       <c r="E274">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F274">
-        <v>106475</v>
+        <v>106459</v>
       </c>
       <c r="G274">
-        <v>153324</v>
+        <v>153301</v>
       </c>
       <c r="H274">
-        <v>31965</v>
+        <v>33155</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>77587</v>
+        <v>77573</v>
       </c>
       <c r="E275">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>92573</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>133305</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11229</v>
+        <v>11204</v>
       </c>
       <c r="E276">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F276">
-        <v>40266</v>
+        <v>40397</v>
       </c>
       <c r="G276">
-        <v>57983</v>
+        <v>58172</v>
       </c>
       <c r="H276">
-        <v>29037</v>
+        <v>29193</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>14353</v>
+        <v>14362</v>
       </c>
       <c r="E277">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F277">
-        <v>32679</v>
+        <v>32751</v>
       </c>
       <c r="G277">
-        <v>47058</v>
+        <v>47161</v>
       </c>
       <c r="H277">
-        <v>18326</v>
+        <v>18389</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,16 +12608,16 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20015</v>
+        <v>20107</v>
       </c>
       <c r="E278">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F278">
-        <v>51814</v>
+        <v>51906</v>
       </c>
       <c r="G278">
-        <v>74612</v>
+        <v>74745</v>
       </c>
       <c r="H278">
         <v>31799</v>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24139</v>
+        <v>24138</v>
       </c>
       <c r="E279">
-        <v>72201</v>
+        <v>72437</v>
       </c>
       <c r="F279">
-        <v>43814</v>
+        <v>43906</v>
       </c>
       <c r="G279">
-        <v>63092</v>
+        <v>63225</v>
       </c>
       <c r="H279">
-        <v>19675</v>
+        <v>19768</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,19 +12697,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11721</v>
+        <v>11760</v>
       </c>
       <c r="E280">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F280">
-        <v>34938</v>
+        <v>35000</v>
       </c>
       <c r="G280">
-        <v>50311</v>
+        <v>50400</v>
       </c>
       <c r="H280">
-        <v>23217</v>
+        <v>23240</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="E281">
-        <v>53688</v>
+        <v>53863</v>
       </c>
       <c r="F281">
         <v>0</v>
@@ -12787,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="E282">
-        <v>44413</v>
+        <v>44558</v>
       </c>
       <c r="F282">
         <v>0</v>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17700</v>
+        <v>17743</v>
       </c>
       <c r="E283">
-        <v>44413</v>
+        <v>44558</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>32743</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>47150</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12873,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="E284">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>49959</v>
+        <v>50070</v>
       </c>
       <c r="E285">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>65070</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>93701</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12959,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="E286">
-        <v>66628</v>
+        <v>66846</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58745</v>
+        <v>58909</v>
       </c>
       <c r="E287">
-        <v>66628</v>
+        <v>66846</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>73909</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>106429</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>35146</v>
+        <v>35152</v>
       </c>
       <c r="E288">
-        <v>61074</v>
+        <v>61274</v>
       </c>
       <c r="F288">
-        <v>55869</v>
+        <v>55934</v>
       </c>
       <c r="G288">
-        <v>80451</v>
+        <v>80545</v>
       </c>
       <c r="H288">
-        <v>20723</v>
+        <v>20782</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23980</v>
+        <v>23948</v>
       </c>
       <c r="E289">
-        <v>61074</v>
+        <v>61274</v>
       </c>
       <c r="F289">
-        <v>39411</v>
+        <v>39476</v>
       </c>
       <c r="G289">
-        <v>56752</v>
+        <v>56845</v>
       </c>
       <c r="H289">
-        <v>15431</v>
+        <v>15528</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13135,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="E290">
-        <v>68480</v>
+        <v>68703</v>
       </c>
       <c r="F290">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="E291">
-        <v>68480</v>
+        <v>68703</v>
       </c>
       <c r="F291">
         <v>0</v>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>46850</v>
+        <v>47245</v>
       </c>
       <c r="E292">
-        <v>61074</v>
+        <v>61274</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>62245</v>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>89633</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23663</v>
+        <v>23710</v>
       </c>
       <c r="E293">
-        <v>61074</v>
+        <v>61274</v>
       </c>
       <c r="F293">
-        <v>39284</v>
+        <v>39381</v>
       </c>
       <c r="G293">
-        <v>56569</v>
+        <v>56709</v>
       </c>
       <c r="H293">
-        <v>15621</v>
+        <v>15671</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>49753</v>
+        <v>49784</v>
       </c>
       <c r="E294">
-        <v>68480</v>
+        <v>68703</v>
       </c>
       <c r="F294">
-        <v>66167</v>
+        <v>66254</v>
       </c>
       <c r="G294">
-        <v>95280</v>
+        <v>95406</v>
       </c>
       <c r="H294">
-        <v>16414</v>
+        <v>16470</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>26026</v>
+        <v>26027</v>
       </c>
       <c r="E295">
-        <v>68480</v>
+        <v>68703</v>
       </c>
       <c r="F295">
-        <v>43118</v>
+        <v>43205</v>
       </c>
       <c r="G295">
-        <v>62090</v>
+        <v>62215</v>
       </c>
       <c r="H295">
-        <v>17092</v>
+        <v>17178</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62473</v>
+        <v>62512</v>
       </c>
       <c r="E296">
-        <v>78662</v>
+        <v>78919</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>77512</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>111617</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13447,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="E297">
-        <v>78662</v>
+        <v>78919</v>
       </c>
       <c r="F297">
         <v>0</v>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74368</v>
+        <v>74414</v>
       </c>
       <c r="E298">
-        <v>94398</v>
+        <v>94706</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>89414</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>128756</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13533,7 +13533,7 @@
         <v>0</v>
       </c>
       <c r="E299">
-        <v>94398</v>
+        <v>94706</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>69229</v>
+        <v>69320</v>
       </c>
       <c r="E300">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F300">
-        <v>88411</v>
+        <v>88532</v>
       </c>
       <c r="G300">
-        <v>127312</v>
+        <v>127486</v>
       </c>
       <c r="H300">
-        <v>19182</v>
+        <v>19212</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33623</v>
+        <v>33629</v>
       </c>
       <c r="E301">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F301">
-        <v>55542</v>
+        <v>55663</v>
       </c>
       <c r="G301">
-        <v>79980</v>
+        <v>80155</v>
       </c>
       <c r="H301">
-        <v>21919</v>
+        <v>22034</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="E302">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F302">
         <v>0</v>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>10753</v>
+        <v>10760</v>
       </c>
       <c r="E303">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F303">
-        <v>37753</v>
+        <v>37760</v>
       </c>
       <c r="G303">
-        <v>54364</v>
+        <v>54374</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>188512</v>
+        <v>174110</v>
       </c>
       <c r="E304">
-        <v>166598</v>
+        <v>167143</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>189110</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>272318</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104549</v>
+        <v>104409</v>
       </c>
       <c r="E305">
-        <v>166598</v>
+        <v>167143</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>119409</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>171949</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>49959</v>
+        <v>50038</v>
       </c>
       <c r="E306">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F306">
-        <v>79939</v>
+        <v>80132</v>
       </c>
       <c r="G306">
-        <v>115112</v>
+        <v>115390</v>
       </c>
       <c r="H306">
-        <v>29980</v>
+        <v>30094</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50371</v>
+        <v>50498</v>
       </c>
       <c r="E307">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F307">
-        <v>69461</v>
+        <v>69654</v>
       </c>
       <c r="G307">
-        <v>100024</v>
+        <v>100302</v>
       </c>
       <c r="H307">
-        <v>19090</v>
+        <v>19156</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,19 +13924,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69134</v>
+        <v>69225</v>
       </c>
       <c r="E308">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F308">
-        <v>97179</v>
+        <v>97497</v>
       </c>
       <c r="G308">
-        <v>139938</v>
+        <v>140396</v>
       </c>
       <c r="H308">
-        <v>28045</v>
+        <v>28272</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77682</v>
+        <v>77668</v>
       </c>
       <c r="E309">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>92668</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>133442</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24567</v>
+        <v>24614</v>
       </c>
       <c r="E310">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F310">
-        <v>41640</v>
+        <v>41777</v>
       </c>
       <c r="G310">
-        <v>59962</v>
+        <v>60159</v>
       </c>
       <c r="H310">
-        <v>17073</v>
+        <v>17163</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>22934</v>
+        <v>22694</v>
       </c>
       <c r="E311">
-        <v>55520</v>
+        <v>55702</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>37694</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>54279</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>65946</v>
+        <v>65876</v>
       </c>
       <c r="E312">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F312">
-        <v>89969</v>
+        <v>80876</v>
       </c>
       <c r="G312">
-        <v>129555</v>
+        <v>116461</v>
       </c>
       <c r="H312">
-        <v>24023</v>
+        <v>15000</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,10 +14146,10 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63234</v>
+        <v>0</v>
       </c>
       <c r="E313">
-        <v>83309</v>
+        <v>83581</v>
       </c>
       <c r="F313">
         <v>0</v>
@@ -14192,7 +14192,7 @@
         <v>0</v>
       </c>
       <c r="E314">
-        <v>38859</v>
+        <v>38986</v>
       </c>
       <c r="F314">
         <v>0</v>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20808</v>
+        <v>22424</v>
       </c>
       <c r="E315">
-        <v>38859</v>
+        <v>38986</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>37424</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>53891</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32339</v>
+        <v>32359</v>
       </c>
       <c r="E316">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F316">
-        <v>49534</v>
+        <v>49535</v>
       </c>
       <c r="G316">
-        <v>71329</v>
+        <v>71330</v>
       </c>
       <c r="H316">
-        <v>17195</v>
+        <v>17176</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26534</v>
+        <v>26535</v>
       </c>
       <c r="E317">
-        <v>59223</v>
+        <v>59417</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>41535</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>59810</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,19 +14366,19 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>15686</v>
+        <v>16172</v>
       </c>
       <c r="E318">
-        <v>44413</v>
+        <v>44558</v>
       </c>
       <c r="F318">
-        <v>33310</v>
+        <v>33419</v>
       </c>
       <c r="G318">
-        <v>47966</v>
+        <v>48123</v>
       </c>
       <c r="H318">
-        <v>17624</v>
+        <v>17247</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29484</v>
+        <v>29550</v>
       </c>
       <c r="E319">
-        <v>44413</v>
+        <v>44558</v>
       </c>
       <c r="F319">
-        <v>0</v>
+        <v>44550</v>
       </c>
       <c r="G319">
-        <v>0</v>
+        <v>64152</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="E320">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F320">
         <v>0</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>47088</v>
+        <v>47070</v>
       </c>
       <c r="E321">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F321">
-        <v>68148</v>
+        <v>68282</v>
       </c>
       <c r="G321">
-        <v>98133</v>
+        <v>98326</v>
       </c>
       <c r="H321">
-        <v>21060</v>
+        <v>21212</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14548,7 +14548,7 @@
         <v>0</v>
       </c>
       <c r="E322">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F322">
         <v>0</v>
@@ -14593,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="E323">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F323">
         <v>0</v>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58698</v>
+        <v>58608</v>
       </c>
       <c r="E324">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F324">
-        <v>90644</v>
+        <v>90635</v>
       </c>
       <c r="G324">
-        <v>130527</v>
+        <v>130514</v>
       </c>
       <c r="H324">
-        <v>31946</v>
+        <v>32027</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>63821</v>
+        <v>63813</v>
       </c>
       <c r="E325">
-        <v>74033</v>
+        <v>74275</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>78813</v>
       </c>
       <c r="G325">
-        <v>0</v>
+        <v>113491</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="E326">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F326">
         <v>0</v>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>9379</v>
       </c>
       <c r="E327">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>35097</v>
       </c>
       <c r="G327">
-        <v>0</v>
+        <v>50540</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>25718</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="E328">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F328">
         <v>0</v>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>17002</v>
+        <v>16997</v>
       </c>
       <c r="E329">
-        <v>64777</v>
+        <v>64989</v>
       </c>
       <c r="F329">
-        <v>38064</v>
+        <v>38145</v>
       </c>
       <c r="G329">
-        <v>54812</v>
+        <v>54929</v>
       </c>
       <c r="H329">
-        <v>21062</v>
+        <v>21148</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20856</v>
+        <v>20901</v>
       </c>
       <c r="E330">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F330">
-        <v>47856</v>
+        <v>47901</v>
       </c>
       <c r="G330">
-        <v>68913</v>
+        <v>68977</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="E331">
-        <v>92546</v>
+        <v>92849</v>
       </c>
       <c r="F331">
         <v>0</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43631</v>
+        <v>43690</v>
       </c>
       <c r="E332">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F332">
-        <v>78631</v>
+        <v>78690</v>
       </c>
       <c r="G332">
-        <v>113229</v>
+        <v>113314</v>
       </c>
       <c r="H332">
         <v>35000</v>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>83233</v>
+        <v>83095</v>
       </c>
       <c r="E333">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F333">
-        <v>0</v>
+        <v>98095</v>
       </c>
       <c r="G333">
-        <v>0</v>
+        <v>141257</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>31720</v>
+        <v>32010</v>
       </c>
       <c r="E334">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F334">
-        <v>66720</v>
+        <v>67010</v>
       </c>
       <c r="G334">
-        <v>96077</v>
+        <v>96494</v>
       </c>
       <c r="H334">
         <v>35000</v>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49293</v>
+        <v>49276</v>
       </c>
       <c r="E335">
-        <v>111059</v>
+        <v>111422</v>
       </c>
       <c r="F335">
-        <v>69030</v>
+        <v>69165</v>
       </c>
       <c r="G335">
-        <v>99403</v>
+        <v>99598</v>
       </c>
       <c r="H335">
-        <v>19737</v>
+        <v>19889</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188797</v>
+        <v>189313</v>
       </c>
       <c r="E336">
-        <v>240650</v>
+        <v>241437</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>204313</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>294211</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>143993</v>
+        <v>143989</v>
       </c>
       <c r="E337">
-        <v>240650</v>
+        <v>241437</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>158989</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>228944</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>59887</v>
+        <v>85396</v>
       </c>
       <c r="E338">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F338">
-        <v>86887</v>
+        <v>0</v>
       </c>
       <c r="G338">
-        <v>125117</v>
+        <v>0</v>
       </c>
       <c r="H338">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,16 +15287,16 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>41791</v>
+        <v>41786</v>
       </c>
       <c r="E339">
-        <v>129572</v>
+        <v>129996</v>
       </c>
       <c r="F339">
-        <v>68791</v>
+        <v>68786</v>
       </c>
       <c r="G339">
-        <v>99059</v>
+        <v>99052</v>
       </c>
       <c r="H339">
         <v>27000</v>
@@ -15333,7 +15333,7 @@
         <v>0</v>
       </c>
       <c r="E340">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F340">
         <v>0</v>
@@ -15372,10 +15372,10 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>109719</v>
+        <v>0</v>
       </c>
       <c r="E341">
-        <v>185111</v>
+        <v>185716</v>
       </c>
       <c r="F341">
         <v>0</v>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>103804</v>
+        <v>103806</v>
       </c>
       <c r="E342">
-        <v>240650</v>
+        <v>241437</v>
       </c>
       <c r="F342">
-        <v>138804</v>
+        <v>130806</v>
       </c>
       <c r="G342">
-        <v>199878</v>
+        <v>188361</v>
       </c>
       <c r="H342">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,10 +15458,10 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>144009</v>
+        <v>0</v>
       </c>
       <c r="E343">
-        <v>240650</v>
+        <v>241437</v>
       </c>
       <c r="F343">
         <v>0</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71970</v>
+        <v>72134</v>
       </c>
       <c r="E2">
         <v>74275</v>
       </c>
       <c r="F2">
-        <v>86970</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>125237</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47848</v>
+        <v>47999</v>
       </c>
       <c r="E3">
         <v>74275</v>
       </c>
       <c r="F3">
-        <v>62848</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90501</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94680</v>
+        <v>95011</v>
       </c>
       <c r="E4">
         <v>85420</v>
       </c>
       <c r="F4">
-        <v>109680</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>157939</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>70669</v>
+        <v>79345</v>
       </c>
       <c r="E5">
         <v>85420</v>
       </c>
       <c r="F5">
-        <v>85669</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>123363</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7173</v>
+        <v>7180</v>
       </c>
       <c r="E7">
         <v>55702</v>
       </c>
       <c r="F7">
-        <v>30593</v>
+        <v>30596</v>
       </c>
       <c r="G7">
-        <v>44054</v>
+        <v>44058</v>
       </c>
       <c r="H7">
-        <v>23420</v>
+        <v>23416</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>38707</v>
+        <v>39386</v>
       </c>
       <c r="E8">
         <v>74275</v>
       </c>
       <c r="F8">
-        <v>55706</v>
+        <v>55178</v>
       </c>
       <c r="G8">
-        <v>80217</v>
+        <v>79456</v>
       </c>
       <c r="H8">
-        <v>16999</v>
+        <v>15792</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>37533</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>74275</v>
       </c>
       <c r="F9">
-        <v>52533</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>75648</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56164</v>
+        <v>56341</v>
       </c>
       <c r="E10">
         <v>111422</v>
       </c>
       <c r="F10">
-        <v>78606</v>
+        <v>78677</v>
       </c>
       <c r="G10">
-        <v>113193</v>
+        <v>113295</v>
       </c>
       <c r="H10">
-        <v>22442</v>
+        <v>22336</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82889</v>
+        <v>83086</v>
       </c>
       <c r="E12">
         <v>83562</v>
       </c>
       <c r="F12">
-        <v>99190</v>
+        <v>99216</v>
       </c>
       <c r="G12">
-        <v>142834</v>
+        <v>142871</v>
       </c>
       <c r="H12">
-        <v>16301</v>
+        <v>16130</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13458</v>
+        <v>13484</v>
       </c>
       <c r="E13">
         <v>83562</v>
       </c>
       <c r="F13">
-        <v>40458</v>
+        <v>40484</v>
       </c>
       <c r="G13">
-        <v>58260</v>
+        <v>58297</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27217</v>
+        <v>27287</v>
       </c>
       <c r="E15">
         <v>74275</v>
       </c>
       <c r="F15">
-        <v>45854</v>
+        <v>45882</v>
       </c>
       <c r="G15">
-        <v>66030</v>
+        <v>66070</v>
       </c>
       <c r="H15">
-        <v>18637</v>
+        <v>18595</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>49229</v>
+        <v>54606</v>
       </c>
       <c r="E21">
         <v>103993</v>
       </c>
       <c r="F21">
-        <v>66249</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>95399</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>17020</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>95807</v>
+        <v>96109</v>
       </c>
       <c r="E23">
         <v>133711</v>
       </c>
       <c r="F23">
-        <v>110807</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>159562</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21361</v>
+        <v>21269</v>
       </c>
       <c r="E27">
         <v>64989</v>
       </c>
       <c r="F27">
-        <v>39890</v>
+        <v>39853</v>
       </c>
       <c r="G27">
-        <v>57442</v>
+        <v>57388</v>
       </c>
       <c r="H27">
-        <v>18529</v>
+        <v>18584</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>80477</v>
+        <v>79584</v>
       </c>
       <c r="E28">
         <v>129996</v>
       </c>
       <c r="F28">
-        <v>96689</v>
+        <v>96523</v>
       </c>
       <c r="G28">
-        <v>139232</v>
+        <v>138993</v>
       </c>
       <c r="H28">
-        <v>16212</v>
+        <v>16939</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38247</v>
+        <v>38081</v>
       </c>
       <c r="E29">
         <v>129996</v>
       </c>
       <c r="F29">
-        <v>65247</v>
+        <v>65081</v>
       </c>
       <c r="G29">
-        <v>93956</v>
+        <v>93717</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>136292</v>
+        <v>136594</v>
       </c>
       <c r="E30">
         <v>185716</v>
       </c>
       <c r="F30">
-        <v>151292</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>217860</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72796</v>
+        <v>71799</v>
       </c>
       <c r="E31">
         <v>185716</v>
       </c>
       <c r="F31">
-        <v>99796</v>
+        <v>98799</v>
       </c>
       <c r="G31">
-        <v>143706</v>
+        <v>142271</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60449</v>
+        <v>60639</v>
       </c>
       <c r="E32">
         <v>111422</v>
       </c>
       <c r="F32">
-        <v>80889</v>
+        <v>80972</v>
       </c>
       <c r="G32">
-        <v>116480</v>
+        <v>116600</v>
       </c>
       <c r="H32">
-        <v>20440</v>
+        <v>20333</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36358</v>
+        <v>36441</v>
       </c>
       <c r="E33">
         <v>111422</v>
       </c>
       <c r="F33">
-        <v>63358</v>
+        <v>63441</v>
       </c>
       <c r="G33">
-        <v>91236</v>
+        <v>91355</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>49260</v>
+        <v>48906</v>
       </c>
       <c r="E36">
         <v>129996</v>
       </c>
       <c r="F36">
-        <v>76260</v>
+        <v>75906</v>
       </c>
       <c r="G36">
-        <v>109814</v>
+        <v>109305</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35406</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>129996</v>
       </c>
       <c r="F37">
-        <v>62406</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89865</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>67701</v>
+        <v>68185</v>
       </c>
       <c r="E38">
         <v>185716</v>
       </c>
       <c r="F38">
-        <v>94701</v>
+        <v>95185</v>
       </c>
       <c r="G38">
-        <v>136369</v>
+        <v>137066</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>98473</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>185716</v>
       </c>
       <c r="F39">
-        <v>117818</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>169658</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>19345</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87825</v>
+        <v>87894</v>
       </c>
       <c r="E40">
         <v>241437</v>
       </c>
       <c r="F40">
-        <v>114825</v>
+        <v>114894</v>
       </c>
       <c r="G40">
-        <v>165348</v>
+        <v>165447</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>33502</v>
+        <v>33607</v>
       </c>
       <c r="E43">
         <v>129996</v>
       </c>
       <c r="F43">
-        <v>60502</v>
+        <v>60607</v>
       </c>
       <c r="G43">
-        <v>87123</v>
+        <v>87274</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,16 +2393,16 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>74367</v>
+        <v>74569</v>
       </c>
       <c r="E45">
         <v>185716</v>
       </c>
       <c r="F45">
-        <v>101367</v>
+        <v>101569</v>
       </c>
       <c r="G45">
-        <v>145968</v>
+        <v>146259</v>
       </c>
       <c r="H45">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>22837</v>
+        <v>22511</v>
       </c>
       <c r="E47">
         <v>111422</v>
       </c>
       <c r="F47">
-        <v>49837</v>
+        <v>49511</v>
       </c>
       <c r="G47">
-        <v>71765</v>
+        <v>71296</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36644</v>
+        <v>36759</v>
       </c>
       <c r="E50">
         <v>64989</v>
       </c>
       <c r="F50">
-        <v>54081</v>
+        <v>54099</v>
       </c>
       <c r="G50">
-        <v>77877</v>
+        <v>77903</v>
       </c>
       <c r="H50">
-        <v>17437</v>
+        <v>17340</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>24122</v>
+        <v>24167</v>
       </c>
       <c r="E51">
         <v>64989</v>
       </c>
       <c r="F51">
-        <v>40995</v>
+        <v>41013</v>
       </c>
       <c r="G51">
-        <v>59033</v>
+        <v>59059</v>
       </c>
       <c r="H51">
-        <v>16873</v>
+        <v>16846</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>51070</v>
+        <v>54112</v>
       </c>
       <c r="E52">
         <v>77990</v>
       </c>
       <c r="F52">
-        <v>66070</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>95141</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,16 +2744,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>67955</v>
+        <v>59000</v>
       </c>
       <c r="E53">
         <v>77990</v>
       </c>
       <c r="F53">
-        <v>82955</v>
+        <v>74000</v>
       </c>
       <c r="G53">
-        <v>119455</v>
+        <v>106560</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44849</v>
+        <v>44990</v>
       </c>
       <c r="E54">
         <v>129996</v>
       </c>
       <c r="F54">
-        <v>79849</v>
+        <v>79990</v>
       </c>
       <c r="G54">
-        <v>114983</v>
+        <v>115186</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44690</v>
+        <v>44847</v>
       </c>
       <c r="E55">
         <v>129996</v>
       </c>
       <c r="F55">
-        <v>71690</v>
+        <v>71847</v>
       </c>
       <c r="G55">
-        <v>103234</v>
+        <v>103460</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>50927</v>
+        <v>51103</v>
       </c>
       <c r="E56">
         <v>148569</v>
       </c>
       <c r="F56">
-        <v>77927</v>
+        <v>78103</v>
       </c>
       <c r="G56">
-        <v>112215</v>
+        <v>112468</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>65956</v>
+        <v>58649</v>
       </c>
       <c r="E57">
         <v>148569</v>
       </c>
       <c r="F57">
-        <v>90324</v>
+        <v>85649</v>
       </c>
       <c r="G57">
-        <v>130067</v>
+        <v>123335</v>
       </c>
       <c r="H57">
-        <v>24368</v>
+        <v>27000</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>16949</v>
+        <v>16859</v>
       </c>
       <c r="E58">
         <v>37128</v>
       </c>
       <c r="F58">
-        <v>38701</v>
+        <v>38709</v>
       </c>
       <c r="G58">
-        <v>55729</v>
+        <v>55741</v>
       </c>
       <c r="H58">
-        <v>21752</v>
+        <v>21850</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6221</v>
+        <v>6241</v>
       </c>
       <c r="E59">
         <v>37128</v>
       </c>
       <c r="F59">
-        <v>22968</v>
+        <v>22976</v>
       </c>
       <c r="G59">
-        <v>33074</v>
+        <v>33085</v>
       </c>
       <c r="H59">
-        <v>16747</v>
+        <v>16735</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24107</v>
+        <v>24198</v>
       </c>
       <c r="E60">
         <v>50130</v>
       </c>
       <c r="F60">
-        <v>48455</v>
+        <v>48536</v>
       </c>
       <c r="G60">
-        <v>69775</v>
+        <v>69892</v>
       </c>
       <c r="H60">
-        <v>24348</v>
+        <v>24338</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25455</v>
+        <v>25536</v>
       </c>
       <c r="E61">
         <v>50130</v>
       </c>
       <c r="F61">
-        <v>40455</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58255</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14235</v>
+        <v>13452</v>
       </c>
       <c r="E63">
         <v>83562</v>
       </c>
       <c r="F63">
-        <v>41235</v>
+        <v>40452</v>
       </c>
       <c r="G63">
-        <v>59378</v>
+        <v>58251</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23218</v>
+        <v>23259</v>
       </c>
       <c r="E65">
         <v>125334</v>
       </c>
       <c r="F65">
-        <v>50218</v>
+        <v>50259</v>
       </c>
       <c r="G65">
-        <v>72314</v>
+        <v>72373</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25820</v>
+        <v>25934</v>
       </c>
       <c r="E66">
         <v>92849</v>
       </c>
       <c r="F66">
-        <v>60820</v>
+        <v>60869</v>
       </c>
       <c r="G66">
-        <v>87581</v>
+        <v>87651</v>
       </c>
       <c r="H66">
-        <v>35000</v>
+        <v>34935</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20774</v>
+        <v>20823</v>
       </c>
       <c r="E67">
         <v>92849</v>
       </c>
       <c r="F67">
-        <v>47774</v>
+        <v>47823</v>
       </c>
       <c r="G67">
-        <v>68795</v>
+        <v>68865</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47991</v>
+        <v>48158</v>
       </c>
       <c r="E68">
         <v>111422</v>
       </c>
       <c r="F68">
-        <v>74991</v>
+        <v>75158</v>
       </c>
       <c r="G68">
-        <v>107987</v>
+        <v>108228</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27598</v>
+        <v>27685</v>
       </c>
       <c r="E69">
         <v>111422</v>
       </c>
       <c r="F69">
-        <v>54598</v>
+        <v>54685</v>
       </c>
       <c r="G69">
-        <v>78621</v>
+        <v>78746</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110471</v>
+        <v>110851</v>
       </c>
       <c r="E70">
         <v>129996</v>
       </c>
       <c r="F70">
-        <v>125471</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>180678</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>52584</v>
       </c>
       <c r="E71">
         <v>129996</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>77732</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>111934</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>25148</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6824</v>
+        <v>6830</v>
       </c>
       <c r="E73">
         <v>27842</v>
       </c>
       <c r="F73">
-        <v>21824</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>31427</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>70319</v>
       </c>
       <c r="E75">
         <v>97492</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85319</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>122859</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>91030</v>
+        <v>89184</v>
       </c>
       <c r="E76">
         <v>129996</v>
       </c>
       <c r="F76">
-        <v>122373</v>
+        <v>123188</v>
       </c>
       <c r="G76">
-        <v>176217</v>
+        <v>177391</v>
       </c>
       <c r="H76">
-        <v>31343</v>
+        <v>34004</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>60147</v>
+        <v>62184</v>
       </c>
       <c r="E77">
         <v>129996</v>
       </c>
       <c r="F77">
-        <v>80757</v>
+        <v>81572</v>
       </c>
       <c r="G77">
-        <v>116290</v>
+        <v>117464</v>
       </c>
       <c r="H77">
-        <v>20610</v>
+        <v>19388</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23265</v>
+        <v>23323</v>
       </c>
       <c r="E81">
         <v>92849</v>
       </c>
       <c r="F81">
-        <v>50265</v>
+        <v>50323</v>
       </c>
       <c r="G81">
-        <v>72382</v>
+        <v>72465</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87142</v>
+        <v>87337</v>
       </c>
       <c r="E83">
         <v>129996</v>
       </c>
       <c r="F83">
-        <v>102142</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>147084</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>49499</v>
+        <v>48763</v>
       </c>
       <c r="E84">
         <v>74275</v>
       </c>
       <c r="F84">
-        <v>68968</v>
+        <v>63763</v>
       </c>
       <c r="G84">
-        <v>99314</v>
+        <v>91819</v>
       </c>
       <c r="H84">
-        <v>19469</v>
+        <v>15000</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>34136</v>
+        <v>34180</v>
       </c>
       <c r="E85">
         <v>74275</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>49180</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>70819</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8189</v>
+        <v>8231</v>
       </c>
       <c r="E90">
         <v>59417</v>
       </c>
       <c r="F90">
-        <v>38652</v>
+        <v>38656</v>
       </c>
       <c r="G90">
-        <v>55659</v>
+        <v>55665</v>
       </c>
       <c r="H90">
-        <v>30463</v>
+        <v>30425</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3698</v>
+        <v>3709</v>
       </c>
       <c r="E91">
         <v>59417</v>
       </c>
       <c r="F91">
-        <v>30652</v>
+        <v>30656</v>
       </c>
       <c r="G91">
-        <v>44139</v>
+        <v>44145</v>
       </c>
       <c r="H91">
-        <v>26954</v>
+        <v>26947</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9506</v>
+        <v>9520</v>
       </c>
       <c r="E93">
         <v>27842</v>
       </c>
       <c r="F93">
-        <v>24506</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35289</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63670</v>
+        <v>63887</v>
       </c>
       <c r="E96">
         <v>83562</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>78887</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>113597</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34549</v>
+        <v>34626</v>
       </c>
       <c r="E97">
         <v>83562</v>
       </c>
       <c r="F97">
-        <v>52409</v>
+        <v>52439</v>
       </c>
       <c r="G97">
-        <v>75469</v>
+        <v>75512</v>
       </c>
       <c r="H97">
-        <v>17860</v>
+        <v>17813</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79255</v>
+        <v>79441</v>
       </c>
       <c r="E98">
         <v>96564</v>
       </c>
       <c r="F98">
-        <v>94255</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>135727</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>42151</v>
+        <v>42284</v>
       </c>
       <c r="E99">
         <v>96564</v>
       </c>
       <c r="F99">
-        <v>60521</v>
+        <v>60574</v>
       </c>
       <c r="G99">
-        <v>87150</v>
+        <v>87227</v>
       </c>
       <c r="H99">
-        <v>18370</v>
+        <v>18290</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60623</v>
+        <v>60767</v>
       </c>
       <c r="E100">
         <v>108265</v>
       </c>
       <c r="F100">
-        <v>78969</v>
+        <v>79026</v>
       </c>
       <c r="G100">
-        <v>113715</v>
+        <v>113797</v>
       </c>
       <c r="H100">
-        <v>18346</v>
+        <v>18259</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>71640</v>
       </c>
       <c r="E105">
         <v>129996</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>86640</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>124762</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>74764</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>185716</v>
       </c>
       <c r="F107">
-        <v>101764</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>146540</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4872</v>
+        <v>6018</v>
       </c>
       <c r="E109">
         <v>129996</v>
       </c>
       <c r="F109">
-        <v>31872</v>
+        <v>33018</v>
       </c>
       <c r="G109">
-        <v>45896</v>
+        <v>47546</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15077</v>
+        <v>15108</v>
       </c>
       <c r="E111">
         <v>167143</v>
       </c>
       <c r="F111">
-        <v>42077</v>
+        <v>42108</v>
       </c>
       <c r="G111">
-        <v>60591</v>
+        <v>60636</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51165</v>
+        <v>51278</v>
       </c>
       <c r="E113">
         <v>129996</v>
       </c>
       <c r="F113">
-        <v>77164</v>
+        <v>77209</v>
       </c>
       <c r="G113">
-        <v>111116</v>
+        <v>111181</v>
       </c>
       <c r="H113">
-        <v>25999</v>
+        <v>25931</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>96823</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>185716</v>
       </c>
       <c r="F115">
-        <v>117158</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>168708</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>20335</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>83349</v>
+        <v>83644</v>
       </c>
       <c r="E118">
         <v>89134</v>
       </c>
       <c r="F118">
-        <v>98349</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>141623</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,16 +5629,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50102</v>
+        <v>46646</v>
       </c>
       <c r="E119">
         <v>89134</v>
       </c>
       <c r="F119">
-        <v>65102</v>
+        <v>61646</v>
       </c>
       <c r="G119">
-        <v>93747</v>
+        <v>88770</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>85603</v>
+        <v>102382</v>
       </c>
       <c r="E121">
         <v>118852</v>
       </c>
       <c r="F121">
-        <v>100603</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>144868</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>114290</v>
       </c>
       <c r="E123">
         <v>148569</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>129290</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>186178</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46134</v>
+        <v>46295</v>
       </c>
       <c r="E124">
         <v>59417</v>
       </c>
       <c r="F124">
-        <v>61134</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>88033</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,16 +5891,16 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35565</v>
+        <v>35518</v>
       </c>
       <c r="E125">
         <v>59417</v>
       </c>
       <c r="F125">
-        <v>50565</v>
+        <v>50518</v>
       </c>
       <c r="G125">
-        <v>72814</v>
+        <v>72746</v>
       </c>
       <c r="H125">
         <v>15000</v>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63670</v>
+        <v>63887</v>
       </c>
       <c r="E126">
         <v>81705</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>78887</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>113597</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>38877</v>
       </c>
       <c r="E128">
         <v>92849</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>65585</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>94442</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>26708</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36977</v>
+        <v>37046</v>
       </c>
       <c r="E129">
         <v>92849</v>
       </c>
       <c r="F129">
-        <v>57002</v>
+        <v>57030</v>
       </c>
       <c r="G129">
-        <v>82083</v>
+        <v>82123</v>
       </c>
       <c r="H129">
-        <v>20025</v>
+        <v>19984</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,7 +6110,7 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12712</v>
+        <v>12768</v>
       </c>
       <c r="E130">
         <v>44558</v>
@@ -6122,7 +6122,7 @@
         <v>48123</v>
       </c>
       <c r="H130">
-        <v>20707</v>
+        <v>20651</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5824</v>
+        <v>5843</v>
       </c>
       <c r="E131">
         <v>44558</v>
       </c>
       <c r="F131">
-        <v>25707</v>
+        <v>25715</v>
       </c>
       <c r="G131">
-        <v>37018</v>
+        <v>37030</v>
       </c>
       <c r="H131">
-        <v>19883</v>
+        <v>19872</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27677</v>
+        <v>27764</v>
       </c>
       <c r="E132">
         <v>59417</v>
       </c>
       <c r="F132">
-        <v>43809</v>
+        <v>43843</v>
       </c>
       <c r="G132">
-        <v>63085</v>
+        <v>63134</v>
       </c>
       <c r="H132">
-        <v>16132</v>
+        <v>16079</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17330</v>
+        <v>17369</v>
       </c>
       <c r="E135">
         <v>60884</v>
       </c>
       <c r="F135">
-        <v>36677</v>
+        <v>36693</v>
       </c>
       <c r="G135">
-        <v>52815</v>
+        <v>52838</v>
       </c>
       <c r="H135">
-        <v>19347</v>
+        <v>19324</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>29233</v>
+        <v>28592</v>
       </c>
       <c r="E137">
         <v>75854</v>
       </c>
       <c r="F137">
-        <v>47276</v>
+        <v>47020</v>
       </c>
       <c r="G137">
-        <v>68077</v>
+        <v>67709</v>
       </c>
       <c r="H137">
-        <v>18043</v>
+        <v>18428</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>28677</v>
+        <v>28608</v>
       </c>
       <c r="E139">
         <v>95486</v>
       </c>
       <c r="F139">
-        <v>54710</v>
+        <v>54683</v>
       </c>
       <c r="G139">
-        <v>78782</v>
+        <v>78744</v>
       </c>
       <c r="H139">
-        <v>26033</v>
+        <v>26075</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58211</v>
+        <v>58347</v>
       </c>
       <c r="E141">
         <v>90992</v>
       </c>
       <c r="F141">
-        <v>73211</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>105424</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,16 +6677,16 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77668</v>
+        <v>76384</v>
       </c>
       <c r="E143">
         <v>129996</v>
       </c>
       <c r="F143">
-        <v>92668</v>
+        <v>91384</v>
       </c>
       <c r="G143">
-        <v>133442</v>
+        <v>131593</v>
       </c>
       <c r="H143">
         <v>15000</v>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87237</v>
+        <v>87433</v>
       </c>
       <c r="E145">
         <v>155999</v>
       </c>
       <c r="F145">
-        <v>102237</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>147221</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86047</v>
+        <v>86318</v>
       </c>
       <c r="E147">
         <v>90992</v>
       </c>
       <c r="F147">
-        <v>101047</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>145508</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122088</v>
+        <v>122473</v>
       </c>
       <c r="E149">
         <v>129996</v>
       </c>
       <c r="F149">
-        <v>137088</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>197407</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38326</v>
+        <v>38415</v>
       </c>
       <c r="E150">
         <v>92849</v>
       </c>
       <c r="F150">
-        <v>63113</v>
+        <v>63148</v>
       </c>
       <c r="G150">
-        <v>90883</v>
+        <v>90933</v>
       </c>
       <c r="H150">
-        <v>24787</v>
+        <v>24733</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,19 +7067,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>22694</v>
+        <v>24772</v>
       </c>
       <c r="E152">
         <v>92849</v>
       </c>
       <c r="F152">
-        <v>53171</v>
+        <v>59772</v>
       </c>
       <c r="G152">
-        <v>76566</v>
+        <v>86072</v>
       </c>
       <c r="H152">
-        <v>30477</v>
+        <v>35000</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>18171</v>
+        <v>29754</v>
       </c>
       <c r="E153">
         <v>92849</v>
       </c>
       <c r="F153">
-        <v>45171</v>
+        <v>54113</v>
       </c>
       <c r="G153">
-        <v>65046</v>
+        <v>77923</v>
       </c>
       <c r="H153">
-        <v>27000</v>
+        <v>24359</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48753</v>
+        <v>48874</v>
       </c>
       <c r="E154">
         <v>92849</v>
@@ -7167,7 +7167,7 @@
         <v>100277</v>
       </c>
       <c r="H154">
-        <v>20884</v>
+        <v>20763</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>76128</v>
+        <v>75907</v>
       </c>
       <c r="E155">
         <v>92849</v>
       </c>
       <c r="F155">
-        <v>91128</v>
+        <v>90907</v>
       </c>
       <c r="G155">
-        <v>131224</v>
+        <v>130906</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65527</v>
+        <v>65670</v>
       </c>
       <c r="E156">
         <v>92849</v>
       </c>
       <c r="F156">
-        <v>80527</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>115959</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38866</v>
+        <v>38988</v>
       </c>
       <c r="E158">
         <v>63131</v>
       </c>
       <c r="F158">
-        <v>65668</v>
+        <v>65766</v>
       </c>
       <c r="G158">
-        <v>94562</v>
+        <v>94703</v>
       </c>
       <c r="H158">
-        <v>26802</v>
+        <v>26778</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42103</v>
+        <v>42188</v>
       </c>
       <c r="E159">
         <v>63131</v>
       </c>
       <c r="F159">
-        <v>57103</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>82228</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>17901</v>
+        <v>17958</v>
       </c>
       <c r="E161">
         <v>55702</v>
       </c>
       <c r="F161">
-        <v>34884</v>
+        <v>34907</v>
       </c>
       <c r="G161">
-        <v>50233</v>
+        <v>50266</v>
       </c>
       <c r="H161">
-        <v>16983</v>
+        <v>16949</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56164</v>
+        <v>56293</v>
       </c>
       <c r="E163">
         <v>74275</v>
       </c>
       <c r="F163">
-        <v>71164</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>102476</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70495</v>
+        <v>70717</v>
       </c>
       <c r="E165">
         <v>111422</v>
       </c>
       <c r="F165">
-        <v>85495</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>123113</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>53942</v>
+        <v>54112</v>
       </c>
       <c r="E166">
         <v>74275</v>
       </c>
       <c r="F166">
-        <v>68942</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>99276</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34025</v>
+        <v>34101</v>
       </c>
       <c r="E167">
         <v>74275</v>
       </c>
       <c r="F167">
-        <v>49025</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70596</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>33454</v>
+        <v>60607</v>
       </c>
       <c r="E168">
         <v>74275</v>
       </c>
       <c r="F168">
-        <v>55706</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>80217</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>22252</v>
+        <v>0</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>73938</v>
+        <v>74171</v>
       </c>
       <c r="E169">
         <v>74275</v>
       </c>
       <c r="F169">
-        <v>88938</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>128071</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,16 +7902,16 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>16203</v>
+        <v>15538</v>
       </c>
       <c r="E171">
         <v>27842</v>
       </c>
       <c r="F171">
-        <v>31203</v>
+        <v>30538</v>
       </c>
       <c r="G171">
-        <v>44932</v>
+        <v>43975</v>
       </c>
       <c r="H171">
         <v>15000</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>29915</v>
+        <v>31394</v>
       </c>
       <c r="E173">
         <v>85420</v>
       </c>
       <c r="F173">
-        <v>51280</v>
+        <v>51871</v>
       </c>
       <c r="G173">
-        <v>73843</v>
+        <v>74694</v>
       </c>
       <c r="H173">
-        <v>21365</v>
+        <v>20477</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7253</v>
+        <v>7769</v>
       </c>
       <c r="E174">
         <v>55721</v>
       </c>
       <c r="F174">
-        <v>37839</v>
+        <v>37858</v>
       </c>
       <c r="G174">
-        <v>54488</v>
+        <v>54516</v>
       </c>
       <c r="H174">
-        <v>30586</v>
+        <v>30089</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5269</v>
+        <v>5317</v>
       </c>
       <c r="E175">
         <v>55721</v>
       </c>
       <c r="F175">
-        <v>29839</v>
+        <v>29858</v>
       </c>
       <c r="G175">
-        <v>42968</v>
+        <v>42996</v>
       </c>
       <c r="H175">
-        <v>24570</v>
+        <v>24541</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10316</v>
+        <v>10348</v>
       </c>
       <c r="E176">
         <v>74275</v>
       </c>
       <c r="F176">
-        <v>42411</v>
+        <v>42435</v>
       </c>
       <c r="G176">
-        <v>61072</v>
+        <v>61106</v>
       </c>
       <c r="H176">
-        <v>32095</v>
+        <v>32087</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7411</v>
+        <v>7435</v>
       </c>
       <c r="E177">
         <v>74275</v>
       </c>
       <c r="F177">
-        <v>34411</v>
+        <v>34435</v>
       </c>
       <c r="G177">
-        <v>49552</v>
+        <v>49586</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,19 +8212,19 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>48927</v>
+        <v>49097</v>
       </c>
       <c r="E178">
         <v>69651</v>
       </c>
       <c r="F178">
-        <v>63927</v>
+        <v>0</v>
       </c>
       <c r="G178">
-        <v>92055</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I178" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21901</v>
+        <v>21954</v>
       </c>
       <c r="E179">
         <v>69651</v>
       </c>
       <c r="F179">
-        <v>41924</v>
+        <v>41945</v>
       </c>
       <c r="G179">
-        <v>60371</v>
+        <v>60401</v>
       </c>
       <c r="H179">
-        <v>20023</v>
+        <v>19991</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46039</v>
+        <v>46057</v>
       </c>
       <c r="E181">
         <v>104940</v>
       </c>
       <c r="F181">
-        <v>65342</v>
+        <v>65349</v>
       </c>
       <c r="G181">
-        <v>94092</v>
+        <v>94103</v>
       </c>
       <c r="H181">
-        <v>19303</v>
+        <v>19292</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67892</v>
+        <v>68138</v>
       </c>
       <c r="E182">
         <v>74275</v>
       </c>
       <c r="F182">
-        <v>86784</v>
+        <v>86578</v>
       </c>
       <c r="G182">
-        <v>124969</v>
+        <v>124672</v>
       </c>
       <c r="H182">
-        <v>18892</v>
+        <v>18440</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10395</v>
+        <v>10189</v>
       </c>
       <c r="E183">
         <v>74275</v>
       </c>
       <c r="F183">
-        <v>37395</v>
+        <v>37189</v>
       </c>
       <c r="G183">
-        <v>53849</v>
+        <v>53552</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60449</v>
+        <v>60639</v>
       </c>
       <c r="E184">
         <v>111422</v>
       </c>
       <c r="F184">
-        <v>80320</v>
+        <v>80396</v>
       </c>
       <c r="G184">
-        <v>115661</v>
+        <v>115770</v>
       </c>
       <c r="H184">
-        <v>19871</v>
+        <v>19757</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45595</v>
+        <v>45738</v>
       </c>
       <c r="E185">
         <v>111422</v>
       </c>
       <c r="F185">
-        <v>67692</v>
+        <v>67750</v>
       </c>
       <c r="G185">
-        <v>97476</v>
+        <v>97560</v>
       </c>
       <c r="H185">
-        <v>22097</v>
+        <v>22012</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79810</v>
+        <v>80062</v>
       </c>
       <c r="E186">
         <v>148569</v>
       </c>
       <c r="F186">
-        <v>110859</v>
+        <v>110977</v>
       </c>
       <c r="G186">
-        <v>159637</v>
+        <v>159807</v>
       </c>
       <c r="H186">
-        <v>31049</v>
+        <v>30915</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81143</v>
+        <v>81399</v>
       </c>
       <c r="E187">
         <v>148569</v>
       </c>
       <c r="F187">
-        <v>96399</v>
+        <v>96502</v>
       </c>
       <c r="G187">
-        <v>138815</v>
+        <v>138963</v>
       </c>
       <c r="H187">
-        <v>15256</v>
+        <v>15103</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>146845</v>
+        <v>147308</v>
       </c>
       <c r="E190">
         <v>157856</v>
       </c>
       <c r="F190">
-        <v>161845</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>233057</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>172047</v>
+        <v>172589</v>
       </c>
       <c r="E192">
         <v>185716</v>
       </c>
       <c r="F192">
-        <v>187047</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>269348</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>6903</v>
+        <v>7371</v>
       </c>
       <c r="E194">
         <v>53863</v>
@@ -8920,7 +8920,7 @@
         <v>50400</v>
       </c>
       <c r="H194">
-        <v>28097</v>
+        <v>27629</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11760</v>
+        <v>11797</v>
       </c>
       <c r="E196">
         <v>83581</v>
       </c>
       <c r="F196">
-        <v>38760</v>
+        <v>38797</v>
       </c>
       <c r="G196">
-        <v>55814</v>
+        <v>55868</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51673</v>
+        <v>51851</v>
       </c>
       <c r="E198">
         <v>92849</v>
@@ -9095,7 +9095,7 @@
         <v>100277</v>
       </c>
       <c r="H198">
-        <v>17964</v>
+        <v>17786</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75081</v>
+        <v>75254</v>
       </c>
       <c r="E199">
         <v>92849</v>
       </c>
       <c r="F199">
-        <v>90081</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129717</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>57576</v>
+        <v>91731</v>
       </c>
       <c r="E200">
         <v>92849</v>
       </c>
       <c r="F200">
-        <v>72576</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>104509</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,19 +9259,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>17512</v>
       </c>
       <c r="E202">
         <v>111422</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>44512</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>64097</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27487</v>
+        <v>27589</v>
       </c>
       <c r="E204">
         <v>92849</v>
       </c>
       <c r="F204">
-        <v>54487</v>
+        <v>54589</v>
       </c>
       <c r="G204">
-        <v>78461</v>
+        <v>78608</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101552</v>
+        <v>101872</v>
       </c>
       <c r="E206">
         <v>129996</v>
       </c>
       <c r="F206">
-        <v>116552</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>167835</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63480</v>
+        <v>63951</v>
       </c>
       <c r="E207">
         <v>129996</v>
       </c>
       <c r="F207">
-        <v>82090</v>
+        <v>82279</v>
       </c>
       <c r="G207">
-        <v>118210</v>
+        <v>118482</v>
       </c>
       <c r="H207">
-        <v>18610</v>
+        <v>18328</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144401</v>
+        <v>144856</v>
       </c>
       <c r="E208">
         <v>185716</v>
       </c>
       <c r="F208">
-        <v>179401</v>
+        <v>179856</v>
       </c>
       <c r="G208">
-        <v>258337</v>
+        <v>258993</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>146036</v>
+        <v>146368</v>
       </c>
       <c r="E209">
         <v>185716</v>
       </c>
       <c r="F209">
-        <v>161036</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>231892</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187250</v>
+        <v>187840</v>
       </c>
       <c r="E210">
         <v>241437</v>
       </c>
       <c r="F210">
-        <v>202250</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>291240</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>159271</v>
+        <v>187617</v>
       </c>
       <c r="E211">
         <v>185716</v>
       </c>
       <c r="F211">
-        <v>174271</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>250950</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>287231</v>
+        <v>288136</v>
       </c>
       <c r="E212">
         <v>371451</v>
       </c>
       <c r="F212">
-        <v>302231</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>435213</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>223894</v>
+        <v>224599</v>
       </c>
       <c r="E213">
         <v>371451</v>
       </c>
       <c r="F213">
-        <v>240423</v>
+        <v>240705</v>
       </c>
       <c r="G213">
-        <v>346209</v>
+        <v>346615</v>
       </c>
       <c r="H213">
-        <v>16529</v>
+        <v>16106</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34787</v>
+        <v>34722</v>
       </c>
       <c r="E214">
         <v>53863</v>
       </c>
       <c r="F214">
-        <v>60646</v>
+        <v>62837</v>
       </c>
       <c r="G214">
-        <v>87330</v>
+        <v>90485</v>
       </c>
       <c r="H214">
-        <v>25859</v>
+        <v>28115</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>37533</v>
+        <v>39641</v>
       </c>
       <c r="E215">
         <v>53863</v>
       </c>
       <c r="F215">
-        <v>52533</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>75648</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>16410</v>
+        <v>46295</v>
       </c>
       <c r="E216">
         <v>53863</v>
       </c>
       <c r="F216">
-        <v>36802</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>52995</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>20392</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16410</v>
+        <v>16461</v>
       </c>
       <c r="E218">
         <v>53863</v>
       </c>
       <c r="F218">
-        <v>36802</v>
+        <v>36823</v>
       </c>
       <c r="G218">
-        <v>52995</v>
+        <v>53025</v>
       </c>
       <c r="H218">
-        <v>20392</v>
+        <v>20362</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13585</v>
+        <v>12943</v>
       </c>
       <c r="E220">
         <v>74275</v>
       </c>
       <c r="F220">
-        <v>46506</v>
+        <v>46526</v>
       </c>
       <c r="G220">
-        <v>66969</v>
+        <v>66997</v>
       </c>
       <c r="H220">
-        <v>32921</v>
+        <v>33583</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11506</v>
+        <v>11526</v>
       </c>
       <c r="E221">
         <v>74275</v>
       </c>
       <c r="F221">
-        <v>38506</v>
+        <v>38526</v>
       </c>
       <c r="G221">
-        <v>55449</v>
+        <v>55477</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21758</v>
+        <v>21476</v>
       </c>
       <c r="E222">
         <v>111422</v>
       </c>
       <c r="F222">
-        <v>48758</v>
+        <v>56476</v>
       </c>
       <c r="G222">
-        <v>70212</v>
+        <v>81325</v>
       </c>
       <c r="H222">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>53634</v>
       </c>
       <c r="E223">
         <v>111422</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>70908</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>102108</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>17274</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16521</v>
+        <v>16557</v>
       </c>
       <c r="E224">
         <v>129996</v>
       </c>
       <c r="F224">
-        <v>45760</v>
+        <v>45794</v>
       </c>
       <c r="G224">
-        <v>65894</v>
+        <v>65943</v>
       </c>
       <c r="H224">
-        <v>29239</v>
+        <v>29237</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10760</v>
+        <v>10794</v>
       </c>
       <c r="E225">
         <v>129996</v>
       </c>
       <c r="F225">
-        <v>37760</v>
+        <v>37794</v>
       </c>
       <c r="G225">
-        <v>54374</v>
+        <v>54423</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26487</v>
+        <v>26586</v>
       </c>
       <c r="E226">
         <v>148569</v>
       </c>
       <c r="F226">
-        <v>61487</v>
+        <v>61586</v>
       </c>
       <c r="G226">
-        <v>88541</v>
+        <v>88684</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38294</v>
+        <v>96220</v>
       </c>
       <c r="E227">
         <v>148569</v>
       </c>
       <c r="F227">
-        <v>65294</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>94023</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35136</v>
+        <v>35215</v>
       </c>
       <c r="E228">
         <v>185716</v>
       </c>
       <c r="F228">
-        <v>70136</v>
+        <v>70215</v>
       </c>
       <c r="G228">
-        <v>100996</v>
+        <v>101110</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>98156</v>
+        <v>98465</v>
       </c>
       <c r="E229">
         <v>185716</v>
       </c>
       <c r="F229">
-        <v>117691</v>
+        <v>117815</v>
       </c>
       <c r="G229">
-        <v>169475</v>
+        <v>169654</v>
       </c>
       <c r="H229">
-        <v>19535</v>
+        <v>19350</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16124</v>
+        <v>16095</v>
       </c>
       <c r="E230">
         <v>59417</v>
       </c>
       <c r="F230">
-        <v>42055</v>
+        <v>42861</v>
       </c>
       <c r="G230">
-        <v>60559</v>
+        <v>61720</v>
       </c>
       <c r="H230">
-        <v>25931</v>
+        <v>26766</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>7681</v>
+        <v>9695</v>
       </c>
       <c r="E231">
         <v>59417</v>
       </c>
       <c r="F231">
-        <v>32245</v>
+        <v>33051</v>
       </c>
       <c r="G231">
-        <v>46433</v>
+        <v>47593</v>
       </c>
       <c r="H231">
-        <v>24564</v>
+        <v>23356</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23392</v>
+        <v>23466</v>
       </c>
       <c r="E233">
         <v>55702</v>
       </c>
       <c r="F233">
-        <v>38392</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>55284</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>41726</v>
       </c>
       <c r="E235">
         <v>111422</v>
       </c>
       <c r="F235">
-        <v>0</v>
+        <v>66145</v>
       </c>
       <c r="G235">
-        <v>0</v>
+        <v>95249</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>24419</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>85841</v>
+        <v>86111</v>
       </c>
       <c r="E237">
         <v>185716</v>
       </c>
       <c r="F237">
-        <v>112765</v>
+        <v>112873</v>
       </c>
       <c r="G237">
-        <v>162382</v>
+        <v>162537</v>
       </c>
       <c r="H237">
-        <v>26924</v>
+        <v>26762</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26630</v>
+        <v>26698</v>
       </c>
       <c r="E238">
         <v>89134</v>
       </c>
       <c r="F238">
-        <v>61514</v>
+        <v>61560</v>
       </c>
       <c r="G238">
-        <v>88580</v>
+        <v>88646</v>
       </c>
       <c r="H238">
-        <v>34884</v>
+        <v>34862</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31819</v>
+        <v>31920</v>
       </c>
       <c r="E239">
         <v>89134</v>
       </c>
       <c r="F239">
-        <v>53490</v>
+        <v>53530</v>
       </c>
       <c r="G239">
-        <v>77026</v>
+        <v>77083</v>
       </c>
       <c r="H239">
-        <v>21671</v>
+        <v>21610</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47055</v>
+        <v>47171</v>
       </c>
       <c r="E240">
         <v>103993</v>
       </c>
       <c r="F240">
-        <v>71619</v>
+        <v>71665</v>
       </c>
       <c r="G240">
-        <v>103131</v>
+        <v>103198</v>
       </c>
       <c r="H240">
-        <v>24564</v>
+        <v>24494</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>110423</v>
+        <v>110771</v>
       </c>
       <c r="E243">
         <v>133711</v>
       </c>
       <c r="F243">
-        <v>125423</v>
+        <v>0</v>
       </c>
       <c r="G243">
-        <v>180609</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64210</v>
+        <v>64428</v>
       </c>
       <c r="E244">
         <v>83581</v>
       </c>
       <c r="F244">
-        <v>79210</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>114062</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>54335</v>
       </c>
       <c r="E245">
         <v>83581</v>
       </c>
       <c r="F245">
-        <v>0</v>
+        <v>69335</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>99842</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75525</v>
+        <v>75763</v>
       </c>
       <c r="E246">
         <v>98440</v>
       </c>
       <c r="F246">
-        <v>108685</v>
+        <v>90763</v>
       </c>
       <c r="G246">
-        <v>156506</v>
+        <v>130699</v>
       </c>
       <c r="H246">
-        <v>33160</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>79509</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>98440</v>
       </c>
       <c r="F247">
-        <v>94509</v>
+        <v>0</v>
       </c>
       <c r="G247">
-        <v>136093</v>
+        <v>0</v>
       </c>
       <c r="H247">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>18393</v>
+        <v>18451</v>
       </c>
       <c r="E248">
         <v>61274</v>
       </c>
       <c r="F248">
-        <v>42302</v>
+        <v>42316</v>
       </c>
       <c r="G248">
-        <v>60915</v>
+        <v>60935</v>
       </c>
       <c r="H248">
-        <v>23909</v>
+        <v>23865</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11014</v>
+        <v>11048</v>
       </c>
       <c r="E249">
         <v>61274</v>
       </c>
       <c r="F249">
-        <v>34302</v>
+        <v>34316</v>
       </c>
       <c r="G249">
-        <v>49395</v>
+        <v>49415</v>
       </c>
       <c r="H249">
-        <v>23288</v>
+        <v>23268</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>15489</v>
+        <v>16636</v>
       </c>
       <c r="E253">
         <v>111422</v>
       </c>
       <c r="F253">
-        <v>42489</v>
+        <v>43636</v>
       </c>
       <c r="G253">
-        <v>61184</v>
+        <v>62836</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11596,16 +11596,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>22583</v>
+        <v>23068</v>
       </c>
       <c r="E255">
         <v>185716</v>
       </c>
       <c r="F255">
-        <v>49583</v>
+        <v>50068</v>
       </c>
       <c r="G255">
-        <v>71400</v>
+        <v>72098</v>
       </c>
       <c r="H255">
         <v>27000</v>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9506</v>
+        <v>9520</v>
       </c>
       <c r="E256">
         <v>53863</v>
       </c>
       <c r="F256">
-        <v>35000</v>
+        <v>40397</v>
       </c>
       <c r="G256">
-        <v>50400</v>
+        <v>58172</v>
       </c>
       <c r="H256">
-        <v>25494</v>
+        <v>30877</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>14901</v>
       </c>
       <c r="E257">
         <v>53863</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>32967</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>47472</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>18066</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12299</v>
+        <v>12338</v>
       </c>
       <c r="E258">
         <v>72437</v>
       </c>
       <c r="F258">
-        <v>39299</v>
+        <v>39338</v>
       </c>
       <c r="G258">
-        <v>56591</v>
+        <v>56647</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8855</v>
+        <v>8899</v>
       </c>
       <c r="E260">
         <v>53863</v>
       </c>
       <c r="F260">
-        <v>39457</v>
+        <v>39451</v>
       </c>
       <c r="G260">
-        <v>56818</v>
+        <v>56809</v>
       </c>
       <c r="H260">
-        <v>30602</v>
+        <v>30552</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11125</v>
+        <v>11112</v>
       </c>
       <c r="E261">
         <v>53863</v>
       </c>
       <c r="F261">
-        <v>31457</v>
+        <v>31451</v>
       </c>
       <c r="G261">
-        <v>45298</v>
+        <v>45289</v>
       </c>
       <c r="H261">
-        <v>20332</v>
+        <v>20339</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12617</v>
+        <v>12449</v>
       </c>
       <c r="E262">
         <v>53863</v>
       </c>
       <c r="F262">
-        <v>39203</v>
+        <v>39216</v>
       </c>
       <c r="G262">
-        <v>56452</v>
+        <v>56471</v>
       </c>
       <c r="H262">
-        <v>26586</v>
+        <v>26767</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10490</v>
+        <v>10523</v>
       </c>
       <c r="E263">
         <v>53863</v>
       </c>
       <c r="F263">
-        <v>31203</v>
+        <v>31216</v>
       </c>
       <c r="G263">
-        <v>44932</v>
+        <v>44951</v>
       </c>
       <c r="H263">
-        <v>20713</v>
+        <v>20693</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18092</v>
+        <v>17990</v>
       </c>
       <c r="E264">
         <v>72437</v>
       </c>
       <c r="F264">
-        <v>51906</v>
+        <v>51936</v>
       </c>
       <c r="G264">
-        <v>74745</v>
+        <v>74788</v>
       </c>
       <c r="H264">
-        <v>33814</v>
+        <v>33946</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24138</v>
+        <v>24214</v>
       </c>
       <c r="E265">
         <v>72437</v>
       </c>
       <c r="F265">
-        <v>43906</v>
+        <v>43936</v>
       </c>
       <c r="G265">
-        <v>63225</v>
+        <v>63268</v>
       </c>
       <c r="H265">
-        <v>19768</v>
+        <v>19722</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34374</v>
+        <v>34499</v>
       </c>
       <c r="E266">
         <v>72437</v>
       </c>
       <c r="F266">
-        <v>54328</v>
+        <v>52396</v>
       </c>
       <c r="G266">
-        <v>78232</v>
+        <v>75450</v>
       </c>
       <c r="H266">
-        <v>19954</v>
+        <v>17897</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>30883</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>72437</v>
       </c>
       <c r="F267">
-        <v>46604</v>
+        <v>0</v>
       </c>
       <c r="G267">
-        <v>67110</v>
+        <v>0</v>
       </c>
       <c r="H267">
-        <v>15721</v>
+        <v>0</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10189</v>
+        <v>10237</v>
       </c>
       <c r="E268">
         <v>27860</v>
       </c>
       <c r="F268">
-        <v>39537</v>
+        <v>39573</v>
       </c>
       <c r="G268">
-        <v>56933</v>
+        <v>56985</v>
       </c>
       <c r="H268">
-        <v>29348</v>
+        <v>29336</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,19 +12211,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>16537</v>
+        <v>16573</v>
       </c>
       <c r="E269">
         <v>27860</v>
       </c>
       <c r="F269">
-        <v>31537</v>
+        <v>0</v>
       </c>
       <c r="G269">
-        <v>45413</v>
+        <v>0</v>
       </c>
       <c r="H269">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12172</v>
+        <v>12163</v>
       </c>
       <c r="E270">
         <v>83581</v>
       </c>
       <c r="F270">
-        <v>39172</v>
+        <v>39163</v>
       </c>
       <c r="G270">
-        <v>56408</v>
+        <v>56395</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>63210</v>
+        <v>63489</v>
       </c>
       <c r="E272">
         <v>98440</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>78489</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>113024</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>40294</v>
+        <v>40421</v>
       </c>
       <c r="E273">
         <v>98440</v>
       </c>
       <c r="F273">
-        <v>60509</v>
+        <v>60560</v>
       </c>
       <c r="G273">
-        <v>87133</v>
+        <v>87206</v>
       </c>
       <c r="H273">
-        <v>20215</v>
+        <v>20139</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>73304</v>
+        <v>73136</v>
       </c>
       <c r="E274">
         <v>111422</v>
       </c>
       <c r="F274">
-        <v>106459</v>
+        <v>88136</v>
       </c>
       <c r="G274">
-        <v>153301</v>
+        <v>126916</v>
       </c>
       <c r="H274">
-        <v>33155</v>
+        <v>15000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>77573</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>111422</v>
       </c>
       <c r="F275">
-        <v>92573</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>133305</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11204</v>
+        <v>11208</v>
       </c>
       <c r="E276">
         <v>53863</v>
       </c>
       <c r="F276">
-        <v>40397</v>
+        <v>35000</v>
       </c>
       <c r="G276">
-        <v>58172</v>
+        <v>50400</v>
       </c>
       <c r="H276">
-        <v>29193</v>
+        <v>23792</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>14362</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>53863</v>
       </c>
       <c r="F277">
-        <v>32751</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>47161</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>18389</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20107</v>
+        <v>20171</v>
       </c>
       <c r="E278">
         <v>72437</v>
       </c>
       <c r="F278">
-        <v>51906</v>
+        <v>46665</v>
       </c>
       <c r="G278">
-        <v>74745</v>
+        <v>67198</v>
       </c>
       <c r="H278">
-        <v>31799</v>
+        <v>26494</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24138</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>72437</v>
       </c>
       <c r="F279">
-        <v>43906</v>
+        <v>0</v>
       </c>
       <c r="G279">
-        <v>63225</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>19768</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11760</v>
+        <v>11781</v>
       </c>
       <c r="E280">
         <v>53863</v>
@@ -12709,7 +12709,7 @@
         <v>50400</v>
       </c>
       <c r="H280">
-        <v>23240</v>
+        <v>23219</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17743</v>
+        <v>17783</v>
       </c>
       <c r="E283">
         <v>44558</v>
       </c>
       <c r="F283">
-        <v>32743</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>47150</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50070</v>
+        <v>50196</v>
       </c>
       <c r="E285">
         <v>55702</v>
       </c>
       <c r="F285">
-        <v>65070</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>93701</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58909</v>
+        <v>59031</v>
       </c>
       <c r="E287">
         <v>66846</v>
       </c>
       <c r="F287">
-        <v>73909</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>106429</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>35152</v>
+        <v>35231</v>
       </c>
       <c r="E288">
         <v>61274</v>
       </c>
       <c r="F288">
-        <v>55934</v>
+        <v>55958</v>
       </c>
       <c r="G288">
-        <v>80545</v>
+        <v>80580</v>
       </c>
       <c r="H288">
-        <v>20782</v>
+        <v>20727</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23948</v>
+        <v>24007</v>
       </c>
       <c r="E289">
         <v>61274</v>
       </c>
       <c r="F289">
-        <v>39476</v>
+        <v>39500</v>
       </c>
       <c r="G289">
-        <v>56845</v>
+        <v>56880</v>
       </c>
       <c r="H289">
-        <v>15528</v>
+        <v>15493</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>47245</v>
+        <v>47235</v>
       </c>
       <c r="E292">
         <v>61274</v>
       </c>
       <c r="F292">
-        <v>62245</v>
+        <v>62268</v>
       </c>
       <c r="G292">
-        <v>89633</v>
+        <v>89666</v>
       </c>
       <c r="H292">
-        <v>15000</v>
+        <v>15033</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23710</v>
+        <v>23769</v>
       </c>
       <c r="E293">
         <v>61274</v>
       </c>
       <c r="F293">
-        <v>39381</v>
+        <v>39404</v>
       </c>
       <c r="G293">
-        <v>56709</v>
+        <v>56742</v>
       </c>
       <c r="H293">
-        <v>15671</v>
+        <v>15635</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>49784</v>
+        <v>49877</v>
       </c>
       <c r="E294">
         <v>68703</v>
       </c>
       <c r="F294">
-        <v>66254</v>
+        <v>66287</v>
       </c>
       <c r="G294">
-        <v>95406</v>
+        <v>95453</v>
       </c>
       <c r="H294">
-        <v>16470</v>
+        <v>16410</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>26027</v>
+        <v>26109</v>
       </c>
       <c r="E295">
         <v>68703</v>
       </c>
       <c r="F295">
-        <v>43205</v>
+        <v>43238</v>
       </c>
       <c r="G295">
-        <v>62215</v>
+        <v>62263</v>
       </c>
       <c r="H295">
-        <v>17178</v>
+        <v>17129</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62512</v>
+        <v>62709</v>
       </c>
       <c r="E296">
         <v>78919</v>
       </c>
       <c r="F296">
-        <v>77512</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>111617</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74414</v>
+        <v>74649</v>
       </c>
       <c r="E298">
         <v>94706</v>
       </c>
       <c r="F298">
-        <v>89414</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>128756</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>69320</v>
+        <v>69554</v>
       </c>
       <c r="E300">
         <v>92849</v>
       </c>
       <c r="F300">
-        <v>88532</v>
+        <v>88574</v>
       </c>
       <c r="G300">
-        <v>127486</v>
+        <v>127547</v>
       </c>
       <c r="H300">
-        <v>19212</v>
+        <v>19020</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33629</v>
+        <v>33734</v>
       </c>
       <c r="E301">
         <v>92849</v>
       </c>
       <c r="F301">
-        <v>55663</v>
+        <v>55705</v>
       </c>
       <c r="G301">
-        <v>80155</v>
+        <v>80215</v>
       </c>
       <c r="H301">
-        <v>22034</v>
+        <v>21971</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>10760</v>
+        <v>12195</v>
       </c>
       <c r="E303">
         <v>129996</v>
       </c>
       <c r="F303">
-        <v>37760</v>
+        <v>39195</v>
       </c>
       <c r="G303">
-        <v>54374</v>
+        <v>56441</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174110</v>
+        <v>174706</v>
       </c>
       <c r="E304">
         <v>167143</v>
       </c>
       <c r="F304">
-        <v>189110</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>272318</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104409</v>
+        <v>104610</v>
       </c>
       <c r="E305">
         <v>167143</v>
       </c>
       <c r="F305">
-        <v>119409</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>171949</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50038</v>
+        <v>50196</v>
       </c>
       <c r="E306">
         <v>111422</v>
       </c>
       <c r="F306">
-        <v>80132</v>
+        <v>80176</v>
       </c>
       <c r="G306">
-        <v>115390</v>
+        <v>115453</v>
       </c>
       <c r="H306">
-        <v>30094</v>
+        <v>29980</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50498</v>
+        <v>50610</v>
       </c>
       <c r="E307">
         <v>111422</v>
       </c>
       <c r="F307">
-        <v>69654</v>
+        <v>69698</v>
       </c>
       <c r="G307">
-        <v>100302</v>
+        <v>100365</v>
       </c>
       <c r="H307">
-        <v>19156</v>
+        <v>19088</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69225</v>
+        <v>69475</v>
       </c>
       <c r="E308">
         <v>129996</v>
@@ -13936,7 +13936,7 @@
         <v>140396</v>
       </c>
       <c r="H308">
-        <v>28272</v>
+        <v>28022</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77668</v>
+        <v>77912</v>
       </c>
       <c r="E309">
         <v>129996</v>
       </c>
       <c r="F309">
-        <v>92668</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>133442</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24614</v>
+        <v>24724</v>
       </c>
       <c r="E310">
         <v>55702</v>
@@ -14026,7 +14026,7 @@
         <v>60159</v>
       </c>
       <c r="H310">
-        <v>17163</v>
+        <v>17053</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,16 +14058,16 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>22694</v>
+        <v>22559</v>
       </c>
       <c r="E311">
         <v>55702</v>
       </c>
       <c r="F311">
-        <v>37694</v>
+        <v>37559</v>
       </c>
       <c r="G311">
-        <v>54279</v>
+        <v>54085</v>
       </c>
       <c r="H311">
         <v>15000</v>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>65876</v>
+        <v>66036</v>
       </c>
       <c r="E312">
         <v>83581</v>
       </c>
       <c r="F312">
-        <v>80876</v>
+        <v>0</v>
       </c>
       <c r="G312">
-        <v>116461</v>
+        <v>0</v>
       </c>
       <c r="H312">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>63441</v>
       </c>
       <c r="E313">
         <v>83581</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>78441</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>112955</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>22424</v>
+        <v>22463</v>
       </c>
       <c r="E315">
         <v>38986</v>
       </c>
       <c r="F315">
-        <v>37424</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>53891</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32359</v>
+        <v>32461</v>
       </c>
       <c r="E316">
         <v>59417</v>
       </c>
       <c r="F316">
-        <v>49535</v>
+        <v>62946</v>
       </c>
       <c r="G316">
-        <v>71330</v>
+        <v>90642</v>
       </c>
       <c r="H316">
-        <v>17176</v>
+        <v>30485</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26535</v>
+        <v>39736</v>
       </c>
       <c r="E317">
         <v>59417</v>
       </c>
       <c r="F317">
-        <v>41535</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>59810</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16172</v>
+        <v>16222</v>
       </c>
       <c r="E318">
         <v>44558</v>
@@ -14378,7 +14378,7 @@
         <v>48123</v>
       </c>
       <c r="H318">
-        <v>17247</v>
+        <v>17197</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29550</v>
+        <v>29420</v>
       </c>
       <c r="E319">
         <v>44558</v>
       </c>
       <c r="F319">
-        <v>44550</v>
+        <v>44420</v>
       </c>
       <c r="G319">
-        <v>64152</v>
+        <v>63965</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>47070</v>
+        <v>0</v>
       </c>
       <c r="E321">
         <v>111422</v>
       </c>
       <c r="F321">
-        <v>68282</v>
+        <v>0</v>
       </c>
       <c r="G321">
-        <v>98326</v>
+        <v>0</v>
       </c>
       <c r="H321">
-        <v>21212</v>
+        <v>0</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58608</v>
+        <v>58777</v>
       </c>
       <c r="E324">
         <v>74275</v>
       </c>
       <c r="F324">
-        <v>90635</v>
+        <v>73777</v>
       </c>
       <c r="G324">
-        <v>130514</v>
+        <v>106239</v>
       </c>
       <c r="H324">
-        <v>32027</v>
+        <v>15000</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>63813</v>
+        <v>0</v>
       </c>
       <c r="E325">
         <v>74275</v>
       </c>
       <c r="F325">
-        <v>78813</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>113491</v>
+        <v>0</v>
       </c>
       <c r="H325">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9379</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>64989</v>
       </c>
       <c r="F327">
-        <v>35097</v>
+        <v>0</v>
       </c>
       <c r="G327">
-        <v>50540</v>
+        <v>0</v>
       </c>
       <c r="H327">
-        <v>25718</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>16997</v>
+        <v>0</v>
       </c>
       <c r="E329">
         <v>64989</v>
       </c>
       <c r="F329">
-        <v>38145</v>
+        <v>0</v>
       </c>
       <c r="G329">
-        <v>54929</v>
+        <v>0</v>
       </c>
       <c r="H329">
-        <v>21148</v>
+        <v>0</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20901</v>
+        <v>20951</v>
       </c>
       <c r="E330">
         <v>92849</v>
       </c>
       <c r="F330">
-        <v>47901</v>
+        <v>47951</v>
       </c>
       <c r="G330">
-        <v>68977</v>
+        <v>69049</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43690</v>
+        <v>43844</v>
       </c>
       <c r="E332">
         <v>111422</v>
       </c>
       <c r="F332">
-        <v>78690</v>
+        <v>78844</v>
       </c>
       <c r="G332">
-        <v>113314</v>
+        <v>113535</v>
       </c>
       <c r="H332">
         <v>35000</v>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>83095</v>
+        <v>83357</v>
       </c>
       <c r="E333">
         <v>111422</v>
       </c>
       <c r="F333">
-        <v>98095</v>
+        <v>0</v>
       </c>
       <c r="G333">
-        <v>141257</v>
+        <v>0</v>
       </c>
       <c r="H333">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32010</v>
+        <v>32015</v>
       </c>
       <c r="E334">
         <v>111422</v>
       </c>
       <c r="F334">
-        <v>67010</v>
+        <v>67015</v>
       </c>
       <c r="G334">
-        <v>96494</v>
+        <v>96502</v>
       </c>
       <c r="H334">
         <v>35000</v>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49276</v>
+        <v>49432</v>
       </c>
       <c r="E335">
         <v>111422</v>
       </c>
       <c r="F335">
-        <v>69165</v>
+        <v>69227</v>
       </c>
       <c r="G335">
-        <v>99598</v>
+        <v>99687</v>
       </c>
       <c r="H335">
-        <v>19889</v>
+        <v>19795</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>189313</v>
+        <v>189559</v>
       </c>
       <c r="E336">
         <v>241437</v>
       </c>
       <c r="F336">
-        <v>204313</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>294211</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>143989</v>
+        <v>0</v>
       </c>
       <c r="E337">
         <v>241437</v>
       </c>
       <c r="F337">
-        <v>158989</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>228944</v>
+        <v>0</v>
       </c>
       <c r="H337">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>85396</v>
+        <v>62804</v>
       </c>
       <c r="E338">
         <v>129996</v>
       </c>
       <c r="F338">
-        <v>0</v>
+        <v>89620</v>
       </c>
       <c r="G338">
-        <v>0</v>
+        <v>129053</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>26816</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>41786</v>
+        <v>0</v>
       </c>
       <c r="E339">
         <v>129996</v>
       </c>
       <c r="F339">
-        <v>68786</v>
+        <v>0</v>
       </c>
       <c r="G339">
-        <v>99052</v>
+        <v>0</v>
       </c>
       <c r="H339">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>110071</v>
       </c>
       <c r="E341">
         <v>185716</v>
       </c>
       <c r="F341">
-        <v>0</v>
+        <v>125071</v>
       </c>
       <c r="G341">
-        <v>0</v>
+        <v>180102</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>103806</v>
+        <v>0</v>
       </c>
       <c r="E342">
         <v>241437</v>
       </c>
       <c r="F342">
-        <v>130806</v>
+        <v>0</v>
       </c>
       <c r="G342">
-        <v>188361</v>
+        <v>0</v>
       </c>
       <c r="H342">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>144458</v>
       </c>
       <c r="E343">
         <v>241437</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>159458</v>
       </c>
       <c r="G343">
-        <v>0</v>
+        <v>229620</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72134</v>
+        <v>71963</v>
       </c>
       <c r="E2">
         <v>74275</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86963</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>125227</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47999</v>
+        <v>47891</v>
       </c>
       <c r="E3">
         <v>74275</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>62891</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90563</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95011</v>
+        <v>94859</v>
       </c>
       <c r="E4">
         <v>85420</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>109859</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>158197</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>79345</v>
+        <v>78975</v>
       </c>
       <c r="E5">
         <v>85420</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>93975</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>135324</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7180</v>
+        <v>7171</v>
       </c>
       <c r="E7">
         <v>55702</v>
       </c>
       <c r="F7">
-        <v>30596</v>
+        <v>30592</v>
       </c>
       <c r="G7">
-        <v>44058</v>
+        <v>44052</v>
       </c>
       <c r="H7">
-        <v>23416</v>
+        <v>23421</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39386</v>
+        <v>39321</v>
       </c>
       <c r="E8">
         <v>74275</v>
       </c>
       <c r="F8">
-        <v>55178</v>
+        <v>55152</v>
       </c>
       <c r="G8">
-        <v>79456</v>
+        <v>79419</v>
       </c>
       <c r="H8">
-        <v>15792</v>
+        <v>15831</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56341</v>
+        <v>56270</v>
       </c>
       <c r="E10">
         <v>111422</v>
       </c>
       <c r="F10">
-        <v>78677</v>
+        <v>78648</v>
       </c>
       <c r="G10">
-        <v>113295</v>
+        <v>113253</v>
       </c>
       <c r="H10">
-        <v>22336</v>
+        <v>22378</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>83086</v>
+        <v>82887</v>
       </c>
       <c r="E12">
         <v>83562</v>
       </c>
       <c r="F12">
-        <v>99216</v>
+        <v>99183</v>
       </c>
       <c r="G12">
-        <v>142871</v>
+        <v>142824</v>
       </c>
       <c r="H12">
-        <v>16130</v>
+        <v>16296</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13484</v>
+        <v>13451</v>
       </c>
       <c r="E13">
         <v>83562</v>
       </c>
       <c r="F13">
-        <v>40484</v>
+        <v>40451</v>
       </c>
       <c r="G13">
-        <v>58297</v>
+        <v>58249</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27287</v>
+        <v>27221</v>
       </c>
       <c r="E15">
         <v>74275</v>
       </c>
       <c r="F15">
-        <v>45882</v>
+        <v>45856</v>
       </c>
       <c r="G15">
-        <v>66070</v>
+        <v>66033</v>
       </c>
       <c r="H15">
-        <v>18595</v>
+        <v>18635</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54606</v>
+        <v>49481</v>
       </c>
       <c r="E21">
         <v>103993</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>66349</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>95543</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>16868</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,7 +1425,7 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96109</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>133711</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21269</v>
+        <v>21370</v>
       </c>
       <c r="E27">
         <v>64989</v>
       </c>
       <c r="F27">
-        <v>39853</v>
+        <v>39894</v>
       </c>
       <c r="G27">
-        <v>57388</v>
+        <v>57447</v>
       </c>
       <c r="H27">
-        <v>18584</v>
+        <v>18524</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>79584</v>
+        <v>78737</v>
       </c>
       <c r="E28">
         <v>129996</v>
       </c>
       <c r="F28">
-        <v>96523</v>
+        <v>96443</v>
       </c>
       <c r="G28">
-        <v>138993</v>
+        <v>138878</v>
       </c>
       <c r="H28">
-        <v>16939</v>
+        <v>17706</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38081</v>
+        <v>38001</v>
       </c>
       <c r="E29">
         <v>129996</v>
       </c>
       <c r="F29">
-        <v>65081</v>
+        <v>65001</v>
       </c>
       <c r="G29">
-        <v>93717</v>
+        <v>93601</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>136594</v>
+        <v>131636</v>
       </c>
       <c r="E30">
         <v>185716</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>146636</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>211156</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>71799</v>
+        <v>72345</v>
       </c>
       <c r="E31">
         <v>185716</v>
       </c>
       <c r="F31">
-        <v>98799</v>
+        <v>99345</v>
       </c>
       <c r="G31">
-        <v>142271</v>
+        <v>143057</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60639</v>
+        <v>60563</v>
       </c>
       <c r="E32">
         <v>111422</v>
       </c>
       <c r="F32">
-        <v>80972</v>
+        <v>80878</v>
       </c>
       <c r="G32">
-        <v>116600</v>
+        <v>116464</v>
       </c>
       <c r="H32">
-        <v>20333</v>
+        <v>20315</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36441</v>
+        <v>36347</v>
       </c>
       <c r="E33">
         <v>111422</v>
       </c>
       <c r="F33">
-        <v>63441</v>
+        <v>63347</v>
       </c>
       <c r="G33">
-        <v>91355</v>
+        <v>91220</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>83809</v>
       </c>
       <c r="E35">
         <v>129996</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>98809</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>142285</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48906</v>
+        <v>48797</v>
       </c>
       <c r="E36">
         <v>129996</v>
       </c>
       <c r="F36">
-        <v>75906</v>
+        <v>75797</v>
       </c>
       <c r="G36">
-        <v>109305</v>
+        <v>109148</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35584</v>
       </c>
       <c r="E37">
         <v>129996</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62584</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>90121</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>68185</v>
+        <v>67829</v>
       </c>
       <c r="E38">
         <v>185716</v>
       </c>
       <c r="F38">
-        <v>95185</v>
+        <v>94829</v>
       </c>
       <c r="G38">
-        <v>137066</v>
+        <v>136554</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>98978</v>
       </c>
       <c r="E39">
         <v>185716</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>118020</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>169949</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>19042</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87894</v>
+        <v>87625</v>
       </c>
       <c r="E40">
         <v>241437</v>
       </c>
       <c r="F40">
-        <v>114894</v>
+        <v>114625</v>
       </c>
       <c r="G40">
-        <v>165447</v>
+        <v>165060</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>134816</v>
       </c>
       <c r="E41">
         <v>185716</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>149816</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>215735</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>33607</v>
+        <v>32977</v>
       </c>
       <c r="E43">
         <v>129996</v>
       </c>
       <c r="F43">
-        <v>60607</v>
+        <v>59977</v>
       </c>
       <c r="G43">
-        <v>87274</v>
+        <v>86367</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,16 +2393,16 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>74569</v>
+        <v>78673</v>
       </c>
       <c r="E45">
         <v>185716</v>
       </c>
       <c r="F45">
-        <v>101569</v>
+        <v>105673</v>
       </c>
       <c r="G45">
-        <v>146259</v>
+        <v>152169</v>
       </c>
       <c r="H45">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>22511</v>
+        <v>22085</v>
       </c>
       <c r="E47">
         <v>111422</v>
       </c>
       <c r="F47">
-        <v>49511</v>
+        <v>49085</v>
       </c>
       <c r="G47">
-        <v>71296</v>
+        <v>70682</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36759</v>
+        <v>36713</v>
       </c>
       <c r="E50">
         <v>64989</v>
       </c>
       <c r="F50">
-        <v>54099</v>
+        <v>54080</v>
       </c>
       <c r="G50">
-        <v>77903</v>
+        <v>77875</v>
       </c>
       <c r="H50">
-        <v>17340</v>
+        <v>17367</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>24167</v>
+        <v>24120</v>
       </c>
       <c r="E51">
         <v>64989</v>
       </c>
       <c r="F51">
-        <v>41013</v>
+        <v>40994</v>
       </c>
       <c r="G51">
-        <v>59059</v>
+        <v>59031</v>
       </c>
       <c r="H51">
-        <v>16846</v>
+        <v>16874</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54112</v>
+        <v>51325</v>
       </c>
       <c r="E52">
         <v>77990</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>66325</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>95508</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>59000</v>
+        <v>59116</v>
       </c>
       <c r="E53">
         <v>77990</v>
       </c>
       <c r="F53">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>106560</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44990</v>
+        <v>44918</v>
       </c>
       <c r="E54">
         <v>129996</v>
       </c>
       <c r="F54">
-        <v>79990</v>
+        <v>79918</v>
       </c>
       <c r="G54">
-        <v>115186</v>
+        <v>115082</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44847</v>
+        <v>44727</v>
       </c>
       <c r="E55">
         <v>129996</v>
       </c>
       <c r="F55">
-        <v>71847</v>
+        <v>71727</v>
       </c>
       <c r="G55">
-        <v>103460</v>
+        <v>103287</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>51103</v>
+        <v>54044</v>
       </c>
       <c r="E56">
         <v>148569</v>
       </c>
       <c r="F56">
-        <v>78103</v>
+        <v>81044</v>
       </c>
       <c r="G56">
-        <v>112468</v>
+        <v>116703</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>58649</v>
+        <v>66017</v>
       </c>
       <c r="E57">
         <v>148569</v>
       </c>
       <c r="F57">
-        <v>85649</v>
+        <v>90349</v>
       </c>
       <c r="G57">
-        <v>123335</v>
+        <v>130103</v>
       </c>
       <c r="H57">
-        <v>27000</v>
+        <v>24332</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>16859</v>
+        <v>16520</v>
       </c>
       <c r="E58">
         <v>37128</v>
       </c>
       <c r="F58">
-        <v>38709</v>
+        <v>38706</v>
       </c>
       <c r="G58">
-        <v>55741</v>
+        <v>55737</v>
       </c>
       <c r="H58">
-        <v>21850</v>
+        <v>22186</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6241</v>
+        <v>6233</v>
       </c>
       <c r="E59">
         <v>37128</v>
       </c>
       <c r="F59">
-        <v>22976</v>
+        <v>22973</v>
       </c>
       <c r="G59">
-        <v>33085</v>
+        <v>33081</v>
       </c>
       <c r="H59">
-        <v>16735</v>
+        <v>16740</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24198</v>
+        <v>24152</v>
       </c>
       <c r="E60">
         <v>50130</v>
       </c>
       <c r="F60">
-        <v>48536</v>
+        <v>48583</v>
       </c>
       <c r="G60">
-        <v>69892</v>
+        <v>69960</v>
       </c>
       <c r="H60">
-        <v>24338</v>
+        <v>24431</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25536</v>
+        <v>25583</v>
       </c>
       <c r="E61">
         <v>50130</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40583</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58440</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13452</v>
+        <v>14183</v>
       </c>
       <c r="E63">
         <v>83562</v>
       </c>
       <c r="F63">
-        <v>40452</v>
+        <v>41183</v>
       </c>
       <c r="G63">
-        <v>58251</v>
+        <v>59304</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23259</v>
+        <v>23214</v>
       </c>
       <c r="E65">
         <v>125334</v>
       </c>
       <c r="F65">
-        <v>50259</v>
+        <v>50214</v>
       </c>
       <c r="G65">
-        <v>72373</v>
+        <v>72308</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25934</v>
+        <v>25885</v>
       </c>
       <c r="E66">
         <v>92849</v>
       </c>
       <c r="F66">
-        <v>60869</v>
+        <v>60827</v>
       </c>
       <c r="G66">
-        <v>87651</v>
+        <v>87591</v>
       </c>
       <c r="H66">
-        <v>34935</v>
+        <v>34942</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20823</v>
+        <v>20781</v>
       </c>
       <c r="E67">
         <v>92849</v>
       </c>
       <c r="F67">
-        <v>47823</v>
+        <v>47781</v>
       </c>
       <c r="G67">
-        <v>68865</v>
+        <v>68805</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48158</v>
+        <v>48082</v>
       </c>
       <c r="E68">
         <v>111422</v>
       </c>
       <c r="F68">
-        <v>75158</v>
+        <v>75219</v>
       </c>
       <c r="G68">
-        <v>108228</v>
+        <v>108315</v>
       </c>
       <c r="H68">
-        <v>27000</v>
+        <v>27137</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27685</v>
+        <v>27746</v>
       </c>
       <c r="E69">
         <v>111422</v>
       </c>
       <c r="F69">
-        <v>54685</v>
+        <v>54746</v>
       </c>
       <c r="G69">
-        <v>78746</v>
+        <v>78834</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110851</v>
+        <v>110680</v>
       </c>
       <c r="E70">
         <v>129996</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>125680</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>180979</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52584</v>
+        <v>52693</v>
       </c>
       <c r="E71">
         <v>129996</v>
       </c>
       <c r="F71">
-        <v>77732</v>
+        <v>77775</v>
       </c>
       <c r="G71">
-        <v>111934</v>
+        <v>111996</v>
       </c>
       <c r="H71">
-        <v>25148</v>
+        <v>25082</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6830</v>
+        <v>6821</v>
       </c>
       <c r="E73">
         <v>27842</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>21821</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>31422</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70319</v>
+        <v>70469</v>
       </c>
       <c r="E75">
         <v>97492</v>
       </c>
       <c r="F75">
-        <v>85319</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>122859</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>89184</v>
+        <v>89374</v>
       </c>
       <c r="E76">
         <v>129996</v>
       </c>
       <c r="F76">
-        <v>123188</v>
+        <v>123131</v>
       </c>
       <c r="G76">
-        <v>177391</v>
+        <v>177309</v>
       </c>
       <c r="H76">
-        <v>34004</v>
+        <v>33757</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>62184</v>
+        <v>62042</v>
       </c>
       <c r="E77">
         <v>129996</v>
       </c>
       <c r="F77">
-        <v>81572</v>
+        <v>81515</v>
       </c>
       <c r="G77">
-        <v>117464</v>
+        <v>117382</v>
       </c>
       <c r="H77">
-        <v>19388</v>
+        <v>19473</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23323</v>
+        <v>23262</v>
       </c>
       <c r="E81">
         <v>92849</v>
       </c>
       <c r="F81">
-        <v>50323</v>
+        <v>50262</v>
       </c>
       <c r="G81">
-        <v>72465</v>
+        <v>72377</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87337</v>
+        <v>87148</v>
       </c>
       <c r="E83">
         <v>129996</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>102148</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>147093</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48763</v>
+        <v>48034</v>
       </c>
       <c r="E84">
         <v>74275</v>
       </c>
       <c r="F84">
-        <v>63763</v>
+        <v>64054</v>
       </c>
       <c r="G84">
-        <v>91819</v>
+        <v>92238</v>
       </c>
       <c r="H84">
-        <v>15000</v>
+        <v>16020</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>34180</v>
+        <v>34471</v>
       </c>
       <c r="E85">
         <v>74275</v>
       </c>
       <c r="F85">
-        <v>49180</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>70819</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8231</v>
+        <v>8204</v>
       </c>
       <c r="E90">
         <v>59417</v>
       </c>
       <c r="F90">
-        <v>38656</v>
+        <v>38648</v>
       </c>
       <c r="G90">
-        <v>55665</v>
+        <v>55653</v>
       </c>
       <c r="H90">
-        <v>30425</v>
+        <v>30444</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3709</v>
+        <v>3689</v>
       </c>
       <c r="E91">
         <v>59417</v>
       </c>
       <c r="F91">
-        <v>30656</v>
+        <v>30648</v>
       </c>
       <c r="G91">
-        <v>44145</v>
+        <v>44133</v>
       </c>
       <c r="H91">
-        <v>26947</v>
+        <v>26959</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9520</v>
+        <v>9492</v>
       </c>
       <c r="E93">
         <v>27842</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24492</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35268</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63887</v>
+        <v>61040</v>
       </c>
       <c r="E96">
         <v>83562</v>
       </c>
       <c r="F96">
-        <v>78887</v>
+        <v>78864</v>
       </c>
       <c r="G96">
-        <v>113597</v>
+        <v>113564</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>17824</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34626</v>
+        <v>34567</v>
       </c>
       <c r="E97">
         <v>83562</v>
       </c>
       <c r="F97">
-        <v>52439</v>
+        <v>52416</v>
       </c>
       <c r="G97">
-        <v>75512</v>
+        <v>75479</v>
       </c>
       <c r="H97">
-        <v>17813</v>
+        <v>17849</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79441</v>
+        <v>79246</v>
       </c>
       <c r="E98">
         <v>96564</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>94246</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>135714</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>42284</v>
+        <v>43900</v>
       </c>
       <c r="E99">
         <v>96564</v>
       </c>
       <c r="F99">
-        <v>60574</v>
+        <v>61220</v>
       </c>
       <c r="G99">
-        <v>87227</v>
+        <v>88157</v>
       </c>
       <c r="H99">
-        <v>18290</v>
+        <v>17320</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60767</v>
+        <v>60627</v>
       </c>
       <c r="E100">
         <v>108265</v>
       </c>
       <c r="F100">
-        <v>79026</v>
+        <v>81199</v>
       </c>
       <c r="G100">
-        <v>113797</v>
+        <v>116927</v>
       </c>
       <c r="H100">
-        <v>18259</v>
+        <v>20572</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>63473</v>
       </c>
       <c r="E101">
         <v>108265</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>78473</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>113001</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71640</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>129996</v>
       </c>
       <c r="F105">
-        <v>86640</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>124762</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>75143</v>
       </c>
       <c r="E107">
         <v>185716</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>102143</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>147086</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6018</v>
+        <v>6169</v>
       </c>
       <c r="E109">
         <v>129996</v>
       </c>
       <c r="F109">
-        <v>33018</v>
+        <v>33169</v>
       </c>
       <c r="G109">
-        <v>47546</v>
+        <v>47763</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15108</v>
+        <v>15089</v>
       </c>
       <c r="E111">
         <v>167143</v>
       </c>
       <c r="F111">
-        <v>42108</v>
+        <v>42089</v>
       </c>
       <c r="G111">
-        <v>60636</v>
+        <v>60608</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51278</v>
+        <v>51166</v>
       </c>
       <c r="E113">
         <v>129996</v>
       </c>
       <c r="F113">
-        <v>77209</v>
+        <v>77165</v>
       </c>
       <c r="G113">
-        <v>111181</v>
+        <v>111118</v>
       </c>
       <c r="H113">
-        <v>25931</v>
+        <v>25999</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>83644</v>
+        <v>80311</v>
       </c>
       <c r="E118">
         <v>89134</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>95311</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>137248</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>46646</v>
+        <v>49099</v>
       </c>
       <c r="E119">
         <v>89134</v>
       </c>
       <c r="F119">
-        <v>61646</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>88770</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102382</v>
+        <v>102158</v>
       </c>
       <c r="E121">
         <v>118852</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>117158</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>168708</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>114290</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>148569</v>
       </c>
       <c r="F123">
-        <v>129290</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>186178</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46295</v>
+        <v>46221</v>
       </c>
       <c r="E124">
         <v>59417</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>61221</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>88158</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35518</v>
+        <v>35584</v>
       </c>
       <c r="E125">
         <v>59417</v>
       </c>
       <c r="F125">
-        <v>50518</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72746</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63887</v>
+        <v>63791</v>
       </c>
       <c r="E126">
         <v>81705</v>
       </c>
       <c r="F126">
-        <v>78887</v>
+        <v>81486</v>
       </c>
       <c r="G126">
-        <v>113597</v>
+        <v>117340</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>17695</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>55857</v>
       </c>
       <c r="E127">
         <v>81705</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>70857</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>102034</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>38877</v>
+        <v>39035</v>
       </c>
       <c r="E128">
         <v>92849</v>
       </c>
       <c r="F128">
-        <v>65585</v>
+        <v>65553</v>
       </c>
       <c r="G128">
-        <v>94442</v>
+        <v>94396</v>
       </c>
       <c r="H128">
-        <v>26708</v>
+        <v>26518</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>37046</v>
+        <v>36968</v>
       </c>
       <c r="E129">
         <v>92849</v>
       </c>
       <c r="F129">
-        <v>57030</v>
+        <v>56998</v>
       </c>
       <c r="G129">
-        <v>82123</v>
+        <v>82077</v>
       </c>
       <c r="H129">
-        <v>19984</v>
+        <v>20030</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12768</v>
+        <v>12736</v>
       </c>
       <c r="E130">
         <v>44558</v>
       </c>
       <c r="F130">
-        <v>33419</v>
+        <v>33203</v>
       </c>
       <c r="G130">
-        <v>48123</v>
+        <v>47812</v>
       </c>
       <c r="H130">
-        <v>20651</v>
+        <v>20467</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5843</v>
+        <v>4563</v>
       </c>
       <c r="E131">
         <v>44558</v>
       </c>
       <c r="F131">
-        <v>25715</v>
+        <v>25203</v>
       </c>
       <c r="G131">
-        <v>37030</v>
+        <v>36292</v>
       </c>
       <c r="H131">
-        <v>19872</v>
+        <v>20640</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27764</v>
+        <v>27730</v>
       </c>
       <c r="E132">
         <v>59417</v>
       </c>
       <c r="F132">
-        <v>43843</v>
+        <v>43830</v>
       </c>
       <c r="G132">
-        <v>63134</v>
+        <v>63115</v>
       </c>
       <c r="H132">
-        <v>16079</v>
+        <v>16100</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17369</v>
+        <v>17331</v>
       </c>
       <c r="E135">
         <v>60884</v>
       </c>
       <c r="F135">
-        <v>36693</v>
+        <v>36677</v>
       </c>
       <c r="G135">
-        <v>52838</v>
+        <v>52815</v>
       </c>
       <c r="H135">
-        <v>19324</v>
+        <v>19346</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28592</v>
+        <v>29049</v>
       </c>
       <c r="E137">
         <v>75854</v>
       </c>
       <c r="F137">
-        <v>47020</v>
+        <v>47203</v>
       </c>
       <c r="G137">
-        <v>67709</v>
+        <v>67972</v>
       </c>
       <c r="H137">
-        <v>18428</v>
+        <v>18154</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>28608</v>
+        <v>28350</v>
       </c>
       <c r="E139">
         <v>95486</v>
       </c>
       <c r="F139">
-        <v>54683</v>
+        <v>54580</v>
       </c>
       <c r="G139">
-        <v>78744</v>
+        <v>78595</v>
       </c>
       <c r="H139">
-        <v>26075</v>
+        <v>26230</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58347</v>
+        <v>58226</v>
       </c>
       <c r="E141">
         <v>90992</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>73226</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>105445</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>76384</v>
+        <v>77656</v>
       </c>
       <c r="E143">
         <v>129996</v>
       </c>
       <c r="F143">
-        <v>91384</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>131593</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87433</v>
+        <v>87243</v>
       </c>
       <c r="E145">
         <v>155999</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>102243</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>147230</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86318</v>
+        <v>86480</v>
       </c>
       <c r="E147">
         <v>90992</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>101480</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>146131</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122473</v>
+        <v>122716</v>
       </c>
       <c r="E149">
         <v>129996</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>137716</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>198311</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38415</v>
+        <v>38335</v>
       </c>
       <c r="E150">
         <v>92849</v>
       </c>
       <c r="F150">
-        <v>63148</v>
+        <v>63116</v>
       </c>
       <c r="G150">
-        <v>90933</v>
+        <v>90887</v>
       </c>
       <c r="H150">
-        <v>24733</v>
+        <v>24781</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24772</v>
+        <v>24931</v>
       </c>
       <c r="E152">
         <v>92849</v>
       </c>
       <c r="F152">
-        <v>59772</v>
+        <v>59931</v>
       </c>
       <c r="G152">
-        <v>86072</v>
+        <v>86301</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29754</v>
+        <v>29685</v>
       </c>
       <c r="E153">
         <v>92849</v>
       </c>
       <c r="F153">
-        <v>54113</v>
+        <v>54085</v>
       </c>
       <c r="G153">
-        <v>77923</v>
+        <v>77882</v>
       </c>
       <c r="H153">
-        <v>24359</v>
+        <v>24400</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48874</v>
+        <v>48749</v>
       </c>
       <c r="E154">
         <v>92849</v>
@@ -7167,7 +7167,7 @@
         <v>100277</v>
       </c>
       <c r="H154">
-        <v>20763</v>
+        <v>20888</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>75907</v>
+        <v>75748</v>
       </c>
       <c r="E155">
         <v>92849</v>
       </c>
       <c r="F155">
-        <v>90907</v>
+        <v>90748</v>
       </c>
       <c r="G155">
-        <v>130906</v>
+        <v>130677</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65670</v>
+        <v>65524</v>
       </c>
       <c r="E156">
         <v>92849</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80524</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>115955</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38988</v>
+        <v>42882</v>
       </c>
       <c r="E158">
         <v>63131</v>
       </c>
       <c r="F158">
-        <v>65766</v>
+        <v>65650</v>
       </c>
       <c r="G158">
-        <v>94703</v>
+        <v>94536</v>
       </c>
       <c r="H158">
-        <v>26778</v>
+        <v>22768</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42188</v>
+        <v>42087</v>
       </c>
       <c r="E159">
         <v>63131</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>57087</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>82205</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>17958</v>
+        <v>17999</v>
       </c>
       <c r="E161">
         <v>55702</v>
       </c>
       <c r="F161">
-        <v>34907</v>
+        <v>34923</v>
       </c>
       <c r="G161">
-        <v>50266</v>
+        <v>50289</v>
       </c>
       <c r="H161">
-        <v>16949</v>
+        <v>16924</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56293</v>
+        <v>56191</v>
       </c>
       <c r="E163">
         <v>74275</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>71191</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>102515</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70717</v>
+        <v>70866</v>
       </c>
       <c r="E165">
         <v>111422</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>85866</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>123647</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54112</v>
+        <v>54044</v>
       </c>
       <c r="E166">
         <v>74275</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>69044</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>99423</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34101</v>
+        <v>34026</v>
       </c>
       <c r="E167">
         <v>74275</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>49026</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70597</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60607</v>
+        <v>60515</v>
       </c>
       <c r="E168">
         <v>74275</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>95515</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>137542</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74171</v>
+        <v>74317</v>
       </c>
       <c r="E169">
         <v>74275</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>89317</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>128616</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,16 +7902,16 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15538</v>
+        <v>15153</v>
       </c>
       <c r="E171">
         <v>27842</v>
       </c>
       <c r="F171">
-        <v>30538</v>
+        <v>30153</v>
       </c>
       <c r="G171">
-        <v>43975</v>
+        <v>43420</v>
       </c>
       <c r="H171">
         <v>15000</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31394</v>
+        <v>30862</v>
       </c>
       <c r="E173">
         <v>85420</v>
       </c>
       <c r="F173">
-        <v>51871</v>
+        <v>51659</v>
       </c>
       <c r="G173">
-        <v>74694</v>
+        <v>74389</v>
       </c>
       <c r="H173">
-        <v>20477</v>
+        <v>20797</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7769</v>
+        <v>7282</v>
       </c>
       <c r="E174">
         <v>55721</v>
       </c>
       <c r="F174">
-        <v>37858</v>
+        <v>37856</v>
       </c>
       <c r="G174">
-        <v>54516</v>
+        <v>54513</v>
       </c>
       <c r="H174">
-        <v>30089</v>
+        <v>30574</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5317</v>
+        <v>5311</v>
       </c>
       <c r="E175">
         <v>55721</v>
       </c>
       <c r="F175">
-        <v>29858</v>
+        <v>29856</v>
       </c>
       <c r="G175">
-        <v>42996</v>
+        <v>42993</v>
       </c>
       <c r="H175">
-        <v>24541</v>
+        <v>24545</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10348</v>
+        <v>10065</v>
       </c>
       <c r="E176">
         <v>74275</v>
       </c>
       <c r="F176">
-        <v>42435</v>
+        <v>44127</v>
       </c>
       <c r="G176">
-        <v>61106</v>
+        <v>63543</v>
       </c>
       <c r="H176">
-        <v>32087</v>
+        <v>34062</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7435</v>
+        <v>9127</v>
       </c>
       <c r="E177">
         <v>74275</v>
       </c>
       <c r="F177">
-        <v>34435</v>
+        <v>36127</v>
       </c>
       <c r="G177">
-        <v>49586</v>
+        <v>52023</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,7 +8212,7 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>49097</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>69651</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21954</v>
+        <v>21894</v>
       </c>
       <c r="E179">
         <v>69651</v>
       </c>
       <c r="F179">
-        <v>41945</v>
+        <v>41921</v>
       </c>
       <c r="G179">
-        <v>60401</v>
+        <v>60366</v>
       </c>
       <c r="H179">
-        <v>19991</v>
+        <v>20027</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46057</v>
+        <v>45951</v>
       </c>
       <c r="E181">
         <v>104940</v>
       </c>
       <c r="F181">
-        <v>65349</v>
+        <v>65307</v>
       </c>
       <c r="G181">
-        <v>94103</v>
+        <v>94042</v>
       </c>
       <c r="H181">
-        <v>19292</v>
+        <v>19356</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68138</v>
+        <v>68020</v>
       </c>
       <c r="E182">
         <v>74275</v>
       </c>
       <c r="F182">
-        <v>86578</v>
+        <v>86549</v>
       </c>
       <c r="G182">
-        <v>124672</v>
+        <v>124631</v>
       </c>
       <c r="H182">
-        <v>18440</v>
+        <v>18529</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10189</v>
+        <v>10160</v>
       </c>
       <c r="E183">
         <v>74275</v>
       </c>
       <c r="F183">
-        <v>37189</v>
+        <v>37160</v>
       </c>
       <c r="G183">
-        <v>53552</v>
+        <v>53510</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60639</v>
+        <v>60563</v>
       </c>
       <c r="E184">
         <v>111422</v>
       </c>
       <c r="F184">
-        <v>80396</v>
+        <v>80436</v>
       </c>
       <c r="G184">
-        <v>115770</v>
+        <v>115828</v>
       </c>
       <c r="H184">
-        <v>19757</v>
+        <v>19873</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45738</v>
+        <v>45840</v>
       </c>
       <c r="E185">
         <v>111422</v>
       </c>
       <c r="F185">
-        <v>67750</v>
+        <v>67790</v>
       </c>
       <c r="G185">
-        <v>97560</v>
+        <v>97618</v>
       </c>
       <c r="H185">
-        <v>22012</v>
+        <v>21950</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>80062</v>
+        <v>79961</v>
       </c>
       <c r="E186">
         <v>148569</v>
       </c>
       <c r="F186">
-        <v>110977</v>
+        <v>111054</v>
       </c>
       <c r="G186">
-        <v>159807</v>
+        <v>159918</v>
       </c>
       <c r="H186">
-        <v>30915</v>
+        <v>31093</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81399</v>
+        <v>81567</v>
       </c>
       <c r="E187">
         <v>148569</v>
       </c>
       <c r="F187">
-        <v>96502</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>138963</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15103</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,7 +8738,7 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>147308</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>157856</v>
@@ -8823,7 +8823,7 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>172589</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>185716</v>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7371</v>
+        <v>7012</v>
       </c>
       <c r="E194">
         <v>53863</v>
@@ -8920,7 +8920,7 @@
         <v>50400</v>
       </c>
       <c r="H194">
-        <v>27629</v>
+        <v>27988</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11797</v>
+        <v>11782</v>
       </c>
       <c r="E196">
         <v>83581</v>
       </c>
       <c r="F196">
-        <v>38797</v>
+        <v>38782</v>
       </c>
       <c r="G196">
-        <v>55868</v>
+        <v>55846</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51851</v>
+        <v>51770</v>
       </c>
       <c r="E198">
         <v>92849</v>
@@ -9095,7 +9095,7 @@
         <v>100277</v>
       </c>
       <c r="H198">
-        <v>17786</v>
+        <v>17867</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75254</v>
+        <v>75080</v>
       </c>
       <c r="E199">
         <v>92849</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>90080</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>129715</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>91731</v>
+        <v>90598</v>
       </c>
       <c r="E200">
         <v>92849</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>105598</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>152061</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>17512</v>
+        <v>17490</v>
       </c>
       <c r="E202">
         <v>111422</v>
       </c>
       <c r="F202">
-        <v>44512</v>
+        <v>44490</v>
       </c>
       <c r="G202">
-        <v>64097</v>
+        <v>64066</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27589</v>
+        <v>27539</v>
       </c>
       <c r="E204">
         <v>92849</v>
       </c>
       <c r="F204">
-        <v>54589</v>
+        <v>54539</v>
       </c>
       <c r="G204">
-        <v>78608</v>
+        <v>78536</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101872</v>
+        <v>101744</v>
       </c>
       <c r="E206">
         <v>129996</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>116744</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>168111</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63951</v>
+        <v>64316</v>
       </c>
       <c r="E207">
         <v>129996</v>
       </c>
       <c r="F207">
-        <v>82279</v>
+        <v>82425</v>
       </c>
       <c r="G207">
-        <v>118482</v>
+        <v>118692</v>
       </c>
       <c r="H207">
-        <v>18328</v>
+        <v>18109</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144856</v>
+        <v>144674</v>
       </c>
       <c r="E208">
         <v>185716</v>
       </c>
       <c r="F208">
-        <v>179856</v>
+        <v>179674</v>
       </c>
       <c r="G208">
-        <v>258993</v>
+        <v>258731</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>146368</v>
+        <v>145310</v>
       </c>
       <c r="E209">
         <v>185716</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>160310</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>230846</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187840</v>
+        <v>187604</v>
       </c>
       <c r="E210">
         <v>241437</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>202604</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>291750</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>187617</v>
+        <v>187191</v>
       </c>
       <c r="E211">
         <v>185716</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>202191</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>291155</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>288136</v>
+        <v>287774</v>
       </c>
       <c r="E212">
         <v>371451</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>302774</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>435995</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>224599</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>371451</v>
       </c>
       <c r="F213">
-        <v>240705</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>346615</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>16106</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34722</v>
+        <v>34583</v>
       </c>
       <c r="E214">
         <v>53863</v>
       </c>
       <c r="F214">
-        <v>62837</v>
+        <v>62743</v>
       </c>
       <c r="G214">
-        <v>90485</v>
+        <v>90350</v>
       </c>
       <c r="H214">
-        <v>28115</v>
+        <v>28160</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>39641</v>
+        <v>39559</v>
       </c>
       <c r="E215">
         <v>53863</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>54559</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>78565</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>46295</v>
+        <v>46221</v>
       </c>
       <c r="E216">
         <v>53863</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>61221</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>88158</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16461</v>
+        <v>16488</v>
       </c>
       <c r="E218">
         <v>53863</v>
       </c>
       <c r="F218">
-        <v>36823</v>
+        <v>36833</v>
       </c>
       <c r="G218">
-        <v>53025</v>
+        <v>53040</v>
       </c>
       <c r="H218">
-        <v>20362</v>
+        <v>20345</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12943</v>
+        <v>13165</v>
       </c>
       <c r="E220">
         <v>74275</v>
       </c>
       <c r="F220">
-        <v>46526</v>
+        <v>46543</v>
       </c>
       <c r="G220">
-        <v>66997</v>
+        <v>67022</v>
       </c>
       <c r="H220">
-        <v>33583</v>
+        <v>33378</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11526</v>
+        <v>11543</v>
       </c>
       <c r="E221">
         <v>74275</v>
       </c>
       <c r="F221">
-        <v>38526</v>
+        <v>38543</v>
       </c>
       <c r="G221">
-        <v>55477</v>
+        <v>55502</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21476</v>
+        <v>21195</v>
       </c>
       <c r="E222">
         <v>111422</v>
       </c>
       <c r="F222">
-        <v>56476</v>
+        <v>56195</v>
       </c>
       <c r="G222">
-        <v>81325</v>
+        <v>80921</v>
       </c>
       <c r="H222">
         <v>35000</v>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>53634</v>
+        <v>53742</v>
       </c>
       <c r="E223">
         <v>111422</v>
       </c>
       <c r="F223">
-        <v>70908</v>
+        <v>70951</v>
       </c>
       <c r="G223">
-        <v>102108</v>
+        <v>102169</v>
       </c>
       <c r="H223">
-        <v>17274</v>
+        <v>17209</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16557</v>
+        <v>16806</v>
       </c>
       <c r="E224">
         <v>129996</v>
       </c>
       <c r="F224">
-        <v>45794</v>
+        <v>46178</v>
       </c>
       <c r="G224">
-        <v>65943</v>
+        <v>66496</v>
       </c>
       <c r="H224">
-        <v>29237</v>
+        <v>29372</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10794</v>
+        <v>11178</v>
       </c>
       <c r="E225">
         <v>129996</v>
       </c>
       <c r="F225">
-        <v>37794</v>
+        <v>38178</v>
       </c>
       <c r="G225">
-        <v>54423</v>
+        <v>54976</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26586</v>
+        <v>26537</v>
       </c>
       <c r="E226">
         <v>148569</v>
       </c>
       <c r="F226">
-        <v>61586</v>
+        <v>61537</v>
       </c>
       <c r="G226">
-        <v>88684</v>
+        <v>88613</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>96220</v>
+        <v>95972</v>
       </c>
       <c r="E227">
         <v>148569</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>110972</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>159800</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35215</v>
+        <v>35139</v>
       </c>
       <c r="E228">
         <v>185716</v>
       </c>
       <c r="F228">
-        <v>70215</v>
+        <v>70139</v>
       </c>
       <c r="G228">
-        <v>101110</v>
+        <v>101000</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>98465</v>
+        <v>98675</v>
       </c>
       <c r="E229">
         <v>185716</v>
       </c>
       <c r="F229">
-        <v>117815</v>
+        <v>117899</v>
       </c>
       <c r="G229">
-        <v>169654</v>
+        <v>169775</v>
       </c>
       <c r="H229">
-        <v>19350</v>
+        <v>19224</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16095</v>
+        <v>16107</v>
       </c>
       <c r="E230">
         <v>59417</v>
       </c>
       <c r="F230">
-        <v>42861</v>
+        <v>42983</v>
       </c>
       <c r="G230">
-        <v>61720</v>
+        <v>61896</v>
       </c>
       <c r="H230">
-        <v>26766</v>
+        <v>26876</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9695</v>
+        <v>10001</v>
       </c>
       <c r="E231">
         <v>59417</v>
       </c>
       <c r="F231">
-        <v>33051</v>
+        <v>33173</v>
       </c>
       <c r="G231">
-        <v>47593</v>
+        <v>47769</v>
       </c>
       <c r="H231">
-        <v>23356</v>
+        <v>23172</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23466</v>
+        <v>23500</v>
       </c>
       <c r="E233">
         <v>55702</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41726</v>
+        <v>41817</v>
       </c>
       <c r="E235">
         <v>111422</v>
       </c>
       <c r="F235">
-        <v>66145</v>
+        <v>66181</v>
       </c>
       <c r="G235">
-        <v>95249</v>
+        <v>95301</v>
       </c>
       <c r="H235">
-        <v>24419</v>
+        <v>24364</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>86111</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>185716</v>
       </c>
       <c r="F237">
-        <v>112873</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>162537</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>26762</v>
+        <v>0</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26698</v>
+        <v>26633</v>
       </c>
       <c r="E238">
         <v>89134</v>
       </c>
       <c r="F238">
-        <v>61560</v>
+        <v>53633</v>
       </c>
       <c r="G238">
-        <v>88646</v>
+        <v>77232</v>
       </c>
       <c r="H238">
-        <v>34862</v>
+        <v>27000</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31920</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>89134</v>
       </c>
       <c r="F239">
-        <v>53530</v>
+        <v>0</v>
       </c>
       <c r="G239">
-        <v>77083</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>21610</v>
+        <v>0</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47171</v>
+        <v>47048</v>
       </c>
       <c r="E240">
         <v>103993</v>
       </c>
       <c r="F240">
-        <v>71665</v>
+        <v>77995</v>
       </c>
       <c r="G240">
-        <v>103198</v>
+        <v>112313</v>
       </c>
       <c r="H240">
-        <v>24494</v>
+        <v>30947</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>85987</v>
       </c>
       <c r="E241">
         <v>103993</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>100987</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>145421</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,7 +11066,7 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>110771</v>
+        <v>0</v>
       </c>
       <c r="E243">
         <v>133711</v>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64428</v>
+        <v>64331</v>
       </c>
       <c r="E244">
         <v>83581</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>79877</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>115023</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>15546</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54335</v>
+        <v>54458</v>
       </c>
       <c r="E245">
         <v>83581</v>
       </c>
       <c r="F245">
-        <v>69335</v>
+        <v>0</v>
       </c>
       <c r="G245">
-        <v>99842</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75763</v>
+        <v>75668</v>
       </c>
       <c r="E246">
         <v>98440</v>
       </c>
       <c r="F246">
-        <v>90763</v>
+        <v>109168</v>
       </c>
       <c r="G246">
-        <v>130699</v>
+        <v>157202</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>33500</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>79929</v>
       </c>
       <c r="E247">
         <v>98440</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>94929</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>136698</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>18451</v>
+        <v>17919</v>
       </c>
       <c r="E248">
         <v>61274</v>
       </c>
       <c r="F248">
-        <v>42316</v>
+        <v>42304</v>
       </c>
       <c r="G248">
-        <v>60935</v>
+        <v>60918</v>
       </c>
       <c r="H248">
-        <v>23865</v>
+        <v>24385</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11048</v>
+        <v>11019</v>
       </c>
       <c r="E249">
         <v>61274</v>
       </c>
       <c r="F249">
-        <v>34316</v>
+        <v>34304</v>
       </c>
       <c r="G249">
-        <v>49415</v>
+        <v>49398</v>
       </c>
       <c r="H249">
-        <v>23268</v>
+        <v>23285</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>26108</v>
       </c>
       <c r="E250">
         <v>74275</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>49867</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>71808</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>23759</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16636</v>
+        <v>16679</v>
       </c>
       <c r="E253">
         <v>111422</v>
       </c>
       <c r="F253">
-        <v>43636</v>
+        <v>43679</v>
       </c>
       <c r="G253">
-        <v>62836</v>
+        <v>62898</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>23068</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>185716</v>
       </c>
       <c r="F255">
-        <v>50068</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>72098</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9520</v>
+        <v>9651</v>
       </c>
       <c r="E256">
         <v>53863</v>
       </c>
       <c r="F256">
-        <v>40397</v>
+        <v>35000</v>
       </c>
       <c r="G256">
-        <v>58172</v>
+        <v>50400</v>
       </c>
       <c r="H256">
-        <v>30877</v>
+        <v>25349</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14901</v>
+        <v>0</v>
       </c>
       <c r="E257">
         <v>53863</v>
       </c>
       <c r="F257">
-        <v>32967</v>
+        <v>0</v>
       </c>
       <c r="G257">
-        <v>47472</v>
+        <v>0</v>
       </c>
       <c r="H257">
-        <v>18066</v>
+        <v>0</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12338</v>
+        <v>12323</v>
       </c>
       <c r="E258">
         <v>72437</v>
       </c>
       <c r="F258">
-        <v>39338</v>
+        <v>39323</v>
       </c>
       <c r="G258">
-        <v>56647</v>
+        <v>56625</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8899</v>
+        <v>8872</v>
       </c>
       <c r="E260">
         <v>53863</v>
       </c>
       <c r="F260">
-        <v>39451</v>
+        <v>39439</v>
       </c>
       <c r="G260">
-        <v>56809</v>
+        <v>56792</v>
       </c>
       <c r="H260">
-        <v>30552</v>
+        <v>30567</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11112</v>
+        <v>11082</v>
       </c>
       <c r="E261">
         <v>53863</v>
       </c>
       <c r="F261">
-        <v>31451</v>
+        <v>31439</v>
       </c>
       <c r="G261">
-        <v>45289</v>
+        <v>45272</v>
       </c>
       <c r="H261">
-        <v>20339</v>
+        <v>20357</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12449</v>
+        <v>12052</v>
       </c>
       <c r="E262">
         <v>53863</v>
       </c>
       <c r="F262">
-        <v>39216</v>
+        <v>39223</v>
       </c>
       <c r="G262">
-        <v>56471</v>
+        <v>56481</v>
       </c>
       <c r="H262">
-        <v>26767</v>
+        <v>27171</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10523</v>
+        <v>10542</v>
       </c>
       <c r="E263">
         <v>53863</v>
       </c>
       <c r="F263">
-        <v>31216</v>
+        <v>31223</v>
       </c>
       <c r="G263">
-        <v>44951</v>
+        <v>44961</v>
       </c>
       <c r="H263">
-        <v>20693</v>
+        <v>20681</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>17990</v>
+        <v>18460</v>
       </c>
       <c r="E264">
         <v>72437</v>
       </c>
       <c r="F264">
-        <v>51936</v>
+        <v>45460</v>
       </c>
       <c r="G264">
-        <v>74788</v>
+        <v>65462</v>
       </c>
       <c r="H264">
-        <v>33946</v>
+        <v>27000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24214</v>
+        <v>0</v>
       </c>
       <c r="E265">
         <v>72437</v>
       </c>
       <c r="F265">
-        <v>43936</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>63268</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>19722</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34499</v>
+        <v>34439</v>
       </c>
       <c r="E266">
         <v>72437</v>
       </c>
       <c r="F266">
-        <v>52396</v>
+        <v>52372</v>
       </c>
       <c r="G266">
-        <v>75450</v>
+        <v>75416</v>
       </c>
       <c r="H266">
-        <v>17897</v>
+        <v>17933</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10237</v>
+        <v>10208</v>
       </c>
       <c r="E268">
         <v>27860</v>
       </c>
       <c r="F268">
-        <v>39573</v>
+        <v>25208</v>
       </c>
       <c r="G268">
-        <v>56985</v>
+        <v>36300</v>
       </c>
       <c r="H268">
-        <v>29336</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,7 +12211,7 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>16573</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>27860</v>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12163</v>
+        <v>12195</v>
       </c>
       <c r="E270">
         <v>83581</v>
       </c>
       <c r="F270">
-        <v>39163</v>
+        <v>39195</v>
       </c>
       <c r="G270">
-        <v>56395</v>
+        <v>56441</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>63489</v>
+        <v>63044</v>
       </c>
       <c r="E272">
         <v>98440</v>
       </c>
       <c r="F272">
-        <v>78489</v>
+        <v>78044</v>
       </c>
       <c r="G272">
-        <v>113024</v>
+        <v>112383</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>40421</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>98440</v>
       </c>
       <c r="F273">
-        <v>60560</v>
+        <v>0</v>
       </c>
       <c r="G273">
-        <v>87206</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>20139</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,16 +12430,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>73136</v>
+        <v>71789</v>
       </c>
       <c r="E274">
         <v>111422</v>
       </c>
       <c r="F274">
-        <v>88136</v>
+        <v>86789</v>
       </c>
       <c r="G274">
-        <v>126916</v>
+        <v>124976</v>
       </c>
       <c r="H274">
         <v>15000</v>
@@ -12519,7 +12519,7 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11208</v>
+        <v>11194</v>
       </c>
       <c r="E276">
         <v>53863</v>
@@ -12531,7 +12531,7 @@
         <v>50400</v>
       </c>
       <c r="H276">
-        <v>23792</v>
+        <v>23806</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20171</v>
+        <v>20177</v>
       </c>
       <c r="E278">
         <v>72437</v>
       </c>
       <c r="F278">
-        <v>46665</v>
+        <v>51956</v>
       </c>
       <c r="G278">
-        <v>67198</v>
+        <v>74817</v>
       </c>
       <c r="H278">
-        <v>26494</v>
+        <v>31779</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>24263</v>
       </c>
       <c r="E279">
         <v>72437</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>43956</v>
       </c>
       <c r="G279">
-        <v>0</v>
+        <v>63297</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>19693</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11781</v>
+        <v>11750</v>
       </c>
       <c r="E280">
         <v>53863</v>
@@ -12709,7 +12709,7 @@
         <v>50400</v>
       </c>
       <c r="H280">
-        <v>23219</v>
+        <v>23250</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17783</v>
+        <v>29765</v>
       </c>
       <c r="E283">
         <v>44558</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>44765</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>64462</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50196</v>
+        <v>50085</v>
       </c>
       <c r="E285">
         <v>55702</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>65085</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>93722</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>59031</v>
+        <v>58814</v>
       </c>
       <c r="E287">
         <v>66846</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>73814</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>106292</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>35231</v>
+        <v>32420</v>
       </c>
       <c r="E288">
         <v>61274</v>
       </c>
       <c r="F288">
-        <v>55958</v>
+        <v>55901</v>
       </c>
       <c r="G288">
-        <v>80580</v>
+        <v>80497</v>
       </c>
       <c r="H288">
-        <v>20727</v>
+        <v>23481</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>24007</v>
+        <v>23866</v>
       </c>
       <c r="E289">
         <v>61274</v>
       </c>
       <c r="F289">
-        <v>39500</v>
+        <v>39443</v>
       </c>
       <c r="G289">
-        <v>56880</v>
+        <v>56798</v>
       </c>
       <c r="H289">
-        <v>15493</v>
+        <v>15577</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>47235</v>
+        <v>46969</v>
       </c>
       <c r="E292">
         <v>61274</v>
       </c>
       <c r="F292">
-        <v>62268</v>
+        <v>62244</v>
       </c>
       <c r="G292">
-        <v>89666</v>
+        <v>89631</v>
       </c>
       <c r="H292">
-        <v>15033</v>
+        <v>15275</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23769</v>
+        <v>23707</v>
       </c>
       <c r="E293">
         <v>61274</v>
       </c>
       <c r="F293">
-        <v>39404</v>
+        <v>39380</v>
       </c>
       <c r="G293">
-        <v>56742</v>
+        <v>56707</v>
       </c>
       <c r="H293">
-        <v>15635</v>
+        <v>15673</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>49877</v>
+        <v>0</v>
       </c>
       <c r="E294">
         <v>68703</v>
       </c>
       <c r="F294">
-        <v>66287</v>
+        <v>0</v>
       </c>
       <c r="G294">
-        <v>95453</v>
+        <v>0</v>
       </c>
       <c r="H294">
-        <v>16410</v>
+        <v>0</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>26109</v>
+        <v>26171</v>
       </c>
       <c r="E295">
         <v>68703</v>
       </c>
       <c r="F295">
-        <v>43238</v>
+        <v>43263</v>
       </c>
       <c r="G295">
-        <v>62263</v>
+        <v>62299</v>
       </c>
       <c r="H295">
-        <v>17129</v>
+        <v>17092</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62709</v>
+        <v>62630</v>
       </c>
       <c r="E296">
         <v>78919</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>77630</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>111787</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74649</v>
+        <v>74555</v>
       </c>
       <c r="E298">
         <v>94706</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>89555</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>128959</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>69554</v>
+        <v>69451</v>
       </c>
       <c r="E300">
         <v>92849</v>
       </c>
       <c r="F300">
-        <v>88574</v>
+        <v>88735</v>
       </c>
       <c r="G300">
-        <v>127547</v>
+        <v>127778</v>
       </c>
       <c r="H300">
-        <v>19020</v>
+        <v>19284</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33734</v>
+        <v>34137</v>
       </c>
       <c r="E301">
         <v>92849</v>
       </c>
       <c r="F301">
-        <v>55705</v>
+        <v>55866</v>
       </c>
       <c r="G301">
-        <v>80215</v>
+        <v>80447</v>
       </c>
       <c r="H301">
-        <v>21971</v>
+        <v>21729</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12195</v>
+        <v>12164</v>
       </c>
       <c r="E303">
         <v>129996</v>
       </c>
       <c r="F303">
-        <v>39195</v>
+        <v>39164</v>
       </c>
       <c r="G303">
-        <v>56441</v>
+        <v>56396</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174706</v>
+        <v>174423</v>
       </c>
       <c r="E304">
         <v>167143</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>189423</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>272769</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104610</v>
+        <v>104813</v>
       </c>
       <c r="E305">
         <v>167143</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>119813</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>172531</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50196</v>
+        <v>50117</v>
       </c>
       <c r="E306">
         <v>111422</v>
       </c>
       <c r="F306">
-        <v>80176</v>
+        <v>80132</v>
       </c>
       <c r="G306">
-        <v>115453</v>
+        <v>115390</v>
       </c>
       <c r="H306">
-        <v>29980</v>
+        <v>30015</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50610</v>
+        <v>50498</v>
       </c>
       <c r="E307">
         <v>111422</v>
       </c>
       <c r="F307">
-        <v>69698</v>
+        <v>69654</v>
       </c>
       <c r="G307">
-        <v>100365</v>
+        <v>100302</v>
       </c>
       <c r="H307">
-        <v>19088</v>
+        <v>19156</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69475</v>
+        <v>69356</v>
       </c>
       <c r="E308">
         <v>129996</v>
@@ -13936,7 +13936,7 @@
         <v>140396</v>
       </c>
       <c r="H308">
-        <v>28022</v>
+        <v>28141</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77912</v>
+        <v>78069</v>
       </c>
       <c r="E309">
         <v>129996</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>93069</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>134019</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24724</v>
+        <v>24693</v>
       </c>
       <c r="E310">
         <v>55702</v>
@@ -14026,7 +14026,7 @@
         <v>60159</v>
       </c>
       <c r="H310">
-        <v>17053</v>
+        <v>17084</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>22559</v>
+        <v>26919</v>
       </c>
       <c r="E311">
         <v>55702</v>
       </c>
       <c r="F311">
-        <v>37559</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>54085</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>66036</v>
+        <v>68036</v>
       </c>
       <c r="E312">
         <v>83581</v>
       </c>
       <c r="F312">
-        <v>0</v>
+        <v>83036</v>
       </c>
       <c r="G312">
-        <v>0</v>
+        <v>119572</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63441</v>
+        <v>0</v>
       </c>
       <c r="E313">
         <v>83581</v>
       </c>
       <c r="F313">
-        <v>78441</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>112955</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>22463</v>
+        <v>22419</v>
       </c>
       <c r="E315">
         <v>38986</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>37419</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>53883</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32461</v>
+        <v>32420</v>
       </c>
       <c r="E316">
         <v>59417</v>
       </c>
       <c r="F316">
-        <v>62946</v>
+        <v>62835</v>
       </c>
       <c r="G316">
-        <v>90642</v>
+        <v>90482</v>
       </c>
       <c r="H316">
-        <v>30485</v>
+        <v>30415</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39736</v>
+        <v>39639</v>
       </c>
       <c r="E317">
         <v>59417</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>54639</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>78680</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16222</v>
+        <v>16202</v>
       </c>
       <c r="E318">
         <v>44558</v>
@@ -14378,7 +14378,7 @@
         <v>48123</v>
       </c>
       <c r="H318">
-        <v>17197</v>
+        <v>17217</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29420</v>
+        <v>29351</v>
       </c>
       <c r="E319">
         <v>44558</v>
       </c>
       <c r="F319">
-        <v>44420</v>
+        <v>44351</v>
       </c>
       <c r="G319">
-        <v>63965</v>
+        <v>63865</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>47318</v>
       </c>
       <c r="E321">
         <v>111422</v>
       </c>
       <c r="F321">
-        <v>0</v>
+        <v>68382</v>
       </c>
       <c r="G321">
-        <v>0</v>
+        <v>98470</v>
       </c>
       <c r="H321">
-        <v>0</v>
+        <v>21064</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58777</v>
+        <v>0</v>
       </c>
       <c r="E324">
         <v>74275</v>
       </c>
       <c r="F324">
-        <v>73777</v>
+        <v>0</v>
       </c>
       <c r="G324">
-        <v>106239</v>
+        <v>0</v>
       </c>
       <c r="H324">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>64141</v>
       </c>
       <c r="E325">
         <v>74275</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>79141</v>
       </c>
       <c r="G325">
-        <v>0</v>
+        <v>113963</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20951</v>
+        <v>20909</v>
       </c>
       <c r="E330">
         <v>92849</v>
       </c>
       <c r="F330">
-        <v>47951</v>
+        <v>47909</v>
       </c>
       <c r="G330">
-        <v>69049</v>
+        <v>68989</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,19 +14979,19 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43844</v>
+        <v>43773</v>
       </c>
       <c r="E332">
         <v>111422</v>
       </c>
       <c r="F332">
-        <v>78844</v>
+        <v>70773</v>
       </c>
       <c r="G332">
-        <v>113535</v>
+        <v>101913</v>
       </c>
       <c r="H332">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I332" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15024,7 +15024,7 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>83357</v>
+        <v>0</v>
       </c>
       <c r="E333">
         <v>111422</v>
@@ -15067,19 +15067,19 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32015</v>
+        <v>31943</v>
       </c>
       <c r="E334">
         <v>111422</v>
       </c>
       <c r="F334">
-        <v>67015</v>
+        <v>58943</v>
       </c>
       <c r="G334">
-        <v>96502</v>
+        <v>84878</v>
       </c>
       <c r="H334">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I334" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49432</v>
+        <v>0</v>
       </c>
       <c r="E335">
         <v>111422</v>
       </c>
       <c r="F335">
-        <v>69227</v>
+        <v>0</v>
       </c>
       <c r="G335">
-        <v>99687</v>
+        <v>0</v>
       </c>
       <c r="H335">
-        <v>19795</v>
+        <v>0</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>189559</v>
+        <v>188892</v>
       </c>
       <c r="E336">
         <v>241437</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>203892</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>293604</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>62804</v>
+        <v>54950</v>
       </c>
       <c r="E338">
         <v>129996</v>
       </c>
       <c r="F338">
-        <v>89620</v>
+        <v>81950</v>
       </c>
       <c r="G338">
-        <v>129053</v>
+        <v>118008</v>
       </c>
       <c r="H338">
-        <v>26816</v>
+        <v>27000</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>110071</v>
+        <v>0</v>
       </c>
       <c r="E341">
         <v>185716</v>
       </c>
       <c r="F341">
-        <v>125071</v>
+        <v>0</v>
       </c>
       <c r="G341">
-        <v>180102</v>
+        <v>0</v>
       </c>
       <c r="H341">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>104336</v>
       </c>
       <c r="E342">
         <v>241437</v>
       </c>
       <c r="F342">
-        <v>0</v>
+        <v>131336</v>
       </c>
       <c r="G342">
-        <v>0</v>
+        <v>189124</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>144458</v>
+        <v>0</v>
       </c>
       <c r="E343">
         <v>241437</v>
       </c>
       <c r="F343">
-        <v>159458</v>
+        <v>0</v>
       </c>
       <c r="G343">
-        <v>229620</v>
+        <v>0</v>
       </c>
       <c r="H343">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71963</v>
+        <v>72035</v>
       </c>
       <c r="E2">
         <v>74275</v>
       </c>
       <c r="F2">
-        <v>86963</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>125227</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,16 +548,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47891</v>
+        <v>47886</v>
       </c>
       <c r="E3">
         <v>74275</v>
       </c>
       <c r="F3">
-        <v>62891</v>
+        <v>62886</v>
       </c>
       <c r="G3">
-        <v>90563</v>
+        <v>90556</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94859</v>
+        <v>94975</v>
       </c>
       <c r="E4">
         <v>85420</v>
       </c>
       <c r="F4">
-        <v>109859</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>158197</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>78975</v>
+        <v>68897</v>
       </c>
       <c r="E5">
         <v>85420</v>
       </c>
       <c r="F5">
-        <v>93975</v>
+        <v>83897</v>
       </c>
       <c r="G5">
-        <v>135324</v>
+        <v>120812</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7171</v>
+        <v>7184</v>
       </c>
       <c r="E7">
         <v>55702</v>
       </c>
       <c r="F7">
-        <v>30592</v>
+        <v>30597</v>
       </c>
       <c r="G7">
-        <v>44052</v>
+        <v>44060</v>
       </c>
       <c r="H7">
-        <v>23421</v>
+        <v>23413</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39321</v>
+        <v>39363</v>
       </c>
       <c r="E8">
         <v>74275</v>
       </c>
       <c r="F8">
-        <v>55152</v>
+        <v>55169</v>
       </c>
       <c r="G8">
-        <v>79419</v>
+        <v>79443</v>
       </c>
       <c r="H8">
-        <v>15831</v>
+        <v>15806</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56270</v>
+        <v>57906</v>
       </c>
       <c r="E10">
         <v>111422</v>
       </c>
       <c r="F10">
-        <v>78648</v>
+        <v>79303</v>
       </c>
       <c r="G10">
-        <v>113253</v>
+        <v>114196</v>
       </c>
       <c r="H10">
-        <v>22378</v>
+        <v>21397</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>75253</v>
       </c>
       <c r="E11">
         <v>111422</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>90253</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>129964</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>82887</v>
+        <v>87567</v>
       </c>
       <c r="E12">
         <v>83562</v>
       </c>
       <c r="F12">
-        <v>99183</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>142824</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>16296</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13451</v>
+        <v>12696</v>
       </c>
       <c r="E13">
         <v>83562</v>
       </c>
       <c r="F13">
-        <v>40451</v>
+        <v>39696</v>
       </c>
       <c r="G13">
-        <v>58249</v>
+        <v>57162</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27221</v>
+        <v>27240</v>
       </c>
       <c r="E15">
         <v>74275</v>
       </c>
       <c r="F15">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="G15">
-        <v>66033</v>
+        <v>66043</v>
       </c>
       <c r="H15">
-        <v>18635</v>
+        <v>18623</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>49481</v>
+        <v>54528</v>
       </c>
       <c r="E21">
         <v>103993</v>
       </c>
       <c r="F21">
-        <v>66349</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>95543</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>16868</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>96488</v>
       </c>
       <c r="E23">
         <v>133711</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>111488</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>160543</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21370</v>
+        <v>21378</v>
       </c>
       <c r="E27">
         <v>64989</v>
       </c>
       <c r="F27">
-        <v>39894</v>
+        <v>39897</v>
       </c>
       <c r="G27">
-        <v>57447</v>
+        <v>57452</v>
       </c>
       <c r="H27">
-        <v>18524</v>
+        <v>18519</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>78737</v>
+        <v>78264</v>
       </c>
       <c r="E28">
         <v>129996</v>
       </c>
       <c r="F28">
-        <v>96443</v>
+        <v>96467</v>
       </c>
       <c r="G28">
-        <v>138878</v>
+        <v>138912</v>
       </c>
       <c r="H28">
-        <v>17706</v>
+        <v>18203</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38001</v>
+        <v>38025</v>
       </c>
       <c r="E29">
         <v>129996</v>
       </c>
       <c r="F29">
-        <v>65001</v>
+        <v>65025</v>
       </c>
       <c r="G29">
-        <v>93601</v>
+        <v>93636</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131636</v>
+        <v>131741</v>
       </c>
       <c r="E30">
         <v>185716</v>
       </c>
       <c r="F30">
-        <v>146636</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>211156</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72345</v>
+        <v>72322</v>
       </c>
       <c r="E31">
         <v>185716</v>
       </c>
       <c r="F31">
-        <v>99345</v>
+        <v>99322</v>
       </c>
       <c r="G31">
-        <v>143057</v>
+        <v>143024</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60563</v>
+        <v>60677</v>
       </c>
       <c r="E32">
         <v>111422</v>
       </c>
       <c r="F32">
-        <v>80878</v>
+        <v>80915</v>
       </c>
       <c r="G32">
-        <v>116464</v>
+        <v>116518</v>
       </c>
       <c r="H32">
-        <v>20315</v>
+        <v>20238</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36347</v>
+        <v>36384</v>
       </c>
       <c r="E33">
         <v>111422</v>
       </c>
       <c r="F33">
-        <v>63347</v>
+        <v>63384</v>
       </c>
       <c r="G33">
-        <v>91220</v>
+        <v>91273</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,16 +1956,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>83809</v>
+        <v>81370</v>
       </c>
       <c r="E35">
         <v>129996</v>
       </c>
       <c r="F35">
-        <v>98809</v>
+        <v>96370</v>
       </c>
       <c r="G35">
-        <v>142285</v>
+        <v>138773</v>
       </c>
       <c r="H35">
         <v>15000</v>
@@ -2000,19 +2000,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48797</v>
+        <v>48841</v>
       </c>
       <c r="E36">
         <v>129996</v>
       </c>
       <c r="F36">
-        <v>75797</v>
+        <v>75864</v>
       </c>
       <c r="G36">
-        <v>109148</v>
+        <v>109244</v>
       </c>
       <c r="H36">
-        <v>27000</v>
+        <v>27023</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2046,16 +2046,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35584</v>
+        <v>35651</v>
       </c>
       <c r="E37">
         <v>129996</v>
       </c>
       <c r="F37">
-        <v>62584</v>
+        <v>62651</v>
       </c>
       <c r="G37">
-        <v>90121</v>
+        <v>90217</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>67829</v>
+        <v>68101</v>
       </c>
       <c r="E38">
         <v>185716</v>
       </c>
       <c r="F38">
-        <v>94829</v>
+        <v>95101</v>
       </c>
       <c r="G38">
-        <v>136554</v>
+        <v>136945</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>98978</v>
+        <v>62669</v>
       </c>
       <c r="E39">
         <v>185716</v>
       </c>
       <c r="F39">
-        <v>118020</v>
+        <v>89669</v>
       </c>
       <c r="G39">
-        <v>169949</v>
+        <v>129123</v>
       </c>
       <c r="H39">
-        <v>19042</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87625</v>
+        <v>87774</v>
       </c>
       <c r="E40">
         <v>241437</v>
       </c>
       <c r="F40">
-        <v>114625</v>
+        <v>114774</v>
       </c>
       <c r="G40">
-        <v>165060</v>
+        <v>165275</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>134816</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>185716</v>
       </c>
       <c r="F41">
-        <v>149816</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>215735</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>32977</v>
+        <v>32338</v>
       </c>
       <c r="E43">
         <v>129996</v>
       </c>
       <c r="F43">
-        <v>59977</v>
+        <v>59338</v>
       </c>
       <c r="G43">
-        <v>86367</v>
+        <v>85447</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>78673</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>185716</v>
       </c>
       <c r="F45">
-        <v>105673</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>152169</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>22085</v>
+        <v>21776</v>
       </c>
       <c r="E47">
         <v>111422</v>
       </c>
       <c r="F47">
-        <v>49085</v>
+        <v>48776</v>
       </c>
       <c r="G47">
-        <v>70682</v>
+        <v>70237</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36713</v>
+        <v>36782</v>
       </c>
       <c r="E50">
         <v>64989</v>
       </c>
       <c r="F50">
-        <v>54080</v>
+        <v>54085</v>
       </c>
       <c r="G50">
-        <v>77875</v>
+        <v>77882</v>
       </c>
       <c r="H50">
-        <v>17367</v>
+        <v>17303</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>24120</v>
+        <v>24134</v>
       </c>
       <c r="E51">
         <v>64989</v>
       </c>
       <c r="F51">
-        <v>40994</v>
+        <v>40999</v>
       </c>
       <c r="G51">
-        <v>59031</v>
+        <v>59039</v>
       </c>
       <c r="H51">
-        <v>16874</v>
+        <v>16865</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>51325</v>
+        <v>54146</v>
       </c>
       <c r="E52">
         <v>77990</v>
       </c>
       <c r="F52">
-        <v>66325</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>95508</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>59116</v>
+        <v>59228</v>
       </c>
       <c r="E53">
         <v>77990</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>74228</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>106888</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44918</v>
+        <v>44970</v>
       </c>
       <c r="E54">
         <v>129996</v>
       </c>
       <c r="F54">
-        <v>79918</v>
+        <v>79970</v>
       </c>
       <c r="G54">
-        <v>115082</v>
+        <v>115157</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44727</v>
+        <v>44492</v>
       </c>
       <c r="E55">
         <v>129996</v>
       </c>
       <c r="F55">
-        <v>71727</v>
+        <v>71492</v>
       </c>
       <c r="G55">
-        <v>103287</v>
+        <v>102948</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>54044</v>
+        <v>51088</v>
       </c>
       <c r="E56">
         <v>148569</v>
       </c>
       <c r="F56">
-        <v>81044</v>
+        <v>78088</v>
       </c>
       <c r="G56">
-        <v>116703</v>
+        <v>112447</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66017</v>
+        <v>66078</v>
       </c>
       <c r="E57">
         <v>148569</v>
       </c>
       <c r="F57">
-        <v>90349</v>
+        <v>90373</v>
       </c>
       <c r="G57">
-        <v>130103</v>
+        <v>130137</v>
       </c>
       <c r="H57">
-        <v>24332</v>
+        <v>24295</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>16520</v>
+        <v>16456</v>
       </c>
       <c r="E58">
         <v>37128</v>
       </c>
       <c r="F58">
-        <v>38706</v>
+        <v>38704</v>
       </c>
       <c r="G58">
-        <v>55737</v>
+        <v>55734</v>
       </c>
       <c r="H58">
-        <v>22186</v>
+        <v>22248</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6233</v>
+        <v>6229</v>
       </c>
       <c r="E59">
         <v>37128</v>
       </c>
       <c r="F59">
-        <v>22973</v>
+        <v>22971</v>
       </c>
       <c r="G59">
-        <v>33081</v>
+        <v>33078</v>
       </c>
       <c r="H59">
-        <v>16740</v>
+        <v>16742</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24152</v>
+        <v>24182</v>
       </c>
       <c r="E60">
         <v>50130</v>
       </c>
       <c r="F60">
-        <v>48583</v>
+        <v>39182</v>
       </c>
       <c r="G60">
-        <v>69960</v>
+        <v>56422</v>
       </c>
       <c r="H60">
-        <v>24431</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25583</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>50130</v>
       </c>
       <c r="F61">
-        <v>40583</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58440</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14183</v>
+        <v>14241</v>
       </c>
       <c r="E63">
         <v>83562</v>
       </c>
       <c r="F63">
-        <v>41183</v>
+        <v>41241</v>
       </c>
       <c r="G63">
-        <v>59304</v>
+        <v>59387</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23214</v>
+        <v>23226</v>
       </c>
       <c r="E65">
         <v>125334</v>
       </c>
       <c r="F65">
-        <v>50214</v>
+        <v>50226</v>
       </c>
       <c r="G65">
-        <v>72308</v>
+        <v>72325</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25885</v>
+        <v>25918</v>
       </c>
       <c r="E66">
         <v>92849</v>
       </c>
       <c r="F66">
-        <v>60827</v>
+        <v>60835</v>
       </c>
       <c r="G66">
-        <v>87591</v>
+        <v>87602</v>
       </c>
       <c r="H66">
-        <v>34942</v>
+        <v>34917</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20781</v>
+        <v>20789</v>
       </c>
       <c r="E67">
         <v>92849</v>
       </c>
       <c r="F67">
-        <v>47781</v>
+        <v>47789</v>
       </c>
       <c r="G67">
-        <v>68805</v>
+        <v>68816</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48082</v>
+        <v>48140</v>
       </c>
       <c r="E68">
         <v>111422</v>
       </c>
       <c r="F68">
-        <v>75219</v>
+        <v>75140</v>
       </c>
       <c r="G68">
-        <v>108315</v>
+        <v>108202</v>
       </c>
       <c r="H68">
-        <v>27137</v>
+        <v>27000</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27746</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>111422</v>
       </c>
       <c r="F69">
-        <v>54746</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>78834</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110680</v>
+        <v>110793</v>
       </c>
       <c r="E70">
         <v>129996</v>
       </c>
       <c r="F70">
-        <v>125680</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>180979</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52693</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>129996</v>
       </c>
       <c r="F71">
-        <v>77775</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>111996</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>25082</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6821</v>
+        <v>6818</v>
       </c>
       <c r="E73">
         <v>27842</v>
       </c>
       <c r="F73">
-        <v>21821</v>
+        <v>21818</v>
       </c>
       <c r="G73">
-        <v>31422</v>
+        <v>31418</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,7 +3712,7 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70469</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>97492</v>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>89374</v>
+        <v>88173</v>
       </c>
       <c r="E76">
         <v>129996</v>
       </c>
       <c r="F76">
-        <v>123131</v>
+        <v>123152</v>
       </c>
       <c r="G76">
-        <v>177309</v>
+        <v>177339</v>
       </c>
       <c r="H76">
-        <v>33757</v>
+        <v>34979</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>62042</v>
+        <v>62095</v>
       </c>
       <c r="E77">
         <v>129996</v>
       </c>
       <c r="F77">
-        <v>81515</v>
+        <v>81536</v>
       </c>
       <c r="G77">
-        <v>117382</v>
+        <v>117412</v>
       </c>
       <c r="H77">
-        <v>19473</v>
+        <v>19441</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23262</v>
+        <v>23290</v>
       </c>
       <c r="E81">
         <v>92849</v>
       </c>
       <c r="F81">
-        <v>50262</v>
+        <v>50290</v>
       </c>
       <c r="G81">
-        <v>72377</v>
+        <v>72418</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87148</v>
+        <v>87217</v>
       </c>
       <c r="E83">
         <v>129996</v>
       </c>
       <c r="F83">
-        <v>102148</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>147093</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48034</v>
+        <v>47408</v>
       </c>
       <c r="E84">
         <v>74275</v>
       </c>
       <c r="F84">
-        <v>64054</v>
+        <v>62408</v>
       </c>
       <c r="G84">
-        <v>92238</v>
+        <v>89868</v>
       </c>
       <c r="H84">
-        <v>16020</v>
+        <v>15000</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>34471</v>
+        <v>34664</v>
       </c>
       <c r="E85">
         <v>74275</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>49664</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>71516</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8204</v>
+        <v>8220</v>
       </c>
       <c r="E90">
         <v>59417</v>
       </c>
       <c r="F90">
-        <v>38648</v>
+        <v>38651</v>
       </c>
       <c r="G90">
-        <v>55653</v>
+        <v>55657</v>
       </c>
       <c r="H90">
-        <v>30444</v>
+        <v>30431</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3689</v>
+        <v>3696</v>
       </c>
       <c r="E91">
         <v>59417</v>
       </c>
       <c r="F91">
-        <v>30648</v>
+        <v>30651</v>
       </c>
       <c r="G91">
-        <v>44133</v>
+        <v>44137</v>
       </c>
       <c r="H91">
-        <v>26959</v>
+        <v>26955</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9492</v>
+        <v>9510</v>
       </c>
       <c r="E93">
         <v>27842</v>
       </c>
       <c r="F93">
-        <v>24492</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35268</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61040</v>
+        <v>64055</v>
       </c>
       <c r="E96">
         <v>83562</v>
       </c>
       <c r="F96">
-        <v>78864</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>113564</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>17824</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34567</v>
+        <v>34584</v>
       </c>
       <c r="E97">
         <v>83562</v>
       </c>
       <c r="F97">
-        <v>52416</v>
+        <v>52423</v>
       </c>
       <c r="G97">
-        <v>75479</v>
+        <v>75489</v>
       </c>
       <c r="H97">
-        <v>17849</v>
+        <v>17839</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79246</v>
+        <v>79315</v>
       </c>
       <c r="E98">
         <v>96564</v>
       </c>
       <c r="F98">
-        <v>94246</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>135714</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>43900</v>
+        <v>43935</v>
       </c>
       <c r="E99">
         <v>96564</v>
       </c>
       <c r="F99">
-        <v>61220</v>
+        <v>61234</v>
       </c>
       <c r="G99">
-        <v>88157</v>
+        <v>88177</v>
       </c>
       <c r="H99">
-        <v>17320</v>
+        <v>17299</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60627</v>
+        <v>60677</v>
       </c>
       <c r="E100">
         <v>108265</v>
       </c>
       <c r="F100">
-        <v>81199</v>
+        <v>78990</v>
       </c>
       <c r="G100">
-        <v>116927</v>
+        <v>113746</v>
       </c>
       <c r="H100">
-        <v>20572</v>
+        <v>18313</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63473</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>108265</v>
       </c>
       <c r="F101">
-        <v>78473</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>113001</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>75143</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>185716</v>
       </c>
       <c r="F107">
-        <v>102143</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>147086</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6169</v>
+        <v>6181</v>
       </c>
       <c r="E109">
         <v>129996</v>
       </c>
       <c r="F109">
-        <v>33169</v>
+        <v>33181</v>
       </c>
       <c r="G109">
-        <v>47763</v>
+        <v>47781</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15089</v>
+        <v>15102</v>
       </c>
       <c r="E111">
         <v>167143</v>
       </c>
       <c r="F111">
-        <v>42089</v>
+        <v>42102</v>
       </c>
       <c r="G111">
-        <v>60608</v>
+        <v>60627</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51166</v>
+        <v>51199</v>
       </c>
       <c r="E113">
         <v>129996</v>
       </c>
       <c r="F113">
-        <v>77165</v>
+        <v>77178</v>
       </c>
       <c r="G113">
-        <v>111118</v>
+        <v>111136</v>
       </c>
       <c r="H113">
-        <v>25999</v>
+        <v>25979</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5541,19 +5541,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>168189</v>
       </c>
       <c r="E117">
         <v>185716</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>183189</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>263792</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80311</v>
+        <v>80367</v>
       </c>
       <c r="E118">
         <v>89134</v>
       </c>
       <c r="F118">
-        <v>95311</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>137248</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>49099</v>
+        <v>50227</v>
       </c>
       <c r="E119">
         <v>89134</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>65227</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>93927</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102158</v>
+        <v>102239</v>
       </c>
       <c r="E121">
         <v>118852</v>
       </c>
       <c r="F121">
-        <v>117158</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>168708</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46221</v>
+        <v>46261</v>
       </c>
       <c r="E124">
         <v>59417</v>
       </c>
       <c r="F124">
-        <v>61221</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>88158</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35584</v>
+        <v>35604</v>
       </c>
       <c r="E125">
         <v>59417</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50604</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72870</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63791</v>
+        <v>63863</v>
       </c>
       <c r="E126">
         <v>81705</v>
       </c>
       <c r="F126">
-        <v>81486</v>
+        <v>78863</v>
       </c>
       <c r="G126">
-        <v>117340</v>
+        <v>113563</v>
       </c>
       <c r="H126">
-        <v>17695</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>55857</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>81705</v>
       </c>
       <c r="F127">
-        <v>70857</v>
+        <v>0</v>
       </c>
       <c r="G127">
-        <v>102034</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>39035</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>92849</v>
       </c>
       <c r="F128">
-        <v>65553</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>94396</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>26518</v>
+        <v>0</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36968</v>
+        <v>36910</v>
       </c>
       <c r="E129">
         <v>92849</v>
       </c>
       <c r="F129">
-        <v>56998</v>
+        <v>56975</v>
       </c>
       <c r="G129">
-        <v>82077</v>
+        <v>82044</v>
       </c>
       <c r="H129">
-        <v>20030</v>
+        <v>20065</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12736</v>
+        <v>12760</v>
       </c>
       <c r="E130">
         <v>44558</v>
       </c>
       <c r="F130">
-        <v>33203</v>
+        <v>33419</v>
       </c>
       <c r="G130">
-        <v>47812</v>
+        <v>48123</v>
       </c>
       <c r="H130">
-        <v>20467</v>
+        <v>20659</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4563</v>
+        <v>5846</v>
       </c>
       <c r="E131">
         <v>44558</v>
       </c>
       <c r="F131">
-        <v>25203</v>
+        <v>25716</v>
       </c>
       <c r="G131">
-        <v>36292</v>
+        <v>37031</v>
       </c>
       <c r="H131">
-        <v>20640</v>
+        <v>19870</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27730</v>
+        <v>27750</v>
       </c>
       <c r="E132">
         <v>59417</v>
       </c>
       <c r="F132">
-        <v>43830</v>
+        <v>43838</v>
       </c>
       <c r="G132">
-        <v>63115</v>
+        <v>63127</v>
       </c>
       <c r="H132">
-        <v>16100</v>
+        <v>16088</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17331</v>
+        <v>17348</v>
       </c>
       <c r="E135">
         <v>60884</v>
       </c>
       <c r="F135">
-        <v>36677</v>
+        <v>36684</v>
       </c>
       <c r="G135">
-        <v>52815</v>
+        <v>52825</v>
       </c>
       <c r="H135">
-        <v>19346</v>
+        <v>19336</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>29049</v>
+        <v>28101</v>
       </c>
       <c r="E137">
         <v>75854</v>
       </c>
       <c r="F137">
-        <v>47203</v>
+        <v>46823</v>
       </c>
       <c r="G137">
-        <v>67972</v>
+        <v>67425</v>
       </c>
       <c r="H137">
-        <v>18154</v>
+        <v>18722</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>28350</v>
+        <v>28212</v>
       </c>
       <c r="E139">
         <v>95486</v>
       </c>
       <c r="F139">
-        <v>54580</v>
+        <v>54524</v>
       </c>
       <c r="G139">
-        <v>78595</v>
+        <v>78515</v>
       </c>
       <c r="H139">
-        <v>26230</v>
+        <v>26312</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58226</v>
+        <v>58272</v>
       </c>
       <c r="E141">
         <v>90992</v>
       </c>
       <c r="F141">
-        <v>73226</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>105445</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77656</v>
+        <v>77722</v>
       </c>
       <c r="E143">
         <v>129996</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>92722</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>133520</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87243</v>
+        <v>87312</v>
       </c>
       <c r="E145">
         <v>155999</v>
       </c>
       <c r="F145">
-        <v>102243</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>147230</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86480</v>
+        <v>88157</v>
       </c>
       <c r="E147">
         <v>90992</v>
       </c>
       <c r="F147">
-        <v>101480</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>146131</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122716</v>
+        <v>126357</v>
       </c>
       <c r="E149">
         <v>129996</v>
       </c>
       <c r="F149">
-        <v>137716</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>198311</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38335</v>
+        <v>38359</v>
       </c>
       <c r="E150">
         <v>92849</v>
       </c>
       <c r="F150">
-        <v>63116</v>
+        <v>63126</v>
       </c>
       <c r="G150">
-        <v>90887</v>
+        <v>90901</v>
       </c>
       <c r="H150">
-        <v>24781</v>
+        <v>24767</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24931</v>
+        <v>24962</v>
       </c>
       <c r="E152">
         <v>92849</v>
       </c>
       <c r="F152">
-        <v>59931</v>
+        <v>59962</v>
       </c>
       <c r="G152">
-        <v>86301</v>
+        <v>86345</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29685</v>
+        <v>29709</v>
       </c>
       <c r="E153">
         <v>92849</v>
       </c>
       <c r="F153">
-        <v>54085</v>
+        <v>54095</v>
       </c>
       <c r="G153">
-        <v>77882</v>
+        <v>77897</v>
       </c>
       <c r="H153">
-        <v>24400</v>
+        <v>24386</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48749</v>
+        <v>48794</v>
       </c>
       <c r="E154">
         <v>92849</v>
@@ -7167,7 +7167,7 @@
         <v>100277</v>
       </c>
       <c r="H154">
-        <v>20888</v>
+        <v>20843</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>75748</v>
+        <v>75604</v>
       </c>
       <c r="E155">
         <v>92849</v>
       </c>
       <c r="F155">
-        <v>90748</v>
+        <v>90604</v>
       </c>
       <c r="G155">
-        <v>130677</v>
+        <v>130470</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65524</v>
+        <v>65568</v>
       </c>
       <c r="E156">
         <v>92849</v>
       </c>
       <c r="F156">
-        <v>80524</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>115955</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>42882</v>
+        <v>42931</v>
       </c>
       <c r="E158">
         <v>63131</v>
       </c>
       <c r="F158">
-        <v>65650</v>
+        <v>65687</v>
       </c>
       <c r="G158">
-        <v>94536</v>
+        <v>94589</v>
       </c>
       <c r="H158">
-        <v>22768</v>
+        <v>22756</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42087</v>
+        <v>42119</v>
       </c>
       <c r="E159">
         <v>63131</v>
       </c>
       <c r="F159">
-        <v>57087</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>82205</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>17999</v>
+        <v>20120</v>
       </c>
       <c r="E161">
         <v>55702</v>
       </c>
       <c r="F161">
-        <v>34923</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>50289</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>16924</v>
+        <v>0</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56191</v>
+        <v>56233</v>
       </c>
       <c r="E163">
         <v>74275</v>
       </c>
       <c r="F163">
-        <v>71191</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>102515</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70866</v>
+        <v>80861</v>
       </c>
       <c r="E165">
         <v>111422</v>
       </c>
       <c r="F165">
-        <v>85866</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>123647</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54044</v>
+        <v>58782</v>
       </c>
       <c r="E166">
         <v>74275</v>
       </c>
       <c r="F166">
-        <v>69044</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>99423</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34026</v>
+        <v>34058</v>
       </c>
       <c r="E167">
         <v>74275</v>
       </c>
       <c r="F167">
-        <v>49026</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70597</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60515</v>
+        <v>60582</v>
       </c>
       <c r="E168">
         <v>74275</v>
       </c>
       <c r="F168">
-        <v>95515</v>
+        <v>75582</v>
       </c>
       <c r="G168">
-        <v>137542</v>
+        <v>108838</v>
       </c>
       <c r="H168">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74317</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>74275</v>
       </c>
       <c r="F169">
-        <v>89317</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>128616</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15153</v>
+        <v>16376</v>
       </c>
       <c r="E171">
         <v>27842</v>
       </c>
       <c r="F171">
-        <v>30153</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>43420</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30862</v>
+        <v>31318</v>
       </c>
       <c r="E173">
         <v>85420</v>
       </c>
       <c r="F173">
-        <v>51659</v>
+        <v>51841</v>
       </c>
       <c r="G173">
-        <v>74389</v>
+        <v>74651</v>
       </c>
       <c r="H173">
-        <v>20797</v>
+        <v>20523</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7282</v>
+        <v>7615</v>
       </c>
       <c r="E174">
         <v>55721</v>
       </c>
       <c r="F174">
-        <v>37856</v>
+        <v>37847</v>
       </c>
       <c r="G174">
-        <v>54513</v>
+        <v>54500</v>
       </c>
       <c r="H174">
-        <v>30574</v>
+        <v>30232</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5311</v>
+        <v>5289</v>
       </c>
       <c r="E175">
         <v>55721</v>
       </c>
       <c r="F175">
-        <v>29856</v>
+        <v>29847</v>
       </c>
       <c r="G175">
-        <v>42993</v>
+        <v>42980</v>
       </c>
       <c r="H175">
-        <v>24545</v>
+        <v>24558</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10065</v>
+        <v>10355</v>
       </c>
       <c r="E176">
         <v>74275</v>
       </c>
       <c r="F176">
-        <v>44127</v>
+        <v>44016</v>
       </c>
       <c r="G176">
-        <v>63543</v>
+        <v>63383</v>
       </c>
       <c r="H176">
-        <v>34062</v>
+        <v>33661</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>9127</v>
+        <v>9016</v>
       </c>
       <c r="E177">
         <v>74275</v>
       </c>
       <c r="F177">
-        <v>36127</v>
+        <v>36016</v>
       </c>
       <c r="G177">
-        <v>52023</v>
+        <v>51863</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21894</v>
+        <v>21920</v>
       </c>
       <c r="E179">
         <v>69651</v>
       </c>
       <c r="F179">
-        <v>41921</v>
+        <v>41932</v>
       </c>
       <c r="G179">
-        <v>60366</v>
+        <v>60382</v>
       </c>
       <c r="H179">
-        <v>20027</v>
+        <v>20012</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45951</v>
+        <v>45974</v>
       </c>
       <c r="E181">
         <v>104940</v>
       </c>
       <c r="F181">
-        <v>65307</v>
+        <v>65316</v>
       </c>
       <c r="G181">
-        <v>94042</v>
+        <v>94055</v>
       </c>
       <c r="H181">
-        <v>19356</v>
+        <v>19342</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68020</v>
+        <v>68085</v>
       </c>
       <c r="E182">
         <v>74275</v>
       </c>
       <c r="F182">
-        <v>86549</v>
+        <v>86791</v>
       </c>
       <c r="G182">
-        <v>124631</v>
+        <v>124979</v>
       </c>
       <c r="H182">
-        <v>18529</v>
+        <v>18706</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10160</v>
+        <v>10402</v>
       </c>
       <c r="E183">
         <v>74275</v>
       </c>
       <c r="F183">
-        <v>37160</v>
+        <v>37402</v>
       </c>
       <c r="G183">
-        <v>53510</v>
+        <v>53859</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60563</v>
+        <v>71972</v>
       </c>
       <c r="E184">
         <v>111422</v>
       </c>
       <c r="F184">
-        <v>80436</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>115828</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>19873</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45840</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>111422</v>
       </c>
       <c r="F185">
-        <v>67790</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>97618</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>21950</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79961</v>
+        <v>89702</v>
       </c>
       <c r="E186">
         <v>148569</v>
       </c>
       <c r="F186">
-        <v>111054</v>
+        <v>108737</v>
       </c>
       <c r="G186">
-        <v>159918</v>
+        <v>156581</v>
       </c>
       <c r="H186">
-        <v>31093</v>
+        <v>19035</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,7 +8611,7 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81567</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>148569</v>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7012</v>
+        <v>7296</v>
       </c>
       <c r="E194">
         <v>53863</v>
@@ -8920,7 +8920,7 @@
         <v>50400</v>
       </c>
       <c r="H194">
-        <v>27988</v>
+        <v>27704</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11782</v>
+        <v>11788</v>
       </c>
       <c r="E196">
         <v>83581</v>
       </c>
       <c r="F196">
-        <v>38782</v>
+        <v>38788</v>
       </c>
       <c r="G196">
-        <v>55846</v>
+        <v>55855</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51770</v>
+        <v>51820</v>
       </c>
       <c r="E198">
         <v>92849</v>
@@ -9095,7 +9095,7 @@
         <v>100277</v>
       </c>
       <c r="H198">
-        <v>17867</v>
+        <v>17817</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75080</v>
+        <v>75142</v>
       </c>
       <c r="E199">
         <v>92849</v>
       </c>
       <c r="F199">
-        <v>90080</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129715</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,16 +9172,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>90598</v>
+        <v>56838</v>
       </c>
       <c r="E200">
         <v>92849</v>
       </c>
       <c r="F200">
-        <v>105598</v>
+        <v>71838</v>
       </c>
       <c r="G200">
-        <v>152061</v>
+        <v>103447</v>
       </c>
       <c r="H200">
         <v>15000</v>
@@ -9259,19 +9259,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>17490</v>
+        <v>36814</v>
       </c>
       <c r="E202">
         <v>111422</v>
       </c>
       <c r="F202">
-        <v>44490</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>64066</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27539</v>
+        <v>27559</v>
       </c>
       <c r="E204">
         <v>92849</v>
       </c>
       <c r="F204">
-        <v>54539</v>
+        <v>54559</v>
       </c>
       <c r="G204">
-        <v>78536</v>
+        <v>78565</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101744</v>
+        <v>0</v>
       </c>
       <c r="E206">
         <v>129996</v>
       </c>
       <c r="F206">
-        <v>116744</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>168111</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>64316</v>
+        <v>64166</v>
       </c>
       <c r="E207">
         <v>129996</v>
       </c>
       <c r="F207">
-        <v>82425</v>
+        <v>82365</v>
       </c>
       <c r="G207">
-        <v>118692</v>
+        <v>118606</v>
       </c>
       <c r="H207">
-        <v>18109</v>
+        <v>18199</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144674</v>
+        <v>144947</v>
       </c>
       <c r="E208">
         <v>185716</v>
       </c>
       <c r="F208">
-        <v>179674</v>
+        <v>179947</v>
       </c>
       <c r="G208">
-        <v>258731</v>
+        <v>259124</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145310</v>
+        <v>145425</v>
       </c>
       <c r="E209">
         <v>185716</v>
       </c>
       <c r="F209">
-        <v>160310</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>230846</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187604</v>
+        <v>187958</v>
       </c>
       <c r="E210">
         <v>241437</v>
       </c>
       <c r="F210">
-        <v>202604</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>291750</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,16 +9654,16 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>187191</v>
+        <v>186747</v>
       </c>
       <c r="E211">
         <v>185716</v>
       </c>
       <c r="F211">
-        <v>202191</v>
+        <v>201747</v>
       </c>
       <c r="G211">
-        <v>291155</v>
+        <v>290516</v>
       </c>
       <c r="H211">
         <v>15000</v>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>287774</v>
+        <v>0</v>
       </c>
       <c r="E212">
         <v>371451</v>
       </c>
       <c r="F212">
-        <v>302774</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>435995</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34583</v>
+        <v>34696</v>
       </c>
       <c r="E214">
         <v>53863</v>
       </c>
       <c r="F214">
-        <v>62743</v>
+        <v>62085</v>
       </c>
       <c r="G214">
-        <v>90350</v>
+        <v>89402</v>
       </c>
       <c r="H214">
-        <v>28160</v>
+        <v>27389</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>39559</v>
+        <v>38901</v>
       </c>
       <c r="E215">
         <v>53863</v>
       </c>
       <c r="F215">
-        <v>54559</v>
+        <v>53901</v>
       </c>
       <c r="G215">
-        <v>78565</v>
+        <v>77617</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>46221</v>
+        <v>60438</v>
       </c>
       <c r="E216">
         <v>53863</v>
       </c>
       <c r="F216">
-        <v>61221</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>88158</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16488</v>
+        <v>67575</v>
       </c>
       <c r="E218">
         <v>53863</v>
       </c>
       <c r="F218">
-        <v>36833</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>53040</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>20345</v>
+        <v>0</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13165</v>
+        <v>13302</v>
       </c>
       <c r="E220">
         <v>74275</v>
       </c>
       <c r="F220">
-        <v>46543</v>
+        <v>40302</v>
       </c>
       <c r="G220">
-        <v>67022</v>
+        <v>58035</v>
       </c>
       <c r="H220">
-        <v>33378</v>
+        <v>27000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,19 +10094,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>11543</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>74275</v>
       </c>
       <c r="F221">
-        <v>38543</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>55502</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21195</v>
+        <v>21171</v>
       </c>
       <c r="E222">
         <v>111422</v>
       </c>
       <c r="F222">
-        <v>56195</v>
+        <v>48171</v>
       </c>
       <c r="G222">
-        <v>80921</v>
+        <v>69366</v>
       </c>
       <c r="H222">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>53742</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>111422</v>
       </c>
       <c r="F223">
-        <v>70951</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>102169</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>17209</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16806</v>
+        <v>16822</v>
       </c>
       <c r="E224">
         <v>129996</v>
       </c>
       <c r="F224">
-        <v>46178</v>
+        <v>47027</v>
       </c>
       <c r="G224">
-        <v>66496</v>
+        <v>67719</v>
       </c>
       <c r="H224">
-        <v>29372</v>
+        <v>30205</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11178</v>
+        <v>12027</v>
       </c>
       <c r="E225">
         <v>129996</v>
       </c>
       <c r="F225">
-        <v>38178</v>
+        <v>39027</v>
       </c>
       <c r="G225">
-        <v>54976</v>
+        <v>56199</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26537</v>
+        <v>26571</v>
       </c>
       <c r="E226">
         <v>148569</v>
       </c>
       <c r="F226">
-        <v>61537</v>
+        <v>61571</v>
       </c>
       <c r="G226">
-        <v>88613</v>
+        <v>88662</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>95972</v>
+        <v>38567</v>
       </c>
       <c r="E227">
         <v>148569</v>
       </c>
       <c r="F227">
-        <v>110972</v>
+        <v>65567</v>
       </c>
       <c r="G227">
-        <v>159800</v>
+        <v>94416</v>
       </c>
       <c r="H227">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,19 +10406,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35139</v>
+        <v>35827</v>
       </c>
       <c r="E228">
         <v>185716</v>
       </c>
       <c r="F228">
-        <v>70139</v>
+        <v>62827</v>
       </c>
       <c r="G228">
-        <v>101000</v>
+        <v>90471</v>
       </c>
       <c r="H228">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>98675</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>185716</v>
       </c>
       <c r="F229">
-        <v>117899</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>169775</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>19224</v>
+        <v>0</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16107</v>
+        <v>16089</v>
       </c>
       <c r="E230">
         <v>59417</v>
       </c>
       <c r="F230">
-        <v>42983</v>
+        <v>42940</v>
       </c>
       <c r="G230">
-        <v>61896</v>
+        <v>61834</v>
       </c>
       <c r="H230">
-        <v>26876</v>
+        <v>26851</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>10001</v>
+        <v>9893</v>
       </c>
       <c r="E231">
         <v>59417</v>
       </c>
       <c r="F231">
-        <v>33173</v>
+        <v>33130</v>
       </c>
       <c r="G231">
-        <v>47769</v>
+        <v>47707</v>
       </c>
       <c r="H231">
-        <v>23172</v>
+        <v>23237</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23500</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>55702</v>
       </c>
       <c r="F233">
-        <v>38500</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>55440</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41817</v>
+        <v>0</v>
       </c>
       <c r="E235">
         <v>111422</v>
       </c>
       <c r="F235">
-        <v>66181</v>
+        <v>0</v>
       </c>
       <c r="G235">
-        <v>95301</v>
+        <v>0</v>
       </c>
       <c r="H235">
-        <v>24364</v>
+        <v>0</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26633</v>
+        <v>26651</v>
       </c>
       <c r="E238">
         <v>89134</v>
       </c>
       <c r="F238">
-        <v>53633</v>
+        <v>53651</v>
       </c>
       <c r="G238">
-        <v>77232</v>
+        <v>77257</v>
       </c>
       <c r="H238">
         <v>27000</v>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47048</v>
+        <v>47089</v>
       </c>
       <c r="E240">
         <v>103993</v>
       </c>
       <c r="F240">
-        <v>77995</v>
+        <v>71633</v>
       </c>
       <c r="G240">
-        <v>112313</v>
+        <v>103152</v>
       </c>
       <c r="H240">
-        <v>30947</v>
+        <v>24544</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>85987</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>103993</v>
       </c>
       <c r="F241">
-        <v>100987</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>145421</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64331</v>
+        <v>64389</v>
       </c>
       <c r="E244">
         <v>83581</v>
       </c>
       <c r="F244">
-        <v>79877</v>
+        <v>79389</v>
       </c>
       <c r="G244">
-        <v>115023</v>
+        <v>114320</v>
       </c>
       <c r="H244">
-        <v>15546</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,7 +11155,7 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>54458</v>
+        <v>0</v>
       </c>
       <c r="E245">
         <v>83581</v>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75668</v>
+        <v>76432</v>
       </c>
       <c r="E246">
         <v>98440</v>
       </c>
       <c r="F246">
-        <v>109168</v>
+        <v>91432</v>
       </c>
       <c r="G246">
-        <v>157202</v>
+        <v>131662</v>
       </c>
       <c r="H246">
-        <v>33500</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>79929</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>98440</v>
       </c>
       <c r="F247">
-        <v>94929</v>
+        <v>0</v>
       </c>
       <c r="G247">
-        <v>136698</v>
+        <v>0</v>
       </c>
       <c r="H247">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17919</v>
+        <v>17937</v>
       </c>
       <c r="E248">
         <v>61274</v>
       </c>
       <c r="F248">
-        <v>42304</v>
+        <v>42574</v>
       </c>
       <c r="G248">
-        <v>60918</v>
+        <v>61307</v>
       </c>
       <c r="H248">
-        <v>24385</v>
+        <v>24637</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11019</v>
+        <v>11693</v>
       </c>
       <c r="E249">
         <v>61274</v>
       </c>
       <c r="F249">
-        <v>34304</v>
+        <v>34574</v>
       </c>
       <c r="G249">
-        <v>49398</v>
+        <v>49787</v>
       </c>
       <c r="H249">
-        <v>23285</v>
+        <v>22881</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>26108</v>
+        <v>26157</v>
       </c>
       <c r="E250">
         <v>74275</v>
       </c>
       <c r="F250">
-        <v>49867</v>
+        <v>49886</v>
       </c>
       <c r="G250">
-        <v>71808</v>
+        <v>71836</v>
       </c>
       <c r="H250">
-        <v>23759</v>
+        <v>23729</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16679</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>111422</v>
       </c>
       <c r="F253">
-        <v>43679</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>62898</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9651</v>
+        <v>9670</v>
       </c>
       <c r="E256">
         <v>53863</v>
@@ -11651,7 +11651,7 @@
         <v>50400</v>
       </c>
       <c r="H256">
-        <v>25349</v>
+        <v>25330</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12323</v>
+        <v>12266</v>
       </c>
       <c r="E258">
         <v>72437</v>
       </c>
       <c r="F258">
-        <v>39323</v>
+        <v>39266</v>
       </c>
       <c r="G258">
-        <v>56625</v>
+        <v>56543</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8872</v>
+        <v>8889</v>
       </c>
       <c r="E260">
         <v>53863</v>
       </c>
       <c r="F260">
-        <v>39439</v>
+        <v>39429</v>
       </c>
       <c r="G260">
-        <v>56792</v>
+        <v>56778</v>
       </c>
       <c r="H260">
-        <v>30567</v>
+        <v>30540</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11082</v>
+        <v>11055</v>
       </c>
       <c r="E261">
         <v>53863</v>
       </c>
       <c r="F261">
-        <v>31439</v>
+        <v>31429</v>
       </c>
       <c r="G261">
-        <v>45272</v>
+        <v>45258</v>
       </c>
       <c r="H261">
-        <v>20357</v>
+        <v>20374</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12052</v>
+        <v>11868</v>
       </c>
       <c r="E262">
         <v>53863</v>
       </c>
       <c r="F262">
-        <v>39223</v>
+        <v>35000</v>
       </c>
       <c r="G262">
-        <v>56481</v>
+        <v>50400</v>
       </c>
       <c r="H262">
-        <v>27171</v>
+        <v>23132</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10542</v>
+        <v>0</v>
       </c>
       <c r="E263">
         <v>53863</v>
       </c>
       <c r="F263">
-        <v>31223</v>
+        <v>0</v>
       </c>
       <c r="G263">
-        <v>44961</v>
+        <v>0</v>
       </c>
       <c r="H263">
-        <v>20681</v>
+        <v>0</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,16 +11991,16 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18460</v>
+        <v>18176</v>
       </c>
       <c r="E264">
         <v>72437</v>
       </c>
       <c r="F264">
-        <v>45460</v>
+        <v>45176</v>
       </c>
       <c r="G264">
-        <v>65462</v>
+        <v>65053</v>
       </c>
       <c r="H264">
         <v>27000</v>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34439</v>
+        <v>34473</v>
       </c>
       <c r="E266">
         <v>72437</v>
       </c>
       <c r="F266">
-        <v>52372</v>
+        <v>52386</v>
       </c>
       <c r="G266">
-        <v>75416</v>
+        <v>75436</v>
       </c>
       <c r="H266">
-        <v>17933</v>
+        <v>17913</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10208</v>
+        <v>10259</v>
       </c>
       <c r="E268">
         <v>27860</v>
       </c>
       <c r="F268">
-        <v>25208</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>36300</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12195</v>
+        <v>12123</v>
       </c>
       <c r="E270">
         <v>83581</v>
       </c>
       <c r="F270">
-        <v>39195</v>
+        <v>39123</v>
       </c>
       <c r="G270">
-        <v>56441</v>
+        <v>56337</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>63044</v>
+        <v>62987</v>
       </c>
       <c r="E272">
         <v>98440</v>
       </c>
       <c r="F272">
-        <v>78044</v>
+        <v>77987</v>
       </c>
       <c r="G272">
-        <v>112383</v>
+        <v>112301</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12430,16 +12430,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>71789</v>
+        <v>71701</v>
       </c>
       <c r="E274">
         <v>111422</v>
       </c>
       <c r="F274">
-        <v>86789</v>
+        <v>86701</v>
       </c>
       <c r="G274">
-        <v>124976</v>
+        <v>124849</v>
       </c>
       <c r="H274">
         <v>15000</v>
@@ -12519,7 +12519,7 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11194</v>
+        <v>11199</v>
       </c>
       <c r="E276">
         <v>53863</v>
@@ -12531,7 +12531,7 @@
         <v>50400</v>
       </c>
       <c r="H276">
-        <v>23806</v>
+        <v>23801</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20177</v>
+        <v>20120</v>
       </c>
       <c r="E278">
         <v>72437</v>
       </c>
       <c r="F278">
-        <v>51956</v>
+        <v>46645</v>
       </c>
       <c r="G278">
-        <v>74817</v>
+        <v>67169</v>
       </c>
       <c r="H278">
-        <v>31779</v>
+        <v>26525</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24263</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>72437</v>
       </c>
       <c r="F279">
-        <v>43956</v>
+        <v>0</v>
       </c>
       <c r="G279">
-        <v>63297</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>19693</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11750</v>
+        <v>11772</v>
       </c>
       <c r="E280">
         <v>53863</v>
@@ -12709,7 +12709,7 @@
         <v>50400</v>
       </c>
       <c r="H280">
-        <v>23250</v>
+        <v>23228</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,16 +12826,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>29765</v>
+        <v>17762</v>
       </c>
       <c r="E283">
         <v>44558</v>
       </c>
       <c r="F283">
-        <v>44765</v>
+        <v>32762</v>
       </c>
       <c r="G283">
-        <v>64462</v>
+        <v>47177</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12912,16 +12912,16 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50085</v>
+        <v>50052</v>
       </c>
       <c r="E285">
         <v>55702</v>
       </c>
       <c r="F285">
-        <v>65085</v>
+        <v>65052</v>
       </c>
       <c r="G285">
-        <v>93722</v>
+        <v>93675</v>
       </c>
       <c r="H285">
         <v>15000</v>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58814</v>
+        <v>58861</v>
       </c>
       <c r="E287">
         <v>66846</v>
       </c>
       <c r="F287">
-        <v>73814</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>106292</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>32420</v>
+        <v>40797</v>
       </c>
       <c r="E288">
         <v>61274</v>
       </c>
       <c r="F288">
-        <v>55901</v>
+        <v>55906</v>
       </c>
       <c r="G288">
-        <v>80497</v>
+        <v>80505</v>
       </c>
       <c r="H288">
-        <v>23481</v>
+        <v>15109</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23866</v>
+        <v>23879</v>
       </c>
       <c r="E289">
         <v>61274</v>
       </c>
       <c r="F289">
-        <v>39443</v>
+        <v>39448</v>
       </c>
       <c r="G289">
-        <v>56798</v>
+        <v>56805</v>
       </c>
       <c r="H289">
-        <v>15577</v>
+        <v>15569</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>46969</v>
+        <v>47009</v>
       </c>
       <c r="E292">
         <v>61274</v>
       </c>
       <c r="F292">
-        <v>62244</v>
+        <v>62255</v>
       </c>
       <c r="G292">
-        <v>89631</v>
+        <v>89647</v>
       </c>
       <c r="H292">
-        <v>15275</v>
+        <v>15246</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23707</v>
+        <v>23736</v>
       </c>
       <c r="E293">
         <v>61274</v>
       </c>
       <c r="F293">
-        <v>39380</v>
+        <v>39391</v>
       </c>
       <c r="G293">
-        <v>56707</v>
+        <v>56723</v>
       </c>
       <c r="H293">
-        <v>15673</v>
+        <v>15655</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>26171</v>
+        <v>0</v>
       </c>
       <c r="E295">
         <v>68703</v>
       </c>
       <c r="F295">
-        <v>43263</v>
+        <v>0</v>
       </c>
       <c r="G295">
-        <v>62299</v>
+        <v>0</v>
       </c>
       <c r="H295">
-        <v>17092</v>
+        <v>0</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62630</v>
+        <v>77738</v>
       </c>
       <c r="E296">
         <v>78919</v>
       </c>
       <c r="F296">
-        <v>77630</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>111787</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74555</v>
+        <v>92553</v>
       </c>
       <c r="E298">
         <v>94706</v>
       </c>
       <c r="F298">
-        <v>89555</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>128959</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>69451</v>
+        <v>69503</v>
       </c>
       <c r="E300">
         <v>92849</v>
       </c>
       <c r="F300">
-        <v>88735</v>
+        <v>88614</v>
       </c>
       <c r="G300">
-        <v>127778</v>
+        <v>127604</v>
       </c>
       <c r="H300">
-        <v>19284</v>
+        <v>19111</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>34137</v>
+        <v>33835</v>
       </c>
       <c r="E301">
         <v>92849</v>
       </c>
       <c r="F301">
-        <v>55866</v>
+        <v>55745</v>
       </c>
       <c r="G301">
-        <v>80447</v>
+        <v>80273</v>
       </c>
       <c r="H301">
-        <v>21729</v>
+        <v>21910</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12164</v>
+        <v>12171</v>
       </c>
       <c r="E303">
         <v>129996</v>
       </c>
       <c r="F303">
-        <v>39164</v>
+        <v>39171</v>
       </c>
       <c r="G303">
-        <v>56396</v>
+        <v>56406</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174423</v>
+        <v>189280</v>
       </c>
       <c r="E304">
         <v>167143</v>
       </c>
       <c r="F304">
-        <v>189423</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>272769</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104813</v>
+        <v>0</v>
       </c>
       <c r="E305">
         <v>167143</v>
       </c>
       <c r="F305">
-        <v>119813</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>172531</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50117</v>
+        <v>50164</v>
       </c>
       <c r="E306">
         <v>111422</v>
       </c>
       <c r="F306">
-        <v>80132</v>
+        <v>80144</v>
       </c>
       <c r="G306">
-        <v>115390</v>
+        <v>115407</v>
       </c>
       <c r="H306">
-        <v>30015</v>
+        <v>29980</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50498</v>
+        <v>50530</v>
       </c>
       <c r="E307">
         <v>111422</v>
       </c>
       <c r="F307">
-        <v>69654</v>
+        <v>69666</v>
       </c>
       <c r="G307">
-        <v>100302</v>
+        <v>100319</v>
       </c>
       <c r="H307">
-        <v>19156</v>
+        <v>19136</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69356</v>
+        <v>69407</v>
       </c>
       <c r="E308">
         <v>129996</v>
@@ -13936,7 +13936,7 @@
         <v>140396</v>
       </c>
       <c r="H308">
-        <v>28141</v>
+        <v>28090</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>78069</v>
+        <v>105807</v>
       </c>
       <c r="E309">
         <v>129996</v>
       </c>
       <c r="F309">
-        <v>93069</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>134019</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24693</v>
+        <v>24596</v>
       </c>
       <c r="E310">
         <v>55702</v>
       </c>
       <c r="F310">
-        <v>41777</v>
+        <v>40905</v>
       </c>
       <c r="G310">
-        <v>60159</v>
+        <v>58903</v>
       </c>
       <c r="H310">
-        <v>17084</v>
+        <v>16309</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,7 +14058,7 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>26919</v>
+        <v>0</v>
       </c>
       <c r="E311">
         <v>55702</v>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>68036</v>
+        <v>68180</v>
       </c>
       <c r="E312">
         <v>83581</v>
       </c>
       <c r="F312">
-        <v>83036</v>
+        <v>0</v>
       </c>
       <c r="G312">
-        <v>119572</v>
+        <v>0</v>
       </c>
       <c r="H312">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,16 +14232,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>22419</v>
+        <v>20868</v>
       </c>
       <c r="E315">
         <v>38986</v>
       </c>
       <c r="F315">
-        <v>37419</v>
+        <v>35868</v>
       </c>
       <c r="G315">
-        <v>53883</v>
+        <v>51650</v>
       </c>
       <c r="H315">
         <v>15000</v>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32420</v>
+        <v>33501</v>
       </c>
       <c r="E316">
         <v>59417</v>
       </c>
       <c r="F316">
-        <v>62835</v>
+        <v>62884</v>
       </c>
       <c r="G316">
-        <v>90482</v>
+        <v>90553</v>
       </c>
       <c r="H316">
-        <v>30415</v>
+        <v>29383</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39639</v>
+        <v>39682</v>
       </c>
       <c r="E317">
         <v>59417</v>
       </c>
       <c r="F317">
-        <v>54639</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>78680</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16202</v>
+        <v>16233</v>
       </c>
       <c r="E318">
         <v>44558</v>
@@ -14378,7 +14378,7 @@
         <v>48123</v>
       </c>
       <c r="H318">
-        <v>17217</v>
+        <v>17186</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29351</v>
+        <v>29327</v>
       </c>
       <c r="E319">
         <v>44558</v>
       </c>
       <c r="F319">
-        <v>44351</v>
+        <v>44327</v>
       </c>
       <c r="G319">
-        <v>63865</v>
+        <v>63831</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>47318</v>
+        <v>0</v>
       </c>
       <c r="E321">
         <v>111422</v>
       </c>
       <c r="F321">
-        <v>68382</v>
+        <v>0</v>
       </c>
       <c r="G321">
-        <v>98470</v>
+        <v>0</v>
       </c>
       <c r="H321">
-        <v>21064</v>
+        <v>0</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>64141</v>
+        <v>0</v>
       </c>
       <c r="E325">
         <v>74275</v>
       </c>
       <c r="F325">
-        <v>79141</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>113963</v>
+        <v>0</v>
       </c>
       <c r="H325">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20909</v>
+        <v>20916</v>
       </c>
       <c r="E330">
         <v>92849</v>
       </c>
       <c r="F330">
-        <v>47909</v>
+        <v>47916</v>
       </c>
       <c r="G330">
-        <v>68989</v>
+        <v>68999</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43773</v>
+        <v>43808</v>
       </c>
       <c r="E332">
         <v>111422</v>
       </c>
       <c r="F332">
-        <v>70773</v>
+        <v>70808</v>
       </c>
       <c r="G332">
-        <v>101913</v>
+        <v>101964</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>31943</v>
+        <v>31079</v>
       </c>
       <c r="E334">
         <v>111422</v>
       </c>
       <c r="F334">
-        <v>58943</v>
+        <v>58079</v>
       </c>
       <c r="G334">
-        <v>84878</v>
+        <v>83634</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188892</v>
+        <v>189137</v>
       </c>
       <c r="E336">
         <v>241437</v>
       </c>
       <c r="F336">
-        <v>203892</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>293604</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,16 +15243,16 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>54950</v>
+        <v>59722</v>
       </c>
       <c r="E338">
         <v>129996</v>
       </c>
       <c r="F338">
-        <v>81950</v>
+        <v>86722</v>
       </c>
       <c r="G338">
-        <v>118008</v>
+        <v>124880</v>
       </c>
       <c r="H338">
         <v>27000</v>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>104336</v>
+        <v>0</v>
       </c>
       <c r="E342">
         <v>241437</v>
       </c>
       <c r="F342">
-        <v>131336</v>
+        <v>0</v>
       </c>
       <c r="G342">
-        <v>189124</v>
+        <v>0</v>
       </c>
       <c r="H342">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72035</v>
+        <v>71773</v>
       </c>
       <c r="E2">
         <v>74275</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86773</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>124953</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,16 +548,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47886</v>
+        <v>47716</v>
       </c>
       <c r="E3">
         <v>74275</v>
       </c>
       <c r="F3">
-        <v>62886</v>
+        <v>62716</v>
       </c>
       <c r="G3">
-        <v>90556</v>
+        <v>90311</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94975</v>
+        <v>94669</v>
       </c>
       <c r="E4">
         <v>85420</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>109669</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>157923</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>68897</v>
+        <v>78387</v>
       </c>
       <c r="E5">
         <v>85420</v>
       </c>
       <c r="F5">
-        <v>83897</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>120812</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7184</v>
+        <v>7155</v>
       </c>
       <c r="E7">
         <v>55702</v>
       </c>
       <c r="F7">
-        <v>30597</v>
+        <v>30586</v>
       </c>
       <c r="G7">
-        <v>44060</v>
+        <v>44044</v>
       </c>
       <c r="H7">
-        <v>23413</v>
+        <v>23431</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39363</v>
+        <v>39241</v>
       </c>
       <c r="E8">
         <v>74275</v>
       </c>
       <c r="F8">
-        <v>55169</v>
+        <v>55706</v>
       </c>
       <c r="G8">
-        <v>79443</v>
+        <v>80217</v>
       </c>
       <c r="H8">
-        <v>15806</v>
+        <v>16465</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>39543</v>
       </c>
       <c r="E9">
         <v>74275</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>54543</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>78542</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>57906</v>
+        <v>56270</v>
       </c>
       <c r="E10">
         <v>111422</v>
       </c>
       <c r="F10">
-        <v>79303</v>
+        <v>78648</v>
       </c>
       <c r="G10">
-        <v>114196</v>
+        <v>113253</v>
       </c>
       <c r="H10">
-        <v>21397</v>
+        <v>22378</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,16 +903,16 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>75253</v>
+        <v>74873</v>
       </c>
       <c r="E11">
         <v>111422</v>
       </c>
       <c r="F11">
-        <v>90253</v>
+        <v>89873</v>
       </c>
       <c r="G11">
-        <v>129964</v>
+        <v>129417</v>
       </c>
       <c r="H11">
         <v>15000</v>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>87567</v>
+        <v>86544</v>
       </c>
       <c r="E12">
         <v>83562</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>101544</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>146223</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>12696</v>
+        <v>12641</v>
       </c>
       <c r="E13">
         <v>83562</v>
       </c>
       <c r="F13">
-        <v>39696</v>
+        <v>39641</v>
       </c>
       <c r="G13">
-        <v>57162</v>
+        <v>57083</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27240</v>
+        <v>27157</v>
       </c>
       <c r="E15">
         <v>74275</v>
       </c>
       <c r="F15">
-        <v>45863</v>
+        <v>45830</v>
       </c>
       <c r="G15">
-        <v>66043</v>
+        <v>65995</v>
       </c>
       <c r="H15">
-        <v>18623</v>
+        <v>18673</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54528</v>
+        <v>49322</v>
       </c>
       <c r="E21">
         <v>103993</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>66286</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>95452</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>16964</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,16 +1425,16 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96488</v>
+        <v>96004</v>
       </c>
       <c r="E23">
         <v>133711</v>
       </c>
       <c r="F23">
-        <v>111488</v>
+        <v>111004</v>
       </c>
       <c r="G23">
-        <v>160543</v>
+        <v>159846</v>
       </c>
       <c r="H23">
         <v>15000</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21378</v>
+        <v>21735</v>
       </c>
       <c r="E27">
         <v>64989</v>
       </c>
       <c r="F27">
-        <v>39897</v>
+        <v>40040</v>
       </c>
       <c r="G27">
-        <v>57452</v>
+        <v>57658</v>
       </c>
       <c r="H27">
-        <v>18519</v>
+        <v>18305</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>78264</v>
+        <v>77767</v>
       </c>
       <c r="E28">
         <v>129996</v>
       </c>
       <c r="F28">
-        <v>96467</v>
+        <v>96332</v>
       </c>
       <c r="G28">
-        <v>138912</v>
+        <v>138718</v>
       </c>
       <c r="H28">
-        <v>18203</v>
+        <v>18565</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38025</v>
+        <v>37890</v>
       </c>
       <c r="E29">
         <v>129996</v>
       </c>
       <c r="F29">
-        <v>65025</v>
+        <v>64890</v>
       </c>
       <c r="G29">
-        <v>93636</v>
+        <v>93442</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131741</v>
+        <v>125769</v>
       </c>
       <c r="E30">
         <v>185716</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>140769</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>202707</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72322</v>
+        <v>69404</v>
       </c>
       <c r="E31">
         <v>185716</v>
       </c>
       <c r="F31">
-        <v>99322</v>
+        <v>96404</v>
       </c>
       <c r="G31">
-        <v>143024</v>
+        <v>138822</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60677</v>
+        <v>60563</v>
       </c>
       <c r="E32">
         <v>111422</v>
       </c>
       <c r="F32">
-        <v>80915</v>
+        <v>80783</v>
       </c>
       <c r="G32">
-        <v>116518</v>
+        <v>116328</v>
       </c>
       <c r="H32">
-        <v>20238</v>
+        <v>20220</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36384</v>
+        <v>36252</v>
       </c>
       <c r="E33">
         <v>111422</v>
       </c>
       <c r="F33">
-        <v>63384</v>
+        <v>63252</v>
       </c>
       <c r="G33">
-        <v>91273</v>
+        <v>91083</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,16 +1956,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>81370</v>
+        <v>80963</v>
       </c>
       <c r="E35">
         <v>129996</v>
       </c>
       <c r="F35">
-        <v>96370</v>
+        <v>95963</v>
       </c>
       <c r="G35">
-        <v>138773</v>
+        <v>138187</v>
       </c>
       <c r="H35">
         <v>15000</v>
@@ -2000,19 +2000,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48841</v>
+        <v>48813</v>
       </c>
       <c r="E36">
         <v>129996</v>
       </c>
       <c r="F36">
-        <v>75864</v>
+        <v>75813</v>
       </c>
       <c r="G36">
-        <v>109244</v>
+        <v>109171</v>
       </c>
       <c r="H36">
-        <v>27023</v>
+        <v>27000</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2046,16 +2046,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35651</v>
+        <v>35473</v>
       </c>
       <c r="E37">
         <v>129996</v>
       </c>
       <c r="F37">
-        <v>62651</v>
+        <v>62473</v>
       </c>
       <c r="G37">
-        <v>90217</v>
+        <v>89961</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>68101</v>
+        <v>68036</v>
       </c>
       <c r="E38">
         <v>185716</v>
       </c>
       <c r="F38">
-        <v>95101</v>
+        <v>95036</v>
       </c>
       <c r="G38">
-        <v>136945</v>
+        <v>136852</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,16 +2134,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>62669</v>
+        <v>63059</v>
       </c>
       <c r="E39">
         <v>185716</v>
       </c>
       <c r="F39">
-        <v>89669</v>
+        <v>90059</v>
       </c>
       <c r="G39">
-        <v>129123</v>
+        <v>129685</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87774</v>
+        <v>87863</v>
       </c>
       <c r="E40">
         <v>241437</v>
       </c>
       <c r="F40">
-        <v>114774</v>
+        <v>114863</v>
       </c>
       <c r="G40">
-        <v>165275</v>
+        <v>165403</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>88499</v>
       </c>
       <c r="E41">
         <v>185716</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>113829</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>163914</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>25330</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>32338</v>
+        <v>31593</v>
       </c>
       <c r="E43">
         <v>129996</v>
       </c>
       <c r="F43">
-        <v>59338</v>
+        <v>58593</v>
       </c>
       <c r="G43">
-        <v>85447</v>
+        <v>84374</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>78164</v>
       </c>
       <c r="E45">
         <v>185716</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>105164</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>151436</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>21776</v>
+        <v>21370</v>
       </c>
       <c r="E47">
         <v>111422</v>
       </c>
       <c r="F47">
-        <v>48776</v>
+        <v>48370</v>
       </c>
       <c r="G47">
-        <v>70237</v>
+        <v>69653</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36782</v>
+        <v>36713</v>
       </c>
       <c r="E50">
         <v>64989</v>
       </c>
       <c r="F50">
-        <v>54085</v>
+        <v>61142</v>
       </c>
       <c r="G50">
-        <v>77882</v>
+        <v>88044</v>
       </c>
       <c r="H50">
-        <v>17303</v>
+        <v>24429</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>24134</v>
+        <v>33056</v>
       </c>
       <c r="E51">
         <v>64989</v>
       </c>
       <c r="F51">
-        <v>40999</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>59039</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>16865</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54146</v>
+        <v>51166</v>
       </c>
       <c r="E52">
         <v>77990</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>66166</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>95279</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,16 +2744,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>59228</v>
+        <v>58925</v>
       </c>
       <c r="E53">
         <v>77990</v>
       </c>
       <c r="F53">
-        <v>74228</v>
+        <v>73925</v>
       </c>
       <c r="G53">
-        <v>106888</v>
+        <v>106452</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44970</v>
+        <v>44838</v>
       </c>
       <c r="E54">
         <v>129996</v>
       </c>
       <c r="F54">
-        <v>79970</v>
+        <v>79838</v>
       </c>
       <c r="G54">
-        <v>115157</v>
+        <v>114967</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44492</v>
+        <v>44234</v>
       </c>
       <c r="E55">
         <v>129996</v>
       </c>
       <c r="F55">
-        <v>71492</v>
+        <v>71234</v>
       </c>
       <c r="G55">
-        <v>102948</v>
+        <v>102577</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>51088</v>
+        <v>50928</v>
       </c>
       <c r="E56">
         <v>148569</v>
       </c>
       <c r="F56">
-        <v>78088</v>
+        <v>77928</v>
       </c>
       <c r="G56">
-        <v>112447</v>
+        <v>112216</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66078</v>
+        <v>65842</v>
       </c>
       <c r="E57">
         <v>148569</v>
       </c>
       <c r="F57">
-        <v>90373</v>
+        <v>90279</v>
       </c>
       <c r="G57">
-        <v>130137</v>
+        <v>130002</v>
       </c>
       <c r="H57">
-        <v>24295</v>
+        <v>24437</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>16456</v>
+        <v>16202</v>
       </c>
       <c r="E58">
         <v>37128</v>
       </c>
       <c r="F58">
-        <v>38704</v>
+        <v>38700</v>
       </c>
       <c r="G58">
-        <v>55734</v>
+        <v>55728</v>
       </c>
       <c r="H58">
-        <v>22248</v>
+        <v>22498</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6229</v>
+        <v>6217</v>
       </c>
       <c r="E59">
         <v>37128</v>
       </c>
       <c r="F59">
-        <v>22971</v>
+        <v>22967</v>
       </c>
       <c r="G59">
-        <v>33078</v>
+        <v>33072</v>
       </c>
       <c r="H59">
-        <v>16742</v>
+        <v>16750</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24182</v>
+        <v>24104</v>
       </c>
       <c r="E60">
         <v>50130</v>
       </c>
       <c r="F60">
-        <v>39182</v>
+        <v>48504</v>
       </c>
       <c r="G60">
-        <v>56422</v>
+        <v>69846</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>24400</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>25504</v>
       </c>
       <c r="E61">
         <v>50130</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40504</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58326</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14241</v>
+        <v>14056</v>
       </c>
       <c r="E63">
         <v>83562</v>
       </c>
       <c r="F63">
-        <v>41241</v>
+        <v>41056</v>
       </c>
       <c r="G63">
-        <v>59387</v>
+        <v>59121</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23226</v>
+        <v>23150</v>
       </c>
       <c r="E65">
         <v>125334</v>
       </c>
       <c r="F65">
-        <v>50226</v>
+        <v>50150</v>
       </c>
       <c r="G65">
-        <v>72325</v>
+        <v>72216</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25918</v>
+        <v>25838</v>
       </c>
       <c r="E66">
         <v>92849</v>
       </c>
       <c r="F66">
-        <v>60835</v>
+        <v>60764</v>
       </c>
       <c r="G66">
-        <v>87602</v>
+        <v>87500</v>
       </c>
       <c r="H66">
-        <v>34917</v>
+        <v>34926</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20789</v>
+        <v>20718</v>
       </c>
       <c r="E67">
         <v>92849</v>
       </c>
       <c r="F67">
-        <v>47789</v>
+        <v>47718</v>
       </c>
       <c r="G67">
-        <v>68816</v>
+        <v>68714</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48140</v>
+        <v>47986</v>
       </c>
       <c r="E68">
         <v>111422</v>
       </c>
       <c r="F68">
-        <v>75140</v>
+        <v>74986</v>
       </c>
       <c r="G68">
-        <v>108202</v>
+        <v>107980</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>27666</v>
       </c>
       <c r="E69">
         <v>111422</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>54666</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>78719</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110793</v>
+        <v>110457</v>
       </c>
       <c r="E70">
         <v>129996</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>125457</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>180658</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>52534</v>
       </c>
       <c r="E71">
         <v>129996</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>77712</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>111905</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>25178</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6818</v>
+        <v>6805</v>
       </c>
       <c r="E73">
         <v>27842</v>
       </c>
       <c r="F73">
-        <v>21818</v>
+        <v>21805</v>
       </c>
       <c r="G73">
-        <v>31418</v>
+        <v>31399</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>70246</v>
       </c>
       <c r="E75">
         <v>97492</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85246</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>122754</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88173</v>
+        <v>87863</v>
       </c>
       <c r="E76">
         <v>129996</v>
       </c>
       <c r="F76">
-        <v>123152</v>
+        <v>122863</v>
       </c>
       <c r="G76">
-        <v>177339</v>
+        <v>176923</v>
       </c>
       <c r="H76">
-        <v>34979</v>
+        <v>35000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>62095</v>
+        <v>61867</v>
       </c>
       <c r="E77">
         <v>129996</v>
       </c>
       <c r="F77">
-        <v>81536</v>
+        <v>81445</v>
       </c>
       <c r="G77">
-        <v>117412</v>
+        <v>117281</v>
       </c>
       <c r="H77">
-        <v>19441</v>
+        <v>19578</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23290</v>
+        <v>23198</v>
       </c>
       <c r="E81">
         <v>92849</v>
       </c>
       <c r="F81">
-        <v>50290</v>
+        <v>50198</v>
       </c>
       <c r="G81">
-        <v>72418</v>
+        <v>72285</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87217</v>
+        <v>86909</v>
       </c>
       <c r="E83">
         <v>129996</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>101909</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>146749</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47408</v>
+        <v>47048</v>
       </c>
       <c r="E84">
         <v>74275</v>
       </c>
       <c r="F84">
-        <v>62408</v>
+        <v>62740</v>
       </c>
       <c r="G84">
-        <v>89868</v>
+        <v>90346</v>
       </c>
       <c r="H84">
-        <v>15000</v>
+        <v>15692</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>34664</v>
+        <v>34996</v>
       </c>
       <c r="E85">
         <v>74275</v>
       </c>
       <c r="F85">
-        <v>49664</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>71516</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8220</v>
+        <v>8189</v>
       </c>
       <c r="E90">
         <v>59417</v>
       </c>
       <c r="F90">
-        <v>38651</v>
+        <v>38648</v>
       </c>
       <c r="G90">
-        <v>55657</v>
+        <v>55653</v>
       </c>
       <c r="H90">
-        <v>30431</v>
+        <v>30459</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3696</v>
+        <v>3689</v>
       </c>
       <c r="E91">
         <v>59417</v>
       </c>
       <c r="F91">
-        <v>30651</v>
+        <v>30648</v>
       </c>
       <c r="G91">
-        <v>44137</v>
+        <v>44133</v>
       </c>
       <c r="H91">
-        <v>26955</v>
+        <v>26959</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9510</v>
+        <v>9476</v>
       </c>
       <c r="E93">
         <v>27842</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24476</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35245</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>64055</v>
+        <v>63679</v>
       </c>
       <c r="E96">
         <v>83562</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>78679</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>113298</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34584</v>
+        <v>34471</v>
       </c>
       <c r="E97">
         <v>83562</v>
       </c>
       <c r="F97">
-        <v>52423</v>
+        <v>52377</v>
       </c>
       <c r="G97">
-        <v>75489</v>
+        <v>75423</v>
       </c>
       <c r="H97">
-        <v>17839</v>
+        <v>17906</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79315</v>
+        <v>79039</v>
       </c>
       <c r="E98">
         <v>96564</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>94039</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>135416</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>43935</v>
+        <v>43773</v>
       </c>
       <c r="E99">
         <v>96564</v>
       </c>
       <c r="F99">
-        <v>61234</v>
+        <v>61169</v>
       </c>
       <c r="G99">
-        <v>88177</v>
+        <v>88083</v>
       </c>
       <c r="H99">
-        <v>17299</v>
+        <v>17396</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60677</v>
+        <v>60452</v>
       </c>
       <c r="E100">
         <v>108265</v>
       </c>
       <c r="F100">
-        <v>78990</v>
+        <v>81199</v>
       </c>
       <c r="G100">
-        <v>113746</v>
+        <v>116927</v>
       </c>
       <c r="H100">
-        <v>18313</v>
+        <v>20747</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>63266</v>
       </c>
       <c r="E101">
         <v>108265</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>78266</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>112703</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>74905</v>
       </c>
       <c r="E107">
         <v>185716</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>101905</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>146743</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6181</v>
+        <v>6153</v>
       </c>
       <c r="E109">
         <v>129996</v>
       </c>
       <c r="F109">
-        <v>33181</v>
+        <v>33153</v>
       </c>
       <c r="G109">
-        <v>47781</v>
+        <v>47740</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15102</v>
+        <v>15041</v>
       </c>
       <c r="E111">
         <v>167143</v>
       </c>
       <c r="F111">
-        <v>42102</v>
+        <v>42041</v>
       </c>
       <c r="G111">
-        <v>60627</v>
+        <v>60539</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51199</v>
+        <v>51023</v>
       </c>
       <c r="E113">
         <v>129996</v>
       </c>
       <c r="F113">
-        <v>77178</v>
+        <v>77107</v>
       </c>
       <c r="G113">
-        <v>111136</v>
+        <v>111034</v>
       </c>
       <c r="H113">
-        <v>25979</v>
+        <v>26084</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5541,19 +5541,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>168189</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>185716</v>
       </c>
       <c r="F117">
-        <v>183189</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>263792</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80367</v>
+        <v>80088</v>
       </c>
       <c r="E118">
         <v>89134</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>95088</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>136927</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,16 +5629,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50227</v>
+        <v>50037</v>
       </c>
       <c r="E119">
         <v>89134</v>
       </c>
       <c r="F119">
-        <v>65227</v>
+        <v>65037</v>
       </c>
       <c r="G119">
-        <v>93927</v>
+        <v>93653</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102239</v>
+        <v>85781</v>
       </c>
       <c r="E121">
         <v>118852</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>100781</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>145125</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>207765</v>
       </c>
       <c r="E122">
         <v>148569</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>222765</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>320782</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46261</v>
+        <v>46126</v>
       </c>
       <c r="E124">
         <v>59417</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>61126</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>88021</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,16 +5891,16 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35604</v>
+        <v>35060</v>
       </c>
       <c r="E125">
         <v>59417</v>
       </c>
       <c r="F125">
-        <v>50604</v>
+        <v>50060</v>
       </c>
       <c r="G125">
-        <v>72870</v>
+        <v>72086</v>
       </c>
       <c r="H125">
         <v>15000</v>
@@ -5935,16 +5935,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63863</v>
+        <v>63648</v>
       </c>
       <c r="E126">
         <v>81705</v>
       </c>
       <c r="F126">
-        <v>78863</v>
+        <v>78648</v>
       </c>
       <c r="G126">
-        <v>113563</v>
+        <v>113253</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>38748</v>
       </c>
       <c r="E128">
         <v>92849</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>65460</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>94262</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>26712</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36910</v>
+        <v>36777</v>
       </c>
       <c r="E129">
         <v>92849</v>
       </c>
       <c r="F129">
-        <v>56975</v>
+        <v>56922</v>
       </c>
       <c r="G129">
-        <v>82044</v>
+        <v>81968</v>
       </c>
       <c r="H129">
-        <v>20065</v>
+        <v>20145</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12760</v>
+        <v>12720</v>
       </c>
       <c r="E130">
         <v>44558</v>
       </c>
       <c r="F130">
-        <v>33419</v>
+        <v>33197</v>
       </c>
       <c r="G130">
-        <v>48123</v>
+        <v>47804</v>
       </c>
       <c r="H130">
-        <v>20659</v>
+        <v>20477</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5846</v>
+        <v>4547</v>
       </c>
       <c r="E131">
         <v>44558</v>
       </c>
       <c r="F131">
-        <v>25716</v>
+        <v>25197</v>
       </c>
       <c r="G131">
-        <v>37031</v>
+        <v>36284</v>
       </c>
       <c r="H131">
-        <v>19870</v>
+        <v>20650</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27750</v>
+        <v>27666</v>
       </c>
       <c r="E132">
         <v>59417</v>
       </c>
       <c r="F132">
-        <v>43838</v>
+        <v>43804</v>
       </c>
       <c r="G132">
-        <v>63127</v>
+        <v>63078</v>
       </c>
       <c r="H132">
-        <v>16088</v>
+        <v>16138</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17348</v>
+        <v>20575</v>
       </c>
       <c r="E135">
         <v>60884</v>
       </c>
       <c r="F135">
-        <v>36684</v>
+        <v>37975</v>
       </c>
       <c r="G135">
-        <v>52825</v>
+        <v>54684</v>
       </c>
       <c r="H135">
-        <v>19336</v>
+        <v>17400</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28101</v>
+        <v>26601</v>
       </c>
       <c r="E137">
         <v>75854</v>
       </c>
       <c r="F137">
-        <v>46823</v>
+        <v>46223</v>
       </c>
       <c r="G137">
-        <v>67425</v>
+        <v>66561</v>
       </c>
       <c r="H137">
-        <v>18722</v>
+        <v>19622</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>28212</v>
+        <v>26537</v>
       </c>
       <c r="E139">
         <v>95486</v>
       </c>
       <c r="F139">
-        <v>54524</v>
+        <v>53537</v>
       </c>
       <c r="G139">
-        <v>78515</v>
+        <v>77093</v>
       </c>
       <c r="H139">
-        <v>26312</v>
+        <v>27000</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58272</v>
+        <v>58051</v>
       </c>
       <c r="E141">
         <v>90992</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>73051</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>105193</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,16 +6677,16 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77722</v>
+        <v>77449</v>
       </c>
       <c r="E143">
         <v>129996</v>
       </c>
       <c r="F143">
-        <v>92722</v>
+        <v>92449</v>
       </c>
       <c r="G143">
-        <v>133520</v>
+        <v>133127</v>
       </c>
       <c r="H143">
         <v>15000</v>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87312</v>
+        <v>86989</v>
       </c>
       <c r="E145">
         <v>155999</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>101989</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>146864</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>88157</v>
+        <v>86210</v>
       </c>
       <c r="E147">
         <v>90992</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>101210</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>145742</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>126357</v>
+        <v>125896</v>
       </c>
       <c r="E149">
         <v>129996</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>140896</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>202890</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38359</v>
+        <v>38224</v>
       </c>
       <c r="E150">
         <v>92849</v>
       </c>
       <c r="F150">
-        <v>63126</v>
+        <v>63072</v>
       </c>
       <c r="G150">
-        <v>90901</v>
+        <v>90824</v>
       </c>
       <c r="H150">
-        <v>24767</v>
+        <v>24848</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24962</v>
+        <v>24884</v>
       </c>
       <c r="E152">
         <v>92849</v>
       </c>
       <c r="F152">
-        <v>59962</v>
+        <v>59884</v>
       </c>
       <c r="G152">
-        <v>86345</v>
+        <v>86233</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29709</v>
+        <v>29606</v>
       </c>
       <c r="E153">
         <v>92849</v>
       </c>
       <c r="F153">
-        <v>54095</v>
+        <v>54054</v>
       </c>
       <c r="G153">
-        <v>77897</v>
+        <v>77838</v>
       </c>
       <c r="H153">
-        <v>24386</v>
+        <v>24448</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48794</v>
+        <v>48622</v>
       </c>
       <c r="E154">
         <v>92849</v>
@@ -7167,7 +7167,7 @@
         <v>100277</v>
       </c>
       <c r="H154">
-        <v>20843</v>
+        <v>21015</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>75604</v>
+        <v>75334</v>
       </c>
       <c r="E155">
         <v>92849</v>
       </c>
       <c r="F155">
-        <v>90604</v>
+        <v>90334</v>
       </c>
       <c r="G155">
-        <v>130470</v>
+        <v>130081</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65568</v>
+        <v>65333</v>
       </c>
       <c r="E156">
         <v>92849</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80333</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>115680</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>42931</v>
+        <v>38939</v>
       </c>
       <c r="E158">
         <v>63131</v>
       </c>
       <c r="F158">
-        <v>65687</v>
+        <v>65504</v>
       </c>
       <c r="G158">
-        <v>94589</v>
+        <v>94326</v>
       </c>
       <c r="H158">
-        <v>22756</v>
+        <v>26565</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42119</v>
+        <v>41960</v>
       </c>
       <c r="E159">
         <v>63131</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>56960</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>82022</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20120</v>
+        <v>20050</v>
       </c>
       <c r="E161">
         <v>55702</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>35744</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>51471</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>15694</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56233</v>
+        <v>56032</v>
       </c>
       <c r="E163">
         <v>74275</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>71032</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>102286</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>80861</v>
+        <v>70644</v>
       </c>
       <c r="E165">
         <v>111422</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>85644</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>123327</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>58782</v>
+        <v>54044</v>
       </c>
       <c r="E166">
         <v>74275</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>69044</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>99423</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34058</v>
+        <v>33931</v>
       </c>
       <c r="E167">
         <v>74275</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>48931</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70461</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60582</v>
+        <v>60388</v>
       </c>
       <c r="E168">
         <v>74275</v>
       </c>
       <c r="F168">
-        <v>75582</v>
+        <v>95388</v>
       </c>
       <c r="G168">
-        <v>108838</v>
+        <v>137359</v>
       </c>
       <c r="H168">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>74094</v>
       </c>
       <c r="E169">
         <v>74275</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>89094</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>128295</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>16376</v>
+        <v>15503</v>
       </c>
       <c r="E171">
         <v>27842</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>30503</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>43924</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31318</v>
+        <v>30353</v>
       </c>
       <c r="E173">
         <v>85420</v>
       </c>
       <c r="F173">
-        <v>51841</v>
+        <v>51455</v>
       </c>
       <c r="G173">
-        <v>74651</v>
+        <v>74095</v>
       </c>
       <c r="H173">
-        <v>20523</v>
+        <v>21102</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7615</v>
+        <v>7775</v>
       </c>
       <c r="E174">
         <v>55721</v>
       </c>
       <c r="F174">
-        <v>37847</v>
+        <v>37843</v>
       </c>
       <c r="G174">
-        <v>54500</v>
+        <v>54494</v>
       </c>
       <c r="H174">
-        <v>30232</v>
+        <v>30068</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5289</v>
+        <v>5279</v>
       </c>
       <c r="E175">
         <v>55721</v>
       </c>
       <c r="F175">
-        <v>29847</v>
+        <v>29843</v>
       </c>
       <c r="G175">
-        <v>42980</v>
+        <v>42974</v>
       </c>
       <c r="H175">
-        <v>24558</v>
+        <v>24564</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10355</v>
+        <v>10128</v>
       </c>
       <c r="E176">
         <v>74275</v>
       </c>
       <c r="F176">
-        <v>44016</v>
+        <v>43793</v>
       </c>
       <c r="G176">
-        <v>63383</v>
+        <v>63062</v>
       </c>
       <c r="H176">
-        <v>33661</v>
+        <v>33665</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>9016</v>
+        <v>8793</v>
       </c>
       <c r="E177">
         <v>74275</v>
       </c>
       <c r="F177">
-        <v>36016</v>
+        <v>35793</v>
       </c>
       <c r="G177">
-        <v>51863</v>
+        <v>51542</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21920</v>
+        <v>21847</v>
       </c>
       <c r="E179">
         <v>69651</v>
       </c>
       <c r="F179">
-        <v>41932</v>
+        <v>41903</v>
       </c>
       <c r="G179">
-        <v>60382</v>
+        <v>60340</v>
       </c>
       <c r="H179">
-        <v>20012</v>
+        <v>20056</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45974</v>
+        <v>45808</v>
       </c>
       <c r="E181">
         <v>104940</v>
       </c>
       <c r="F181">
-        <v>65316</v>
+        <v>65250</v>
       </c>
       <c r="G181">
-        <v>94055</v>
+        <v>93960</v>
       </c>
       <c r="H181">
-        <v>19342</v>
+        <v>19442</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68085</v>
+        <v>67877</v>
       </c>
       <c r="E182">
         <v>74275</v>
       </c>
       <c r="F182">
-        <v>86791</v>
+        <v>86183</v>
       </c>
       <c r="G182">
-        <v>124979</v>
+        <v>124104</v>
       </c>
       <c r="H182">
-        <v>18706</v>
+        <v>18306</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10402</v>
+        <v>9794</v>
       </c>
       <c r="E183">
         <v>74275</v>
       </c>
       <c r="F183">
-        <v>37402</v>
+        <v>36794</v>
       </c>
       <c r="G183">
-        <v>53859</v>
+        <v>52983</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>71972</v>
+        <v>60563</v>
       </c>
       <c r="E184">
         <v>111422</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>80365</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>115726</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>19802</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>48781</v>
       </c>
       <c r="E185">
         <v>111422</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>68967</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>99312</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>20186</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>89702</v>
+        <v>79961</v>
       </c>
       <c r="E186">
         <v>148569</v>
       </c>
       <c r="F186">
-        <v>108737</v>
+        <v>110937</v>
       </c>
       <c r="G186">
-        <v>156581</v>
+        <v>159749</v>
       </c>
       <c r="H186">
-        <v>19035</v>
+        <v>30976</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>81313</v>
       </c>
       <c r="E187">
         <v>148569</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>96467</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>138912</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>15154</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>141908</v>
       </c>
       <c r="E190">
         <v>157856</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>156908</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>225948</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7296</v>
+        <v>7076</v>
       </c>
       <c r="E194">
         <v>53863</v>
@@ -8920,7 +8920,7 @@
         <v>50400</v>
       </c>
       <c r="H194">
-        <v>27704</v>
+        <v>27924</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11788</v>
+        <v>11750</v>
       </c>
       <c r="E196">
         <v>83581</v>
       </c>
       <c r="F196">
-        <v>38788</v>
+        <v>38750</v>
       </c>
       <c r="G196">
-        <v>55855</v>
+        <v>55800</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51820</v>
+        <v>51659</v>
       </c>
       <c r="E198">
         <v>92849</v>
@@ -9095,7 +9095,7 @@
         <v>100277</v>
       </c>
       <c r="H198">
-        <v>17817</v>
+        <v>17978</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75142</v>
+        <v>74873</v>
       </c>
       <c r="E199">
         <v>92849</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>89873</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>129417</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,16 +9172,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>56838</v>
+        <v>56636</v>
       </c>
       <c r="E200">
         <v>92849</v>
       </c>
       <c r="F200">
-        <v>71838</v>
+        <v>71636</v>
       </c>
       <c r="G200">
-        <v>103447</v>
+        <v>103156</v>
       </c>
       <c r="H200">
         <v>15000</v>
@@ -9259,19 +9259,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36814</v>
+        <v>36713</v>
       </c>
       <c r="E202">
         <v>111422</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>63713</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>91747</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27559</v>
+        <v>27475</v>
       </c>
       <c r="E204">
         <v>92849</v>
       </c>
       <c r="F204">
-        <v>54559</v>
+        <v>54475</v>
       </c>
       <c r="G204">
-        <v>78565</v>
+        <v>78444</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>101744</v>
       </c>
       <c r="E206">
         <v>129996</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>116744</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>168111</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>64166</v>
+        <v>63743</v>
       </c>
       <c r="E207">
         <v>129996</v>
       </c>
       <c r="F207">
-        <v>82365</v>
+        <v>82195</v>
       </c>
       <c r="G207">
-        <v>118606</v>
+        <v>118361</v>
       </c>
       <c r="H207">
-        <v>18199</v>
+        <v>18452</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144947</v>
+        <v>144674</v>
       </c>
       <c r="E208">
         <v>185716</v>
       </c>
       <c r="F208">
-        <v>179947</v>
+        <v>179674</v>
       </c>
       <c r="G208">
-        <v>259124</v>
+        <v>258731</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145425</v>
+        <v>144579</v>
       </c>
       <c r="E209">
         <v>185716</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>159579</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>229794</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187958</v>
+        <v>187604</v>
       </c>
       <c r="E210">
         <v>241437</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>202604</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>291750</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,16 +9654,16 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>186747</v>
+        <v>185951</v>
       </c>
       <c r="E211">
         <v>185716</v>
       </c>
       <c r="F211">
-        <v>201747</v>
+        <v>200951</v>
       </c>
       <c r="G211">
-        <v>290516</v>
+        <v>289369</v>
       </c>
       <c r="H211">
         <v>15000</v>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>287774</v>
       </c>
       <c r="E212">
         <v>371451</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>302774</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>435995</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>224349</v>
       </c>
       <c r="E213">
         <v>371451</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>240605</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>346471</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>16256</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34696</v>
+        <v>34455</v>
       </c>
       <c r="E214">
         <v>53863</v>
       </c>
       <c r="F214">
-        <v>62085</v>
+        <v>61153</v>
       </c>
       <c r="G214">
-        <v>89402</v>
+        <v>88060</v>
       </c>
       <c r="H214">
-        <v>27389</v>
+        <v>26698</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>38901</v>
+        <v>37969</v>
       </c>
       <c r="E215">
         <v>53863</v>
       </c>
       <c r="F215">
-        <v>53901</v>
+        <v>52969</v>
       </c>
       <c r="G215">
-        <v>77617</v>
+        <v>76275</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>60438</v>
+        <v>16441</v>
       </c>
       <c r="E216">
         <v>53863</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>36815</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>53014</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>20374</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67575</v>
+        <v>16441</v>
       </c>
       <c r="E218">
         <v>53863</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>36815</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>53014</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>20374</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13302</v>
+        <v>12561</v>
       </c>
       <c r="E220">
         <v>74275</v>
       </c>
       <c r="F220">
-        <v>40302</v>
+        <v>44604</v>
       </c>
       <c r="G220">
-        <v>58035</v>
+        <v>64230</v>
       </c>
       <c r="H220">
-        <v>27000</v>
+        <v>32043</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,19 +10094,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>9604</v>
       </c>
       <c r="E221">
         <v>74275</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>36604</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>52710</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>21171</v>
+        <v>20924</v>
       </c>
       <c r="E222">
         <v>111422</v>
       </c>
       <c r="F222">
-        <v>48171</v>
+        <v>55924</v>
       </c>
       <c r="G222">
-        <v>69366</v>
+        <v>80531</v>
       </c>
       <c r="H222">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>53567</v>
       </c>
       <c r="E223">
         <v>111422</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>70881</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>102069</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>17314</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16822</v>
+        <v>16759</v>
       </c>
       <c r="E224">
         <v>129996</v>
       </c>
       <c r="F224">
-        <v>47027</v>
+        <v>46146</v>
       </c>
       <c r="G224">
-        <v>67719</v>
+        <v>66450</v>
       </c>
       <c r="H224">
-        <v>30205</v>
+        <v>29387</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>12027</v>
+        <v>11146</v>
       </c>
       <c r="E225">
         <v>129996</v>
       </c>
       <c r="F225">
-        <v>39027</v>
+        <v>38146</v>
       </c>
       <c r="G225">
-        <v>56199</v>
+        <v>54930</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26571</v>
+        <v>26489</v>
       </c>
       <c r="E226">
         <v>148569</v>
       </c>
       <c r="F226">
-        <v>61571</v>
+        <v>61489</v>
       </c>
       <c r="G226">
-        <v>88662</v>
+        <v>88544</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38567</v>
+        <v>95416</v>
       </c>
       <c r="E227">
         <v>148569</v>
       </c>
       <c r="F227">
-        <v>65567</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>94416</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35827</v>
+        <v>35711</v>
       </c>
       <c r="E228">
         <v>185716</v>
       </c>
       <c r="F228">
-        <v>62827</v>
+        <v>62711</v>
       </c>
       <c r="G228">
-        <v>90471</v>
+        <v>90304</v>
       </c>
       <c r="H228">
         <v>27000</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>16089</v>
+        <v>15741</v>
       </c>
       <c r="E230">
         <v>59417</v>
       </c>
       <c r="F230">
-        <v>42940</v>
+        <v>43002</v>
       </c>
       <c r="G230">
-        <v>61834</v>
+        <v>61923</v>
       </c>
       <c r="H230">
-        <v>26851</v>
+        <v>27261</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9893</v>
+        <v>10049</v>
       </c>
       <c r="E231">
         <v>59417</v>
       </c>
       <c r="F231">
-        <v>33130</v>
+        <v>33192</v>
       </c>
       <c r="G231">
-        <v>47707</v>
+        <v>47796</v>
       </c>
       <c r="H231">
-        <v>23237</v>
+        <v>23143</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>41674</v>
       </c>
       <c r="E235">
         <v>111422</v>
       </c>
       <c r="F235">
-        <v>0</v>
+        <v>66124</v>
       </c>
       <c r="G235">
-        <v>0</v>
+        <v>95219</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>24450</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>86019</v>
       </c>
       <c r="E237">
         <v>185716</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>112837</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>162485</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>26818</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26651</v>
+        <v>26553</v>
       </c>
       <c r="E238">
         <v>89134</v>
       </c>
       <c r="F238">
-        <v>53651</v>
+        <v>61541</v>
       </c>
       <c r="G238">
-        <v>77257</v>
+        <v>88619</v>
       </c>
       <c r="H238">
-        <v>27000</v>
+        <v>34988</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>31880</v>
       </c>
       <c r="E239">
         <v>89134</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>53514</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>77060</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>21634</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47089</v>
+        <v>46921</v>
       </c>
       <c r="E240">
         <v>103993</v>
       </c>
       <c r="F240">
-        <v>71633</v>
+        <v>77995</v>
       </c>
       <c r="G240">
-        <v>103152</v>
+        <v>112313</v>
       </c>
       <c r="H240">
-        <v>24544</v>
+        <v>31074</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>85733</v>
       </c>
       <c r="E241">
         <v>103993</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>100733</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>145056</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>110664</v>
       </c>
       <c r="E243">
         <v>133711</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>125664</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>180956</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,16 +11109,16 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64389</v>
+        <v>64188</v>
       </c>
       <c r="E244">
         <v>83581</v>
       </c>
       <c r="F244">
-        <v>79389</v>
+        <v>79188</v>
       </c>
       <c r="G244">
-        <v>114320</v>
+        <v>114031</v>
       </c>
       <c r="H244">
         <v>15000</v>
@@ -11199,16 +11199,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>76432</v>
+        <v>75668</v>
       </c>
       <c r="E246">
         <v>98440</v>
       </c>
       <c r="F246">
-        <v>91432</v>
+        <v>90668</v>
       </c>
       <c r="G246">
-        <v>131662</v>
+        <v>130562</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17937</v>
+        <v>17840</v>
       </c>
       <c r="E248">
         <v>61274</v>
       </c>
       <c r="F248">
-        <v>42574</v>
+        <v>42578</v>
       </c>
       <c r="G248">
-        <v>61307</v>
+        <v>61312</v>
       </c>
       <c r="H248">
-        <v>24637</v>
+        <v>24738</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11693</v>
+        <v>11702</v>
       </c>
       <c r="E249">
         <v>61274</v>
       </c>
       <c r="F249">
-        <v>34574</v>
+        <v>34578</v>
       </c>
       <c r="G249">
-        <v>49787</v>
+        <v>49792</v>
       </c>
       <c r="H249">
-        <v>22881</v>
+        <v>22876</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>26157</v>
+        <v>0</v>
       </c>
       <c r="E250">
         <v>74275</v>
       </c>
       <c r="F250">
-        <v>49886</v>
+        <v>0</v>
       </c>
       <c r="G250">
-        <v>71836</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>23729</v>
+        <v>0</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>16631</v>
       </c>
       <c r="E253">
         <v>111422</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>43631</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>62829</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9670</v>
+        <v>9635</v>
       </c>
       <c r="E256">
         <v>53863</v>
       </c>
       <c r="F256">
-        <v>35000</v>
+        <v>40397</v>
       </c>
       <c r="G256">
-        <v>50400</v>
+        <v>58172</v>
       </c>
       <c r="H256">
-        <v>25330</v>
+        <v>30762</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>14882</v>
       </c>
       <c r="E257">
         <v>53863</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>32959</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>47461</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>18077</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12266</v>
+        <v>12243</v>
       </c>
       <c r="E258">
         <v>72437</v>
       </c>
       <c r="F258">
-        <v>39266</v>
+        <v>39243</v>
       </c>
       <c r="G258">
-        <v>56543</v>
+        <v>56510</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8889</v>
+        <v>8856</v>
       </c>
       <c r="E260">
         <v>53863</v>
       </c>
       <c r="F260">
-        <v>39429</v>
+        <v>39414</v>
       </c>
       <c r="G260">
-        <v>56778</v>
+        <v>56756</v>
       </c>
       <c r="H260">
-        <v>30540</v>
+        <v>30558</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11055</v>
+        <v>11019</v>
       </c>
       <c r="E261">
         <v>53863</v>
       </c>
       <c r="F261">
-        <v>31429</v>
+        <v>31414</v>
       </c>
       <c r="G261">
-        <v>45258</v>
+        <v>45236</v>
       </c>
       <c r="H261">
-        <v>20374</v>
+        <v>20395</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>11868</v>
+        <v>11607</v>
       </c>
       <c r="E262">
         <v>53863</v>
       </c>
       <c r="F262">
-        <v>35000</v>
+        <v>39211</v>
       </c>
       <c r="G262">
-        <v>50400</v>
+        <v>56464</v>
       </c>
       <c r="H262">
-        <v>23132</v>
+        <v>27604</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>10510</v>
       </c>
       <c r="E263">
         <v>53863</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>31211</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>44944</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>20701</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,16 +11991,16 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18176</v>
+        <v>17951</v>
       </c>
       <c r="E264">
         <v>72437</v>
       </c>
       <c r="F264">
-        <v>45176</v>
+        <v>44951</v>
       </c>
       <c r="G264">
-        <v>65053</v>
+        <v>64729</v>
       </c>
       <c r="H264">
         <v>27000</v>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34473</v>
+        <v>34360</v>
       </c>
       <c r="E266">
         <v>72437</v>
       </c>
       <c r="F266">
-        <v>52386</v>
+        <v>54328</v>
       </c>
       <c r="G266">
-        <v>75436</v>
+        <v>78232</v>
       </c>
       <c r="H266">
-        <v>17913</v>
+        <v>19968</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>30941</v>
       </c>
       <c r="E267">
         <v>72437</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>46627</v>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>67143</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>15686</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10259</v>
+        <v>10256</v>
       </c>
       <c r="E268">
         <v>27860</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>25256</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>36369</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12123</v>
+        <v>12084</v>
       </c>
       <c r="E270">
         <v>83581</v>
       </c>
       <c r="F270">
-        <v>39123</v>
+        <v>39084</v>
       </c>
       <c r="G270">
-        <v>56337</v>
+        <v>56281</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62987</v>
+        <v>62487</v>
       </c>
       <c r="E272">
         <v>98440</v>
       </c>
       <c r="F272">
-        <v>77987</v>
+        <v>77487</v>
       </c>
       <c r="G272">
-        <v>112301</v>
+        <v>111581</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>38891</v>
       </c>
       <c r="E273">
         <v>98440</v>
       </c>
       <c r="F273">
-        <v>0</v>
+        <v>59948</v>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>86325</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>21057</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>71701</v>
+        <v>71423</v>
       </c>
       <c r="E274">
         <v>111422</v>
       </c>
       <c r="F274">
-        <v>86701</v>
+        <v>106423</v>
       </c>
       <c r="G274">
-        <v>124849</v>
+        <v>153249</v>
       </c>
       <c r="H274">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>77735</v>
       </c>
       <c r="E275">
         <v>111422</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>92735</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>133538</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,7 +12519,7 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11199</v>
+        <v>11162</v>
       </c>
       <c r="E276">
         <v>53863</v>
@@ -12531,7 +12531,7 @@
         <v>50400</v>
       </c>
       <c r="H276">
-        <v>23801</v>
+        <v>23838</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20120</v>
+        <v>20066</v>
       </c>
       <c r="E278">
         <v>72437</v>
       </c>
       <c r="F278">
-        <v>46645</v>
+        <v>46623</v>
       </c>
       <c r="G278">
-        <v>67169</v>
+        <v>67137</v>
       </c>
       <c r="H278">
-        <v>26525</v>
+        <v>26557</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11772</v>
+        <v>11718</v>
       </c>
       <c r="E280">
         <v>53863</v>
@@ -12709,7 +12709,7 @@
         <v>50400</v>
       </c>
       <c r="H280">
-        <v>23228</v>
+        <v>23282</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,16 +12826,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17762</v>
+        <v>17697</v>
       </c>
       <c r="E283">
         <v>44558</v>
       </c>
       <c r="F283">
-        <v>32762</v>
+        <v>32697</v>
       </c>
       <c r="G283">
-        <v>47177</v>
+        <v>47084</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12912,16 +12912,16 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50052</v>
+        <v>49878</v>
       </c>
       <c r="E285">
         <v>55702</v>
       </c>
       <c r="F285">
-        <v>65052</v>
+        <v>64878</v>
       </c>
       <c r="G285">
-        <v>93675</v>
+        <v>93424</v>
       </c>
       <c r="H285">
         <v>15000</v>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58861</v>
+        <v>58655</v>
       </c>
       <c r="E287">
         <v>66846</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>73655</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>106063</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>40797</v>
+        <v>34646</v>
       </c>
       <c r="E288">
         <v>61274</v>
       </c>
       <c r="F288">
-        <v>55906</v>
+        <v>55844</v>
       </c>
       <c r="G288">
-        <v>80505</v>
+        <v>80415</v>
       </c>
       <c r="H288">
-        <v>15109</v>
+        <v>21198</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23879</v>
+        <v>23723</v>
       </c>
       <c r="E289">
         <v>61274</v>
       </c>
       <c r="F289">
-        <v>39448</v>
+        <v>39386</v>
       </c>
       <c r="G289">
-        <v>56805</v>
+        <v>56716</v>
       </c>
       <c r="H289">
-        <v>15569</v>
+        <v>15663</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>47009</v>
+        <v>44488</v>
       </c>
       <c r="E292">
         <v>61274</v>
       </c>
       <c r="F292">
-        <v>62255</v>
+        <v>62218</v>
       </c>
       <c r="G292">
-        <v>89647</v>
+        <v>89594</v>
       </c>
       <c r="H292">
-        <v>15246</v>
+        <v>17730</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23736</v>
+        <v>23643</v>
       </c>
       <c r="E293">
         <v>61274</v>
       </c>
       <c r="F293">
-        <v>39391</v>
+        <v>39354</v>
       </c>
       <c r="G293">
-        <v>56723</v>
+        <v>56670</v>
       </c>
       <c r="H293">
-        <v>15655</v>
+        <v>15711</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>49910</v>
       </c>
       <c r="E294">
         <v>68703</v>
       </c>
       <c r="F294">
-        <v>0</v>
+        <v>64910</v>
       </c>
       <c r="G294">
-        <v>0</v>
+        <v>93470</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>26092</v>
       </c>
       <c r="E295">
         <v>68703</v>
       </c>
       <c r="F295">
-        <v>0</v>
+        <v>43231</v>
       </c>
       <c r="G295">
-        <v>0</v>
+        <v>62253</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>17139</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>77738</v>
+        <v>62630</v>
       </c>
       <c r="E296">
         <v>78919</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>77630</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>111787</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>92553</v>
+        <v>74555</v>
       </c>
       <c r="E298">
         <v>94706</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>89555</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>128959</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>69503</v>
+        <v>69292</v>
       </c>
       <c r="E300">
         <v>92849</v>
       </c>
       <c r="F300">
-        <v>88614</v>
+        <v>88557</v>
       </c>
       <c r="G300">
-        <v>127604</v>
+        <v>127522</v>
       </c>
       <c r="H300">
-        <v>19111</v>
+        <v>19265</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33835</v>
+        <v>33692</v>
       </c>
       <c r="E301">
         <v>92849</v>
       </c>
       <c r="F301">
-        <v>55745</v>
+        <v>55688</v>
       </c>
       <c r="G301">
-        <v>80273</v>
+        <v>80191</v>
       </c>
       <c r="H301">
-        <v>21910</v>
+        <v>21996</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12171</v>
+        <v>11178</v>
       </c>
       <c r="E303">
         <v>129996</v>
       </c>
       <c r="F303">
-        <v>39171</v>
+        <v>38178</v>
       </c>
       <c r="G303">
-        <v>56406</v>
+        <v>54976</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>189280</v>
+        <v>174041</v>
       </c>
       <c r="E304">
         <v>167143</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>189041</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>272219</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>104765</v>
       </c>
       <c r="E305">
         <v>167143</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>119765</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>172462</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50164</v>
+        <v>50006</v>
       </c>
       <c r="E306">
         <v>111422</v>
       </c>
       <c r="F306">
-        <v>80144</v>
+        <v>80074</v>
       </c>
       <c r="G306">
-        <v>115407</v>
+        <v>115307</v>
       </c>
       <c r="H306">
-        <v>29980</v>
+        <v>30068</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50530</v>
+        <v>50355</v>
       </c>
       <c r="E307">
         <v>111422</v>
       </c>
       <c r="F307">
-        <v>69666</v>
+        <v>69596</v>
       </c>
       <c r="G307">
-        <v>100319</v>
+        <v>100218</v>
       </c>
       <c r="H307">
-        <v>19136</v>
+        <v>19241</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69407</v>
+        <v>69213</v>
       </c>
       <c r="E308">
         <v>129996</v>
@@ -13936,7 +13936,7 @@
         <v>140396</v>
       </c>
       <c r="H308">
-        <v>28090</v>
+        <v>28284</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>105807</v>
+        <v>77831</v>
       </c>
       <c r="E309">
         <v>129996</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>92831</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>133677</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24596</v>
+        <v>23977</v>
       </c>
       <c r="E310">
         <v>55702</v>
       </c>
       <c r="F310">
-        <v>40905</v>
+        <v>41777</v>
       </c>
       <c r="G310">
-        <v>58903</v>
+        <v>60159</v>
       </c>
       <c r="H310">
-        <v>16309</v>
+        <v>17800</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>37445</v>
       </c>
       <c r="E311">
         <v>55702</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>52445</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>75521</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>68180</v>
+        <v>66160</v>
       </c>
       <c r="E312">
         <v>83581</v>
       </c>
       <c r="F312">
-        <v>0</v>
+        <v>90116</v>
       </c>
       <c r="G312">
-        <v>0</v>
+        <v>129767</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>23956</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>63362</v>
       </c>
       <c r="E313">
         <v>83581</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>78362</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>112841</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,16 +14232,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20868</v>
+        <v>20797</v>
       </c>
       <c r="E315">
         <v>38986</v>
       </c>
       <c r="F315">
-        <v>35868</v>
+        <v>35797</v>
       </c>
       <c r="G315">
-        <v>51650</v>
+        <v>51548</v>
       </c>
       <c r="H315">
         <v>15000</v>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>33501</v>
+        <v>32420</v>
       </c>
       <c r="E316">
         <v>59417</v>
       </c>
       <c r="F316">
-        <v>62884</v>
+        <v>49585</v>
       </c>
       <c r="G316">
-        <v>90553</v>
+        <v>71402</v>
       </c>
       <c r="H316">
-        <v>29383</v>
+        <v>17165</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39682</v>
+        <v>26585</v>
       </c>
       <c r="E317">
         <v>59417</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>41585</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>59882</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16233</v>
+        <v>16202</v>
       </c>
       <c r="E318">
         <v>44558</v>
@@ -14378,7 +14378,7 @@
         <v>48123</v>
       </c>
       <c r="H318">
-        <v>17186</v>
+        <v>17217</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29327</v>
+        <v>29208</v>
       </c>
       <c r="E319">
         <v>44558</v>
       </c>
       <c r="F319">
-        <v>44327</v>
+        <v>44208</v>
       </c>
       <c r="G319">
-        <v>63831</v>
+        <v>63660</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>58862</v>
       </c>
       <c r="E324">
         <v>74275</v>
       </c>
       <c r="F324">
-        <v>0</v>
+        <v>90793</v>
       </c>
       <c r="G324">
-        <v>0</v>
+        <v>130742</v>
       </c>
       <c r="H324">
-        <v>0</v>
+        <v>31931</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>63950</v>
       </c>
       <c r="E325">
         <v>74275</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>78950</v>
       </c>
       <c r="G325">
-        <v>0</v>
+        <v>113688</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>9397</v>
       </c>
       <c r="E327">
         <v>64989</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>35105</v>
       </c>
       <c r="G327">
-        <v>0</v>
+        <v>50551</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>25708</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>17045</v>
       </c>
       <c r="E329">
         <v>64989</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>38164</v>
       </c>
       <c r="G329">
-        <v>0</v>
+        <v>54956</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>21119</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20916</v>
+        <v>20845</v>
       </c>
       <c r="E330">
         <v>92849</v>
       </c>
       <c r="F330">
-        <v>47916</v>
+        <v>47845</v>
       </c>
       <c r="G330">
-        <v>68999</v>
+        <v>68897</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43808</v>
+        <v>43677</v>
       </c>
       <c r="E332">
         <v>111422</v>
       </c>
       <c r="F332">
-        <v>70808</v>
+        <v>70677</v>
       </c>
       <c r="G332">
-        <v>101964</v>
+        <v>101775</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,19 +15067,19 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>31079</v>
+        <v>30957</v>
       </c>
       <c r="E334">
         <v>111422</v>
       </c>
       <c r="F334">
-        <v>58079</v>
+        <v>65957</v>
       </c>
       <c r="G334">
-        <v>83634</v>
+        <v>94978</v>
       </c>
       <c r="H334">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I334" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>49385</v>
       </c>
       <c r="E335">
         <v>111422</v>
       </c>
       <c r="F335">
-        <v>0</v>
+        <v>69208</v>
       </c>
       <c r="G335">
-        <v>0</v>
+        <v>99660</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>19823</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>189137</v>
+        <v>188622</v>
       </c>
       <c r="E336">
         <v>241437</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>203622</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>293216</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>144293</v>
       </c>
       <c r="E337">
         <v>241437</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>159293</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>229382</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>59722</v>
+        <v>64411</v>
       </c>
       <c r="E338">
         <v>129996</v>
       </c>
       <c r="F338">
-        <v>86722</v>
+        <v>90263</v>
       </c>
       <c r="G338">
-        <v>124880</v>
+        <v>129979</v>
       </c>
       <c r="H338">
-        <v>27000</v>
+        <v>25852</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>41881</v>
       </c>
       <c r="E339">
         <v>129996</v>
       </c>
       <c r="F339">
-        <v>0</v>
+        <v>68881</v>
       </c>
       <c r="G339">
-        <v>0</v>
+        <v>99189</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>104018</v>
       </c>
       <c r="E342">
         <v>241437</v>
       </c>
       <c r="F342">
-        <v>0</v>
+        <v>131018</v>
       </c>
       <c r="G342">
-        <v>0</v>
+        <v>188666</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71773</v>
+        <v>71929</v>
       </c>
       <c r="E2">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F2">
-        <v>86773</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>124953</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47716</v>
+        <v>48022</v>
       </c>
       <c r="E3">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F3">
-        <v>62716</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90311</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94669</v>
+        <v>95037</v>
       </c>
       <c r="E4">
-        <v>85420</v>
+        <v>85141</v>
       </c>
       <c r="F4">
-        <v>109669</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>157923</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>78387</v>
+        <v>78604</v>
       </c>
       <c r="E5">
-        <v>85420</v>
+        <v>85141</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>93604</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>134790</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7155</v>
+        <v>7187</v>
       </c>
       <c r="E7">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F7">
-        <v>30586</v>
+        <v>30528</v>
       </c>
       <c r="G7">
-        <v>44044</v>
+        <v>43960</v>
       </c>
       <c r="H7">
-        <v>23431</v>
+        <v>23341</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39241</v>
+        <v>39398</v>
       </c>
       <c r="E8">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F8">
-        <v>55706</v>
+        <v>55525</v>
       </c>
       <c r="G8">
-        <v>80217</v>
+        <v>79956</v>
       </c>
       <c r="H8">
-        <v>16465</v>
+        <v>16127</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>39543</v>
+        <v>39717</v>
       </c>
       <c r="E9">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F9">
-        <v>54543</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>78542</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56270</v>
+        <v>58003</v>
       </c>
       <c r="E10">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F10">
-        <v>78648</v>
+        <v>79178</v>
       </c>
       <c r="G10">
-        <v>113253</v>
+        <v>114016</v>
       </c>
       <c r="H10">
-        <v>22378</v>
+        <v>21175</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>74873</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F11">
-        <v>89873</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>129417</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>86544</v>
+        <v>86797</v>
       </c>
       <c r="E12">
-        <v>83562</v>
+        <v>83290</v>
       </c>
       <c r="F12">
-        <v>101544</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>146223</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>12641</v>
+        <v>13495</v>
       </c>
       <c r="E13">
-        <v>83562</v>
+        <v>83290</v>
       </c>
       <c r="F13">
-        <v>39641</v>
+        <v>40495</v>
       </c>
       <c r="G13">
-        <v>57083</v>
+        <v>58313</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27157</v>
+        <v>27293</v>
       </c>
       <c r="E15">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F15">
-        <v>45830</v>
+        <v>45790</v>
       </c>
       <c r="G15">
-        <v>65995</v>
+        <v>65938</v>
       </c>
       <c r="H15">
-        <v>18673</v>
+        <v>18497</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>89134</v>
+        <v>88844</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>89134</v>
+        <v>88844</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>133711</v>
+        <v>133275</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>133711</v>
+        <v>133275</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>103993</v>
+        <v>103654</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>49322</v>
+        <v>54633</v>
       </c>
       <c r="E21">
-        <v>103993</v>
+        <v>103654</v>
       </c>
       <c r="F21">
-        <v>66286</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>95452</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>16964</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>133711</v>
+        <v>133275</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96004</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>133711</v>
+        <v>133275</v>
       </c>
       <c r="F23">
-        <v>111004</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>159846</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>163428</v>
+        <v>162896</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>163428</v>
+        <v>162896</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21735</v>
+        <v>21863</v>
       </c>
       <c r="E27">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F27">
-        <v>40040</v>
+        <v>40008</v>
       </c>
       <c r="G27">
-        <v>57658</v>
+        <v>57612</v>
       </c>
       <c r="H27">
-        <v>18305</v>
+        <v>18145</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>77767</v>
+        <v>77678</v>
       </c>
       <c r="E28">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F28">
-        <v>96332</v>
+        <v>96546</v>
       </c>
       <c r="G28">
-        <v>138718</v>
+        <v>139026</v>
       </c>
       <c r="H28">
-        <v>18565</v>
+        <v>18868</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>37890</v>
+        <v>38104</v>
       </c>
       <c r="E29">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F29">
-        <v>64890</v>
+        <v>65104</v>
       </c>
       <c r="G29">
-        <v>93442</v>
+        <v>93750</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>125769</v>
+        <v>126466</v>
       </c>
       <c r="E30">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F30">
-        <v>140769</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>202707</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>69404</v>
+        <v>69709</v>
       </c>
       <c r="E31">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F31">
-        <v>96404</v>
+        <v>96709</v>
       </c>
       <c r="G31">
-        <v>138822</v>
+        <v>139261</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60563</v>
+        <v>61133</v>
       </c>
       <c r="E32">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F32">
-        <v>80783</v>
+        <v>80991</v>
       </c>
       <c r="G32">
-        <v>116328</v>
+        <v>116627</v>
       </c>
       <c r="H32">
-        <v>20220</v>
+        <v>19858</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36252</v>
+        <v>36460</v>
       </c>
       <c r="E33">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F33">
-        <v>63252</v>
+        <v>63460</v>
       </c>
       <c r="G33">
-        <v>91083</v>
+        <v>91382</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>80963</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F35">
-        <v>95963</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>138187</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48813</v>
+        <v>48597</v>
       </c>
       <c r="E36">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F36">
-        <v>75813</v>
+        <v>75597</v>
       </c>
       <c r="G36">
-        <v>109171</v>
+        <v>108860</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35473</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F37">
-        <v>62473</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89961</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>68036</v>
+        <v>68128</v>
       </c>
       <c r="E38">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F38">
-        <v>95036</v>
+        <v>95128</v>
       </c>
       <c r="G38">
-        <v>136852</v>
+        <v>136984</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>63059</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F39">
-        <v>90059</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>129685</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87863</v>
+        <v>87803</v>
       </c>
       <c r="E40">
-        <v>241437</v>
+        <v>240650</v>
       </c>
       <c r="F40">
-        <v>114863</v>
+        <v>114803</v>
       </c>
       <c r="G40">
-        <v>165403</v>
+        <v>165316</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>88499</v>
+        <v>88889</v>
       </c>
       <c r="E41">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F41">
-        <v>113829</v>
+        <v>113749</v>
       </c>
       <c r="G41">
-        <v>163914</v>
+        <v>163799</v>
       </c>
       <c r="H41">
-        <v>25330</v>
+        <v>24860</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31593</v>
+        <v>31748</v>
       </c>
       <c r="E43">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F43">
-        <v>58593</v>
+        <v>58748</v>
       </c>
       <c r="G43">
-        <v>84374</v>
+        <v>84597</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>78164</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F45">
-        <v>105164</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>151436</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>21370</v>
+        <v>21224</v>
       </c>
       <c r="E47">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F47">
-        <v>48370</v>
+        <v>48224</v>
       </c>
       <c r="G47">
-        <v>69653</v>
+        <v>69443</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36713</v>
+        <v>40372</v>
       </c>
       <c r="E50">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F50">
-        <v>61142</v>
+        <v>66120</v>
       </c>
       <c r="G50">
-        <v>88044</v>
+        <v>95213</v>
       </c>
       <c r="H50">
-        <v>24429</v>
+        <v>25748</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33056</v>
+        <v>42496</v>
       </c>
       <c r="E51">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>57496</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>82794</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>51166</v>
+        <v>59696</v>
       </c>
       <c r="E52">
-        <v>77990</v>
+        <v>77736</v>
       </c>
       <c r="F52">
-        <v>66166</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>95279</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>58925</v>
+        <v>67936</v>
       </c>
       <c r="E53">
-        <v>77990</v>
+        <v>77736</v>
       </c>
       <c r="F53">
-        <v>73925</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>106452</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>44838</v>
+        <v>45003</v>
       </c>
       <c r="E54">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F54">
-        <v>79838</v>
+        <v>80003</v>
       </c>
       <c r="G54">
-        <v>114967</v>
+        <v>115204</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44234</v>
+        <v>44668</v>
       </c>
       <c r="E55">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F55">
-        <v>71234</v>
+        <v>71668</v>
       </c>
       <c r="G55">
-        <v>102577</v>
+        <v>103202</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>50928</v>
+        <v>51120</v>
       </c>
       <c r="E56">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F56">
-        <v>77928</v>
+        <v>78120</v>
       </c>
       <c r="G56">
-        <v>112216</v>
+        <v>112493</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>65842</v>
+        <v>66196</v>
       </c>
       <c r="E57">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F57">
-        <v>90279</v>
+        <v>90231</v>
       </c>
       <c r="G57">
-        <v>130002</v>
+        <v>129933</v>
       </c>
       <c r="H57">
-        <v>24437</v>
+        <v>24035</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>16202</v>
+        <v>16098</v>
       </c>
       <c r="E58">
-        <v>37128</v>
+        <v>37007</v>
       </c>
       <c r="F58">
-        <v>38700</v>
+        <v>38664</v>
       </c>
       <c r="G58">
-        <v>55728</v>
+        <v>55676</v>
       </c>
       <c r="H58">
-        <v>22498</v>
+        <v>22566</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6217</v>
+        <v>6244</v>
       </c>
       <c r="E59">
-        <v>37128</v>
+        <v>37007</v>
       </c>
       <c r="F59">
-        <v>22967</v>
+        <v>22931</v>
       </c>
       <c r="G59">
-        <v>33072</v>
+        <v>33021</v>
       </c>
       <c r="H59">
-        <v>16750</v>
+        <v>16687</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24104</v>
+        <v>24195</v>
       </c>
       <c r="E60">
-        <v>50130</v>
+        <v>49967</v>
       </c>
       <c r="F60">
-        <v>48504</v>
+        <v>39195</v>
       </c>
       <c r="G60">
-        <v>69846</v>
+        <v>56441</v>
       </c>
       <c r="H60">
-        <v>24400</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25504</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>50130</v>
+        <v>49967</v>
       </c>
       <c r="F61">
-        <v>40504</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58326</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>83562</v>
+        <v>83290</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14056</v>
+        <v>14277</v>
       </c>
       <c r="E63">
-        <v>83562</v>
+        <v>83290</v>
       </c>
       <c r="F63">
-        <v>41056</v>
+        <v>41277</v>
       </c>
       <c r="G63">
-        <v>59121</v>
+        <v>59439</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>125334</v>
+        <v>124926</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23150</v>
+        <v>23268</v>
       </c>
       <c r="E65">
-        <v>125334</v>
+        <v>124926</v>
       </c>
       <c r="F65">
-        <v>50150</v>
+        <v>50268</v>
       </c>
       <c r="G65">
-        <v>72216</v>
+        <v>72386</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25838</v>
+        <v>25935</v>
       </c>
       <c r="E66">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F66">
-        <v>60764</v>
+        <v>60871</v>
       </c>
       <c r="G66">
-        <v>87500</v>
+        <v>87654</v>
       </c>
       <c r="H66">
-        <v>34926</v>
+        <v>34936</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20718</v>
+        <v>20825</v>
       </c>
       <c r="E67">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F67">
-        <v>47718</v>
+        <v>47825</v>
       </c>
       <c r="G67">
-        <v>68714</v>
+        <v>68868</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47986</v>
+        <v>48181</v>
       </c>
       <c r="E68">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F68">
-        <v>74986</v>
+        <v>75181</v>
       </c>
       <c r="G68">
-        <v>107980</v>
+        <v>108261</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27666</v>
+        <v>27788</v>
       </c>
       <c r="E69">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F69">
-        <v>54666</v>
+        <v>54788</v>
       </c>
       <c r="G69">
-        <v>78719</v>
+        <v>78895</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110457</v>
+        <v>110880</v>
       </c>
       <c r="E70">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F70">
-        <v>125457</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>180658</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52534</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F71">
-        <v>77712</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>111905</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>25178</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>27842</v>
+        <v>27751</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6805</v>
+        <v>6787</v>
       </c>
       <c r="E73">
-        <v>27842</v>
+        <v>27751</v>
       </c>
       <c r="F73">
-        <v>21805</v>
+        <v>21787</v>
       </c>
       <c r="G73">
-        <v>31399</v>
+        <v>31373</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>97492</v>
+        <v>97175</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70246</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>97492</v>
+        <v>97175</v>
       </c>
       <c r="F75">
-        <v>85246</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>122754</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87863</v>
+        <v>88346</v>
       </c>
       <c r="E76">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F76">
-        <v>122863</v>
+        <v>122832</v>
       </c>
       <c r="G76">
-        <v>176923</v>
+        <v>176878</v>
       </c>
       <c r="H76">
-        <v>35000</v>
+        <v>34486</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>61867</v>
+        <v>62203</v>
       </c>
       <c r="E77">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F77">
-        <v>81445</v>
+        <v>81414</v>
       </c>
       <c r="G77">
-        <v>117281</v>
+        <v>117236</v>
       </c>
       <c r="H77">
-        <v>19578</v>
+        <v>19211</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23198</v>
+        <v>23332</v>
       </c>
       <c r="E81">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F81">
-        <v>50198</v>
+        <v>50332</v>
       </c>
       <c r="G81">
-        <v>72285</v>
+        <v>72478</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86909</v>
+        <v>87372</v>
       </c>
       <c r="E83">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F83">
-        <v>101909</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>146749</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47048</v>
+        <v>47080</v>
       </c>
       <c r="E84">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F84">
-        <v>62740</v>
+        <v>62080</v>
       </c>
       <c r="G84">
-        <v>90346</v>
+        <v>89395</v>
       </c>
       <c r="H84">
-        <v>15692</v>
+        <v>15000</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>34996</v>
+        <v>35581</v>
       </c>
       <c r="E85">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>50581</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>72837</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8189</v>
+        <v>8225</v>
       </c>
       <c r="E90">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F90">
-        <v>38648</v>
+        <v>38579</v>
       </c>
       <c r="G90">
-        <v>55653</v>
+        <v>55554</v>
       </c>
       <c r="H90">
-        <v>30459</v>
+        <v>30354</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3689</v>
+        <v>3705</v>
       </c>
       <c r="E91">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F91">
-        <v>30648</v>
+        <v>30579</v>
       </c>
       <c r="G91">
-        <v>44133</v>
+        <v>44034</v>
       </c>
       <c r="H91">
-        <v>26959</v>
+        <v>26874</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>27842</v>
+        <v>27751</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9476</v>
+        <v>9518</v>
       </c>
       <c r="E93">
-        <v>27842</v>
+        <v>27751</v>
       </c>
       <c r="F93">
-        <v>24476</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35245</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4546,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>35271</v>
+        <v>35156</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>35271</v>
+        <v>35156</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63679</v>
+        <v>63928</v>
       </c>
       <c r="E96">
-        <v>83562</v>
+        <v>83290</v>
       </c>
       <c r="F96">
-        <v>78679</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>113298</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34471</v>
+        <v>34655</v>
       </c>
       <c r="E97">
-        <v>83562</v>
+        <v>83290</v>
       </c>
       <c r="F97">
-        <v>52377</v>
+        <v>52345</v>
       </c>
       <c r="G97">
-        <v>75423</v>
+        <v>75377</v>
       </c>
       <c r="H97">
-        <v>17906</v>
+        <v>17690</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79039</v>
+        <v>79467</v>
       </c>
       <c r="E98">
-        <v>96564</v>
+        <v>96249</v>
       </c>
       <c r="F98">
-        <v>94039</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>135416</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>43773</v>
+        <v>44013</v>
       </c>
       <c r="E99">
-        <v>96564</v>
+        <v>96249</v>
       </c>
       <c r="F99">
-        <v>61169</v>
+        <v>61142</v>
       </c>
       <c r="G99">
-        <v>88083</v>
+        <v>88044</v>
       </c>
       <c r="H99">
-        <v>17396</v>
+        <v>17129</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60452</v>
+        <v>60782</v>
       </c>
       <c r="E100">
-        <v>108265</v>
+        <v>107912</v>
       </c>
       <c r="F100">
-        <v>81199</v>
+        <v>78873</v>
       </c>
       <c r="G100">
-        <v>116927</v>
+        <v>113577</v>
       </c>
       <c r="H100">
-        <v>20747</v>
+        <v>18091</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63266</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>108265</v>
+        <v>107912</v>
       </c>
       <c r="F101">
-        <v>78266</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>112703</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>139283</v>
+        <v>138829</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>139283</v>
+        <v>138829</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5112,16 +5112,16 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>74905</v>
+        <v>75235</v>
       </c>
       <c r="E107">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F107">
-        <v>101905</v>
+        <v>102235</v>
       </c>
       <c r="G107">
-        <v>146743</v>
+        <v>147218</v>
       </c>
       <c r="H107">
         <v>27000</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6153</v>
+        <v>5765</v>
       </c>
       <c r="E109">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F109">
-        <v>33153</v>
+        <v>32765</v>
       </c>
       <c r="G109">
-        <v>47740</v>
+        <v>47182</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5244,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>167143</v>
+        <v>166598</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15041</v>
+        <v>15124</v>
       </c>
       <c r="E111">
-        <v>167143</v>
+        <v>166598</v>
       </c>
       <c r="F111">
-        <v>42041</v>
+        <v>42124</v>
       </c>
       <c r="G111">
-        <v>60539</v>
+        <v>60659</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51023</v>
+        <v>51296</v>
       </c>
       <c r="E113">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F113">
-        <v>77107</v>
+        <v>77052</v>
       </c>
       <c r="G113">
-        <v>111034</v>
+        <v>110955</v>
       </c>
       <c r="H113">
-        <v>26084</v>
+        <v>25756</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>99014</v>
       </c>
       <c r="E115">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>117799</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>169631</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>18785</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80088</v>
+        <v>80521</v>
       </c>
       <c r="E118">
-        <v>89134</v>
+        <v>88844</v>
       </c>
       <c r="F118">
-        <v>95088</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>136927</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,16 +5629,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50037</v>
+        <v>47239</v>
       </c>
       <c r="E119">
-        <v>89134</v>
+        <v>88844</v>
       </c>
       <c r="F119">
-        <v>65037</v>
+        <v>62239</v>
       </c>
       <c r="G119">
-        <v>93653</v>
+        <v>89624</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5676,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>118852</v>
+        <v>118465</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>85781</v>
+        <v>102432</v>
       </c>
       <c r="E121">
-        <v>118852</v>
+        <v>118465</v>
       </c>
       <c r="F121">
-        <v>100781</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>145125</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>207765</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F122">
-        <v>222765</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>320782</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46126</v>
+        <v>46297</v>
       </c>
       <c r="E124">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F124">
-        <v>61126</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>88021</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35060</v>
+        <v>35246</v>
       </c>
       <c r="E125">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F125">
-        <v>50060</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72086</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63648</v>
+        <v>63912</v>
       </c>
       <c r="E126">
-        <v>81705</v>
+        <v>81439</v>
       </c>
       <c r="F126">
-        <v>78648</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>113253</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>81705</v>
+        <v>81439</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>38748</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F128">
-        <v>65460</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>94262</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>26712</v>
+        <v>0</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36777</v>
+        <v>36875</v>
       </c>
       <c r="E129">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F129">
-        <v>56922</v>
+        <v>56843</v>
       </c>
       <c r="G129">
-        <v>81968</v>
+        <v>81854</v>
       </c>
       <c r="H129">
-        <v>20145</v>
+        <v>19968</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12720</v>
+        <v>12760</v>
       </c>
       <c r="E130">
-        <v>44558</v>
+        <v>44413</v>
       </c>
       <c r="F130">
-        <v>33197</v>
+        <v>33148</v>
       </c>
       <c r="G130">
-        <v>47804</v>
+        <v>47733</v>
       </c>
       <c r="H130">
-        <v>20477</v>
+        <v>20388</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4547</v>
+        <v>4567</v>
       </c>
       <c r="E131">
-        <v>44558</v>
+        <v>44413</v>
       </c>
       <c r="F131">
-        <v>25197</v>
+        <v>25148</v>
       </c>
       <c r="G131">
-        <v>36284</v>
+        <v>36213</v>
       </c>
       <c r="H131">
-        <v>20650</v>
+        <v>20581</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27666</v>
+        <v>27772</v>
       </c>
       <c r="E132">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F132">
-        <v>43804</v>
+        <v>43759</v>
       </c>
       <c r="G132">
-        <v>63078</v>
+        <v>63013</v>
       </c>
       <c r="H132">
-        <v>16138</v>
+        <v>15987</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -6292,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>60884</v>
+        <v>60686</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>20575</v>
+        <v>17375</v>
       </c>
       <c r="E135">
-        <v>60884</v>
+        <v>60686</v>
       </c>
       <c r="F135">
-        <v>37975</v>
+        <v>36618</v>
       </c>
       <c r="G135">
-        <v>54684</v>
+        <v>52730</v>
       </c>
       <c r="H135">
-        <v>17400</v>
+        <v>19243</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6379,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>75854</v>
+        <v>75607</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>26601</v>
+        <v>28155</v>
       </c>
       <c r="E137">
-        <v>75854</v>
+        <v>75607</v>
       </c>
       <c r="F137">
-        <v>46223</v>
+        <v>46749</v>
       </c>
       <c r="G137">
-        <v>66561</v>
+        <v>67319</v>
       </c>
       <c r="H137">
-        <v>19622</v>
+        <v>18594</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>95486</v>
+        <v>95175</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>26537</v>
+        <v>27948</v>
       </c>
       <c r="E139">
-        <v>95486</v>
+        <v>95175</v>
       </c>
       <c r="F139">
-        <v>53537</v>
+        <v>54298</v>
       </c>
       <c r="G139">
-        <v>77093</v>
+        <v>78189</v>
       </c>
       <c r="H139">
-        <v>27000</v>
+        <v>26350</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>90992</v>
+        <v>90695</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58051</v>
+        <v>58370</v>
       </c>
       <c r="E141">
-        <v>90992</v>
+        <v>90695</v>
       </c>
       <c r="F141">
-        <v>73051</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>105193</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77449</v>
+        <v>77870</v>
       </c>
       <c r="E143">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F143">
-        <v>92449</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>133127</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>155999</v>
+        <v>155491</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>86989</v>
+        <v>87468</v>
       </c>
       <c r="E145">
-        <v>155999</v>
+        <v>155491</v>
       </c>
       <c r="F145">
-        <v>101989</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>146864</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>90992</v>
+        <v>90695</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86210</v>
+        <v>86589</v>
       </c>
       <c r="E147">
-        <v>90992</v>
+        <v>90695</v>
       </c>
       <c r="F147">
-        <v>101210</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>145742</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6896,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>125896</v>
+        <v>126546</v>
       </c>
       <c r="E149">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F149">
-        <v>140896</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>202890</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38224</v>
+        <v>38440</v>
       </c>
       <c r="E150">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F150">
-        <v>63072</v>
+        <v>63022</v>
       </c>
       <c r="G150">
-        <v>90824</v>
+        <v>90752</v>
       </c>
       <c r="H150">
-        <v>24848</v>
+        <v>24582</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24884</v>
+        <v>24211</v>
       </c>
       <c r="E152">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F152">
-        <v>59884</v>
+        <v>59211</v>
       </c>
       <c r="G152">
-        <v>86233</v>
+        <v>85264</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29606</v>
+        <v>29768</v>
       </c>
       <c r="E153">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F153">
-        <v>54054</v>
+        <v>54000</v>
       </c>
       <c r="G153">
-        <v>77838</v>
+        <v>77760</v>
       </c>
       <c r="H153">
-        <v>24448</v>
+        <v>24232</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,19 +7155,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48622</v>
+        <v>48884</v>
       </c>
       <c r="E154">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F154">
-        <v>69637</v>
+        <v>69410</v>
       </c>
       <c r="G154">
-        <v>100277</v>
+        <v>99950</v>
       </c>
       <c r="H154">
-        <v>21015</v>
+        <v>20526</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>75334</v>
+        <v>75985</v>
       </c>
       <c r="E155">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F155">
-        <v>90334</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>130081</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65333</v>
+        <v>65701</v>
       </c>
       <c r="E156">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F156">
-        <v>80333</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>115680</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7292,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>38939</v>
+        <v>42975</v>
       </c>
       <c r="E158">
-        <v>63131</v>
+        <v>62926</v>
       </c>
       <c r="F158">
-        <v>65504</v>
+        <v>65772</v>
       </c>
       <c r="G158">
-        <v>94326</v>
+        <v>94712</v>
       </c>
       <c r="H158">
-        <v>26565</v>
+        <v>22797</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>41960</v>
+        <v>42193</v>
       </c>
       <c r="E159">
-        <v>63131</v>
+        <v>62926</v>
       </c>
       <c r="F159">
-        <v>56960</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>82022</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20050</v>
+        <v>20170</v>
       </c>
       <c r="E161">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F161">
-        <v>35744</v>
+        <v>35721</v>
       </c>
       <c r="G161">
-        <v>51471</v>
+        <v>51438</v>
       </c>
       <c r="H161">
-        <v>15694</v>
+        <v>15551</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7510,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56032</v>
+        <v>56294</v>
       </c>
       <c r="E163">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F163">
-        <v>71032</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>102286</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70644</v>
+        <v>81000</v>
       </c>
       <c r="E165">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F165">
-        <v>85644</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>123327</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54044</v>
+        <v>59009</v>
       </c>
       <c r="E166">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F166">
-        <v>69044</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>99423</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33931</v>
+        <v>34112</v>
       </c>
       <c r="E167">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F167">
-        <v>48931</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70461</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,16 +7769,16 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60388</v>
+        <v>60622</v>
       </c>
       <c r="E168">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F168">
-        <v>95388</v>
+        <v>95622</v>
       </c>
       <c r="G168">
-        <v>137359</v>
+        <v>137696</v>
       </c>
       <c r="H168">
         <v>35000</v>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74094</v>
+        <v>74420</v>
       </c>
       <c r="E169">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F169">
-        <v>89094</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>128295</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7861,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>27842</v>
+        <v>27751</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -7902,16 +7902,16 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15503</v>
+        <v>15124</v>
       </c>
       <c r="E171">
-        <v>27842</v>
+        <v>27751</v>
       </c>
       <c r="F171">
-        <v>30503</v>
+        <v>30124</v>
       </c>
       <c r="G171">
-        <v>43924</v>
+        <v>43379</v>
       </c>
       <c r="H171">
         <v>15000</v>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>85420</v>
+        <v>85141</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30353</v>
+        <v>30263</v>
       </c>
       <c r="E173">
-        <v>85420</v>
+        <v>85141</v>
       </c>
       <c r="F173">
-        <v>51455</v>
+        <v>51310</v>
       </c>
       <c r="G173">
-        <v>74095</v>
+        <v>73886</v>
       </c>
       <c r="H173">
-        <v>21102</v>
+        <v>21047</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7775</v>
+        <v>7410</v>
       </c>
       <c r="E174">
-        <v>55721</v>
+        <v>55539</v>
       </c>
       <c r="F174">
-        <v>37843</v>
+        <v>37774</v>
       </c>
       <c r="G174">
-        <v>54494</v>
+        <v>54395</v>
       </c>
       <c r="H174">
-        <v>30068</v>
+        <v>30364</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5279</v>
+        <v>5286</v>
       </c>
       <c r="E175">
-        <v>55721</v>
+        <v>55539</v>
       </c>
       <c r="F175">
-        <v>29843</v>
+        <v>29774</v>
       </c>
       <c r="G175">
-        <v>42974</v>
+        <v>42875</v>
       </c>
       <c r="H175">
-        <v>24564</v>
+        <v>24488</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10128</v>
+        <v>10365</v>
       </c>
       <c r="E176">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F176">
-        <v>43793</v>
+        <v>43656</v>
       </c>
       <c r="G176">
-        <v>63062</v>
+        <v>62865</v>
       </c>
       <c r="H176">
-        <v>33665</v>
+        <v>33291</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>8793</v>
+        <v>8656</v>
       </c>
       <c r="E177">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F177">
-        <v>35793</v>
+        <v>35656</v>
       </c>
       <c r="G177">
-        <v>51542</v>
+        <v>51345</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8215,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>69651</v>
+        <v>69424</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21847</v>
+        <v>21959</v>
       </c>
       <c r="E179">
-        <v>69651</v>
+        <v>69424</v>
       </c>
       <c r="F179">
-        <v>41903</v>
+        <v>41859</v>
       </c>
       <c r="G179">
-        <v>60340</v>
+        <v>60277</v>
       </c>
       <c r="H179">
-        <v>20056</v>
+        <v>19900</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>104940</v>
+        <v>104598</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45808</v>
+        <v>46201</v>
       </c>
       <c r="E181">
-        <v>104940</v>
+        <v>104598</v>
       </c>
       <c r="F181">
-        <v>65250</v>
+        <v>65274</v>
       </c>
       <c r="G181">
-        <v>93960</v>
+        <v>93995</v>
       </c>
       <c r="H181">
-        <v>19442</v>
+        <v>19073</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67877</v>
+        <v>68144</v>
       </c>
       <c r="E182">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F182">
-        <v>86183</v>
+        <v>86227</v>
       </c>
       <c r="G182">
-        <v>124104</v>
+        <v>124167</v>
       </c>
       <c r="H182">
-        <v>18306</v>
+        <v>18083</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>9794</v>
+        <v>9838</v>
       </c>
       <c r="E183">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F183">
-        <v>36794</v>
+        <v>36838</v>
       </c>
       <c r="G183">
-        <v>52983</v>
+        <v>53047</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60563</v>
+        <v>71785</v>
       </c>
       <c r="E184">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F184">
-        <v>80365</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>115726</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>19802</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>48781</v>
+        <v>0</v>
       </c>
       <c r="E185">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F185">
-        <v>68967</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>99312</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>20186</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>79961</v>
+        <v>89783</v>
       </c>
       <c r="E186">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F186">
-        <v>110937</v>
+        <v>111064</v>
       </c>
       <c r="G186">
-        <v>159749</v>
+        <v>159932</v>
       </c>
       <c r="H186">
-        <v>30976</v>
+        <v>21281</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81313</v>
+        <v>81671</v>
       </c>
       <c r="E187">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F187">
-        <v>96467</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>138912</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15154</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8657,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="E188">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="E189">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>141908</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>157856</v>
+        <v>157342</v>
       </c>
       <c r="F190">
-        <v>156908</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>225948</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8784,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="E191">
-        <v>157856</v>
+        <v>157342</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>172444</v>
       </c>
       <c r="E192">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>187444</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>269919</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8869,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -8908,19 +8908,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7076</v>
+        <v>7298</v>
       </c>
       <c r="E194">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F194">
-        <v>35000</v>
+        <v>34938</v>
       </c>
       <c r="G194">
-        <v>50400</v>
+        <v>50311</v>
       </c>
       <c r="H194">
-        <v>27924</v>
+        <v>27640</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8956,7 +8956,7 @@
         <v>0</v>
       </c>
       <c r="E195">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11750</v>
+        <v>11802</v>
       </c>
       <c r="E196">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F196">
-        <v>38750</v>
+        <v>38802</v>
       </c>
       <c r="G196">
-        <v>55800</v>
+        <v>55875</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9044,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="E197">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -9083,19 +9083,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51659</v>
+        <v>51855</v>
       </c>
       <c r="E198">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F198">
-        <v>69637</v>
+        <v>69410</v>
       </c>
       <c r="G198">
-        <v>100277</v>
+        <v>99950</v>
       </c>
       <c r="H198">
-        <v>17978</v>
+        <v>17555</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74873</v>
+        <v>75283</v>
       </c>
       <c r="E199">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F199">
-        <v>89873</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129417</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>56636</v>
+        <v>56949</v>
       </c>
       <c r="E200">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F200">
-        <v>71636</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>103156</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="E201">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36713</v>
+        <v>36859</v>
       </c>
       <c r="E202">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F202">
-        <v>63713</v>
+        <v>63859</v>
       </c>
       <c r="G202">
-        <v>91747</v>
+        <v>91957</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9308,7 +9308,7 @@
         <v>0</v>
       </c>
       <c r="E203">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27475</v>
+        <v>27596</v>
       </c>
       <c r="E204">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F204">
-        <v>54475</v>
+        <v>54596</v>
       </c>
       <c r="G204">
-        <v>78444</v>
+        <v>78618</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9397,7 +9397,7 @@
         <v>0</v>
       </c>
       <c r="E205">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>101744</v>
+        <v>0</v>
       </c>
       <c r="E206">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F206">
-        <v>116744</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>168111</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63743</v>
+        <v>63896</v>
       </c>
       <c r="E207">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F207">
-        <v>82195</v>
+        <v>82092</v>
       </c>
       <c r="G207">
-        <v>118361</v>
+        <v>118212</v>
       </c>
       <c r="H207">
-        <v>18452</v>
+        <v>18196</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,19 +9524,19 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>144674</v>
+        <v>0</v>
       </c>
       <c r="E208">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F208">
-        <v>179674</v>
+        <v>0</v>
       </c>
       <c r="G208">
-        <v>258731</v>
+        <v>0</v>
       </c>
       <c r="H208">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I208" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>144579</v>
+        <v>145359</v>
       </c>
       <c r="E209">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F209">
-        <v>159579</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>229794</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>187604</v>
+        <v>0</v>
       </c>
       <c r="E210">
-        <v>241437</v>
+        <v>240650</v>
       </c>
       <c r="F210">
-        <v>202604</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>291750</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>185951</v>
+        <v>186961</v>
       </c>
       <c r="E211">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F211">
-        <v>200951</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>289369</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>287774</v>
+        <v>289041</v>
       </c>
       <c r="E212">
-        <v>371451</v>
+        <v>370241</v>
       </c>
       <c r="F212">
-        <v>302774</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>435995</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>224349</v>
+        <v>0</v>
       </c>
       <c r="E213">
-        <v>371451</v>
+        <v>370241</v>
       </c>
       <c r="F213">
-        <v>240605</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>346471</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>16256</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34455</v>
+        <v>34463</v>
       </c>
       <c r="E214">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F214">
-        <v>61153</v>
+        <v>59372</v>
       </c>
       <c r="G214">
-        <v>88060</v>
+        <v>85496</v>
       </c>
       <c r="H214">
-        <v>26698</v>
+        <v>24909</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>37969</v>
+        <v>36188</v>
       </c>
       <c r="E215">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F215">
-        <v>52969</v>
+        <v>51188</v>
       </c>
       <c r="G215">
-        <v>76275</v>
+        <v>73711</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>16441</v>
+        <v>16513</v>
       </c>
       <c r="E216">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F216">
-        <v>36815</v>
+        <v>36765</v>
       </c>
       <c r="G216">
-        <v>53014</v>
+        <v>52942</v>
       </c>
       <c r="H216">
-        <v>20374</v>
+        <v>20252</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16441</v>
+        <v>16513</v>
       </c>
       <c r="E218">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F218">
-        <v>36815</v>
+        <v>36765</v>
       </c>
       <c r="G218">
-        <v>53014</v>
+        <v>52942</v>
       </c>
       <c r="H218">
-        <v>20374</v>
+        <v>20252</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10008,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="E219">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12561</v>
+        <v>12872</v>
       </c>
       <c r="E220">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F220">
-        <v>44604</v>
+        <v>39872</v>
       </c>
       <c r="G220">
-        <v>64230</v>
+        <v>57416</v>
       </c>
       <c r="H220">
-        <v>32043</v>
+        <v>27000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,19 +10094,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>9604</v>
+        <v>0</v>
       </c>
       <c r="E221">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F221">
-        <v>36604</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>52710</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>20924</v>
+        <v>22550</v>
       </c>
       <c r="E222">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F222">
-        <v>55924</v>
+        <v>49550</v>
       </c>
       <c r="G222">
-        <v>80531</v>
+        <v>71352</v>
       </c>
       <c r="H222">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>53567</v>
+        <v>0</v>
       </c>
       <c r="E223">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F223">
-        <v>70881</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>102069</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>17314</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16759</v>
+        <v>17008</v>
       </c>
       <c r="E224">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F224">
-        <v>46146</v>
+        <v>46195</v>
       </c>
       <c r="G224">
-        <v>66450</v>
+        <v>66521</v>
       </c>
       <c r="H224">
-        <v>29387</v>
+        <v>29187</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11146</v>
+        <v>11195</v>
       </c>
       <c r="E225">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F225">
-        <v>38146</v>
+        <v>38195</v>
       </c>
       <c r="G225">
-        <v>54930</v>
+        <v>55001</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26489</v>
+        <v>26590</v>
       </c>
       <c r="E226">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F226">
-        <v>61489</v>
+        <v>61590</v>
       </c>
       <c r="G226">
-        <v>88544</v>
+        <v>88690</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>95416</v>
+        <v>38552</v>
       </c>
       <c r="E227">
-        <v>148569</v>
+        <v>148085</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>65552</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>94395</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35711</v>
+        <v>35853</v>
       </c>
       <c r="E228">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F228">
-        <v>62711</v>
+        <v>62853</v>
       </c>
       <c r="G228">
-        <v>90304</v>
+        <v>90508</v>
       </c>
       <c r="H228">
         <v>27000</v>
@@ -10455,7 +10455,7 @@
         <v>0</v>
       </c>
       <c r="E229">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F229">
         <v>0</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15741</v>
+        <v>15922</v>
       </c>
       <c r="E230">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F230">
-        <v>43002</v>
+        <v>42836</v>
       </c>
       <c r="G230">
-        <v>61923</v>
+        <v>61684</v>
       </c>
       <c r="H230">
-        <v>27261</v>
+        <v>26914</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>10049</v>
+        <v>9822</v>
       </c>
       <c r="E231">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F231">
-        <v>33192</v>
+        <v>33026</v>
       </c>
       <c r="G231">
-        <v>47796</v>
+        <v>47557</v>
       </c>
       <c r="H231">
-        <v>23143</v>
+        <v>23204</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10588,7 +10588,7 @@
         <v>0</v>
       </c>
       <c r="E232">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F232">
         <v>0</v>
@@ -10631,7 +10631,7 @@
         <v>0</v>
       </c>
       <c r="E233">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F233">
         <v>0</v>
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="E234">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41674</v>
+        <v>0</v>
       </c>
       <c r="E235">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F235">
-        <v>66124</v>
+        <v>0</v>
       </c>
       <c r="G235">
-        <v>95219</v>
+        <v>0</v>
       </c>
       <c r="H235">
-        <v>24450</v>
+        <v>0</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10760,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="E236">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F236">
         <v>0</v>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>86019</v>
+        <v>86398</v>
       </c>
       <c r="E237">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F237">
-        <v>112837</v>
+        <v>112752</v>
       </c>
       <c r="G237">
-        <v>162485</v>
+        <v>162363</v>
       </c>
       <c r="H237">
-        <v>26818</v>
+        <v>26354</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26553</v>
+        <v>26702</v>
       </c>
       <c r="E238">
-        <v>89134</v>
+        <v>88844</v>
       </c>
       <c r="F238">
-        <v>61541</v>
+        <v>53702</v>
       </c>
       <c r="G238">
-        <v>88619</v>
+        <v>77331</v>
       </c>
       <c r="H238">
-        <v>34988</v>
+        <v>27000</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31880</v>
+        <v>0</v>
       </c>
       <c r="E239">
-        <v>89134</v>
+        <v>88844</v>
       </c>
       <c r="F239">
-        <v>53514</v>
+        <v>0</v>
       </c>
       <c r="G239">
-        <v>77060</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>21634</v>
+        <v>0</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46921</v>
+        <v>47175</v>
       </c>
       <c r="E240">
-        <v>103993</v>
+        <v>103654</v>
       </c>
       <c r="F240">
-        <v>77995</v>
+        <v>71515</v>
       </c>
       <c r="G240">
-        <v>112313</v>
+        <v>102982</v>
       </c>
       <c r="H240">
-        <v>31074</v>
+        <v>24340</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>85733</v>
+        <v>0</v>
       </c>
       <c r="E241">
-        <v>103993</v>
+        <v>103654</v>
       </c>
       <c r="F241">
-        <v>100733</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>145056</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="E242">
-        <v>133711</v>
+        <v>133275</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>110664</v>
+        <v>0</v>
       </c>
       <c r="E243">
-        <v>133711</v>
+        <v>133275</v>
       </c>
       <c r="F243">
-        <v>125664</v>
+        <v>0</v>
       </c>
       <c r="G243">
-        <v>180956</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64188</v>
+        <v>64439</v>
       </c>
       <c r="E244">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F244">
-        <v>79188</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>114031</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11158,7 +11158,7 @@
         <v>0</v>
       </c>
       <c r="E245">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75668</v>
+        <v>76512</v>
       </c>
       <c r="E246">
-        <v>98440</v>
+        <v>98119</v>
       </c>
       <c r="F246">
-        <v>90668</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>130562</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11248,7 +11248,7 @@
         <v>0</v>
       </c>
       <c r="E247">
-        <v>98440</v>
+        <v>98119</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17840</v>
+        <v>17711</v>
       </c>
       <c r="E248">
-        <v>61274</v>
+        <v>61074</v>
       </c>
       <c r="F248">
-        <v>42578</v>
+        <v>42527</v>
       </c>
       <c r="G248">
-        <v>61312</v>
+        <v>61239</v>
       </c>
       <c r="H248">
-        <v>24738</v>
+        <v>24816</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11702</v>
+        <v>11770</v>
       </c>
       <c r="E249">
-        <v>61274</v>
+        <v>61074</v>
       </c>
       <c r="F249">
-        <v>34578</v>
+        <v>34527</v>
       </c>
       <c r="G249">
-        <v>49792</v>
+        <v>49719</v>
       </c>
       <c r="H249">
-        <v>22876</v>
+        <v>22757</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11382,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="E250">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F250">
         <v>0</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F251">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="E252">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F252">
         <v>0</v>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16631</v>
+        <v>0</v>
       </c>
       <c r="E253">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F253">
-        <v>43631</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>62829</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11557,7 +11557,7 @@
         <v>0</v>
       </c>
       <c r="E254">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F254">
         <v>0</v>
@@ -11599,7 +11599,7 @@
         <v>0</v>
       </c>
       <c r="E255">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F255">
         <v>0</v>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9635</v>
+        <v>9678</v>
       </c>
       <c r="E256">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F256">
-        <v>40397</v>
+        <v>40266</v>
       </c>
       <c r="G256">
-        <v>58172</v>
+        <v>57983</v>
       </c>
       <c r="H256">
-        <v>30762</v>
+        <v>30588</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14882</v>
+        <v>14948</v>
       </c>
       <c r="E257">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F257">
-        <v>32959</v>
+        <v>32917</v>
       </c>
       <c r="G257">
-        <v>47461</v>
+        <v>47400</v>
       </c>
       <c r="H257">
-        <v>18077</v>
+        <v>17969</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12243</v>
+        <v>12281</v>
       </c>
       <c r="E258">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F258">
-        <v>39243</v>
+        <v>39281</v>
       </c>
       <c r="G258">
-        <v>56510</v>
+        <v>56565</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11775,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="E259">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F259">
         <v>0</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8856</v>
+        <v>8895</v>
       </c>
       <c r="E260">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F260">
-        <v>39414</v>
+        <v>39346</v>
       </c>
       <c r="G260">
-        <v>56756</v>
+        <v>56658</v>
       </c>
       <c r="H260">
-        <v>30558</v>
+        <v>30451</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11862,16 +11862,16 @@
         <v>11019</v>
       </c>
       <c r="E261">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F261">
-        <v>31414</v>
+        <v>31346</v>
       </c>
       <c r="G261">
-        <v>45236</v>
+        <v>45138</v>
       </c>
       <c r="H261">
-        <v>20395</v>
+        <v>20327</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>11607</v>
+        <v>11562</v>
       </c>
       <c r="E262">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F262">
-        <v>39211</v>
+        <v>34938</v>
       </c>
       <c r="G262">
-        <v>56464</v>
+        <v>50311</v>
       </c>
       <c r="H262">
-        <v>27604</v>
+        <v>23376</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10510</v>
+        <v>0</v>
       </c>
       <c r="E263">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F263">
-        <v>31211</v>
+        <v>0</v>
       </c>
       <c r="G263">
-        <v>44944</v>
+        <v>0</v>
       </c>
       <c r="H263">
-        <v>20701</v>
+        <v>0</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>17951</v>
+        <v>18605</v>
       </c>
       <c r="E264">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F264">
-        <v>44951</v>
+        <v>51875</v>
       </c>
       <c r="G264">
-        <v>64729</v>
+        <v>74700</v>
       </c>
       <c r="H264">
-        <v>27000</v>
+        <v>33270</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>24290</v>
       </c>
       <c r="E265">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>43875</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>63180</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>19585</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34360</v>
+        <v>34495</v>
       </c>
       <c r="E266">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F266">
-        <v>54328</v>
+        <v>54151</v>
       </c>
       <c r="G266">
-        <v>78232</v>
+        <v>77977</v>
       </c>
       <c r="H266">
-        <v>19968</v>
+        <v>19656</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>30941</v>
+        <v>31078</v>
       </c>
       <c r="E267">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F267">
-        <v>46627</v>
+        <v>46590</v>
       </c>
       <c r="G267">
-        <v>67143</v>
+        <v>67090</v>
       </c>
       <c r="H267">
-        <v>15686</v>
+        <v>15512</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10256</v>
+        <v>10285</v>
       </c>
       <c r="E268">
-        <v>27860</v>
+        <v>27770</v>
       </c>
       <c r="F268">
-        <v>25256</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>36369</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12214,7 +12214,7 @@
         <v>0</v>
       </c>
       <c r="E269">
-        <v>27860</v>
+        <v>27770</v>
       </c>
       <c r="F269">
         <v>0</v>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12084</v>
+        <v>12217</v>
       </c>
       <c r="E270">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F270">
-        <v>39084</v>
+        <v>39217</v>
       </c>
       <c r="G270">
-        <v>56281</v>
+        <v>56472</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12302,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="E271">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F271">
         <v>0</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62487</v>
+        <v>62666</v>
       </c>
       <c r="E272">
-        <v>98440</v>
+        <v>98119</v>
       </c>
       <c r="F272">
-        <v>77487</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>111581</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>38891</v>
+        <v>39063</v>
       </c>
       <c r="E273">
-        <v>98440</v>
+        <v>98119</v>
       </c>
       <c r="F273">
-        <v>59948</v>
+        <v>59891</v>
       </c>
       <c r="G273">
-        <v>86325</v>
+        <v>86243</v>
       </c>
       <c r="H273">
-        <v>21057</v>
+        <v>20828</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,16 +12430,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>71423</v>
+        <v>71003</v>
       </c>
       <c r="E274">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F274">
-        <v>106423</v>
+        <v>106003</v>
       </c>
       <c r="G274">
-        <v>153249</v>
+        <v>152644</v>
       </c>
       <c r="H274">
         <v>35000</v>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>77735</v>
+        <v>78077</v>
       </c>
       <c r="E275">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F275">
-        <v>92735</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>133538</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11162</v>
+        <v>11211</v>
       </c>
       <c r="E276">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F276">
-        <v>35000</v>
+        <v>37870</v>
       </c>
       <c r="G276">
-        <v>50400</v>
+        <v>54533</v>
       </c>
       <c r="H276">
-        <v>23838</v>
+        <v>26659</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>7330</v>
       </c>
       <c r="E277">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>29870</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>43013</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>22540</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20066</v>
+        <v>20138</v>
       </c>
       <c r="E278">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F278">
-        <v>46623</v>
+        <v>51875</v>
       </c>
       <c r="G278">
-        <v>67137</v>
+        <v>74700</v>
       </c>
       <c r="H278">
-        <v>26557</v>
+        <v>31737</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>24290</v>
       </c>
       <c r="E279">
-        <v>72437</v>
+        <v>72201</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>43875</v>
       </c>
       <c r="G279">
-        <v>0</v>
+        <v>63180</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>19585</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,19 +12697,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11718</v>
+        <v>11786</v>
       </c>
       <c r="E280">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F280">
-        <v>35000</v>
+        <v>34938</v>
       </c>
       <c r="G280">
-        <v>50400</v>
+        <v>50311</v>
       </c>
       <c r="H280">
-        <v>23282</v>
+        <v>23152</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="E281">
-        <v>53863</v>
+        <v>53688</v>
       </c>
       <c r="F281">
         <v>0</v>
@@ -12787,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="E282">
-        <v>44558</v>
+        <v>44413</v>
       </c>
       <c r="F282">
         <v>0</v>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17697</v>
+        <v>17743</v>
       </c>
       <c r="E283">
-        <v>44558</v>
+        <v>44413</v>
       </c>
       <c r="F283">
-        <v>32697</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>47084</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12873,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="E284">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>49878</v>
+        <v>50242</v>
       </c>
       <c r="E285">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F285">
-        <v>64878</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>93424</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12959,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="E286">
-        <v>66846</v>
+        <v>66628</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58655</v>
+        <v>59073</v>
       </c>
       <c r="E287">
-        <v>66846</v>
+        <v>66628</v>
       </c>
       <c r="F287">
-        <v>73655</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>106063</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>34646</v>
+        <v>34799</v>
       </c>
       <c r="E288">
-        <v>61274</v>
+        <v>61074</v>
       </c>
       <c r="F288">
-        <v>55844</v>
+        <v>55814</v>
       </c>
       <c r="G288">
-        <v>80415</v>
+        <v>80372</v>
       </c>
       <c r="H288">
-        <v>21198</v>
+        <v>21015</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23723</v>
+        <v>23843</v>
       </c>
       <c r="E289">
-        <v>61274</v>
+        <v>61074</v>
       </c>
       <c r="F289">
-        <v>39386</v>
+        <v>39356</v>
       </c>
       <c r="G289">
-        <v>56716</v>
+        <v>56673</v>
       </c>
       <c r="H289">
-        <v>15663</v>
+        <v>15513</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13135,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="E290">
-        <v>68703</v>
+        <v>68480</v>
       </c>
       <c r="F290">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="E291">
-        <v>68703</v>
+        <v>68480</v>
       </c>
       <c r="F291">
         <v>0</v>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>44488</v>
+        <v>44844</v>
       </c>
       <c r="E292">
-        <v>61274</v>
+        <v>61074</v>
       </c>
       <c r="F292">
-        <v>62218</v>
+        <v>62194</v>
       </c>
       <c r="G292">
-        <v>89594</v>
+        <v>89559</v>
       </c>
       <c r="H292">
-        <v>17730</v>
+        <v>17350</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23643</v>
+        <v>23779</v>
       </c>
       <c r="E293">
-        <v>61274</v>
+        <v>61074</v>
       </c>
       <c r="F293">
-        <v>39354</v>
+        <v>39330</v>
       </c>
       <c r="G293">
-        <v>56670</v>
+        <v>56635</v>
       </c>
       <c r="H293">
-        <v>15711</v>
+        <v>15551</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>49910</v>
+        <v>50082</v>
       </c>
       <c r="E294">
-        <v>68703</v>
+        <v>68480</v>
       </c>
       <c r="F294">
-        <v>64910</v>
+        <v>0</v>
       </c>
       <c r="G294">
-        <v>93470</v>
+        <v>0</v>
       </c>
       <c r="H294">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>26092</v>
+        <v>0</v>
       </c>
       <c r="E295">
-        <v>68703</v>
+        <v>68480</v>
       </c>
       <c r="F295">
-        <v>43231</v>
+        <v>0</v>
       </c>
       <c r="G295">
-        <v>62253</v>
+        <v>0</v>
       </c>
       <c r="H295">
-        <v>17139</v>
+        <v>0</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62630</v>
+        <v>62906</v>
       </c>
       <c r="E296">
-        <v>78919</v>
+        <v>78662</v>
       </c>
       <c r="F296">
-        <v>77630</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>111787</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13447,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="E297">
-        <v>78919</v>
+        <v>78662</v>
       </c>
       <c r="F297">
         <v>0</v>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74555</v>
+        <v>74883</v>
       </c>
       <c r="E298">
-        <v>94706</v>
+        <v>94398</v>
       </c>
       <c r="F298">
-        <v>89555</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>128959</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13533,7 +13533,7 @@
         <v>0</v>
       </c>
       <c r="E299">
-        <v>94706</v>
+        <v>94398</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>69292</v>
+        <v>70795</v>
       </c>
       <c r="E300">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F300">
-        <v>88557</v>
+        <v>89278</v>
       </c>
       <c r="G300">
-        <v>127522</v>
+        <v>128560</v>
       </c>
       <c r="H300">
-        <v>19265</v>
+        <v>18483</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33692</v>
+        <v>35789</v>
       </c>
       <c r="E301">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F301">
-        <v>55688</v>
+        <v>56409</v>
       </c>
       <c r="G301">
-        <v>80191</v>
+        <v>81229</v>
       </c>
       <c r="H301">
-        <v>21996</v>
+        <v>20620</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="E302">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F302">
         <v>0</v>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>11178</v>
+        <v>11227</v>
       </c>
       <c r="E303">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F303">
-        <v>38178</v>
+        <v>38227</v>
       </c>
       <c r="G303">
-        <v>54976</v>
+        <v>55047</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174041</v>
+        <v>174744</v>
       </c>
       <c r="E304">
-        <v>167143</v>
+        <v>166598</v>
       </c>
       <c r="F304">
-        <v>189041</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>272219</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>104765</v>
+        <v>0</v>
       </c>
       <c r="E305">
-        <v>167143</v>
+        <v>166598</v>
       </c>
       <c r="F305">
-        <v>119765</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>172462</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50006</v>
+        <v>50210</v>
       </c>
       <c r="E306">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F306">
-        <v>80074</v>
+        <v>80041</v>
       </c>
       <c r="G306">
-        <v>115307</v>
+        <v>115259</v>
       </c>
       <c r="H306">
-        <v>30068</v>
+        <v>29831</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50355</v>
+        <v>50625</v>
       </c>
       <c r="E307">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F307">
-        <v>69596</v>
+        <v>69563</v>
       </c>
       <c r="G307">
-        <v>100218</v>
+        <v>100171</v>
       </c>
       <c r="H307">
-        <v>19241</v>
+        <v>18938</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,19 +13924,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69213</v>
+        <v>69485</v>
       </c>
       <c r="E308">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F308">
-        <v>97497</v>
+        <v>97179</v>
       </c>
       <c r="G308">
-        <v>140396</v>
+        <v>139938</v>
       </c>
       <c r="H308">
-        <v>28284</v>
+        <v>27694</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77831</v>
+        <v>105897</v>
       </c>
       <c r="E309">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F309">
-        <v>92831</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>133677</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>23977</v>
+        <v>24626</v>
       </c>
       <c r="E310">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F310">
-        <v>41777</v>
+        <v>40834</v>
       </c>
       <c r="G310">
-        <v>60159</v>
+        <v>58801</v>
       </c>
       <c r="H310">
-        <v>17800</v>
+        <v>16208</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>37445</v>
+        <v>0</v>
       </c>
       <c r="E311">
-        <v>55702</v>
+        <v>55520</v>
       </c>
       <c r="F311">
-        <v>52445</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>75521</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>66160</v>
+        <v>68591</v>
       </c>
       <c r="E312">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F312">
-        <v>90116</v>
+        <v>83591</v>
       </c>
       <c r="G312">
-        <v>129767</v>
+        <v>120371</v>
       </c>
       <c r="H312">
-        <v>23956</v>
+        <v>15000</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63362</v>
+        <v>0</v>
       </c>
       <c r="E313">
-        <v>83581</v>
+        <v>83309</v>
       </c>
       <c r="F313">
-        <v>78362</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>112841</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14192,7 +14192,7 @@
         <v>0</v>
       </c>
       <c r="E314">
-        <v>38986</v>
+        <v>38859</v>
       </c>
       <c r="F314">
         <v>0</v>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20797</v>
+        <v>20905</v>
       </c>
       <c r="E315">
-        <v>38986</v>
+        <v>38859</v>
       </c>
       <c r="F315">
-        <v>35797</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>51548</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32420</v>
+        <v>32563</v>
       </c>
       <c r="E316">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F316">
-        <v>49585</v>
+        <v>49702</v>
       </c>
       <c r="G316">
-        <v>71402</v>
+        <v>71571</v>
       </c>
       <c r="H316">
-        <v>17165</v>
+        <v>17139</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26585</v>
+        <v>26702</v>
       </c>
       <c r="E317">
-        <v>59417</v>
+        <v>59223</v>
       </c>
       <c r="F317">
-        <v>41585</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>59882</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,19 +14366,19 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16202</v>
+        <v>19563</v>
       </c>
       <c r="E318">
-        <v>44558</v>
+        <v>44413</v>
       </c>
       <c r="F318">
-        <v>33419</v>
+        <v>0</v>
       </c>
       <c r="G318">
-        <v>48123</v>
+        <v>0</v>
       </c>
       <c r="H318">
-        <v>17217</v>
+        <v>0</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29208</v>
+        <v>29592</v>
       </c>
       <c r="E319">
-        <v>44558</v>
+        <v>44413</v>
       </c>
       <c r="F319">
-        <v>44208</v>
+        <v>0</v>
       </c>
       <c r="G319">
-        <v>63660</v>
+        <v>0</v>
       </c>
       <c r="H319">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14456,19 +14456,19 @@
         <v>15</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>50705</v>
       </c>
       <c r="E320">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F320">
-        <v>0</v>
+        <v>76258</v>
       </c>
       <c r="G320">
-        <v>0</v>
+        <v>109812</v>
       </c>
       <c r="H320">
-        <v>0</v>
+        <v>25553</v>
       </c>
       <c r="I320" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14505,7 +14505,7 @@
         <v>0</v>
       </c>
       <c r="E321">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F321">
         <v>0</v>
@@ -14548,7 +14548,7 @@
         <v>0</v>
       </c>
       <c r="E322">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F322">
         <v>0</v>
@@ -14593,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="E323">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F323">
         <v>0</v>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>58862</v>
+        <v>0</v>
       </c>
       <c r="E324">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F324">
-        <v>90793</v>
+        <v>0</v>
       </c>
       <c r="G324">
-        <v>130742</v>
+        <v>0</v>
       </c>
       <c r="H324">
-        <v>31931</v>
+        <v>0</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>63950</v>
+        <v>0</v>
       </c>
       <c r="E325">
-        <v>74275</v>
+        <v>74033</v>
       </c>
       <c r="F325">
-        <v>78950</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>113688</v>
+        <v>0</v>
       </c>
       <c r="H325">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14724,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="E326">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F326">
         <v>0</v>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9397</v>
+        <v>0</v>
       </c>
       <c r="E327">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F327">
-        <v>35105</v>
+        <v>0</v>
       </c>
       <c r="G327">
-        <v>50551</v>
+        <v>0</v>
       </c>
       <c r="H327">
-        <v>25708</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="E328">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F328">
         <v>0</v>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>17045</v>
+        <v>17120</v>
       </c>
       <c r="E329">
-        <v>64989</v>
+        <v>64777</v>
       </c>
       <c r="F329">
-        <v>38164</v>
+        <v>38111</v>
       </c>
       <c r="G329">
-        <v>54956</v>
+        <v>54880</v>
       </c>
       <c r="H329">
-        <v>21119</v>
+        <v>20991</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20845</v>
+        <v>20953</v>
       </c>
       <c r="E330">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F330">
-        <v>47845</v>
+        <v>47953</v>
       </c>
       <c r="G330">
-        <v>68897</v>
+        <v>69052</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="E331">
-        <v>92849</v>
+        <v>92546</v>
       </c>
       <c r="F331">
         <v>0</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43677</v>
+        <v>43854</v>
       </c>
       <c r="E332">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F332">
-        <v>70677</v>
+        <v>70854</v>
       </c>
       <c r="G332">
-        <v>101775</v>
+        <v>102030</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15027,7 +15027,7 @@
         <v>0</v>
       </c>
       <c r="E333">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F333">
         <v>0</v>
@@ -15067,19 +15067,19 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>30957</v>
+        <v>31126</v>
       </c>
       <c r="E334">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F334">
-        <v>65957</v>
+        <v>58126</v>
       </c>
       <c r="G334">
-        <v>94978</v>
+        <v>83701</v>
       </c>
       <c r="H334">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I334" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49385</v>
+        <v>0</v>
       </c>
       <c r="E335">
-        <v>111422</v>
+        <v>111059</v>
       </c>
       <c r="F335">
-        <v>69208</v>
+        <v>0</v>
       </c>
       <c r="G335">
-        <v>99660</v>
+        <v>0</v>
       </c>
       <c r="H335">
-        <v>19823</v>
+        <v>0</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188622</v>
+        <v>189740</v>
       </c>
       <c r="E336">
-        <v>241437</v>
+        <v>240650</v>
       </c>
       <c r="F336">
-        <v>203622</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>293216</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>144293</v>
+        <v>0</v>
       </c>
       <c r="E337">
-        <v>241437</v>
+        <v>240650</v>
       </c>
       <c r="F337">
-        <v>159293</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>229382</v>
+        <v>0</v>
       </c>
       <c r="H337">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>64411</v>
+        <v>64120</v>
       </c>
       <c r="E338">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F338">
-        <v>90263</v>
+        <v>89955</v>
       </c>
       <c r="G338">
-        <v>129979</v>
+        <v>129535</v>
       </c>
       <c r="H338">
-        <v>25852</v>
+        <v>25835</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>41881</v>
+        <v>0</v>
       </c>
       <c r="E339">
-        <v>129996</v>
+        <v>129572</v>
       </c>
       <c r="F339">
-        <v>68881</v>
+        <v>0</v>
       </c>
       <c r="G339">
-        <v>99189</v>
+        <v>0</v>
       </c>
       <c r="H339">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15333,7 +15333,7 @@
         <v>0</v>
       </c>
       <c r="E340">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F340">
         <v>0</v>
@@ -15375,7 +15375,7 @@
         <v>0</v>
       </c>
       <c r="E341">
-        <v>185716</v>
+        <v>185111</v>
       </c>
       <c r="F341">
         <v>0</v>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>104018</v>
+        <v>0</v>
       </c>
       <c r="E342">
-        <v>241437</v>
+        <v>240650</v>
       </c>
       <c r="F342">
-        <v>131018</v>
+        <v>0</v>
       </c>
       <c r="G342">
-        <v>188666</v>
+        <v>0</v>
       </c>
       <c r="H342">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15461,7 +15461,7 @@
         <v>0</v>
       </c>
       <c r="E343">
-        <v>241437</v>
+        <v>240650</v>
       </c>
       <c r="F343">
         <v>0</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71929</v>
+        <v>72214</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>87214</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>125588</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>48022</v>
+        <v>48052</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>63052</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90795</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95037</v>
+        <v>95097</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>110097</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>158540</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>78604</v>
+        <v>78462</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>93604</v>
+        <v>93462</v>
       </c>
       <c r="G5">
-        <v>134790</v>
+        <v>134585</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7187</v>
+        <v>7191</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30528</v>
+        <v>30529</v>
       </c>
       <c r="G7">
-        <v>43960</v>
+        <v>43962</v>
       </c>
       <c r="H7">
-        <v>23341</v>
+        <v>23338</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39398</v>
+        <v>39662</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55525</v>
+        <v>55180</v>
       </c>
       <c r="G8">
-        <v>79956</v>
+        <v>79459</v>
       </c>
       <c r="H8">
-        <v>16127</v>
+        <v>15518</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,7 +814,7 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>39717</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>74033</v>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>58003</v>
+        <v>56553</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>79178</v>
+        <v>78598</v>
       </c>
       <c r="G10">
-        <v>114016</v>
+        <v>113181</v>
       </c>
       <c r="H10">
-        <v>21175</v>
+        <v>22045</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>86797</v>
+        <v>86851</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>101851</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>146665</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13495</v>
+        <v>13503</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40495</v>
+        <v>40503</v>
       </c>
       <c r="G13">
-        <v>58313</v>
+        <v>58324</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27293</v>
+        <v>27310</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45790</v>
+        <v>45797</v>
       </c>
       <c r="G15">
-        <v>65938</v>
+        <v>65948</v>
       </c>
       <c r="H15">
-        <v>18497</v>
+        <v>18487</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54633</v>
+        <v>54668</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>69668</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100322</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21863</v>
+        <v>21877</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>40008</v>
+        <v>40014</v>
       </c>
       <c r="G27">
-        <v>57612</v>
+        <v>57620</v>
       </c>
       <c r="H27">
-        <v>18145</v>
+        <v>18137</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>77678</v>
+        <v>77231</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96546</v>
+        <v>96570</v>
       </c>
       <c r="G28">
-        <v>139026</v>
+        <v>139061</v>
       </c>
       <c r="H28">
-        <v>18868</v>
+        <v>19339</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38104</v>
+        <v>38128</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>65104</v>
+        <v>65128</v>
       </c>
       <c r="G29">
-        <v>93750</v>
+        <v>93784</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>126466</v>
+        <v>123126</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>138550</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>199512</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15424</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>69709</v>
+        <v>72757</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>96709</v>
+        <v>99757</v>
       </c>
       <c r="G31">
-        <v>139261</v>
+        <v>143650</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>61133</v>
+        <v>61171</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80991</v>
+        <v>81013</v>
       </c>
       <c r="G32">
-        <v>116627</v>
+        <v>116659</v>
       </c>
       <c r="H32">
-        <v>19858</v>
+        <v>19842</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36460</v>
+        <v>36482</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63460</v>
+        <v>63482</v>
       </c>
       <c r="G33">
-        <v>91382</v>
+        <v>91414</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48597</v>
+        <v>48276</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75597</v>
+        <v>75276</v>
       </c>
       <c r="G36">
-        <v>108860</v>
+        <v>108397</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>68128</v>
+        <v>68251</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>95128</v>
+        <v>95251</v>
       </c>
       <c r="G38">
-        <v>136984</v>
+        <v>137161</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87803</v>
+        <v>87554</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>114803</v>
+        <v>114554</v>
       </c>
       <c r="G40">
-        <v>165316</v>
+        <v>164958</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>88889</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>113749</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>163799</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>24860</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31748</v>
+        <v>31768</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58748</v>
+        <v>58768</v>
       </c>
       <c r="G43">
-        <v>84597</v>
+        <v>84626</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>21224</v>
+        <v>20918</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>48224</v>
+        <v>47918</v>
       </c>
       <c r="G47">
-        <v>69443</v>
+        <v>69002</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>40372</v>
+        <v>40701</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>66120</v>
+        <v>66170</v>
       </c>
       <c r="G50">
-        <v>95213</v>
+        <v>95285</v>
       </c>
       <c r="H50">
-        <v>25748</v>
+        <v>25469</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>42496</v>
+        <v>42539</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>57496</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>82794</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>59696</v>
+        <v>59733</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>74733</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>107616</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>67936</v>
+        <v>67979</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>82979</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>119490</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,16 +2788,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>45003</v>
+        <v>45032</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>80003</v>
+        <v>80032</v>
       </c>
       <c r="G54">
-        <v>115204</v>
+        <v>115246</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44668</v>
+        <v>44872</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71668</v>
+        <v>71872</v>
       </c>
       <c r="G55">
-        <v>103202</v>
+        <v>103496</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>51120</v>
+        <v>51152</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>78120</v>
+        <v>78152</v>
       </c>
       <c r="G56">
-        <v>112493</v>
+        <v>112539</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66196</v>
+        <v>66237</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90231</v>
+        <v>90248</v>
       </c>
       <c r="G57">
-        <v>129933</v>
+        <v>129957</v>
       </c>
       <c r="H57">
-        <v>24035</v>
+        <v>24011</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>16098</v>
+        <v>15964</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38664</v>
+        <v>38665</v>
       </c>
       <c r="G58">
-        <v>55676</v>
+        <v>55678</v>
       </c>
       <c r="H58">
-        <v>22566</v>
+        <v>22701</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22931</v>
+        <v>22932</v>
       </c>
       <c r="G59">
-        <v>33021</v>
+        <v>33022</v>
       </c>
       <c r="H59">
-        <v>16687</v>
+        <v>16684</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24195</v>
+        <v>24210</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>39195</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>56441</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14277</v>
+        <v>14286</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41277</v>
+        <v>41286</v>
       </c>
       <c r="G63">
-        <v>59439</v>
+        <v>59452</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>23268</v>
+        <v>34181</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>50268</v>
+        <v>61181</v>
       </c>
       <c r="G65">
-        <v>72386</v>
+        <v>88101</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25935</v>
+        <v>25952</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60871</v>
+        <v>60884</v>
       </c>
       <c r="G66">
-        <v>87654</v>
+        <v>87673</v>
       </c>
       <c r="H66">
-        <v>34936</v>
+        <v>34932</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20825</v>
+        <v>20838</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47825</v>
+        <v>47838</v>
       </c>
       <c r="G67">
-        <v>68868</v>
+        <v>68887</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48181</v>
+        <v>48212</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75181</v>
+        <v>75212</v>
       </c>
       <c r="G68">
-        <v>108261</v>
+        <v>108305</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27788</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>54788</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>78895</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110880</v>
+        <v>110949</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>125949</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>181367</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6787</v>
+        <v>6839</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21787</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>31373</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88346</v>
+        <v>88401</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>122832</v>
+        <v>123289</v>
       </c>
       <c r="G76">
-        <v>176878</v>
+        <v>177536</v>
       </c>
       <c r="H76">
-        <v>34486</v>
+        <v>34888</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>62203</v>
+        <v>63345</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>81414</v>
+        <v>81871</v>
       </c>
       <c r="G77">
-        <v>117236</v>
+        <v>117894</v>
       </c>
       <c r="H77">
-        <v>19211</v>
+        <v>18526</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23332</v>
+        <v>23347</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>50332</v>
+        <v>50347</v>
       </c>
       <c r="G81">
-        <v>72478</v>
+        <v>72500</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87372</v>
+        <v>87427</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>102427</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>147495</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47080</v>
+        <v>47109</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>62080</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>89395</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>35581</v>
+        <v>36626</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>50581</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>72837</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8225</v>
+        <v>8230</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38579</v>
+        <v>38580</v>
       </c>
       <c r="G90">
-        <v>55554</v>
+        <v>55555</v>
       </c>
       <c r="H90">
-        <v>30354</v>
+        <v>30350</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3705</v>
+        <v>3707</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30579</v>
+        <v>30580</v>
       </c>
       <c r="G91">
-        <v>44034</v>
+        <v>44035</v>
       </c>
       <c r="H91">
-        <v>26874</v>
+        <v>26873</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9518</v>
+        <v>9524</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24524</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35315</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63928</v>
+        <v>64144</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>79144</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>113967</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34655</v>
+        <v>34677</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52345</v>
+        <v>52354</v>
       </c>
       <c r="G97">
-        <v>75377</v>
+        <v>75390</v>
       </c>
       <c r="H97">
-        <v>17690</v>
+        <v>17677</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79467</v>
+        <v>79516</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>94516</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>136103</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>44013</v>
+        <v>42363</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>61142</v>
+        <v>60482</v>
       </c>
       <c r="G99">
-        <v>88044</v>
+        <v>87094</v>
       </c>
       <c r="H99">
-        <v>17129</v>
+        <v>18119</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60782</v>
+        <v>60820</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>78873</v>
+        <v>80934</v>
       </c>
       <c r="G100">
-        <v>113577</v>
+        <v>116545</v>
       </c>
       <c r="H100">
-        <v>18091</v>
+        <v>20114</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>63457</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>78457</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>112978</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>75235</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>102235</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>147218</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>5765</v>
+        <v>6200</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>32765</v>
+        <v>33200</v>
       </c>
       <c r="G109">
-        <v>47182</v>
+        <v>47808</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15124</v>
+        <v>15133</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42124</v>
+        <v>42133</v>
       </c>
       <c r="G111">
-        <v>60659</v>
+        <v>60672</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51296</v>
+        <v>50545</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>77052</v>
+        <v>76751</v>
       </c>
       <c r="G113">
-        <v>110955</v>
+        <v>110521</v>
       </c>
       <c r="H113">
-        <v>25756</v>
+        <v>26206</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>99014</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>117799</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>169631</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>18785</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80521</v>
+        <v>80571</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>95571</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>137622</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>47239</v>
+        <v>50337</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>62239</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>89624</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102432</v>
+        <v>86036</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>101036</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>145492</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46297</v>
+        <v>46326</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>61326</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>88309</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35246</v>
+        <v>35268</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50268</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72386</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63912</v>
+        <v>63952</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>78952</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>113691</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36875</v>
+        <v>36898</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56843</v>
+        <v>56852</v>
       </c>
       <c r="G129">
-        <v>81854</v>
+        <v>81867</v>
       </c>
       <c r="H129">
-        <v>19968</v>
+        <v>19954</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12760</v>
+        <v>12768</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33148</v>
+        <v>33310</v>
       </c>
       <c r="G130">
-        <v>47733</v>
+        <v>47966</v>
       </c>
       <c r="H130">
-        <v>20388</v>
+        <v>20542</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4567</v>
+        <v>5849</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25148</v>
+        <v>25660</v>
       </c>
       <c r="G131">
-        <v>36213</v>
+        <v>36950</v>
       </c>
       <c r="H131">
-        <v>20581</v>
+        <v>19811</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27772</v>
+        <v>27789</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43759</v>
+        <v>43766</v>
       </c>
       <c r="G132">
-        <v>63013</v>
+        <v>63023</v>
       </c>
       <c r="H132">
-        <v>15987</v>
+        <v>15977</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17375</v>
+        <v>17386</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36618</v>
+        <v>36622</v>
       </c>
       <c r="G135">
-        <v>52730</v>
+        <v>52736</v>
       </c>
       <c r="H135">
-        <v>19243</v>
+        <v>19236</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28155</v>
+        <v>28173</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46749</v>
+        <v>46756</v>
       </c>
       <c r="G137">
-        <v>67319</v>
+        <v>67329</v>
       </c>
       <c r="H137">
-        <v>18594</v>
+        <v>18583</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27948</v>
+        <v>27821</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54298</v>
+        <v>54247</v>
       </c>
       <c r="G139">
-        <v>78189</v>
+        <v>78116</v>
       </c>
       <c r="H139">
-        <v>26350</v>
+        <v>26426</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58370</v>
+        <v>58407</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>73407</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>105706</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77870</v>
+        <v>77918</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>92918</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>133802</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87468</v>
+        <v>87522</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>102522</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>147632</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86589</v>
+        <v>88337</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>103337</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>148805</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>126546</v>
+        <v>122710</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>137710</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>198302</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38440</v>
+        <v>38464</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>63022</v>
+        <v>63032</v>
       </c>
       <c r="G150">
-        <v>90752</v>
+        <v>90766</v>
       </c>
       <c r="H150">
-        <v>24582</v>
+        <v>24568</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24211</v>
+        <v>23251</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>59211</v>
+        <v>58251</v>
       </c>
       <c r="G152">
-        <v>85264</v>
+        <v>83881</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29768</v>
+        <v>29787</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>54000</v>
+        <v>54008</v>
       </c>
       <c r="G153">
-        <v>77760</v>
+        <v>77772</v>
       </c>
       <c r="H153">
-        <v>24232</v>
+        <v>24221</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48884</v>
+        <v>48915</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20526</v>
+        <v>20495</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>75985</v>
+        <v>76033</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>91033</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>131088</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65701</v>
+        <v>65742</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80742</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>116268</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>42975</v>
+        <v>46789</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65772</v>
+        <v>65802</v>
       </c>
       <c r="G158">
-        <v>94712</v>
+        <v>94755</v>
       </c>
       <c r="H158">
-        <v>22797</v>
+        <v>19013</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42193</v>
+        <v>42219</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>57219</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>82395</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20170</v>
+        <v>17993</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>35721</v>
+        <v>34850</v>
       </c>
       <c r="G161">
-        <v>51438</v>
+        <v>50184</v>
       </c>
       <c r="H161">
-        <v>15551</v>
+        <v>16857</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56294</v>
+        <v>56345</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>71345</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>102737</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>81000</v>
+        <v>81051</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>96051</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>138313</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>59009</v>
+        <v>59046</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>74046</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>106626</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34112</v>
+        <v>34133</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>49133</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70752</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>60622</v>
+        <v>67755</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>95622</v>
+        <v>102703</v>
       </c>
       <c r="G168">
-        <v>137696</v>
+        <v>147892</v>
       </c>
       <c r="H168">
-        <v>35000</v>
+        <v>34948</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74420</v>
+        <v>74307</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>89307</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>128602</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15124</v>
+        <v>16108</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>30124</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>43379</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>30263</v>
+        <v>31193</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51310</v>
+        <v>51682</v>
       </c>
       <c r="G173">
-        <v>73886</v>
+        <v>74422</v>
       </c>
       <c r="H173">
-        <v>21047</v>
+        <v>20489</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7410</v>
+        <v>7638</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37774</v>
+        <v>37776</v>
       </c>
       <c r="G174">
-        <v>54395</v>
+        <v>54397</v>
       </c>
       <c r="H174">
-        <v>30364</v>
+        <v>30138</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5286</v>
+        <v>5289</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29774</v>
+        <v>29776</v>
       </c>
       <c r="G175">
-        <v>42875</v>
+        <v>42877</v>
       </c>
       <c r="H175">
-        <v>24488</v>
+        <v>24487</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10365</v>
+        <v>10371</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>43656</v>
+        <v>43469</v>
       </c>
       <c r="G176">
-        <v>62865</v>
+        <v>62595</v>
       </c>
       <c r="H176">
-        <v>33291</v>
+        <v>33098</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>8656</v>
+        <v>8469</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>35656</v>
+        <v>35469</v>
       </c>
       <c r="G177">
-        <v>51345</v>
+        <v>51075</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21959</v>
+        <v>21381</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41859</v>
+        <v>41628</v>
       </c>
       <c r="G179">
-        <v>60277</v>
+        <v>59944</v>
       </c>
       <c r="H179">
-        <v>19900</v>
+        <v>20247</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46201</v>
+        <v>46230</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65274</v>
+        <v>65285</v>
       </c>
       <c r="G181">
-        <v>93995</v>
+        <v>94010</v>
       </c>
       <c r="H181">
-        <v>19073</v>
+        <v>19055</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68144</v>
+        <v>68187</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86227</v>
+        <v>85881</v>
       </c>
       <c r="G182">
-        <v>124167</v>
+        <v>123669</v>
       </c>
       <c r="H182">
-        <v>18083</v>
+        <v>17694</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>9838</v>
+        <v>9492</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>36838</v>
+        <v>36492</v>
       </c>
       <c r="G183">
-        <v>53047</v>
+        <v>52548</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>71785</v>
+        <v>60868</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>80324</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>115667</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>19456</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>45831</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>67645</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>97409</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>21814</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>89783</v>
+        <v>80363</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>111064</v>
+        <v>111028</v>
       </c>
       <c r="G186">
-        <v>159932</v>
+        <v>159880</v>
       </c>
       <c r="H186">
-        <v>21281</v>
+        <v>30665</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81671</v>
+        <v>81546</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>96546</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>139026</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>172444</v>
+        <v>172185</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>187444</v>
+        <v>187185</v>
       </c>
       <c r="G192">
-        <v>269919</v>
+        <v>269546</v>
       </c>
       <c r="H192">
         <v>15000</v>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7298</v>
+        <v>7175</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>27640</v>
+        <v>27763</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11802</v>
+        <v>11809</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38802</v>
+        <v>38809</v>
       </c>
       <c r="G196">
-        <v>55875</v>
+        <v>55885</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51855</v>
+        <v>51887</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17555</v>
+        <v>17523</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75283</v>
+        <v>75330</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>90330</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>130075</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>56949</v>
+        <v>56985</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>71985</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>103658</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36859</v>
+        <v>36882</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63859</v>
+        <v>63882</v>
       </c>
       <c r="G202">
-        <v>91957</v>
+        <v>91990</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27596</v>
+        <v>27613</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54596</v>
+        <v>54613</v>
       </c>
       <c r="G204">
-        <v>78618</v>
+        <v>78643</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63896</v>
+        <v>63728</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82092</v>
+        <v>82024</v>
       </c>
       <c r="G207">
-        <v>118212</v>
+        <v>118115</v>
       </c>
       <c r="H207">
-        <v>18196</v>
+        <v>18296</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,19 +9524,19 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>145402</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>0</v>
+        <v>180402</v>
       </c>
       <c r="G208">
-        <v>0</v>
+        <v>259779</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I208" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145359</v>
+        <v>145450</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>160450</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>231048</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>188548</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>203548</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>293109</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>186961</v>
+        <v>186343</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>201343</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>289934</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>289041</v>
+        <v>289222</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>304222</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>438080</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34463</v>
+        <v>34884</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>59372</v>
+        <v>60881</v>
       </c>
       <c r="G214">
-        <v>85496</v>
+        <v>87669</v>
       </c>
       <c r="H214">
-        <v>24909</v>
+        <v>25997</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>36188</v>
+        <v>37697</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>51188</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>73711</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>16513</v>
+        <v>60532</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>36765</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>52942</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>20252</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16513</v>
+        <v>67675</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>36765</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>52942</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>20252</v>
+        <v>0</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,16 +10048,16 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12872</v>
+        <v>13199</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>39872</v>
+        <v>40199</v>
       </c>
       <c r="G220">
-        <v>57416</v>
+        <v>57887</v>
       </c>
       <c r="H220">
         <v>27000</v>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>22550</v>
+        <v>27150</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>49550</v>
+        <v>62150</v>
       </c>
       <c r="G222">
-        <v>71352</v>
+        <v>89496</v>
       </c>
       <c r="H222">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>53725</v>
       </c>
       <c r="E223">
         <v>111059</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>70803</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>101956</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>17078</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>17008</v>
+        <v>17290</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46195</v>
+        <v>46554</v>
       </c>
       <c r="G224">
-        <v>66521</v>
+        <v>67038</v>
       </c>
       <c r="H224">
-        <v>29187</v>
+        <v>29264</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11195</v>
+        <v>11554</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38195</v>
+        <v>38554</v>
       </c>
       <c r="G225">
-        <v>55001</v>
+        <v>55518</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26590</v>
+        <v>26607</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61590</v>
+        <v>61607</v>
       </c>
       <c r="G226">
-        <v>88690</v>
+        <v>88714</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38552</v>
+        <v>95496</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>65552</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>94395</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35853</v>
+        <v>35859</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>62853</v>
+        <v>62859</v>
       </c>
       <c r="G228">
-        <v>90508</v>
+        <v>90517</v>
       </c>
       <c r="H228">
         <v>27000</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15922</v>
+        <v>15948</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42836</v>
+        <v>42838</v>
       </c>
       <c r="G230">
-        <v>61684</v>
+        <v>61687</v>
       </c>
       <c r="H230">
-        <v>26914</v>
+        <v>26890</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9822</v>
+        <v>9828</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>33026</v>
+        <v>33028</v>
       </c>
       <c r="G231">
-        <v>47557</v>
+        <v>47560</v>
       </c>
       <c r="H231">
-        <v>23204</v>
+        <v>23200</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>86398</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>112752</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>162363</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>26354</v>
+        <v>0</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26702</v>
+        <v>26719</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>53702</v>
+        <v>53719</v>
       </c>
       <c r="G238">
-        <v>77331</v>
+        <v>77355</v>
       </c>
       <c r="H238">
         <v>27000</v>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47175</v>
+        <v>47205</v>
       </c>
       <c r="E240">
         <v>103654</v>
       </c>
       <c r="F240">
-        <v>71515</v>
+        <v>71527</v>
       </c>
       <c r="G240">
-        <v>102982</v>
+        <v>102999</v>
       </c>
       <c r="H240">
-        <v>24340</v>
+        <v>24322</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64439</v>
+        <v>64479</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>79479</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>114450</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>76512</v>
+        <v>76544</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>91544</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>131823</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17711</v>
+        <v>17466</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42527</v>
+        <v>42530</v>
       </c>
       <c r="G248">
-        <v>61239</v>
+        <v>61243</v>
       </c>
       <c r="H248">
-        <v>24816</v>
+        <v>25064</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11770</v>
+        <v>11777</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34527</v>
+        <v>34530</v>
       </c>
       <c r="G249">
-        <v>49719</v>
+        <v>49723</v>
       </c>
       <c r="H249">
-        <v>22757</v>
+        <v>22753</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>16683</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>43683</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>62904</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9678</v>
+        <v>9620</v>
       </c>
       <c r="E256">
         <v>53688</v>
       </c>
       <c r="F256">
-        <v>40266</v>
+        <v>34938</v>
       </c>
       <c r="G256">
-        <v>57983</v>
+        <v>50311</v>
       </c>
       <c r="H256">
-        <v>30588</v>
+        <v>25318</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14948</v>
+        <v>0</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>32917</v>
+        <v>0</v>
       </c>
       <c r="G257">
-        <v>47400</v>
+        <v>0</v>
       </c>
       <c r="H257">
-        <v>17969</v>
+        <v>0</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12281</v>
+        <v>12353</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39281</v>
+        <v>39353</v>
       </c>
       <c r="G258">
-        <v>56565</v>
+        <v>56668</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8895</v>
+        <v>8901</v>
       </c>
       <c r="E260">
         <v>53688</v>
       </c>
       <c r="F260">
-        <v>39346</v>
+        <v>39349</v>
       </c>
       <c r="G260">
-        <v>56658</v>
+        <v>56663</v>
       </c>
       <c r="H260">
-        <v>30451</v>
+        <v>30448</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11019</v>
+        <v>11026</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>31346</v>
+        <v>31349</v>
       </c>
       <c r="G261">
-        <v>45138</v>
+        <v>45143</v>
       </c>
       <c r="H261">
-        <v>20327</v>
+        <v>20323</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,7 +11903,7 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>11562</v>
+        <v>11570</v>
       </c>
       <c r="E262">
         <v>53688</v>
@@ -11915,7 +11915,7 @@
         <v>50311</v>
       </c>
       <c r="H262">
-        <v>23376</v>
+        <v>23368</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18605</v>
+        <v>18617</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>51875</v>
+        <v>45617</v>
       </c>
       <c r="G264">
-        <v>74700</v>
+        <v>65688</v>
       </c>
       <c r="H264">
-        <v>33270</v>
+        <v>27000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24290</v>
+        <v>0</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>43875</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>63180</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>19585</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34495</v>
+        <v>34517</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>54151</v>
+        <v>52297</v>
       </c>
       <c r="G266">
-        <v>77977</v>
+        <v>75308</v>
       </c>
       <c r="H266">
-        <v>19656</v>
+        <v>17780</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>31078</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>72201</v>
       </c>
       <c r="F267">
-        <v>46590</v>
+        <v>0</v>
       </c>
       <c r="G267">
-        <v>67090</v>
+        <v>0</v>
       </c>
       <c r="H267">
-        <v>15512</v>
+        <v>0</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10285</v>
+        <v>10291</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>25291</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>36419</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12217</v>
+        <v>12225</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>39217</v>
+        <v>39225</v>
       </c>
       <c r="G270">
-        <v>56472</v>
+        <v>56484</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62666</v>
+        <v>62386</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>77386</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>111436</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>39063</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>59891</v>
+        <v>0</v>
       </c>
       <c r="G273">
-        <v>86243</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>20828</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>71003</v>
+        <v>70008</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>106003</v>
+        <v>85008</v>
       </c>
       <c r="G274">
-        <v>152644</v>
+        <v>122412</v>
       </c>
       <c r="H274">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,7 +12476,7 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>78077</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>111059</v>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11211</v>
+        <v>11218</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>37870</v>
+        <v>34938</v>
       </c>
       <c r="G276">
-        <v>54533</v>
+        <v>50311</v>
       </c>
       <c r="H276">
-        <v>26659</v>
+        <v>23720</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>7330</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>29870</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>43013</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>22540</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20138</v>
+        <v>20263</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>51875</v>
+        <v>46596</v>
       </c>
       <c r="G278">
-        <v>74700</v>
+        <v>67098</v>
       </c>
       <c r="H278">
-        <v>31737</v>
+        <v>26333</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24290</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>43875</v>
+        <v>0</v>
       </c>
       <c r="G279">
-        <v>63180</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>19585</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11786</v>
+        <v>11793</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23152</v>
+        <v>23145</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17743</v>
+        <v>17754</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>32754</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>47166</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50242</v>
+        <v>50273</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>65273</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>93993</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>59073</v>
+        <v>59110</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>74110</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>106718</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,7 +13042,7 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>34799</v>
+        <v>40126</v>
       </c>
       <c r="E288">
         <v>61074</v>
@@ -13054,7 +13054,7 @@
         <v>80372</v>
       </c>
       <c r="H288">
-        <v>21015</v>
+        <v>15688</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,7 +13088,7 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23843</v>
+        <v>23842</v>
       </c>
       <c r="E289">
         <v>61074</v>
@@ -13100,7 +13100,7 @@
         <v>56673</v>
       </c>
       <c r="H289">
-        <v>15513</v>
+        <v>15514</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>44844</v>
+        <v>44872</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>62194</v>
+        <v>62200</v>
       </c>
       <c r="G292">
-        <v>89559</v>
+        <v>89568</v>
       </c>
       <c r="H292">
-        <v>17350</v>
+        <v>17328</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23779</v>
+        <v>23794</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39330</v>
+        <v>39336</v>
       </c>
       <c r="G293">
-        <v>56635</v>
+        <v>56644</v>
       </c>
       <c r="H293">
-        <v>15551</v>
+        <v>15542</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,7 +13310,7 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>50082</v>
+        <v>0</v>
       </c>
       <c r="E294">
         <v>68480</v>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62906</v>
+        <v>62945</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>77945</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>112241</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>74883</v>
+        <v>92700</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>107700</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>155088</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>70795</v>
+        <v>70839</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>89278</v>
+        <v>89120</v>
       </c>
       <c r="G300">
-        <v>128560</v>
+        <v>128333</v>
       </c>
       <c r="H300">
-        <v>18483</v>
+        <v>18281</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>35789</v>
+        <v>35396</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>56409</v>
+        <v>56251</v>
       </c>
       <c r="G301">
-        <v>81229</v>
+        <v>81001</v>
       </c>
       <c r="H301">
-        <v>20620</v>
+        <v>20855</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>11227</v>
+        <v>12113</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>38227</v>
+        <v>39113</v>
       </c>
       <c r="G303">
-        <v>55047</v>
+        <v>56323</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174744</v>
+        <v>174853</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>189853</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>273388</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50210</v>
+        <v>50241</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>80041</v>
+        <v>80054</v>
       </c>
       <c r="G306">
-        <v>115259</v>
+        <v>115278</v>
       </c>
       <c r="H306">
-        <v>29831</v>
+        <v>29813</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50625</v>
+        <v>50657</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69563</v>
+        <v>69576</v>
       </c>
       <c r="G307">
-        <v>100171</v>
+        <v>100189</v>
       </c>
       <c r="H307">
-        <v>18938</v>
+        <v>18919</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69485</v>
+        <v>69529</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>27694</v>
+        <v>27650</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>105897</v>
+        <v>105963</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>120963</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>174187</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24626</v>
+        <v>24769</v>
       </c>
       <c r="E310">
         <v>55520</v>
       </c>
       <c r="F310">
-        <v>40834</v>
+        <v>40892</v>
       </c>
       <c r="G310">
-        <v>58801</v>
+        <v>58884</v>
       </c>
       <c r="H310">
-        <v>16208</v>
+        <v>16123</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>68591</v>
+        <v>68634</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>83591</v>
+        <v>0</v>
       </c>
       <c r="G312">
-        <v>120371</v>
+        <v>0</v>
       </c>
       <c r="H312">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20905</v>
+        <v>20918</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>35918</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>51722</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32563</v>
+        <v>34037</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>49702</v>
+        <v>62990</v>
       </c>
       <c r="G316">
-        <v>71571</v>
+        <v>90706</v>
       </c>
       <c r="H316">
-        <v>17139</v>
+        <v>28953</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26702</v>
+        <v>39774</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>54774</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>78875</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,19 +14366,19 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>19563</v>
+        <v>16284</v>
       </c>
       <c r="E318">
         <v>44413</v>
       </c>
       <c r="F318">
-        <v>0</v>
+        <v>33310</v>
       </c>
       <c r="G318">
-        <v>0</v>
+        <v>47966</v>
       </c>
       <c r="H318">
-        <v>0</v>
+        <v>17026</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29592</v>
+        <v>29611</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>0</v>
+        <v>44611</v>
       </c>
       <c r="G319">
-        <v>0</v>
+        <v>64240</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14456,19 +14456,19 @@
         <v>15</v>
       </c>
       <c r="D320">
-        <v>50705</v>
+        <v>50625</v>
       </c>
       <c r="E320">
         <v>111059</v>
       </c>
       <c r="F320">
-        <v>76258</v>
+        <v>76226</v>
       </c>
       <c r="G320">
-        <v>109812</v>
+        <v>109765</v>
       </c>
       <c r="H320">
-        <v>25553</v>
+        <v>25601</v>
       </c>
       <c r="I320" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>9428</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>35034</v>
       </c>
       <c r="G327">
-        <v>0</v>
+        <v>50449</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>25606</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>17120</v>
+        <v>0</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>38111</v>
+        <v>0</v>
       </c>
       <c r="G329">
-        <v>54880</v>
+        <v>0</v>
       </c>
       <c r="H329">
-        <v>20991</v>
+        <v>0</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20953</v>
+        <v>20966</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47953</v>
+        <v>47966</v>
       </c>
       <c r="G330">
-        <v>69052</v>
+        <v>69071</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43854</v>
+        <v>43881</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>70854</v>
+        <v>70881</v>
       </c>
       <c r="G332">
-        <v>102030</v>
+        <v>102069</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>31126</v>
+        <v>32503</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>58126</v>
+        <v>59503</v>
       </c>
       <c r="G334">
-        <v>83701</v>
+        <v>85684</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>189740</v>
+        <v>189858</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>204858</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>294996</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>64120</v>
+        <v>63760</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89955</v>
+        <v>89811</v>
       </c>
       <c r="G338">
-        <v>129535</v>
+        <v>129328</v>
       </c>
       <c r="H338">
-        <v>25835</v>
+        <v>26051</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72214</v>
+        <v>72349</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>87214</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>125588</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>48052</v>
+        <v>48142</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>63052</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90795</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95097</v>
+        <v>95276</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>110097</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>158540</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>78462</v>
+        <v>78401</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>93462</v>
+        <v>93401</v>
       </c>
       <c r="G5">
-        <v>134585</v>
+        <v>134497</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7191</v>
+        <v>7205</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30529</v>
+        <v>30535</v>
       </c>
       <c r="G7">
-        <v>43962</v>
+        <v>43970</v>
       </c>
       <c r="H7">
-        <v>23338</v>
+        <v>23330</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39662</v>
+        <v>39737</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55180</v>
+        <v>55210</v>
       </c>
       <c r="G8">
-        <v>79459</v>
+        <v>79502</v>
       </c>
       <c r="H8">
-        <v>15518</v>
+        <v>15473</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56553</v>
+        <v>56659</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78598</v>
+        <v>78640</v>
       </c>
       <c r="G10">
-        <v>113181</v>
+        <v>113242</v>
       </c>
       <c r="H10">
-        <v>22045</v>
+        <v>21981</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>75231</v>
       </c>
       <c r="E11">
         <v>111059</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>90231</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>129933</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>86851</v>
+        <v>85173</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>101851</v>
+        <v>101060</v>
       </c>
       <c r="G12">
-        <v>146665</v>
+        <v>145526</v>
       </c>
       <c r="H12">
-        <v>15000</v>
+        <v>15887</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13503</v>
+        <v>12712</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40503</v>
+        <v>39712</v>
       </c>
       <c r="G13">
-        <v>58324</v>
+        <v>57185</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27310</v>
+        <v>27361</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45797</v>
+        <v>45817</v>
       </c>
       <c r="G15">
-        <v>65948</v>
+        <v>65976</v>
       </c>
       <c r="H15">
-        <v>18487</v>
+        <v>18456</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54668</v>
+        <v>49567</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>69668</v>
+        <v>66252</v>
       </c>
       <c r="G21">
-        <v>100322</v>
+        <v>95403</v>
       </c>
       <c r="H21">
-        <v>15000</v>
+        <v>16685</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>96460</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>111460</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>160502</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21877</v>
+        <v>21918</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>40014</v>
+        <v>40030</v>
       </c>
       <c r="G27">
-        <v>57620</v>
+        <v>57643</v>
       </c>
       <c r="H27">
-        <v>18137</v>
+        <v>18112</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>77231</v>
+        <v>77216</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96570</v>
+        <v>96642</v>
       </c>
       <c r="G28">
-        <v>139061</v>
+        <v>139164</v>
       </c>
       <c r="H28">
-        <v>19339</v>
+        <v>19426</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38128</v>
+        <v>38200</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>65128</v>
+        <v>65200</v>
       </c>
       <c r="G29">
-        <v>93784</v>
+        <v>93888</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>123126</v>
+        <v>120331</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>138550</v>
+        <v>138833</v>
       </c>
       <c r="G30">
-        <v>199512</v>
+        <v>199920</v>
       </c>
       <c r="H30">
-        <v>15424</v>
+        <v>18502</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72757</v>
+        <v>80066</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>99757</v>
+        <v>107066</v>
       </c>
       <c r="G31">
-        <v>143650</v>
+        <v>154175</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>61171</v>
+        <v>60982</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>81013</v>
+        <v>81082</v>
       </c>
       <c r="G32">
-        <v>116659</v>
+        <v>116758</v>
       </c>
       <c r="H32">
-        <v>19842</v>
+        <v>20100</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36482</v>
+        <v>36551</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63482</v>
+        <v>63551</v>
       </c>
       <c r="G33">
-        <v>91414</v>
+        <v>91513</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48276</v>
+        <v>48366</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75276</v>
+        <v>75366</v>
       </c>
       <c r="G36">
-        <v>108397</v>
+        <v>108527</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87554</v>
+        <v>87559</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>114554</v>
+        <v>114559</v>
       </c>
       <c r="G40">
-        <v>164958</v>
+        <v>164965</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31768</v>
+        <v>31828</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58768</v>
+        <v>58828</v>
       </c>
       <c r="G43">
-        <v>84626</v>
+        <v>84712</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>20918</v>
+        <v>20637</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>47918</v>
+        <v>47637</v>
       </c>
       <c r="G47">
-        <v>69002</v>
+        <v>68597</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>40701</v>
+        <v>36967</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>66170</v>
+        <v>57053</v>
       </c>
       <c r="G50">
-        <v>95285</v>
+        <v>82156</v>
       </c>
       <c r="H50">
-        <v>25469</v>
+        <v>20086</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>42539</v>
+        <v>34053</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>49053</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>70636</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,16 +2698,16 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>59733</v>
+        <v>54418</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>74733</v>
+        <v>69418</v>
       </c>
       <c r="G52">
-        <v>107616</v>
+        <v>99962</v>
       </c>
       <c r="H52">
         <v>15000</v>
@@ -2744,16 +2744,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>67979</v>
+        <v>59221</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>82979</v>
+        <v>74221</v>
       </c>
       <c r="G53">
-        <v>119490</v>
+        <v>106878</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>45032</v>
+        <v>49535</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>80032</v>
+        <v>82749</v>
       </c>
       <c r="G54">
-        <v>115246</v>
+        <v>119159</v>
       </c>
       <c r="H54">
-        <v>35000</v>
+        <v>33214</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44872</v>
+        <v>44956</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71872</v>
+        <v>71956</v>
       </c>
       <c r="G55">
-        <v>103496</v>
+        <v>103617</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>51152</v>
+        <v>53938</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>78152</v>
+        <v>80938</v>
       </c>
       <c r="G56">
-        <v>112539</v>
+        <v>116551</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66237</v>
+        <v>66361</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90248</v>
+        <v>90297</v>
       </c>
       <c r="G57">
-        <v>129957</v>
+        <v>130028</v>
       </c>
       <c r="H57">
-        <v>24011</v>
+        <v>23936</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>15964</v>
+        <v>15834</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38665</v>
+        <v>38670</v>
       </c>
       <c r="G58">
-        <v>55678</v>
+        <v>55685</v>
       </c>
       <c r="H58">
-        <v>22701</v>
+        <v>22836</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6248</v>
+        <v>6260</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22932</v>
+        <v>22937</v>
       </c>
       <c r="G59">
-        <v>33022</v>
+        <v>33029</v>
       </c>
       <c r="H59">
-        <v>16684</v>
+        <v>16677</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24210</v>
+        <v>24255</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>39255</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>56527</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14286</v>
+        <v>13961</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41286</v>
+        <v>40961</v>
       </c>
       <c r="G63">
-        <v>59452</v>
+        <v>58984</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>34181</v>
+        <v>34245</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>61181</v>
+        <v>61245</v>
       </c>
       <c r="G65">
-        <v>88101</v>
+        <v>88193</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25952</v>
+        <v>25984</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60884</v>
+        <v>60923</v>
       </c>
       <c r="G66">
-        <v>87673</v>
+        <v>87729</v>
       </c>
       <c r="H66">
-        <v>34932</v>
+        <v>34939</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20838</v>
+        <v>20877</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47838</v>
+        <v>47877</v>
       </c>
       <c r="G67">
-        <v>68887</v>
+        <v>68943</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48212</v>
+        <v>48302</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75212</v>
+        <v>75297</v>
       </c>
       <c r="G68">
-        <v>108305</v>
+        <v>108428</v>
       </c>
       <c r="H68">
-        <v>27000</v>
+        <v>26995</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>27793</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>54793</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>78902</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110949</v>
+        <v>111157</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>125949</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>181367</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>52785</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>77647</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>111812</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>24862</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6839</v>
+        <v>6788</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>21788</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>31375</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88401</v>
+        <v>88567</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>123289</v>
+        <v>123343</v>
       </c>
       <c r="G76">
-        <v>177536</v>
+        <v>177614</v>
       </c>
       <c r="H76">
-        <v>34888</v>
+        <v>34776</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>63345</v>
+        <v>63480</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>81871</v>
+        <v>81925</v>
       </c>
       <c r="G77">
-        <v>117894</v>
+        <v>117972</v>
       </c>
       <c r="H77">
-        <v>18526</v>
+        <v>18445</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>23347</v>
+        <v>24687</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>50347</v>
+        <v>51687</v>
       </c>
       <c r="G81">
-        <v>72500</v>
+        <v>74429</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87427</v>
+        <v>87591</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>102427</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>147495</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47109</v>
+        <v>46621</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>66777</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>96159</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>20156</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>36626</v>
+        <v>43067</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>58067</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>83616</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8230</v>
+        <v>8245</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38580</v>
+        <v>38583</v>
       </c>
       <c r="G90">
-        <v>55555</v>
+        <v>55560</v>
       </c>
       <c r="H90">
-        <v>30350</v>
+        <v>30338</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3707</v>
+        <v>3714</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30580</v>
+        <v>30583</v>
       </c>
       <c r="G91">
-        <v>44035</v>
+        <v>44040</v>
       </c>
       <c r="H91">
-        <v>26873</v>
+        <v>26869</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9524</v>
+        <v>9542</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>24524</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>35315</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>64144</v>
+        <v>64264</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>79144</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>113967</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34677</v>
+        <v>34742</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52354</v>
+        <v>52380</v>
       </c>
       <c r="G97">
-        <v>75390</v>
+        <v>75427</v>
       </c>
       <c r="H97">
-        <v>17677</v>
+        <v>17638</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79516</v>
+        <v>79666</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>94516</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>136103</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>42363</v>
+        <v>44124</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>60482</v>
+        <v>61187</v>
       </c>
       <c r="G99">
-        <v>87094</v>
+        <v>88109</v>
       </c>
       <c r="H99">
-        <v>18119</v>
+        <v>17063</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60820</v>
+        <v>61126</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>80934</v>
+        <v>79011</v>
       </c>
       <c r="G100">
-        <v>116545</v>
+        <v>113776</v>
       </c>
       <c r="H100">
-        <v>20114</v>
+        <v>17885</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63457</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>78457</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>112978</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>75279</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>102279</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>147282</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6200</v>
+        <v>6212</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33200</v>
+        <v>33212</v>
       </c>
       <c r="G109">
-        <v>47808</v>
+        <v>47825</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15133</v>
+        <v>15161</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42133</v>
+        <v>42161</v>
       </c>
       <c r="G111">
-        <v>60672</v>
+        <v>60712</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>50545</v>
+        <v>50640</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>76751</v>
+        <v>76789</v>
       </c>
       <c r="G113">
-        <v>110521</v>
+        <v>110576</v>
       </c>
       <c r="H113">
-        <v>26206</v>
+        <v>26149</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>97853</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>117334</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>168961</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>19481</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80571</v>
+        <v>80722</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>95571</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>137622</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50337</v>
+        <v>46781</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>61781</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>88965</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>86036</v>
+        <v>102688</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>101036</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>145492</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46326</v>
+        <v>46413</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>61326</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>88309</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35268</v>
+        <v>35334</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>50268</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72386</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63952</v>
+        <v>64072</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>78952</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>113691</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>36898</v>
+        <v>32452</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>56852</v>
+        <v>55074</v>
       </c>
       <c r="G129">
-        <v>81867</v>
+        <v>79307</v>
       </c>
       <c r="H129">
-        <v>19954</v>
+        <v>22622</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,7 +6110,7 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12768</v>
+        <v>12792</v>
       </c>
       <c r="E130">
         <v>44413</v>
@@ -6122,7 +6122,7 @@
         <v>47966</v>
       </c>
       <c r="H130">
-        <v>20542</v>
+        <v>20518</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5849</v>
+        <v>5748</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25660</v>
+        <v>25620</v>
       </c>
       <c r="G131">
-        <v>36950</v>
+        <v>36893</v>
       </c>
       <c r="H131">
-        <v>19811</v>
+        <v>19872</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27789</v>
+        <v>27841</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43766</v>
+        <v>43787</v>
       </c>
       <c r="G132">
-        <v>63023</v>
+        <v>63053</v>
       </c>
       <c r="H132">
-        <v>15977</v>
+        <v>15946</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17386</v>
+        <v>17419</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36622</v>
+        <v>36635</v>
       </c>
       <c r="G135">
-        <v>52736</v>
+        <v>52754</v>
       </c>
       <c r="H135">
-        <v>19236</v>
+        <v>19216</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28173</v>
+        <v>28226</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46756</v>
+        <v>46777</v>
       </c>
       <c r="G137">
-        <v>67329</v>
+        <v>67359</v>
       </c>
       <c r="H137">
-        <v>18583</v>
+        <v>18551</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27821</v>
+        <v>27729</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54247</v>
+        <v>54210</v>
       </c>
       <c r="G139">
-        <v>78116</v>
+        <v>78062</v>
       </c>
       <c r="H139">
-        <v>26426</v>
+        <v>26481</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58407</v>
+        <v>58517</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>73407</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>105706</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77918</v>
+        <v>78065</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>92918</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>133802</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87522</v>
+        <v>87687</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>102522</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>147632</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>88337</v>
+        <v>88503</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>103337</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>148805</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122710</v>
+        <v>126847</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>137710</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>198302</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38464</v>
+        <v>38536</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>63032</v>
+        <v>63060</v>
       </c>
       <c r="G150">
-        <v>90766</v>
+        <v>90806</v>
       </c>
       <c r="H150">
-        <v>24568</v>
+        <v>24524</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>23251</v>
+        <v>24703</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>58251</v>
+        <v>59703</v>
       </c>
       <c r="G152">
-        <v>83881</v>
+        <v>85972</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29787</v>
+        <v>29843</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>54008</v>
+        <v>54030</v>
       </c>
       <c r="G153">
-        <v>77772</v>
+        <v>77803</v>
       </c>
       <c r="H153">
-        <v>24221</v>
+        <v>24187</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48915</v>
+        <v>49007</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20495</v>
+        <v>20403</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>76033</v>
+        <v>76416</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>91033</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>131088</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65742</v>
+        <v>65865</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80742</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>116268</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>46789</v>
+        <v>39208</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65802</v>
+        <v>65893</v>
       </c>
       <c r="G158">
-        <v>94755</v>
+        <v>94886</v>
       </c>
       <c r="H158">
-        <v>19013</v>
+        <v>26685</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42219</v>
+        <v>42298</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>57219</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>82395</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>17993</v>
+        <v>18027</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>34850</v>
+        <v>34864</v>
       </c>
       <c r="G161">
-        <v>50184</v>
+        <v>50204</v>
       </c>
       <c r="H161">
-        <v>16857</v>
+        <v>16837</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56345</v>
+        <v>56451</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>71345</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>102737</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>81051</v>
+        <v>81203</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>96051</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>138313</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>59046</v>
+        <v>54418</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>74046</v>
+        <v>74110</v>
       </c>
       <c r="G166">
-        <v>106626</v>
+        <v>106718</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>19692</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34133</v>
+        <v>34197</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>49133</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70752</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>67755</v>
+        <v>63063</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>102703</v>
+        <v>98063</v>
       </c>
       <c r="G168">
-        <v>147892</v>
+        <v>141211</v>
       </c>
       <c r="H168">
-        <v>34948</v>
+        <v>35000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74307</v>
+        <v>74447</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>89307</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>128602</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>16108</v>
+        <v>15834</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>30834</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>44401</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31193</v>
+        <v>31700</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51682</v>
+        <v>51885</v>
       </c>
       <c r="G173">
-        <v>74422</v>
+        <v>74714</v>
       </c>
       <c r="H173">
-        <v>20489</v>
+        <v>20185</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7638</v>
+        <v>7621</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37776</v>
+        <v>37792</v>
       </c>
       <c r="G174">
-        <v>54397</v>
+        <v>54420</v>
       </c>
       <c r="H174">
-        <v>30138</v>
+        <v>30171</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5289</v>
+        <v>5331</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29776</v>
+        <v>29792</v>
       </c>
       <c r="G175">
-        <v>42877</v>
+        <v>42900</v>
       </c>
       <c r="H175">
-        <v>24487</v>
+        <v>24461</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10371</v>
+        <v>10390</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>43469</v>
+        <v>42509</v>
       </c>
       <c r="G176">
-        <v>62595</v>
+        <v>61213</v>
       </c>
       <c r="H176">
-        <v>33098</v>
+        <v>32119</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>8469</v>
+        <v>7509</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>35469</v>
+        <v>34509</v>
       </c>
       <c r="G177">
-        <v>51075</v>
+        <v>49693</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,19 +8212,19 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>49231</v>
       </c>
       <c r="E178">
         <v>69424</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>64231</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>92493</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I178" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21381</v>
+        <v>22014</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41628</v>
+        <v>41881</v>
       </c>
       <c r="G179">
-        <v>59944</v>
+        <v>60309</v>
       </c>
       <c r="H179">
-        <v>20247</v>
+        <v>19867</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46230</v>
+        <v>46205</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65285</v>
+        <v>65275</v>
       </c>
       <c r="G181">
-        <v>94010</v>
+        <v>93996</v>
       </c>
       <c r="H181">
-        <v>19055</v>
+        <v>19070</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68187</v>
+        <v>68315</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>85881</v>
+        <v>86844</v>
       </c>
       <c r="G182">
-        <v>123669</v>
+        <v>125055</v>
       </c>
       <c r="H182">
-        <v>17694</v>
+        <v>18529</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>9492</v>
+        <v>10455</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>36492</v>
+        <v>37455</v>
       </c>
       <c r="G183">
-        <v>52548</v>
+        <v>53935</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60868</v>
+        <v>60982</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80324</v>
+        <v>80369</v>
       </c>
       <c r="G184">
-        <v>115667</v>
+        <v>115731</v>
       </c>
       <c r="H184">
-        <v>19456</v>
+        <v>19387</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>45831</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>67645</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>97409</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>21814</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>80363</v>
+        <v>80514</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>111028</v>
+        <v>104844</v>
       </c>
       <c r="G186">
-        <v>159880</v>
+        <v>150975</v>
       </c>
       <c r="H186">
-        <v>30665</v>
+        <v>24330</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81546</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>96546</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>139026</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>172185</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>187185</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>269546</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7175</v>
+        <v>7269</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>27763</v>
+        <v>27669</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11809</v>
+        <v>11831</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38809</v>
+        <v>38831</v>
       </c>
       <c r="G196">
-        <v>55885</v>
+        <v>55917</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51887</v>
+        <v>51984</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17523</v>
+        <v>17426</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75330</v>
+        <v>75471</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>90330</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>130075</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>56985</v>
+        <v>57092</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>71985</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>103658</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36882</v>
+        <v>36951</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63882</v>
+        <v>63951</v>
       </c>
       <c r="G202">
-        <v>91990</v>
+        <v>92089</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27613</v>
+        <v>27665</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54613</v>
+        <v>54665</v>
       </c>
       <c r="G204">
-        <v>78643</v>
+        <v>78718</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>102448</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>117448</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>169125</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63728</v>
+        <v>63656</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>82024</v>
+        <v>81996</v>
       </c>
       <c r="G207">
-        <v>118115</v>
+        <v>118074</v>
       </c>
       <c r="H207">
-        <v>18296</v>
+        <v>18340</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>145402</v>
+        <v>145675</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>180402</v>
+        <v>180675</v>
       </c>
       <c r="G208">
-        <v>259779</v>
+        <v>260172</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145450</v>
+        <v>145579</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>160450</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>231048</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>188548</v>
+        <v>188902</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>203548</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>293109</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>186343</v>
+        <v>186693</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>201343</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>289934</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>289222</v>
+        <v>289765</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>304222</v>
+        <v>0</v>
       </c>
       <c r="G212">
-        <v>438080</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34884</v>
+        <v>34678</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>60881</v>
+        <v>57806</v>
       </c>
       <c r="G214">
-        <v>87669</v>
+        <v>83241</v>
       </c>
       <c r="H214">
-        <v>25997</v>
+        <v>23128</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>37697</v>
+        <v>34806</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>49806</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>71721</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>60532</v>
+        <v>60646</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>75646</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>108930</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67675</v>
+        <v>67802</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>82802</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>119235</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>13199</v>
+        <v>12728</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>40199</v>
+        <v>44654</v>
       </c>
       <c r="G220">
-        <v>57887</v>
+        <v>64302</v>
       </c>
       <c r="H220">
-        <v>27000</v>
+        <v>31926</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,19 +10094,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>9654</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>36654</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>52782</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>27150</v>
+        <v>24111</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>62150</v>
+        <v>59111</v>
       </c>
       <c r="G222">
-        <v>89496</v>
+        <v>85120</v>
       </c>
       <c r="H222">
         <v>35000</v>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>53725</v>
+        <v>53826</v>
       </c>
       <c r="E223">
         <v>111059</v>
       </c>
       <c r="F223">
-        <v>70803</v>
+        <v>70843</v>
       </c>
       <c r="G223">
-        <v>101956</v>
+        <v>102014</v>
       </c>
       <c r="H223">
-        <v>17078</v>
+        <v>17017</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>17290</v>
+        <v>17435</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46554</v>
+        <v>46559</v>
       </c>
       <c r="G224">
-        <v>67038</v>
+        <v>67045</v>
       </c>
       <c r="H224">
-        <v>29264</v>
+        <v>29124</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11554</v>
+        <v>11559</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38554</v>
+        <v>38559</v>
       </c>
       <c r="G225">
-        <v>55518</v>
+        <v>55525</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26607</v>
+        <v>26657</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61607</v>
+        <v>61657</v>
       </c>
       <c r="G226">
-        <v>88714</v>
+        <v>88786</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>95496</v>
+        <v>95660</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>110660</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>159350</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35859</v>
+        <v>35926</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>62859</v>
+        <v>62926</v>
       </c>
       <c r="G228">
-        <v>90517</v>
+        <v>90613</v>
       </c>
       <c r="H228">
         <v>27000</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15948</v>
+        <v>15866</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42838</v>
+        <v>42903</v>
       </c>
       <c r="G230">
-        <v>61687</v>
+        <v>61780</v>
       </c>
       <c r="H230">
-        <v>26890</v>
+        <v>27037</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9828</v>
+        <v>9990</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>33028</v>
+        <v>33093</v>
       </c>
       <c r="G231">
-        <v>47560</v>
+        <v>47654</v>
       </c>
       <c r="H231">
-        <v>23200</v>
+        <v>23103</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>86438</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>112768</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>162386</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>26330</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26719</v>
+        <v>26769</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>53719</v>
+        <v>53769</v>
       </c>
       <c r="G238">
-        <v>77355</v>
+        <v>77427</v>
       </c>
       <c r="H238">
         <v>27000</v>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47205</v>
+        <v>47294</v>
       </c>
       <c r="E240">
         <v>103654</v>
       </c>
       <c r="F240">
-        <v>71527</v>
+        <v>71562</v>
       </c>
       <c r="G240">
-        <v>102999</v>
+        <v>103049</v>
       </c>
       <c r="H240">
-        <v>24322</v>
+        <v>24268</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64479</v>
+        <v>64600</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79479</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>114450</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>76544</v>
+        <v>76704</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>91544</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>131823</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17466</v>
+        <v>17163</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42530</v>
+        <v>42538</v>
       </c>
       <c r="G248">
-        <v>61243</v>
+        <v>61255</v>
       </c>
       <c r="H248">
-        <v>25064</v>
+        <v>25375</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11777</v>
+        <v>11799</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34530</v>
+        <v>34538</v>
       </c>
       <c r="G249">
-        <v>49723</v>
+        <v>49735</v>
       </c>
       <c r="H249">
-        <v>22753</v>
+        <v>22739</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>31444</v>
       </c>
       <c r="E250">
         <v>74033</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>51893</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>74726</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>20449</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16683</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>43683</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>62904</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>23455</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>50455</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>72655</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9620</v>
+        <v>9638</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>50311</v>
       </c>
       <c r="H256">
-        <v>25318</v>
+        <v>25300</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12353</v>
+        <v>12376</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39353</v>
+        <v>39376</v>
       </c>
       <c r="G258">
-        <v>56668</v>
+        <v>56701</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8901</v>
+        <v>8918</v>
       </c>
       <c r="E260">
         <v>53688</v>
       </c>
       <c r="F260">
-        <v>39349</v>
+        <v>39357</v>
       </c>
       <c r="G260">
-        <v>56663</v>
+        <v>56674</v>
       </c>
       <c r="H260">
-        <v>30448</v>
+        <v>30439</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11026</v>
+        <v>11047</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>31349</v>
+        <v>31357</v>
       </c>
       <c r="G261">
-        <v>45143</v>
+        <v>45154</v>
       </c>
       <c r="H261">
-        <v>20323</v>
+        <v>20310</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>11570</v>
+        <v>12936</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>34938</v>
+        <v>35334</v>
       </c>
       <c r="G262">
-        <v>50311</v>
+        <v>50881</v>
       </c>
       <c r="H262">
-        <v>23368</v>
+        <v>22398</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>18617</v>
+        <v>19820</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>45617</v>
+        <v>46419</v>
       </c>
       <c r="G264">
-        <v>65688</v>
+        <v>66843</v>
       </c>
       <c r="H264">
-        <v>27000</v>
+        <v>26599</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34517</v>
+        <v>34582</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>52297</v>
+        <v>52323</v>
       </c>
       <c r="G266">
-        <v>75308</v>
+        <v>75345</v>
       </c>
       <c r="H266">
-        <v>17780</v>
+        <v>17741</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10291</v>
+        <v>10342</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>25291</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>36419</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12225</v>
+        <v>12264</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>39225</v>
+        <v>39264</v>
       </c>
       <c r="G270">
-        <v>56484</v>
+        <v>56540</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62386</v>
+        <v>62439</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>77386</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>111436</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,16 +12430,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>70008</v>
+        <v>69483</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>85008</v>
+        <v>84483</v>
       </c>
       <c r="G274">
-        <v>122412</v>
+        <v>121656</v>
       </c>
       <c r="H274">
         <v>15000</v>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11218</v>
+        <v>11239</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>34938</v>
+        <v>37871</v>
       </c>
       <c r="G276">
-        <v>50311</v>
+        <v>54534</v>
       </c>
       <c r="H276">
-        <v>23720</v>
+        <v>26632</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>7333</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>29871</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>43014</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>22538</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20263</v>
+        <v>20301</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>46596</v>
+        <v>46611</v>
       </c>
       <c r="G278">
-        <v>67098</v>
+        <v>67120</v>
       </c>
       <c r="H278">
-        <v>26333</v>
+        <v>26310</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11793</v>
+        <v>11815</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23145</v>
+        <v>23123</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17754</v>
+        <v>17819</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32754</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>47166</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,16 +12912,16 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50273</v>
+        <v>50271</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>65273</v>
+        <v>65271</v>
       </c>
       <c r="G285">
-        <v>93993</v>
+        <v>93990</v>
       </c>
       <c r="H285">
         <v>15000</v>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>59110</v>
+        <v>59301</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>74110</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>106718</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>40126</v>
+        <v>40105</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55814</v>
+        <v>55832</v>
       </c>
       <c r="G288">
-        <v>80372</v>
+        <v>80398</v>
       </c>
       <c r="H288">
-        <v>15688</v>
+        <v>15727</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23842</v>
+        <v>23887</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39356</v>
+        <v>39374</v>
       </c>
       <c r="G289">
-        <v>56673</v>
+        <v>56699</v>
       </c>
       <c r="H289">
-        <v>15514</v>
+        <v>15487</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>44872</v>
+        <v>42042</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>62200</v>
+        <v>62218</v>
       </c>
       <c r="G292">
-        <v>89568</v>
+        <v>89594</v>
       </c>
       <c r="H292">
-        <v>17328</v>
+        <v>20176</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23794</v>
+        <v>23839</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39336</v>
+        <v>39354</v>
       </c>
       <c r="G293">
-        <v>56644</v>
+        <v>56670</v>
       </c>
       <c r="H293">
-        <v>15542</v>
+        <v>15515</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62945</v>
+        <v>63063</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>77945</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>112241</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>92700</v>
+        <v>92874</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>107700</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>155088</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>70839</v>
+        <v>70972</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>89120</v>
+        <v>88961</v>
       </c>
       <c r="G300">
-        <v>128333</v>
+        <v>128104</v>
       </c>
       <c r="H300">
-        <v>18281</v>
+        <v>17989</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>35396</v>
+        <v>34998</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>56251</v>
+        <v>56092</v>
       </c>
       <c r="G301">
-        <v>81001</v>
+        <v>80772</v>
       </c>
       <c r="H301">
-        <v>20855</v>
+        <v>21094</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12113</v>
+        <v>12056</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>39113</v>
+        <v>39056</v>
       </c>
       <c r="G303">
-        <v>56323</v>
+        <v>56241</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,19 +13748,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>174853</v>
+        <v>175181</v>
       </c>
       <c r="E304">
         <v>166598</v>
       </c>
       <c r="F304">
-        <v>189853</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>273388</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>50241</v>
+        <v>52545</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>80054</v>
+        <v>80092</v>
       </c>
       <c r="G306">
-        <v>115278</v>
+        <v>115332</v>
       </c>
       <c r="H306">
-        <v>29813</v>
+        <v>27547</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50657</v>
+        <v>50752</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69576</v>
+        <v>69614</v>
       </c>
       <c r="G307">
-        <v>100189</v>
+        <v>100244</v>
       </c>
       <c r="H307">
-        <v>18919</v>
+        <v>18862</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69529</v>
+        <v>69660</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>27650</v>
+        <v>27519</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>105963</v>
+        <v>106242</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>120963</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>174187</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24769</v>
+        <v>24591</v>
       </c>
       <c r="E310">
         <v>55520</v>
       </c>
       <c r="F310">
-        <v>40892</v>
+        <v>40820</v>
       </c>
       <c r="G310">
-        <v>58884</v>
+        <v>58781</v>
       </c>
       <c r="H310">
-        <v>16123</v>
+        <v>16229</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>68634</v>
+        <v>68843</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>0</v>
+        <v>83843</v>
       </c>
       <c r="G312">
-        <v>0</v>
+        <v>120734</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20918</v>
+        <v>20957</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>35918</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>51722</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>34037</v>
+        <v>34101</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>62990</v>
+        <v>63076</v>
       </c>
       <c r="G316">
-        <v>90706</v>
+        <v>90829</v>
       </c>
       <c r="H316">
-        <v>28953</v>
+        <v>28975</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39774</v>
+        <v>39849</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>54774</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>78875</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,19 +14366,19 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>16284</v>
+        <v>19388</v>
       </c>
       <c r="E318">
         <v>44413</v>
       </c>
       <c r="F318">
-        <v>33310</v>
+        <v>0</v>
       </c>
       <c r="G318">
-        <v>47966</v>
+        <v>0</v>
       </c>
       <c r="H318">
-        <v>17026</v>
+        <v>0</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29611</v>
+        <v>29651</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44611</v>
+        <v>0</v>
       </c>
       <c r="G319">
-        <v>64240</v>
+        <v>0</v>
       </c>
       <c r="H319">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14456,19 +14456,19 @@
         <v>15</v>
       </c>
       <c r="D320">
-        <v>50625</v>
+        <v>0</v>
       </c>
       <c r="E320">
         <v>111059</v>
       </c>
       <c r="F320">
-        <v>76226</v>
+        <v>0</v>
       </c>
       <c r="G320">
-        <v>109765</v>
+        <v>0</v>
       </c>
       <c r="H320">
-        <v>25601</v>
+        <v>0</v>
       </c>
       <c r="I320" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9428</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>35034</v>
+        <v>0</v>
       </c>
       <c r="G327">
-        <v>50449</v>
+        <v>0</v>
       </c>
       <c r="H327">
-        <v>25606</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>20966</v>
+        <v>21005</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>47966</v>
+        <v>48005</v>
       </c>
       <c r="G330">
-        <v>69071</v>
+        <v>69127</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43881</v>
+        <v>43963</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>70881</v>
+        <v>70963</v>
       </c>
       <c r="G332">
-        <v>102069</v>
+        <v>102187</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32503</v>
+        <v>33333</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>59503</v>
+        <v>60333</v>
       </c>
       <c r="G334">
-        <v>85684</v>
+        <v>86880</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>189858</v>
+        <v>190215</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>204858</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>294996</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>63760</v>
+        <v>63544</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89811</v>
+        <v>89725</v>
       </c>
       <c r="G338">
-        <v>129328</v>
+        <v>129204</v>
       </c>
       <c r="H338">
-        <v>26051</v>
+        <v>26181</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72349</v>
+        <v>72186</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>87186</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>125548</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>48142</v>
+        <v>48092</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>63092</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90852</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95276</v>
+        <v>95335</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>110335</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>158882</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>78401</v>
+        <v>71722</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>93401</v>
+        <v>86722</v>
       </c>
       <c r="G5">
-        <v>134497</v>
+        <v>124880</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7205</v>
+        <v>7209</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30535</v>
+        <v>30536</v>
       </c>
       <c r="G7">
-        <v>43970</v>
+        <v>43972</v>
       </c>
       <c r="H7">
-        <v>23330</v>
+        <v>23327</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39737</v>
+        <v>39762</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55210</v>
+        <v>55220</v>
       </c>
       <c r="G8">
-        <v>79502</v>
+        <v>79517</v>
       </c>
       <c r="H8">
-        <v>15473</v>
+        <v>15458</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56659</v>
+        <v>58185</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78640</v>
+        <v>79250</v>
       </c>
       <c r="G10">
-        <v>113242</v>
+        <v>114120</v>
       </c>
       <c r="H10">
-        <v>21981</v>
+        <v>21065</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>75231</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>111059</v>
       </c>
       <c r="F11">
-        <v>90231</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>129933</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>85173</v>
+        <v>85226</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>101060</v>
+        <v>101052</v>
       </c>
       <c r="G12">
-        <v>145526</v>
+        <v>145515</v>
       </c>
       <c r="H12">
-        <v>15887</v>
+        <v>15826</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>12712</v>
+        <v>12704</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>39712</v>
+        <v>39704</v>
       </c>
       <c r="G13">
-        <v>57185</v>
+        <v>57174</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27361</v>
+        <v>27378</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45817</v>
+        <v>45824</v>
       </c>
       <c r="G15">
-        <v>65976</v>
+        <v>65987</v>
       </c>
       <c r="H15">
-        <v>18456</v>
+        <v>18446</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>49567</v>
+        <v>54804</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>66252</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>95403</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>16685</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96460</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>111460</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>160502</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21918</v>
+        <v>22636</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>40030</v>
+        <v>40317</v>
       </c>
       <c r="G27">
-        <v>57643</v>
+        <v>58056</v>
       </c>
       <c r="H27">
-        <v>18112</v>
+        <v>17681</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>77216</v>
+        <v>74093</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96642</v>
+        <v>96425</v>
       </c>
       <c r="G28">
-        <v>139164</v>
+        <v>138852</v>
       </c>
       <c r="H28">
-        <v>19426</v>
+        <v>22332</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>38200</v>
+        <v>37983</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>65200</v>
+        <v>64983</v>
       </c>
       <c r="G29">
-        <v>93888</v>
+        <v>93576</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,7 +1730,7 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>120331</v>
+        <v>123194</v>
       </c>
       <c r="E30">
         <v>185111</v>
@@ -1742,7 +1742,7 @@
         <v>199920</v>
       </c>
       <c r="H30">
-        <v>18502</v>
+        <v>15639</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,19 +1776,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>80066</v>
+        <v>98203</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>107066</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>154175</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60982</v>
+        <v>62270</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>81082</v>
+        <v>80960</v>
       </c>
       <c r="G32">
-        <v>116758</v>
+        <v>116582</v>
       </c>
       <c r="H32">
-        <v>20100</v>
+        <v>18690</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36551</v>
+        <v>36429</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63551</v>
+        <v>63429</v>
       </c>
       <c r="G33">
-        <v>91513</v>
+        <v>91338</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48366</v>
+        <v>48861</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75366</v>
+        <v>75861</v>
       </c>
       <c r="G36">
-        <v>108527</v>
+        <v>109240</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35677</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62677</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>90255</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>68251</v>
+        <v>68021</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>95251</v>
+        <v>95021</v>
       </c>
       <c r="G38">
-        <v>137161</v>
+        <v>136830</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>67540</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>94540</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>136138</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87559</v>
+        <v>86989</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>114559</v>
+        <v>113989</v>
       </c>
       <c r="G40">
-        <v>164965</v>
+        <v>164144</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31828</v>
+        <v>31848</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58828</v>
+        <v>58848</v>
       </c>
       <c r="G43">
-        <v>84712</v>
+        <v>84741</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>80164</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>107164</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>154316</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>20637</v>
+        <v>20329</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>47637</v>
+        <v>47329</v>
       </c>
       <c r="G47">
-        <v>68597</v>
+        <v>68154</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36967</v>
+        <v>40803</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>57053</v>
+        <v>66292</v>
       </c>
       <c r="G50">
-        <v>82156</v>
+        <v>95460</v>
       </c>
       <c r="H50">
-        <v>20086</v>
+        <v>25489</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>34053</v>
+        <v>42645</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>49053</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>70636</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54418</v>
+        <v>59899</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>69418</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>99962</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>59221</v>
+        <v>68069</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>74221</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>106878</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>49535</v>
+        <v>49566</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>82749</v>
+        <v>82782</v>
       </c>
       <c r="G54">
-        <v>119159</v>
+        <v>119206</v>
       </c>
       <c r="H54">
-        <v>33214</v>
+        <v>33216</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44956</v>
+        <v>44984</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71956</v>
+        <v>71984</v>
       </c>
       <c r="G55">
-        <v>103617</v>
+        <v>103657</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53938</v>
+        <v>54212</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>80938</v>
+        <v>81212</v>
       </c>
       <c r="G56">
-        <v>116551</v>
+        <v>116945</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66361</v>
+        <v>66403</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90297</v>
+        <v>90314</v>
       </c>
       <c r="G57">
-        <v>130028</v>
+        <v>130052</v>
       </c>
       <c r="H57">
-        <v>23936</v>
+        <v>23911</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>15834</v>
+        <v>15668</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38670</v>
+        <v>38672</v>
       </c>
       <c r="G58">
-        <v>55685</v>
+        <v>55688</v>
       </c>
       <c r="H58">
-        <v>22836</v>
+        <v>23004</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22937</v>
+        <v>22939</v>
       </c>
       <c r="G59">
-        <v>33029</v>
+        <v>33032</v>
       </c>
       <c r="H59">
-        <v>16677</v>
+        <v>16675</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24255</v>
+        <v>24270</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>39255</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>56527</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>25648</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40648</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58533</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13961</v>
+        <v>14322</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>40961</v>
+        <v>41322</v>
       </c>
       <c r="G63">
-        <v>58984</v>
+        <v>59504</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>34245</v>
+        <v>34267</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>61245</v>
+        <v>61267</v>
       </c>
       <c r="G65">
-        <v>88193</v>
+        <v>88224</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25984</v>
+        <v>26033</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60923</v>
+        <v>60808</v>
       </c>
       <c r="G66">
-        <v>87729</v>
+        <v>87564</v>
       </c>
       <c r="H66">
-        <v>34939</v>
+        <v>34775</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20877</v>
+        <v>20762</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47877</v>
+        <v>47762</v>
       </c>
       <c r="G67">
-        <v>68943</v>
+        <v>68777</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48302</v>
+        <v>48332</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75297</v>
+        <v>75309</v>
       </c>
       <c r="G68">
-        <v>108428</v>
+        <v>108445</v>
       </c>
       <c r="H68">
-        <v>26995</v>
+        <v>26977</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27793</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>54793</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>78902</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>111157</v>
+        <v>111243</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>126243</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>181790</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52785</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>77647</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>111812</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>24862</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6788</v>
+        <v>6857</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21788</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>31375</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88567</v>
+        <v>88623</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>123343</v>
+        <v>121046</v>
       </c>
       <c r="G76">
-        <v>177614</v>
+        <v>174306</v>
       </c>
       <c r="H76">
-        <v>34776</v>
+        <v>32423</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>63480</v>
+        <v>57736</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>81925</v>
+        <v>79628</v>
       </c>
       <c r="G77">
-        <v>117972</v>
+        <v>114664</v>
       </c>
       <c r="H77">
-        <v>18445</v>
+        <v>21892</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>24687</v>
+        <v>24703</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>51687</v>
+        <v>51703</v>
       </c>
       <c r="G81">
-        <v>74429</v>
+        <v>74452</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87591</v>
+        <v>87645</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>102645</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>147809</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>46621</v>
+        <v>46490</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>66777</v>
+        <v>67637</v>
       </c>
       <c r="G84">
-        <v>96159</v>
+        <v>97397</v>
       </c>
       <c r="H84">
-        <v>20156</v>
+        <v>21147</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>43067</v>
+        <v>43815</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>58067</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>83616</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8245</v>
+        <v>8250</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38583</v>
+        <v>38584</v>
       </c>
       <c r="G90">
-        <v>55560</v>
+        <v>55561</v>
       </c>
       <c r="H90">
-        <v>30338</v>
+        <v>30334</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3714</v>
+        <v>3717</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30583</v>
+        <v>30584</v>
       </c>
       <c r="G91">
-        <v>44040</v>
+        <v>44041</v>
       </c>
       <c r="H91">
-        <v>26869</v>
+        <v>26867</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9542</v>
+        <v>9548</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>24548</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>35349</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>64264</v>
+        <v>64304</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>79304</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>114198</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34742</v>
+        <v>34763</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52380</v>
+        <v>52389</v>
       </c>
       <c r="G97">
-        <v>75427</v>
+        <v>75440</v>
       </c>
       <c r="H97">
-        <v>17638</v>
+        <v>17626</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79666</v>
+        <v>79716</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>94716</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>136391</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>44124</v>
+        <v>44151</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>61187</v>
+        <v>61198</v>
       </c>
       <c r="G99">
-        <v>88109</v>
+        <v>88125</v>
       </c>
       <c r="H99">
-        <v>17063</v>
+        <v>17047</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61126</v>
+        <v>61341</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>79011</v>
+        <v>79097</v>
       </c>
       <c r="G100">
-        <v>113776</v>
+        <v>113900</v>
       </c>
       <c r="H100">
-        <v>17885</v>
+        <v>17756</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>71962</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>86962</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>125225</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>75279</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>102279</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>147282</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33212</v>
+        <v>33216</v>
       </c>
       <c r="G109">
-        <v>47825</v>
+        <v>47831</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15161</v>
+        <v>15171</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42161</v>
+        <v>42171</v>
       </c>
       <c r="G111">
-        <v>60712</v>
+        <v>60726</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>50640</v>
+        <v>51568</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>76789</v>
+        <v>77160</v>
       </c>
       <c r="G113">
-        <v>110576</v>
+        <v>111110</v>
       </c>
       <c r="H113">
-        <v>26149</v>
+        <v>25592</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>97853</v>
+        <v>94502</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>117334</v>
+        <v>115994</v>
       </c>
       <c r="G115">
-        <v>168961</v>
+        <v>167031</v>
       </c>
       <c r="H115">
-        <v>19481</v>
+        <v>21492</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80722</v>
+        <v>80773</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>95773</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>137913</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>46781</v>
+        <v>50463</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>61781</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>88965</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102688</v>
+        <v>102752</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>117752</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>169563</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46413</v>
+        <v>46458</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>61458</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>88500</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35334</v>
+        <v>35356</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50356</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72513</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>64072</v>
+        <v>64112</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>79112</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>113921</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>32452</v>
+        <v>32473</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>55074</v>
+        <v>55082</v>
       </c>
       <c r="G129">
-        <v>79307</v>
+        <v>79318</v>
       </c>
       <c r="H129">
-        <v>22622</v>
+        <v>22609</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,7 +6110,7 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12792</v>
+        <v>12800</v>
       </c>
       <c r="E130">
         <v>44413</v>
@@ -6122,7 +6122,7 @@
         <v>47966</v>
       </c>
       <c r="H130">
-        <v>20518</v>
+        <v>20510</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5748</v>
+        <v>5559</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25620</v>
+        <v>25544</v>
       </c>
       <c r="G131">
-        <v>36893</v>
+        <v>36783</v>
       </c>
       <c r="H131">
-        <v>19872</v>
+        <v>19985</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27841</v>
+        <v>27859</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43787</v>
+        <v>43794</v>
       </c>
       <c r="G132">
-        <v>63053</v>
+        <v>63063</v>
       </c>
       <c r="H132">
-        <v>15946</v>
+        <v>15935</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17419</v>
+        <v>17430</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36635</v>
+        <v>36640</v>
       </c>
       <c r="G135">
-        <v>52754</v>
+        <v>52762</v>
       </c>
       <c r="H135">
-        <v>19216</v>
+        <v>19210</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28226</v>
+        <v>28243</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46777</v>
+        <v>46784</v>
       </c>
       <c r="G137">
-        <v>67359</v>
+        <v>67369</v>
       </c>
       <c r="H137">
-        <v>18551</v>
+        <v>18541</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27729</v>
+        <v>27586</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54210</v>
+        <v>54153</v>
       </c>
       <c r="G139">
-        <v>78062</v>
+        <v>77980</v>
       </c>
       <c r="H139">
-        <v>26481</v>
+        <v>26567</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58517</v>
+        <v>58553</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>73553</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>105916</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>78065</v>
+        <v>78114</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>93114</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>134084</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87687</v>
+        <v>87742</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>102742</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>147948</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>88503</v>
+        <v>88879</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>103879</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>149586</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>126847</v>
+        <v>127343</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>142343</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>204974</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38536</v>
+        <v>38560</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>63060</v>
+        <v>63070</v>
       </c>
       <c r="G150">
-        <v>90806</v>
+        <v>90821</v>
       </c>
       <c r="H150">
-        <v>24524</v>
+        <v>24510</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24703</v>
+        <v>23774</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>59703</v>
+        <v>58774</v>
       </c>
       <c r="G152">
-        <v>85972</v>
+        <v>84635</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29843</v>
+        <v>29861</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>54030</v>
+        <v>54037</v>
       </c>
       <c r="G153">
-        <v>77803</v>
+        <v>77813</v>
       </c>
       <c r="H153">
-        <v>24187</v>
+        <v>24176</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>49007</v>
+        <v>49037</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20403</v>
+        <v>20373</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>76416</v>
+        <v>76463</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>91463</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>131707</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65865</v>
+        <v>65906</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80906</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>116505</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>39208</v>
+        <v>39233</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65893</v>
+        <v>65924</v>
       </c>
       <c r="G158">
-        <v>94886</v>
+        <v>94931</v>
       </c>
       <c r="H158">
-        <v>26685</v>
+        <v>26691</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42298</v>
+        <v>42325</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>57325</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>82548</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>18027</v>
+        <v>20233</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>34864</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>50204</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>16837</v>
+        <v>0</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56451</v>
+        <v>56487</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>71487</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>102941</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>81203</v>
+        <v>81253</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>96253</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>138604</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54418</v>
+        <v>54452</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>74110</v>
+        <v>69452</v>
       </c>
       <c r="G166">
-        <v>106718</v>
+        <v>100011</v>
       </c>
       <c r="H166">
-        <v>19692</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34197</v>
+        <v>34219</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>49219</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70875</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>63063</v>
+        <v>67925</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>98063</v>
+        <v>82925</v>
       </c>
       <c r="G168">
-        <v>141211</v>
+        <v>119412</v>
       </c>
       <c r="H168">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,7 +7815,7 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74447</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>74033</v>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15834</v>
+        <v>16757</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>30834</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>44401</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31700</v>
+        <v>31720</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51885</v>
+        <v>51893</v>
       </c>
       <c r="G173">
-        <v>74714</v>
+        <v>74726</v>
       </c>
       <c r="H173">
-        <v>20185</v>
+        <v>20173</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7621</v>
+        <v>7577</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37792</v>
+        <v>37794</v>
       </c>
       <c r="G174">
-        <v>54420</v>
+        <v>54423</v>
       </c>
       <c r="H174">
-        <v>30171</v>
+        <v>30217</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5331</v>
+        <v>5335</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29792</v>
+        <v>29794</v>
       </c>
       <c r="G175">
-        <v>42900</v>
+        <v>42903</v>
       </c>
       <c r="H175">
-        <v>24461</v>
+        <v>24459</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10390</v>
+        <v>10397</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>42509</v>
+        <v>43122</v>
       </c>
       <c r="G176">
-        <v>61213</v>
+        <v>62096</v>
       </c>
       <c r="H176">
-        <v>32119</v>
+        <v>32725</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7509</v>
+        <v>8122</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>34509</v>
+        <v>35122</v>
       </c>
       <c r="G177">
-        <v>49693</v>
+        <v>50576</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,19 +8212,19 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>49231</v>
+        <v>49262</v>
       </c>
       <c r="E178">
         <v>69424</v>
       </c>
       <c r="F178">
-        <v>64231</v>
+        <v>0</v>
       </c>
       <c r="G178">
-        <v>92493</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I178" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>22014</v>
+        <v>22028</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41881</v>
+        <v>41887</v>
       </c>
       <c r="G179">
-        <v>60309</v>
+        <v>60317</v>
       </c>
       <c r="H179">
-        <v>19867</v>
+        <v>19859</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65275</v>
+        <v>65281</v>
       </c>
       <c r="G181">
-        <v>93996</v>
+        <v>94005</v>
       </c>
       <c r="H181">
-        <v>19070</v>
+        <v>19063</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68315</v>
+        <v>68373</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86844</v>
+        <v>86594</v>
       </c>
       <c r="G182">
-        <v>125055</v>
+        <v>124695</v>
       </c>
       <c r="H182">
-        <v>18529</v>
+        <v>18221</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10455</v>
+        <v>10205</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37455</v>
+        <v>37205</v>
       </c>
       <c r="G183">
-        <v>53935</v>
+        <v>53575</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60982</v>
+        <v>61020</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80369</v>
+        <v>80384</v>
       </c>
       <c r="G184">
-        <v>115731</v>
+        <v>115753</v>
       </c>
       <c r="H184">
-        <v>19387</v>
+        <v>19364</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>80514</v>
+        <v>80565</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>104844</v>
+        <v>104864</v>
       </c>
       <c r="G186">
-        <v>150975</v>
+        <v>151004</v>
       </c>
       <c r="H186">
-        <v>24330</v>
+        <v>24299</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7269</v>
+        <v>7273</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>27669</v>
+        <v>27665</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11831</v>
+        <v>11839</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38831</v>
+        <v>38839</v>
       </c>
       <c r="G196">
-        <v>55917</v>
+        <v>55928</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51984</v>
+        <v>52033</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17426</v>
+        <v>17377</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75471</v>
+        <v>75518</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>90518</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>130346</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>57092</v>
+        <v>57127</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>72127</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>103863</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36951</v>
+        <v>36974</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63951</v>
+        <v>63974</v>
       </c>
       <c r="G202">
-        <v>92089</v>
+        <v>92123</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27665</v>
+        <v>27683</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54665</v>
+        <v>54683</v>
       </c>
       <c r="G204">
-        <v>78718</v>
+        <v>78744</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>102448</v>
+        <v>102512</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>117448</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>169125</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63656</v>
+        <v>63471</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>81996</v>
+        <v>81922</v>
       </c>
       <c r="G207">
-        <v>118074</v>
+        <v>117968</v>
       </c>
       <c r="H207">
-        <v>18340</v>
+        <v>18451</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>145675</v>
+        <v>145766</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>180675</v>
+        <v>180766</v>
       </c>
       <c r="G208">
-        <v>260172</v>
+        <v>260303</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145579</v>
+        <v>145670</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>160670</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>231365</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>188902</v>
+        <v>189020</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>204020</v>
       </c>
       <c r="G210">
-        <v>0</v>
+        <v>293789</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>186693</v>
+        <v>187594</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>202594</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>291735</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>289765</v>
+        <v>289946</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>304946</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>439122</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34678</v>
+        <v>34555</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>57806</v>
+        <v>60503</v>
       </c>
       <c r="G214">
-        <v>83241</v>
+        <v>87124</v>
       </c>
       <c r="H214">
-        <v>23128</v>
+        <v>25948</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>34806</v>
+        <v>37503</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>49806</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>71721</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>60646</v>
+        <v>60700</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>75646</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>108930</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67802</v>
+        <v>67845</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>82802</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>119235</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12728</v>
+        <v>12736</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>44654</v>
+        <v>39736</v>
       </c>
       <c r="G220">
-        <v>64302</v>
+        <v>57220</v>
       </c>
       <c r="H220">
-        <v>31926</v>
+        <v>27000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,19 +10094,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>9654</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>36654</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>52782</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>24111</v>
+        <v>23838</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>59111</v>
+        <v>50838</v>
       </c>
       <c r="G222">
-        <v>85120</v>
+        <v>73207</v>
       </c>
       <c r="H222">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>53826</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>111059</v>
       </c>
       <c r="F223">
-        <v>70843</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>102014</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>17017</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>17435</v>
+        <v>17414</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46559</v>
+        <v>46374</v>
       </c>
       <c r="G224">
-        <v>67045</v>
+        <v>66779</v>
       </c>
       <c r="H224">
-        <v>29124</v>
+        <v>28960</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11559</v>
+        <v>11374</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38559</v>
+        <v>38374</v>
       </c>
       <c r="G225">
-        <v>55525</v>
+        <v>55259</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26657</v>
+        <v>26673</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61657</v>
+        <v>61673</v>
       </c>
       <c r="G226">
-        <v>88786</v>
+        <v>88809</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,19 +10362,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>95660</v>
+        <v>38592</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>110660</v>
+        <v>65592</v>
       </c>
       <c r="G227">
-        <v>159350</v>
+        <v>94452</v>
       </c>
       <c r="H227">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35926</v>
+        <v>35933</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>62926</v>
+        <v>62933</v>
       </c>
       <c r="G228">
-        <v>90613</v>
+        <v>90624</v>
       </c>
       <c r="H228">
         <v>27000</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15866</v>
+        <v>15876</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42903</v>
+        <v>42905</v>
       </c>
       <c r="G230">
-        <v>61780</v>
+        <v>61783</v>
       </c>
       <c r="H230">
-        <v>27037</v>
+        <v>27029</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9990</v>
+        <v>9996</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>33093</v>
+        <v>33095</v>
       </c>
       <c r="G231">
-        <v>47654</v>
+        <v>47657</v>
       </c>
       <c r="H231">
-        <v>23103</v>
+        <v>23099</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>86438</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>112768</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>162386</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>26330</v>
+        <v>0</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,16 +10842,16 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26769</v>
+        <v>26785</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>53769</v>
+        <v>53785</v>
       </c>
       <c r="G238">
-        <v>77427</v>
+        <v>77450</v>
       </c>
       <c r="H238">
         <v>27000</v>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47294</v>
+        <v>47323</v>
       </c>
       <c r="E240">
         <v>103654</v>
       </c>
       <c r="F240">
-        <v>71562</v>
+        <v>71574</v>
       </c>
       <c r="G240">
-        <v>103049</v>
+        <v>103067</v>
       </c>
       <c r="H240">
-        <v>24268</v>
+        <v>24251</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64600</v>
+        <v>64657</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>79657</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>114706</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>76704</v>
+        <v>76239</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>91239</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>131384</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17163</v>
+        <v>17029</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42538</v>
+        <v>42542</v>
       </c>
       <c r="G248">
-        <v>61255</v>
+        <v>61260</v>
       </c>
       <c r="H248">
-        <v>25375</v>
+        <v>25513</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11799</v>
+        <v>11807</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34538</v>
+        <v>34542</v>
       </c>
       <c r="G249">
-        <v>49735</v>
+        <v>49740</v>
       </c>
       <c r="H249">
-        <v>22739</v>
+        <v>22735</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>31444</v>
+        <v>0</v>
       </c>
       <c r="E250">
         <v>74033</v>
       </c>
       <c r="F250">
-        <v>51893</v>
+        <v>0</v>
       </c>
       <c r="G250">
-        <v>74726</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>20449</v>
+        <v>0</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,19 +11511,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>16725</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>43725</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>62964</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>23455</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>50455</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>72655</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9638</v>
+        <v>9644</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>50311</v>
       </c>
       <c r="H256">
-        <v>25300</v>
+        <v>25294</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12376</v>
+        <v>12383</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39376</v>
+        <v>39383</v>
       </c>
       <c r="G258">
-        <v>56701</v>
+        <v>56712</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8918</v>
+        <v>8923</v>
       </c>
       <c r="E260">
         <v>53688</v>
       </c>
       <c r="F260">
-        <v>39357</v>
+        <v>39385</v>
       </c>
       <c r="G260">
-        <v>56674</v>
+        <v>56714</v>
       </c>
       <c r="H260">
-        <v>30439</v>
+        <v>30462</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11047</v>
+        <v>11118</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>31357</v>
+        <v>31385</v>
       </c>
       <c r="G261">
-        <v>45154</v>
+        <v>45194</v>
       </c>
       <c r="H261">
-        <v>20310</v>
+        <v>20267</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12936</v>
+        <v>12944</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>35334</v>
+        <v>35337</v>
       </c>
       <c r="G262">
-        <v>50881</v>
+        <v>50885</v>
       </c>
       <c r="H262">
-        <v>22398</v>
+        <v>22393</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>19820</v>
+        <v>19464</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>46419</v>
+        <v>46276</v>
       </c>
       <c r="G264">
-        <v>66843</v>
+        <v>66637</v>
       </c>
       <c r="H264">
-        <v>26599</v>
+        <v>26812</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34582</v>
+        <v>34619</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>52323</v>
+        <v>52338</v>
       </c>
       <c r="G266">
-        <v>75345</v>
+        <v>75367</v>
       </c>
       <c r="H266">
-        <v>17741</v>
+        <v>17719</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10342</v>
+        <v>10221</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>25221</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>36318</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12264</v>
+        <v>12271</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>39264</v>
+        <v>39271</v>
       </c>
       <c r="G270">
-        <v>56540</v>
+        <v>56550</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,19 +12341,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62439</v>
+        <v>63647</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>78647</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>113252</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>69483</v>
+        <v>69511</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>84483</v>
+        <v>0</v>
       </c>
       <c r="G274">
-        <v>121656</v>
+        <v>0</v>
       </c>
       <c r="H274">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11239</v>
+        <v>11246</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>37871</v>
+        <v>34938</v>
       </c>
       <c r="G276">
-        <v>54534</v>
+        <v>50311</v>
       </c>
       <c r="H276">
-        <v>26632</v>
+        <v>23692</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>7333</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>29871</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>43014</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>22538</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20301</v>
+        <v>20313</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>46611</v>
+        <v>46616</v>
       </c>
       <c r="G278">
-        <v>67120</v>
+        <v>67127</v>
       </c>
       <c r="H278">
-        <v>26310</v>
+        <v>26303</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11815</v>
+        <v>11823</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23123</v>
+        <v>23115</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17819</v>
+        <v>17846</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>32846</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>47298</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50271</v>
+        <v>50303</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>65271</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>93990</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>59301</v>
+        <v>59338</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>74338</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>107047</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>40105</v>
+        <v>35404</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55832</v>
+        <v>55870</v>
       </c>
       <c r="G288">
-        <v>80398</v>
+        <v>80453</v>
       </c>
       <c r="H288">
-        <v>15727</v>
+        <v>20466</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23887</v>
+        <v>23982</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39374</v>
+        <v>39412</v>
       </c>
       <c r="G289">
-        <v>56699</v>
+        <v>56753</v>
       </c>
       <c r="H289">
-        <v>15487</v>
+        <v>15430</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>42042</v>
+        <v>38736</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>62218</v>
+        <v>62224</v>
       </c>
       <c r="G292">
-        <v>89594</v>
+        <v>89603</v>
       </c>
       <c r="H292">
-        <v>20176</v>
+        <v>23488</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23839</v>
+        <v>23854</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39354</v>
+        <v>39360</v>
       </c>
       <c r="G293">
-        <v>56670</v>
+        <v>56678</v>
       </c>
       <c r="H293">
-        <v>15515</v>
+        <v>15506</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>63063</v>
+        <v>70632</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>85632</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>123310</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>92874</v>
+        <v>75118</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>90118</v>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>129770</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>70972</v>
+        <v>71017</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>88961</v>
+        <v>88822</v>
       </c>
       <c r="G300">
-        <v>128104</v>
+        <v>127904</v>
       </c>
       <c r="H300">
-        <v>17989</v>
+        <v>17805</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>34998</v>
+        <v>34651</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>56092</v>
+        <v>55953</v>
       </c>
       <c r="G301">
-        <v>80772</v>
+        <v>80572</v>
       </c>
       <c r="H301">
-        <v>21094</v>
+        <v>21302</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12056</v>
+        <v>12095</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>39056</v>
+        <v>39095</v>
       </c>
       <c r="G303">
-        <v>56241</v>
+        <v>56297</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13748,7 +13748,7 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>175181</v>
+        <v>0</v>
       </c>
       <c r="E304">
         <v>166598</v>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>52545</v>
+        <v>52594</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>80092</v>
+        <v>80104</v>
       </c>
       <c r="G306">
-        <v>115332</v>
+        <v>115350</v>
       </c>
       <c r="H306">
-        <v>27547</v>
+        <v>27510</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50752</v>
+        <v>50783</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69614</v>
+        <v>69626</v>
       </c>
       <c r="G307">
-        <v>100244</v>
+        <v>100261</v>
       </c>
       <c r="H307">
-        <v>18862</v>
+        <v>18843</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69660</v>
+        <v>69719</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>27519</v>
+        <v>27460</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>106242</v>
+        <v>106309</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>121309</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>174685</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24591</v>
+        <v>24607</v>
       </c>
       <c r="E310">
         <v>55520</v>
       </c>
       <c r="F310">
-        <v>40820</v>
+        <v>40827</v>
       </c>
       <c r="G310">
-        <v>58781</v>
+        <v>58791</v>
       </c>
       <c r="H310">
-        <v>16229</v>
+        <v>16220</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>68843</v>
+        <v>68886</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>83843</v>
+        <v>0</v>
       </c>
       <c r="G312">
-        <v>120734</v>
+        <v>0</v>
       </c>
       <c r="H312">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20957</v>
+        <v>20970</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>35970</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>51797</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>34101</v>
+        <v>34555</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>63076</v>
+        <v>49737</v>
       </c>
       <c r="G316">
-        <v>90829</v>
+        <v>71621</v>
       </c>
       <c r="H316">
-        <v>28975</v>
+        <v>15182</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39849</v>
+        <v>26737</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>41737</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>60101</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,19 +14366,19 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>19388</v>
+        <v>12143</v>
       </c>
       <c r="E318">
         <v>44413</v>
       </c>
       <c r="F318">
-        <v>0</v>
+        <v>33310</v>
       </c>
       <c r="G318">
-        <v>0</v>
+        <v>47966</v>
       </c>
       <c r="H318">
-        <v>0</v>
+        <v>21167</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29651</v>
+        <v>29669</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>0</v>
+        <v>44669</v>
       </c>
       <c r="G319">
-        <v>0</v>
+        <v>64323</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>21005</v>
+        <v>22252</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>48005</v>
+        <v>49252</v>
       </c>
       <c r="G330">
-        <v>69127</v>
+        <v>70923</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43963</v>
+        <v>44007</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>70963</v>
+        <v>71007</v>
       </c>
       <c r="G332">
-        <v>102187</v>
+        <v>102250</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>33333</v>
+        <v>32905</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>60333</v>
+        <v>59905</v>
       </c>
       <c r="G334">
-        <v>86880</v>
+        <v>86263</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>190215</v>
+        <v>190430</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>205430</v>
       </c>
       <c r="G336">
-        <v>0</v>
+        <v>295819</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>63544</v>
+        <v>63295</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89725</v>
+        <v>89625</v>
       </c>
       <c r="G338">
-        <v>129204</v>
+        <v>129060</v>
       </c>
       <c r="H338">
-        <v>26181</v>
+        <v>26330</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>145093</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>160093</v>
       </c>
       <c r="G343">
-        <v>0</v>
+        <v>230534</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72186</v>
+        <v>72013</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>87186</v>
+        <v>87108</v>
       </c>
       <c r="G2">
-        <v>125548</v>
+        <v>125436</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>15095</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,16 +548,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>48092</v>
+        <v>48014</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>63092</v>
+        <v>63014</v>
       </c>
       <c r="G3">
-        <v>90852</v>
+        <v>90740</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -592,16 +592,16 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95335</v>
+        <v>95276</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>110335</v>
+        <v>110276</v>
       </c>
       <c r="G4">
-        <v>158882</v>
+        <v>158797</v>
       </c>
       <c r="H4">
         <v>15000</v>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>71722</v>
+        <v>71597</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>86722</v>
+        <v>86597</v>
       </c>
       <c r="G5">
-        <v>124880</v>
+        <v>124700</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7209</v>
+        <v>7205</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30536</v>
+        <v>30535</v>
       </c>
       <c r="G7">
-        <v>43972</v>
+        <v>43970</v>
       </c>
       <c r="H7">
-        <v>23327</v>
+        <v>23330</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39762</v>
+        <v>39769</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55220</v>
+        <v>55223</v>
       </c>
       <c r="G8">
-        <v>79517</v>
+        <v>79521</v>
       </c>
       <c r="H8">
-        <v>15458</v>
+        <v>15454</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>58185</v>
+        <v>56659</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>79250</v>
+        <v>78640</v>
       </c>
       <c r="G10">
-        <v>114120</v>
+        <v>113242</v>
       </c>
       <c r="H10">
-        <v>21065</v>
+        <v>21981</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>85226</v>
+        <v>85077</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>101052</v>
+        <v>101860</v>
       </c>
       <c r="G12">
-        <v>145515</v>
+        <v>146678</v>
       </c>
       <c r="H12">
-        <v>15826</v>
+        <v>16783</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>12704</v>
+        <v>13512</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>39704</v>
+        <v>40512</v>
       </c>
       <c r="G13">
-        <v>57174</v>
+        <v>58337</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27378</v>
+        <v>27329</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45824</v>
+        <v>45804</v>
       </c>
       <c r="G15">
-        <v>65987</v>
+        <v>65958</v>
       </c>
       <c r="H15">
-        <v>18446</v>
+        <v>18475</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54804</v>
+        <v>35862</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>60770</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>87509</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>24908</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>96460</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>111460</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>160502</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>22636</v>
+        <v>22046</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>40317</v>
+        <v>40081</v>
       </c>
       <c r="G27">
-        <v>58056</v>
+        <v>57717</v>
       </c>
       <c r="H27">
-        <v>17681</v>
+        <v>18035</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74093</v>
+        <v>75583</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96425</v>
+        <v>96354</v>
       </c>
       <c r="G28">
-        <v>138852</v>
+        <v>138750</v>
       </c>
       <c r="H28">
-        <v>22332</v>
+        <v>20771</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>37983</v>
+        <v>37912</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>64983</v>
+        <v>64912</v>
       </c>
       <c r="G29">
-        <v>93576</v>
+        <v>93473</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>123194</v>
+        <v>122973</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>138833</v>
+        <v>138489</v>
       </c>
       <c r="G30">
-        <v>199920</v>
+        <v>199424</v>
       </c>
       <c r="H30">
-        <v>15639</v>
+        <v>15516</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,19 +1776,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>98203</v>
+        <v>98045</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>117411</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>169072</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>19366</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>62270</v>
+        <v>60982</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80960</v>
+        <v>80938</v>
       </c>
       <c r="G32">
-        <v>116582</v>
+        <v>116551</v>
       </c>
       <c r="H32">
-        <v>18690</v>
+        <v>19956</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36429</v>
+        <v>36407</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63429</v>
+        <v>63407</v>
       </c>
       <c r="G33">
-        <v>91338</v>
+        <v>91306</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48861</v>
+        <v>48991</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75861</v>
+        <v>75991</v>
       </c>
       <c r="G36">
-        <v>109240</v>
+        <v>109427</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35677</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>62677</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>90255</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>68021</v>
+        <v>67594</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>95021</v>
+        <v>94594</v>
       </c>
       <c r="G38">
-        <v>136830</v>
+        <v>136215</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>67540</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>94540</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>136138</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>86989</v>
+        <v>87751</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>113989</v>
+        <v>114751</v>
       </c>
       <c r="G40">
-        <v>164144</v>
+        <v>165241</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31848</v>
+        <v>31812</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58848</v>
+        <v>58812</v>
       </c>
       <c r="G43">
-        <v>84741</v>
+        <v>84689</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>80164</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>107164</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>154316</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>20329</v>
+        <v>20013</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>47329</v>
+        <v>47013</v>
       </c>
       <c r="G47">
-        <v>68154</v>
+        <v>67699</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>40803</v>
+        <v>40777</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>66292</v>
+        <v>66207</v>
       </c>
       <c r="G50">
-        <v>95460</v>
+        <v>95338</v>
       </c>
       <c r="H50">
-        <v>25489</v>
+        <v>25430</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>42645</v>
+        <v>42571</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>57571</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>82902</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>59899</v>
+        <v>54418</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>69418</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>99962</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>68069</v>
+        <v>68251</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>83251</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>119881</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>49566</v>
+        <v>49471</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>82782</v>
+        <v>82706</v>
       </c>
       <c r="G54">
-        <v>119206</v>
+        <v>119097</v>
       </c>
       <c r="H54">
-        <v>33216</v>
+        <v>33235</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44984</v>
+        <v>44908</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71984</v>
+        <v>71908</v>
       </c>
       <c r="G55">
-        <v>103657</v>
+        <v>103548</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>54212</v>
+        <v>54354</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>81212</v>
+        <v>81354</v>
       </c>
       <c r="G56">
-        <v>116945</v>
+        <v>117150</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66403</v>
+        <v>66281</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90314</v>
+        <v>90265</v>
       </c>
       <c r="G57">
-        <v>130052</v>
+        <v>129982</v>
       </c>
       <c r="H57">
-        <v>23911</v>
+        <v>23984</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>15668</v>
+        <v>17643</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38672</v>
+        <v>38670</v>
       </c>
       <c r="G58">
-        <v>55688</v>
+        <v>55685</v>
       </c>
       <c r="H58">
-        <v>23004</v>
+        <v>21027</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6264</v>
+        <v>6260</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22939</v>
+        <v>22937</v>
       </c>
       <c r="G59">
-        <v>33032</v>
+        <v>33029</v>
       </c>
       <c r="H59">
-        <v>16675</v>
+        <v>16677</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24270</v>
+        <v>24255</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>39255</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>56527</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25648</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>40648</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58533</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14322</v>
+        <v>14297</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41322</v>
+        <v>41297</v>
       </c>
       <c r="G63">
-        <v>59504</v>
+        <v>59468</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>34267</v>
+        <v>34197</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>61267</v>
+        <v>61197</v>
       </c>
       <c r="G65">
-        <v>88224</v>
+        <v>88124</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>26033</v>
+        <v>26000</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60808</v>
+        <v>60779</v>
       </c>
       <c r="G66">
-        <v>87564</v>
+        <v>87522</v>
       </c>
       <c r="H66">
-        <v>34775</v>
+        <v>34779</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20762</v>
+        <v>20733</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47762</v>
+        <v>47733</v>
       </c>
       <c r="G67">
-        <v>68777</v>
+        <v>68736</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48332</v>
+        <v>48286</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75309</v>
+        <v>75286</v>
       </c>
       <c r="G68">
-        <v>108445</v>
+        <v>108412</v>
       </c>
       <c r="H68">
-        <v>26977</v>
+        <v>27000</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,16 +3495,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>111243</v>
+        <v>111141</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>126243</v>
+        <v>126141</v>
       </c>
       <c r="G70">
-        <v>181790</v>
+        <v>181643</v>
       </c>
       <c r="H70">
         <v>15000</v>
@@ -3626,19 +3626,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6857</v>
+        <v>6852</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>21852</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>31467</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88623</v>
+        <v>88455</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>121046</v>
+        <v>121006</v>
       </c>
       <c r="G76">
-        <v>174306</v>
+        <v>174249</v>
       </c>
       <c r="H76">
-        <v>32423</v>
+        <v>32551</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>57736</v>
+        <v>57636</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>79628</v>
+        <v>79588</v>
       </c>
       <c r="G77">
-        <v>114664</v>
+        <v>114607</v>
       </c>
       <c r="H77">
-        <v>21892</v>
+        <v>21952</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>24703</v>
+        <v>21694</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>51703</v>
+        <v>48694</v>
       </c>
       <c r="G81">
-        <v>74452</v>
+        <v>70119</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,16 +4060,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87645</v>
+        <v>87495</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>102645</v>
+        <v>102495</v>
       </c>
       <c r="G83">
-        <v>147809</v>
+        <v>147593</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>46490</v>
+        <v>46237</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>67637</v>
+        <v>67550</v>
       </c>
       <c r="G84">
-        <v>97397</v>
+        <v>97272</v>
       </c>
       <c r="H84">
-        <v>21147</v>
+        <v>21313</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>43815</v>
+        <v>43739</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>58739</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>84584</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8250</v>
+        <v>8902</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38584</v>
+        <v>38583</v>
       </c>
       <c r="G90">
-        <v>55561</v>
+        <v>55560</v>
       </c>
       <c r="H90">
-        <v>30334</v>
+        <v>29681</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3717</v>
+        <v>3714</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30584</v>
+        <v>30583</v>
       </c>
       <c r="G91">
-        <v>44041</v>
+        <v>44040</v>
       </c>
       <c r="H91">
-        <v>26867</v>
+        <v>26869</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,16 +4499,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9548</v>
+        <v>8645</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>24548</v>
+        <v>23645</v>
       </c>
       <c r="G93">
-        <v>35349</v>
+        <v>34049</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>64304</v>
+        <v>64264</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>79304</v>
+        <v>79282</v>
       </c>
       <c r="G96">
-        <v>114198</v>
+        <v>114166</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>15018</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34763</v>
+        <v>34710</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52389</v>
+        <v>52367</v>
       </c>
       <c r="G97">
-        <v>75440</v>
+        <v>75408</v>
       </c>
       <c r="H97">
-        <v>17626</v>
+        <v>17657</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79716</v>
+        <v>79570</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>94716</v>
+        <v>94686</v>
       </c>
       <c r="G98">
-        <v>136391</v>
+        <v>136348</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>15116</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>44151</v>
+        <v>44076</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>61198</v>
+        <v>61168</v>
       </c>
       <c r="G99">
-        <v>88125</v>
+        <v>88082</v>
       </c>
       <c r="H99">
-        <v>17047</v>
+        <v>17092</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61341</v>
+        <v>61911</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>79097</v>
+        <v>79325</v>
       </c>
       <c r="G100">
-        <v>113900</v>
+        <v>114228</v>
       </c>
       <c r="H100">
-        <v>17756</v>
+        <v>17414</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71962</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>86962</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>125225</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6216</v>
+        <v>6196</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33216</v>
+        <v>33196</v>
       </c>
       <c r="G109">
-        <v>47831</v>
+        <v>47802</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15171</v>
+        <v>15145</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42171</v>
+        <v>42145</v>
       </c>
       <c r="G111">
-        <v>60726</v>
+        <v>60689</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51568</v>
+        <v>51472</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>77160</v>
+        <v>77122</v>
       </c>
       <c r="G113">
-        <v>111110</v>
+        <v>111056</v>
       </c>
       <c r="H113">
-        <v>25592</v>
+        <v>25650</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>94502</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>115994</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>167031</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>21492</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,16 +5584,16 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80773</v>
+        <v>80626</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>95773</v>
+        <v>95626</v>
       </c>
       <c r="G118">
-        <v>137913</v>
+        <v>137701</v>
       </c>
       <c r="H118">
         <v>15000</v>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50463</v>
+        <v>50383</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>65383</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>94152</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,16 +5716,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>102752</v>
+        <v>86198</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>117752</v>
+        <v>101198</v>
       </c>
       <c r="G121">
-        <v>169563</v>
+        <v>145725</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46458</v>
+        <v>46413</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>61458</v>
+        <v>61804</v>
       </c>
       <c r="G124">
-        <v>88500</v>
+        <v>88998</v>
       </c>
       <c r="H124">
-        <v>15000</v>
+        <v>15391</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35356</v>
+        <v>35702</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>50356</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72513</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,16 +5935,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>64112</v>
+        <v>64056</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>79112</v>
+        <v>79056</v>
       </c>
       <c r="G126">
-        <v>113921</v>
+        <v>113841</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>32473</v>
+        <v>32452</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>55082</v>
+        <v>55074</v>
       </c>
       <c r="G129">
-        <v>79318</v>
+        <v>79307</v>
       </c>
       <c r="H129">
-        <v>22609</v>
+        <v>22622</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,7 +6110,7 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12800</v>
+        <v>12792</v>
       </c>
       <c r="E130">
         <v>44413</v>
@@ -6122,7 +6122,7 @@
         <v>47966</v>
       </c>
       <c r="H130">
-        <v>20510</v>
+        <v>20518</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5559</v>
+        <v>5347</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25544</v>
+        <v>25460</v>
       </c>
       <c r="G131">
-        <v>36783</v>
+        <v>36662</v>
       </c>
       <c r="H131">
-        <v>19985</v>
+        <v>20113</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27859</v>
+        <v>27841</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43794</v>
+        <v>43787</v>
       </c>
       <c r="G132">
-        <v>63063</v>
+        <v>63053</v>
       </c>
       <c r="H132">
-        <v>15935</v>
+        <v>15946</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17430</v>
+        <v>17403</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36640</v>
+        <v>36629</v>
       </c>
       <c r="G135">
-        <v>52762</v>
+        <v>52746</v>
       </c>
       <c r="H135">
-        <v>19210</v>
+        <v>19226</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28243</v>
+        <v>28194</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46784</v>
+        <v>46765</v>
       </c>
       <c r="G137">
-        <v>67369</v>
+        <v>67342</v>
       </c>
       <c r="H137">
-        <v>18541</v>
+        <v>18571</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27586</v>
+        <v>27409</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54153</v>
+        <v>54082</v>
       </c>
       <c r="G139">
-        <v>77980</v>
+        <v>77878</v>
       </c>
       <c r="H139">
-        <v>26567</v>
+        <v>26673</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,16 +6591,16 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>58553</v>
+        <v>56307</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>73553</v>
+        <v>71307</v>
       </c>
       <c r="G141">
-        <v>105916</v>
+        <v>102682</v>
       </c>
       <c r="H141">
         <v>15000</v>
@@ -6677,16 +6677,16 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>78114</v>
+        <v>77985</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>93114</v>
+        <v>92985</v>
       </c>
       <c r="G143">
-        <v>134084</v>
+        <v>133898</v>
       </c>
       <c r="H143">
         <v>15000</v>
@@ -6763,16 +6763,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87742</v>
+        <v>87591</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>102742</v>
+        <v>102591</v>
       </c>
       <c r="G145">
-        <v>147948</v>
+        <v>147731</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6849,16 +6849,16 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>88879</v>
+        <v>86630</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>103879</v>
+        <v>101630</v>
       </c>
       <c r="G147">
-        <v>149586</v>
+        <v>146347</v>
       </c>
       <c r="H147">
         <v>15000</v>
@@ -6935,16 +6935,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>127343</v>
+        <v>127119</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>142343</v>
+        <v>142119</v>
       </c>
       <c r="G149">
-        <v>204974</v>
+        <v>204651</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38560</v>
+        <v>38488</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>63070</v>
+        <v>63041</v>
       </c>
       <c r="G150">
-        <v>90821</v>
+        <v>90779</v>
       </c>
       <c r="H150">
-        <v>24510</v>
+        <v>24553</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>23774</v>
+        <v>22942</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>58774</v>
+        <v>57942</v>
       </c>
       <c r="G152">
-        <v>84635</v>
+        <v>83436</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29861</v>
+        <v>29811</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>54037</v>
+        <v>54017</v>
       </c>
       <c r="G153">
-        <v>77813</v>
+        <v>77784</v>
       </c>
       <c r="H153">
-        <v>24176</v>
+        <v>24206</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>49037</v>
+        <v>48959</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20373</v>
+        <v>20451</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>76463</v>
+        <v>76192</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>91463</v>
+        <v>91192</v>
       </c>
       <c r="G155">
-        <v>131707</v>
+        <v>131316</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7244,16 +7244,16 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65906</v>
+        <v>65785</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80906</v>
+        <v>80785</v>
       </c>
       <c r="G156">
-        <v>116505</v>
+        <v>116330</v>
       </c>
       <c r="H156">
         <v>15000</v>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>39233</v>
+        <v>39208</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65924</v>
+        <v>65849</v>
       </c>
       <c r="G158">
-        <v>94931</v>
+        <v>94823</v>
       </c>
       <c r="H158">
-        <v>26691</v>
+        <v>26641</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,16 +7378,16 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42325</v>
+        <v>42250</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>57325</v>
+        <v>57250</v>
       </c>
       <c r="G159">
-        <v>82548</v>
+        <v>82440</v>
       </c>
       <c r="H159">
         <v>15000</v>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20233</v>
+        <v>20189</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>35728</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>51448</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>15539</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,16 +7549,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56487</v>
+        <v>56403</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>71487</v>
+        <v>71403</v>
       </c>
       <c r="G163">
-        <v>102941</v>
+        <v>102820</v>
       </c>
       <c r="H163">
         <v>15000</v>
@@ -7635,16 +7635,16 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>81253</v>
+        <v>81107</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>96253</v>
+        <v>96107</v>
       </c>
       <c r="G165">
-        <v>138604</v>
+        <v>138394</v>
       </c>
       <c r="H165">
         <v>15000</v>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54452</v>
+        <v>69756</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>69452</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>100011</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,16 +7725,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34219</v>
+        <v>34165</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>49219</v>
+        <v>49165</v>
       </c>
       <c r="G167">
-        <v>70875</v>
+        <v>70798</v>
       </c>
       <c r="H167">
         <v>15000</v>
@@ -7769,16 +7769,16 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>67925</v>
+        <v>67802</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>82925</v>
+        <v>82802</v>
       </c>
       <c r="G168">
-        <v>119412</v>
+        <v>119235</v>
       </c>
       <c r="H168">
         <v>15000</v>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>16757</v>
+        <v>16346</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>31346</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>45138</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31720</v>
+        <v>31652</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51893</v>
+        <v>51866</v>
       </c>
       <c r="G173">
-        <v>74726</v>
+        <v>74687</v>
       </c>
       <c r="H173">
-        <v>20173</v>
+        <v>20214</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7577</v>
+        <v>7573</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37794</v>
+        <v>37786</v>
       </c>
       <c r="G174">
-        <v>54423</v>
+        <v>54412</v>
       </c>
       <c r="H174">
-        <v>30217</v>
+        <v>30213</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5335</v>
+        <v>5315</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29794</v>
+        <v>29786</v>
       </c>
       <c r="G175">
-        <v>42903</v>
+        <v>42892</v>
       </c>
       <c r="H175">
-        <v>24459</v>
+        <v>24471</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10397</v>
+        <v>10278</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>43122</v>
+        <v>42925</v>
       </c>
       <c r="G176">
-        <v>62096</v>
+        <v>61812</v>
       </c>
       <c r="H176">
-        <v>32725</v>
+        <v>32647</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>8122</v>
+        <v>7925</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>35122</v>
+        <v>34925</v>
       </c>
       <c r="G177">
-        <v>50576</v>
+        <v>50292</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8212,7 +8212,7 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>49262</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>69424</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>22028</v>
+        <v>21998</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41887</v>
+        <v>41875</v>
       </c>
       <c r="G179">
-        <v>60317</v>
+        <v>60300</v>
       </c>
       <c r="H179">
-        <v>19859</v>
+        <v>19877</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46218</v>
+        <v>46141</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65281</v>
+        <v>65250</v>
       </c>
       <c r="G181">
-        <v>94005</v>
+        <v>93960</v>
       </c>
       <c r="H181">
-        <v>19063</v>
+        <v>19109</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68373</v>
+        <v>68315</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86594</v>
+        <v>86651</v>
       </c>
       <c r="G182">
-        <v>124695</v>
+        <v>124777</v>
       </c>
       <c r="H182">
-        <v>18221</v>
+        <v>18336</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10205</v>
+        <v>10262</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37205</v>
+        <v>37262</v>
       </c>
       <c r="G183">
-        <v>53575</v>
+        <v>53657</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>61020</v>
+        <v>71549</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80384</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>115753</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>19364</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>76352</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>91352</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>131547</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>80565</v>
+        <v>90008</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>104864</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>151004</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>24299</v>
+        <v>0</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>142601</v>
       </c>
       <c r="E190">
         <v>157342</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>157601</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>226945</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7273</v>
+        <v>6724</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>27665</v>
+        <v>28214</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11839</v>
+        <v>11831</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38839</v>
+        <v>38831</v>
       </c>
       <c r="G196">
-        <v>55928</v>
+        <v>55917</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>52033</v>
+        <v>51984</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17377</v>
+        <v>17426</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,16 +9128,16 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75518</v>
+        <v>75375</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>90518</v>
+        <v>90375</v>
       </c>
       <c r="G199">
-        <v>130346</v>
+        <v>130140</v>
       </c>
       <c r="H199">
         <v>15000</v>
@@ -9172,16 +9172,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>57127</v>
+        <v>57028</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>72127</v>
+        <v>72028</v>
       </c>
       <c r="G200">
-        <v>103863</v>
+        <v>103720</v>
       </c>
       <c r="H200">
         <v>15000</v>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36974</v>
+        <v>36935</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63974</v>
+        <v>63935</v>
       </c>
       <c r="G202">
-        <v>92123</v>
+        <v>92066</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27683</v>
+        <v>27649</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54683</v>
+        <v>54649</v>
       </c>
       <c r="G204">
-        <v>78744</v>
+        <v>78695</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>102512</v>
+        <v>102448</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>117448</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>169125</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63471</v>
+        <v>63191</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>81922</v>
+        <v>81810</v>
       </c>
       <c r="G207">
-        <v>117968</v>
+        <v>117806</v>
       </c>
       <c r="H207">
-        <v>18451</v>
+        <v>18619</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>145766</v>
+        <v>145675</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>180766</v>
+        <v>180675</v>
       </c>
       <c r="G208">
-        <v>260303</v>
+        <v>260172</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,16 +9567,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145670</v>
+        <v>145339</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>160670</v>
+        <v>160339</v>
       </c>
       <c r="G209">
-        <v>231365</v>
+        <v>230888</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9611,16 +9611,16 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>189020</v>
+        <v>188902</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>204020</v>
+        <v>203902</v>
       </c>
       <c r="G210">
-        <v>293789</v>
+        <v>293619</v>
       </c>
       <c r="H210">
         <v>15000</v>
@@ -9654,16 +9654,16 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>187594</v>
+        <v>187253</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>202594</v>
+        <v>202253</v>
       </c>
       <c r="G211">
-        <v>291735</v>
+        <v>291244</v>
       </c>
       <c r="H211">
         <v>15000</v>
@@ -9698,16 +9698,16 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>289946</v>
+        <v>289765</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>304946</v>
+        <v>304765</v>
       </c>
       <c r="G212">
-        <v>439122</v>
+        <v>438862</v>
       </c>
       <c r="H212">
         <v>15000</v>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>225437</v>
       </c>
       <c r="E213">
         <v>370241</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>240569</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>346419</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>15132</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34555</v>
+        <v>35014</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>60503</v>
+        <v>60255</v>
       </c>
       <c r="G214">
-        <v>87124</v>
+        <v>86767</v>
       </c>
       <c r="H214">
-        <v>25948</v>
+        <v>25241</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>37503</v>
+        <v>37255</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>52255</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>75247</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,7 +9873,7 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>60700</v>
+        <v>0</v>
       </c>
       <c r="E216">
         <v>53688</v>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67845</v>
+        <v>67786</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>82786</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>119212</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,16 +10048,16 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12736</v>
+        <v>12728</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>39736</v>
+        <v>39728</v>
       </c>
       <c r="G220">
-        <v>57220</v>
+        <v>57208</v>
       </c>
       <c r="H220">
         <v>27000</v>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>23838</v>
+        <v>23663</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>50838</v>
+        <v>58663</v>
       </c>
       <c r="G222">
-        <v>73207</v>
+        <v>84475</v>
       </c>
       <c r="H222">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>53826</v>
       </c>
       <c r="E223">
         <v>111059</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>70843</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>102014</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>17017</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>17414</v>
+        <v>17387</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46374</v>
+        <v>46143</v>
       </c>
       <c r="G224">
-        <v>66779</v>
+        <v>66446</v>
       </c>
       <c r="H224">
-        <v>28960</v>
+        <v>28756</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11374</v>
+        <v>11143</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38374</v>
+        <v>38143</v>
       </c>
       <c r="G225">
-        <v>55259</v>
+        <v>54926</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26673</v>
+        <v>26641</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61673</v>
+        <v>61641</v>
       </c>
       <c r="G226">
-        <v>88809</v>
+        <v>88763</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,16 +10362,16 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38592</v>
+        <v>38568</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>65592</v>
+        <v>65568</v>
       </c>
       <c r="G227">
-        <v>94452</v>
+        <v>94418</v>
       </c>
       <c r="H227">
         <v>27000</v>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35933</v>
+        <v>35894</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>62933</v>
+        <v>62894</v>
       </c>
       <c r="G228">
-        <v>90624</v>
+        <v>90567</v>
       </c>
       <c r="H228">
         <v>27000</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15876</v>
+        <v>15770</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42905</v>
+        <v>42954</v>
       </c>
       <c r="G230">
-        <v>61783</v>
+        <v>61854</v>
       </c>
       <c r="H230">
-        <v>27029</v>
+        <v>27184</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9996</v>
+        <v>10118</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>33095</v>
+        <v>33144</v>
       </c>
       <c r="G231">
-        <v>47657</v>
+        <v>47727</v>
       </c>
       <c r="H231">
-        <v>23099</v>
+        <v>23026</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26785</v>
+        <v>26929</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>53785</v>
+        <v>61484</v>
       </c>
       <c r="G238">
-        <v>77450</v>
+        <v>88537</v>
       </c>
       <c r="H238">
-        <v>27000</v>
+        <v>34555</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>32036</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>53464</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>76988</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>21428</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,19 +10931,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47323</v>
+        <v>47246</v>
       </c>
       <c r="E240">
         <v>103654</v>
       </c>
       <c r="F240">
-        <v>71574</v>
+        <v>77741</v>
       </c>
       <c r="G240">
-        <v>103067</v>
+        <v>111947</v>
       </c>
       <c r="H240">
-        <v>24251</v>
+        <v>30495</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>84757</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>99757</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>143650</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,16 +11109,16 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64657</v>
+        <v>64584</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79657</v>
+        <v>79584</v>
       </c>
       <c r="G244">
-        <v>114706</v>
+        <v>114601</v>
       </c>
       <c r="H244">
         <v>15000</v>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>44780</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>0</v>
+        <v>59780</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>86083</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,16 +11199,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>76239</v>
+        <v>76192</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>91239</v>
+        <v>91192</v>
       </c>
       <c r="G246">
-        <v>131384</v>
+        <v>131316</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17029</v>
+        <v>17003</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42542</v>
+        <v>42532</v>
       </c>
       <c r="G248">
-        <v>61260</v>
+        <v>61246</v>
       </c>
       <c r="H248">
-        <v>25513</v>
+        <v>25529</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11807</v>
+        <v>11783</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34542</v>
+        <v>34532</v>
       </c>
       <c r="G249">
-        <v>49740</v>
+        <v>49726</v>
       </c>
       <c r="H249">
-        <v>22735</v>
+        <v>22749</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16725</v>
+        <v>16714</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>43725</v>
+        <v>43714</v>
       </c>
       <c r="G253">
-        <v>62964</v>
+        <v>62948</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9644</v>
+        <v>9638</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>50311</v>
       </c>
       <c r="H256">
-        <v>25294</v>
+        <v>25300</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12383</v>
+        <v>12360</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39383</v>
+        <v>39360</v>
       </c>
       <c r="G258">
-        <v>56712</v>
+        <v>56678</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8923</v>
+        <v>8918</v>
       </c>
       <c r="E260">
         <v>53688</v>
       </c>
       <c r="F260">
-        <v>39385</v>
+        <v>39376</v>
       </c>
       <c r="G260">
-        <v>56714</v>
+        <v>56701</v>
       </c>
       <c r="H260">
-        <v>30462</v>
+        <v>30458</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11118</v>
+        <v>11095</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>31385</v>
+        <v>31376</v>
       </c>
       <c r="G261">
-        <v>45194</v>
+        <v>45181</v>
       </c>
       <c r="H261">
-        <v>20267</v>
+        <v>20281</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12944</v>
+        <v>12824</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>35337</v>
+        <v>35289</v>
       </c>
       <c r="G262">
-        <v>50885</v>
+        <v>50816</v>
       </c>
       <c r="H262">
-        <v>22393</v>
+        <v>22465</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>19464</v>
+        <v>19372</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>46276</v>
+        <v>51880</v>
       </c>
       <c r="G264">
-        <v>66637</v>
+        <v>74707</v>
       </c>
       <c r="H264">
-        <v>26812</v>
+        <v>32508</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>24303</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>43880</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>63187</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>19577</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34619</v>
+        <v>34582</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>52338</v>
+        <v>52323</v>
       </c>
       <c r="G266">
-        <v>75367</v>
+        <v>75345</v>
       </c>
       <c r="H266">
-        <v>17719</v>
+        <v>17741</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,16 +12166,16 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10221</v>
+        <v>10214</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>25221</v>
+        <v>25214</v>
       </c>
       <c r="G268">
-        <v>36318</v>
+        <v>36308</v>
       </c>
       <c r="H268">
         <v>15000</v>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12271</v>
+        <v>12264</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>39271</v>
+        <v>39264</v>
       </c>
       <c r="G270">
-        <v>56550</v>
+        <v>56540</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>63647</v>
+        <v>63512</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>78647</v>
+        <v>78512</v>
       </c>
       <c r="G272">
-        <v>113252</v>
+        <v>113057</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>69511</v>
+        <v>69435</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>84435</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>121586</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11246</v>
+        <v>11239</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>34938</v>
+        <v>37871</v>
       </c>
       <c r="G276">
-        <v>50311</v>
+        <v>54534</v>
       </c>
       <c r="H276">
-        <v>23692</v>
+        <v>26632</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>7333</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>29871</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>43014</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>22538</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20313</v>
+        <v>20301</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>46616</v>
+        <v>51880</v>
       </c>
       <c r="G278">
-        <v>67127</v>
+        <v>74707</v>
       </c>
       <c r="H278">
-        <v>26303</v>
+        <v>31579</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>24303</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>43880</v>
       </c>
       <c r="G279">
-        <v>0</v>
+        <v>63187</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>19577</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11823</v>
+        <v>11799</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23115</v>
+        <v>23139</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,16 +12826,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17846</v>
+        <v>17819</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32846</v>
+        <v>32819</v>
       </c>
       <c r="G283">
-        <v>47298</v>
+        <v>47259</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50303</v>
+        <v>50191</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>65191</v>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>93875</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,16 +12998,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>59338</v>
+        <v>58997</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>74338</v>
+        <v>73997</v>
       </c>
       <c r="G287">
-        <v>107047</v>
+        <v>106556</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>35404</v>
+        <v>33765</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55870</v>
+        <v>55851</v>
       </c>
       <c r="G288">
-        <v>80453</v>
+        <v>80425</v>
       </c>
       <c r="H288">
-        <v>20466</v>
+        <v>22086</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23982</v>
+        <v>23935</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39412</v>
+        <v>39393</v>
       </c>
       <c r="G289">
-        <v>56753</v>
+        <v>56726</v>
       </c>
       <c r="H289">
-        <v>15430</v>
+        <v>15458</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>38736</v>
+        <v>44940</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>62224</v>
+        <v>62161</v>
       </c>
       <c r="G292">
-        <v>89603</v>
+        <v>89512</v>
       </c>
       <c r="H292">
-        <v>23488</v>
+        <v>17221</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23854</v>
+        <v>23695</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39360</v>
+        <v>39297</v>
       </c>
       <c r="G293">
-        <v>56678</v>
+        <v>56588</v>
       </c>
       <c r="H293">
-        <v>15506</v>
+        <v>15602</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>87479</v>
       </c>
       <c r="E294">
         <v>68480</v>
       </c>
       <c r="F294">
-        <v>0</v>
+        <v>102479</v>
       </c>
       <c r="G294">
-        <v>0</v>
+        <v>147570</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>23743</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>0</v>
+        <v>42204</v>
       </c>
       <c r="G295">
-        <v>0</v>
+        <v>60774</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>18461</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,16 +13399,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>70632</v>
+        <v>63063</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>85632</v>
+        <v>78063</v>
       </c>
       <c r="G296">
-        <v>123310</v>
+        <v>112411</v>
       </c>
       <c r="H296">
         <v>15000</v>
@@ -13486,16 +13486,16 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>75118</v>
+        <v>75071</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>90118</v>
+        <v>90071</v>
       </c>
       <c r="G298">
-        <v>129770</v>
+        <v>129702</v>
       </c>
       <c r="H298">
         <v>15000</v>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>71017</v>
+        <v>70892</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>88822</v>
+        <v>88506</v>
       </c>
       <c r="G300">
-        <v>127904</v>
+        <v>127449</v>
       </c>
       <c r="H300">
-        <v>17805</v>
+        <v>17614</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>34651</v>
+        <v>33861</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>55953</v>
+        <v>55637</v>
       </c>
       <c r="G301">
-        <v>80572</v>
+        <v>80117</v>
       </c>
       <c r="H301">
-        <v>21302</v>
+        <v>21776</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>12095</v>
+        <v>11927</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>39095</v>
+        <v>38927</v>
       </c>
       <c r="G303">
-        <v>56297</v>
+        <v>56055</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>105570</v>
       </c>
       <c r="E305">
         <v>166598</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>120570</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>173621</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>52594</v>
+        <v>52513</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>80104</v>
+        <v>80072</v>
       </c>
       <c r="G306">
-        <v>115350</v>
+        <v>115304</v>
       </c>
       <c r="H306">
-        <v>27510</v>
+        <v>27559</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50783</v>
+        <v>50704</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69626</v>
+        <v>69594</v>
       </c>
       <c r="G307">
-        <v>100261</v>
+        <v>100215</v>
       </c>
       <c r="H307">
-        <v>18843</v>
+        <v>18890</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69719</v>
+        <v>69644</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>27460</v>
+        <v>27535</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,16 +13970,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>106309</v>
+        <v>78209</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>121309</v>
+        <v>93209</v>
       </c>
       <c r="G309">
-        <v>174685</v>
+        <v>134221</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14014,19 +14014,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24607</v>
+        <v>24816</v>
       </c>
       <c r="E310">
         <v>55520</v>
       </c>
       <c r="F310">
-        <v>40827</v>
+        <v>41640</v>
       </c>
       <c r="G310">
-        <v>58791</v>
+        <v>59962</v>
       </c>
       <c r="H310">
-        <v>16220</v>
+        <v>16824</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>37624</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>52624</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>75779</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>68886</v>
+        <v>66490</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>0</v>
+        <v>90473</v>
       </c>
       <c r="G312">
-        <v>0</v>
+        <v>130281</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>23983</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>63672</v>
       </c>
       <c r="E313">
         <v>83309</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>78672</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>113288</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,16 +14232,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20970</v>
+        <v>20925</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>35970</v>
+        <v>35925</v>
       </c>
       <c r="G315">
-        <v>51797</v>
+        <v>51732</v>
       </c>
       <c r="H315">
         <v>15000</v>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>34555</v>
+        <v>32644</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>49737</v>
+        <v>63021</v>
       </c>
       <c r="G316">
-        <v>71621</v>
+        <v>90750</v>
       </c>
       <c r="H316">
-        <v>15182</v>
+        <v>30377</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26737</v>
+        <v>39801</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>41737</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>60101</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>12143</v>
+        <v>12136</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>21167</v>
+        <v>21174</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29669</v>
+        <v>29586</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44669</v>
+        <v>44586</v>
       </c>
       <c r="G319">
-        <v>64323</v>
+        <v>64204</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>38504</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>0</v>
+        <v>64714</v>
       </c>
       <c r="G321">
-        <v>0</v>
+        <v>93188</v>
       </c>
       <c r="H321">
-        <v>0</v>
+        <v>26210</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>59157</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>0</v>
+        <v>74157</v>
       </c>
       <c r="G324">
-        <v>0</v>
+        <v>106786</v>
       </c>
       <c r="H324">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>9446</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>35041</v>
       </c>
       <c r="G327">
-        <v>0</v>
+        <v>50459</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>25595</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>22252</v>
+        <v>22110</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>49252</v>
+        <v>49110</v>
       </c>
       <c r="G330">
-        <v>70923</v>
+        <v>70718</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>44007</v>
+        <v>43947</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>71007</v>
+        <v>70947</v>
       </c>
       <c r="G332">
-        <v>102250</v>
+        <v>102164</v>
       </c>
       <c r="H332">
         <v>27000</v>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32905</v>
+        <v>32084</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>59905</v>
+        <v>59084</v>
       </c>
       <c r="G334">
-        <v>86263</v>
+        <v>85081</v>
       </c>
       <c r="H334">
         <v>27000</v>
@@ -15155,16 +15155,16 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>190430</v>
+        <v>190103</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>205430</v>
+        <v>205103</v>
       </c>
       <c r="G336">
-        <v>295819</v>
+        <v>295348</v>
       </c>
       <c r="H336">
         <v>15000</v>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>144987</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>159987</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>230381</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>63295</v>
+        <v>62839</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89625</v>
+        <v>89443</v>
       </c>
       <c r="G338">
-        <v>129060</v>
+        <v>128798</v>
       </c>
       <c r="H338">
-        <v>26330</v>
+        <v>26604</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,19 +15287,19 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>42074</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>0</v>
+        <v>69074</v>
       </c>
       <c r="G339">
-        <v>0</v>
+        <v>99467</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I339" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>104513</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>0</v>
+        <v>131513</v>
       </c>
       <c r="G342">
-        <v>0</v>
+        <v>189379</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>145093</v>
+        <v>0</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>160093</v>
+        <v>0</v>
       </c>
       <c r="G343">
-        <v>230534</v>
+        <v>0</v>
       </c>
       <c r="H343">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72013</v>
+        <v>71156</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>87108</v>
+        <v>86675</v>
       </c>
       <c r="G2">
-        <v>125436</v>
+        <v>124812</v>
       </c>
       <c r="H2">
-        <v>15095</v>
+        <v>15519</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,16 +548,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>48014</v>
+        <v>47581</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>63014</v>
+        <v>62581</v>
       </c>
       <c r="G3">
-        <v>90740</v>
+        <v>90117</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -592,16 +592,16 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>95276</v>
+        <v>94445</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>110276</v>
+        <v>109445</v>
       </c>
       <c r="G4">
-        <v>158797</v>
+        <v>157601</v>
       </c>
       <c r="H4">
         <v>15000</v>
@@ -638,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>71597</v>
+        <v>66534</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>86597</v>
+        <v>81534</v>
       </c>
       <c r="G5">
-        <v>124700</v>
+        <v>117409</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7205</v>
+        <v>7141</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30535</v>
+        <v>30509</v>
       </c>
       <c r="G7">
-        <v>43970</v>
+        <v>43933</v>
       </c>
       <c r="H7">
-        <v>23330</v>
+        <v>23368</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39769</v>
+        <v>39372</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55223</v>
+        <v>55064</v>
       </c>
       <c r="G8">
-        <v>79521</v>
+        <v>79292</v>
       </c>
       <c r="H8">
-        <v>15454</v>
+        <v>15692</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56659</v>
+        <v>56412</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78640</v>
+        <v>78541</v>
       </c>
       <c r="G10">
-        <v>113242</v>
+        <v>113099</v>
       </c>
       <c r="H10">
-        <v>21981</v>
+        <v>22129</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>85077</v>
+        <v>84354</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>101860</v>
+        <v>101738</v>
       </c>
       <c r="G12">
-        <v>146678</v>
+        <v>146503</v>
       </c>
       <c r="H12">
-        <v>16783</v>
+        <v>17384</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13512</v>
+        <v>13390</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40512</v>
+        <v>40390</v>
       </c>
       <c r="G13">
-        <v>58337</v>
+        <v>58162</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>27329</v>
+        <v>26588</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45804</v>
+        <v>45508</v>
       </c>
       <c r="G15">
-        <v>65958</v>
+        <v>65532</v>
       </c>
       <c r="H15">
-        <v>18475</v>
+        <v>18920</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>35862</v>
+        <v>54244</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>60770</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>87509</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>24908</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,16 +1425,16 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96460</v>
+        <v>96039</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>111460</v>
+        <v>111039</v>
       </c>
       <c r="G23">
-        <v>160502</v>
+        <v>159896</v>
       </c>
       <c r="H23">
         <v>15000</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>22046</v>
+        <v>21121</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>40081</v>
+        <v>39711</v>
       </c>
       <c r="G27">
-        <v>57717</v>
+        <v>57184</v>
       </c>
       <c r="H27">
-        <v>18035</v>
+        <v>18590</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75583</v>
+        <v>75587</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>96354</v>
+        <v>94542</v>
       </c>
       <c r="G28">
-        <v>138750</v>
+        <v>136140</v>
       </c>
       <c r="H28">
-        <v>20771</v>
+        <v>18955</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>37912</v>
+        <v>33474</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>64912</v>
+        <v>60474</v>
       </c>
       <c r="G29">
-        <v>93473</v>
+        <v>87083</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>122973</v>
+        <v>119167</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>138489</v>
+        <v>136967</v>
       </c>
       <c r="G30">
-        <v>199424</v>
+        <v>197232</v>
       </c>
       <c r="H30">
-        <v>15516</v>
+        <v>17800</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,19 +1776,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>98045</v>
+        <v>72384</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>117411</v>
+        <v>99384</v>
       </c>
       <c r="G31">
-        <v>169072</v>
+        <v>143113</v>
       </c>
       <c r="H31">
-        <v>19366</v>
+        <v>27000</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60982</v>
+        <v>60715</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80938</v>
+        <v>80731</v>
       </c>
       <c r="G32">
-        <v>116551</v>
+        <v>116253</v>
       </c>
       <c r="H32">
-        <v>19956</v>
+        <v>20016</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36407</v>
+        <v>36200</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63407</v>
+        <v>63200</v>
       </c>
       <c r="G33">
-        <v>91306</v>
+        <v>91008</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>83318</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>98318</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>141578</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48991</v>
+        <v>48569</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75991</v>
+        <v>75569</v>
       </c>
       <c r="G36">
-        <v>109427</v>
+        <v>108819</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35498</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62498</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>89997</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>67594</v>
+        <v>66996</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>94594</v>
+        <v>93996</v>
       </c>
       <c r="G38">
-        <v>136215</v>
+        <v>135354</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>62262</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>89262</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>128537</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,16 +2177,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87751</v>
+        <v>87718</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>114751</v>
+        <v>114718</v>
       </c>
       <c r="G40">
-        <v>165241</v>
+        <v>165194</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>88531</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>113606</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>163593</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>25075</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31812</v>
+        <v>31529</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58812</v>
+        <v>58529</v>
       </c>
       <c r="G43">
-        <v>84689</v>
+        <v>84282</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>80194</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>107194</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>154359</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>20013</v>
+        <v>16673</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>47013</v>
+        <v>43673</v>
       </c>
       <c r="G47">
-        <v>67699</v>
+        <v>62889</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>40777</v>
+        <v>34733</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>66207</v>
+        <v>57748</v>
       </c>
       <c r="G50">
-        <v>95338</v>
+        <v>83157</v>
       </c>
       <c r="H50">
-        <v>25430</v>
+        <v>23015</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,16 +2654,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>42571</v>
+        <v>34112</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>57571</v>
+        <v>49112</v>
       </c>
       <c r="G51">
-        <v>82902</v>
+        <v>70721</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2698,16 +2698,16 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54418</v>
+        <v>54180</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>69418</v>
+        <v>69180</v>
       </c>
       <c r="G52">
-        <v>99962</v>
+        <v>99619</v>
       </c>
       <c r="H52">
         <v>15000</v>
@@ -2744,16 +2744,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>68251</v>
+        <v>58962</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>83251</v>
+        <v>73962</v>
       </c>
       <c r="G53">
-        <v>119881</v>
+        <v>106505</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>49471</v>
+        <v>48665</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>82706</v>
+        <v>82318</v>
       </c>
       <c r="G54">
-        <v>119097</v>
+        <v>118538</v>
       </c>
       <c r="H54">
-        <v>33235</v>
+        <v>33653</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44908</v>
+        <v>44520</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71908</v>
+        <v>71520</v>
       </c>
       <c r="G55">
-        <v>103548</v>
+        <v>102989</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>54354</v>
+        <v>53383</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>81354</v>
+        <v>80383</v>
       </c>
       <c r="G56">
-        <v>117150</v>
+        <v>115752</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>66281</v>
+        <v>65721</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90265</v>
+        <v>90041</v>
       </c>
       <c r="G57">
-        <v>129982</v>
+        <v>129659</v>
       </c>
       <c r="H57">
-        <v>23984</v>
+        <v>24320</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>17643</v>
+        <v>17167</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38670</v>
+        <v>38646</v>
       </c>
       <c r="G58">
-        <v>55685</v>
+        <v>55650</v>
       </c>
       <c r="H58">
-        <v>21027</v>
+        <v>21479</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6260</v>
+        <v>6201</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22937</v>
+        <v>22913</v>
       </c>
       <c r="G59">
-        <v>33029</v>
+        <v>32995</v>
       </c>
       <c r="H59">
-        <v>16677</v>
+        <v>16712</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24255</v>
+        <v>23623</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>39255</v>
+        <v>48520</v>
       </c>
       <c r="G60">
-        <v>56527</v>
+        <v>69869</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>24897</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>25520</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40520</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>58349</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>14297</v>
+        <v>13836</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>41297</v>
+        <v>40836</v>
       </c>
       <c r="G63">
-        <v>59468</v>
+        <v>58804</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>34197</v>
+        <v>33904</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>61197</v>
+        <v>60904</v>
       </c>
       <c r="G65">
-        <v>88124</v>
+        <v>87702</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>26000</v>
+        <v>25823</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60779</v>
+        <v>60481</v>
       </c>
       <c r="G66">
-        <v>87522</v>
+        <v>87093</v>
       </c>
       <c r="H66">
-        <v>34779</v>
+        <v>34658</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20733</v>
+        <v>20435</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47733</v>
+        <v>47435</v>
       </c>
       <c r="G67">
-        <v>68736</v>
+        <v>68306</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>48286</v>
+        <v>47948</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75286</v>
+        <v>74948</v>
       </c>
       <c r="G68">
-        <v>108412</v>
+        <v>107925</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>27672</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>54672</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>78728</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,16 +3495,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>111141</v>
+        <v>110353</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>126141</v>
+        <v>125353</v>
       </c>
       <c r="G70">
-        <v>181643</v>
+        <v>180508</v>
       </c>
       <c r="H70">
         <v>15000</v>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>52554</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>77555</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>111679</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>25001</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6852</v>
+        <v>6790</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21852</v>
+        <v>21790</v>
       </c>
       <c r="G73">
-        <v>31467</v>
+        <v>31378</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>70279</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85279</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>122802</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88455</v>
+        <v>87718</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>121006</v>
+        <v>120809</v>
       </c>
       <c r="G76">
-        <v>174249</v>
+        <v>173965</v>
       </c>
       <c r="H76">
-        <v>32551</v>
+        <v>33091</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>57636</v>
+        <v>57145</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>79588</v>
+        <v>79391</v>
       </c>
       <c r="G77">
-        <v>114607</v>
+        <v>114323</v>
       </c>
       <c r="H77">
-        <v>21952</v>
+        <v>22246</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>21694</v>
+        <v>19335</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>48694</v>
+        <v>46335</v>
       </c>
       <c r="G81">
-        <v>70119</v>
+        <v>66722</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,16 +4060,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87495</v>
+        <v>86761</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>102495</v>
+        <v>101761</v>
       </c>
       <c r="G83">
-        <v>147593</v>
+        <v>146536</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>46237</v>
+        <v>45541</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>67550</v>
+        <v>67184</v>
       </c>
       <c r="G84">
-        <v>97272</v>
+        <v>96745</v>
       </c>
       <c r="H84">
-        <v>21313</v>
+        <v>21643</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,16 +4148,16 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>43739</v>
+        <v>43373</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>58739</v>
+        <v>58373</v>
       </c>
       <c r="G85">
-        <v>84584</v>
+        <v>84057</v>
       </c>
       <c r="H85">
         <v>15000</v>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8902</v>
+        <v>8942</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38583</v>
+        <v>38570</v>
       </c>
       <c r="G90">
-        <v>55560</v>
+        <v>55541</v>
       </c>
       <c r="H90">
-        <v>29681</v>
+        <v>29628</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3714</v>
+        <v>3682</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30583</v>
+        <v>30570</v>
       </c>
       <c r="G91">
-        <v>44040</v>
+        <v>44021</v>
       </c>
       <c r="H91">
-        <v>26869</v>
+        <v>26888</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,16 +4499,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>8645</v>
+        <v>7763</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>23645</v>
+        <v>22763</v>
       </c>
       <c r="G93">
-        <v>34049</v>
+        <v>32779</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>64264</v>
+        <v>63314</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>79282</v>
+        <v>79164</v>
       </c>
       <c r="G96">
-        <v>114166</v>
+        <v>113996</v>
       </c>
       <c r="H96">
-        <v>15018</v>
+        <v>15850</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34710</v>
+        <v>34414</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52367</v>
+        <v>52249</v>
       </c>
       <c r="G97">
-        <v>75408</v>
+        <v>75239</v>
       </c>
       <c r="H97">
-        <v>17657</v>
+        <v>17835</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79570</v>
+        <v>78903</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>94686</v>
+        <v>94532</v>
       </c>
       <c r="G98">
-        <v>136348</v>
+        <v>136126</v>
       </c>
       <c r="H98">
-        <v>15116</v>
+        <v>15629</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>44076</v>
+        <v>43692</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>61168</v>
+        <v>61014</v>
       </c>
       <c r="G99">
-        <v>88082</v>
+        <v>87860</v>
       </c>
       <c r="H99">
-        <v>17092</v>
+        <v>17322</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61911</v>
+        <v>61018</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>79325</v>
+        <v>80934</v>
       </c>
       <c r="G100">
-        <v>114228</v>
+        <v>116545</v>
       </c>
       <c r="H100">
-        <v>17414</v>
+        <v>19916</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>63282</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>78282</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>112726</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>71602</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>86602</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>124707</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6196</v>
+        <v>6153</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33196</v>
+        <v>33153</v>
       </c>
       <c r="G109">
-        <v>47802</v>
+        <v>47740</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15145</v>
+        <v>15015</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42145</v>
+        <v>42015</v>
       </c>
       <c r="G111">
-        <v>60689</v>
+        <v>60502</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51472</v>
+        <v>51040</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>77122</v>
+        <v>76949</v>
       </c>
       <c r="G113">
-        <v>111056</v>
+        <v>110807</v>
       </c>
       <c r="H113">
-        <v>25650</v>
+        <v>25909</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>98525</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>117603</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>169348</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>19078</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80626</v>
+        <v>79939</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>95626</v>
+        <v>95199</v>
       </c>
       <c r="G118">
-        <v>137701</v>
+        <v>137087</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>15260</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,16 +5629,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50383</v>
+        <v>49956</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>65383</v>
+        <v>64956</v>
       </c>
       <c r="G119">
-        <v>94152</v>
+        <v>93537</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5716,16 +5716,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>86198</v>
+        <v>85821</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>101198</v>
+        <v>100821</v>
       </c>
       <c r="G121">
-        <v>145725</v>
+        <v>145182</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>110831</v>
       </c>
       <c r="E123">
         <v>148085</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>125831</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>181197</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46413</v>
+        <v>60205</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>61804</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>88998</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>15391</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35702</v>
+        <v>35403</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50403</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72580</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>64056</v>
+        <v>86235</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>79056</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>113841</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>52554</v>
       </c>
       <c r="E127">
         <v>81439</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>67554</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>97278</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>32452</v>
+        <v>32310</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>55074</v>
+        <v>55017</v>
       </c>
       <c r="G129">
-        <v>79307</v>
+        <v>79224</v>
       </c>
       <c r="H129">
-        <v>22622</v>
+        <v>22707</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12792</v>
+        <v>13836</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33310</v>
+        <v>33144</v>
       </c>
       <c r="G130">
-        <v>47966</v>
+        <v>47727</v>
       </c>
       <c r="H130">
-        <v>20518</v>
+        <v>19308</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>5347</v>
+        <v>4559</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25460</v>
+        <v>25144</v>
       </c>
       <c r="G131">
-        <v>36662</v>
+        <v>36207</v>
       </c>
       <c r="H131">
-        <v>20113</v>
+        <v>20585</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27841</v>
+        <v>28612</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43787</v>
+        <v>44095</v>
       </c>
       <c r="G132">
-        <v>63053</v>
+        <v>63497</v>
       </c>
       <c r="H132">
-        <v>15946</v>
+        <v>15483</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17403</v>
+        <v>17263</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36629</v>
+        <v>36573</v>
       </c>
       <c r="G135">
-        <v>52746</v>
+        <v>52665</v>
       </c>
       <c r="H135">
-        <v>19226</v>
+        <v>19310</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28194</v>
+        <v>27943</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46765</v>
+        <v>46664</v>
       </c>
       <c r="G137">
-        <v>67342</v>
+        <v>67196</v>
       </c>
       <c r="H137">
-        <v>18571</v>
+        <v>18721</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>27409</v>
+        <v>26986</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>54082</v>
+        <v>53913</v>
       </c>
       <c r="G139">
-        <v>77878</v>
+        <v>77635</v>
       </c>
       <c r="H139">
-        <v>26673</v>
+        <v>26927</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>56307</v>
+        <v>57958</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>71307</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>102682</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,16 +6677,16 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77985</v>
+        <v>77309</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>92985</v>
+        <v>92309</v>
       </c>
       <c r="G143">
-        <v>133898</v>
+        <v>132925</v>
       </c>
       <c r="H143">
         <v>15000</v>
@@ -6763,16 +6763,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87591</v>
+        <v>86841</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>102591</v>
+        <v>101841</v>
       </c>
       <c r="G145">
-        <v>147731</v>
+        <v>146651</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6849,16 +6849,16 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86630</v>
+        <v>86251</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>101630</v>
+        <v>101251</v>
       </c>
       <c r="G147">
-        <v>146347</v>
+        <v>145801</v>
       </c>
       <c r="H147">
         <v>15000</v>
@@ -6935,16 +6935,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>127119</v>
+        <v>122403</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>142119</v>
+        <v>137403</v>
       </c>
       <c r="G149">
-        <v>204651</v>
+        <v>197860</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38488</v>
+        <v>38160</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>63041</v>
+        <v>62910</v>
       </c>
       <c r="G150">
-        <v>90779</v>
+        <v>90590</v>
       </c>
       <c r="H150">
-        <v>24553</v>
+        <v>24750</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>22942</v>
+        <v>24133</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>57942</v>
+        <v>59133</v>
       </c>
       <c r="G152">
-        <v>83436</v>
+        <v>85152</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29811</v>
+        <v>29553</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>54017</v>
+        <v>53914</v>
       </c>
       <c r="G153">
-        <v>77784</v>
+        <v>77636</v>
       </c>
       <c r="H153">
-        <v>24206</v>
+        <v>24361</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48959</v>
+        <v>48537</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20451</v>
+        <v>20873</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>76192</v>
+        <v>75556</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>91192</v>
+        <v>90556</v>
       </c>
       <c r="G155">
-        <v>131316</v>
+        <v>130401</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7244,16 +7244,16 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65785</v>
+        <v>65226</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80785</v>
+        <v>80226</v>
       </c>
       <c r="G156">
-        <v>116330</v>
+        <v>115525</v>
       </c>
       <c r="H156">
         <v>15000</v>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>39208</v>
+        <v>39037</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65849</v>
+        <v>65489</v>
       </c>
       <c r="G158">
-        <v>94823</v>
+        <v>94304</v>
       </c>
       <c r="H158">
-        <v>26641</v>
+        <v>26452</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,16 +7378,16 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42250</v>
+        <v>41890</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>57250</v>
+        <v>56890</v>
       </c>
       <c r="G159">
-        <v>82440</v>
+        <v>81922</v>
       </c>
       <c r="H159">
         <v>15000</v>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>20189</v>
+        <v>18538</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>35728</v>
+        <v>35068</v>
       </c>
       <c r="G161">
-        <v>51448</v>
+        <v>50498</v>
       </c>
       <c r="H161">
-        <v>15539</v>
+        <v>16530</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,16 +7549,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56403</v>
+        <v>55918</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>71403</v>
+        <v>70918</v>
       </c>
       <c r="G163">
-        <v>102820</v>
+        <v>102122</v>
       </c>
       <c r="H163">
         <v>15000</v>
@@ -7635,16 +7635,16 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>81107</v>
+        <v>70678</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>96107</v>
+        <v>85678</v>
       </c>
       <c r="G165">
-        <v>138394</v>
+        <v>123376</v>
       </c>
       <c r="H165">
         <v>15000</v>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>69756</v>
+        <v>54180</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>69180</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>99619</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,16 +7725,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>34165</v>
+        <v>33873</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>49165</v>
+        <v>48873</v>
       </c>
       <c r="G167">
-        <v>70798</v>
+        <v>70377</v>
       </c>
       <c r="H167">
         <v>15000</v>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>67802</v>
+        <v>5196</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>82802</v>
+        <v>40196</v>
       </c>
       <c r="G168">
-        <v>119235</v>
+        <v>57882</v>
       </c>
       <c r="H168">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>74121</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>89121</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>128334</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,16 +7902,16 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>16346</v>
+        <v>15239</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>31346</v>
+        <v>30239</v>
       </c>
       <c r="G171">
-        <v>45138</v>
+        <v>43544</v>
       </c>
       <c r="H171">
         <v>15000</v>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31652</v>
+        <v>31386</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51866</v>
+        <v>51760</v>
       </c>
       <c r="G173">
-        <v>74687</v>
+        <v>74534</v>
       </c>
       <c r="H173">
-        <v>20214</v>
+        <v>20374</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7573</v>
+        <v>7508</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37786</v>
+        <v>37770</v>
       </c>
       <c r="G174">
-        <v>54412</v>
+        <v>54389</v>
       </c>
       <c r="H174">
-        <v>30213</v>
+        <v>30262</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5315</v>
+        <v>5276</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29786</v>
+        <v>29770</v>
       </c>
       <c r="G175">
-        <v>42892</v>
+        <v>42869</v>
       </c>
       <c r="H175">
-        <v>24471</v>
+        <v>24494</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10278</v>
+        <v>10313</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>42925</v>
+        <v>42476</v>
       </c>
       <c r="G176">
-        <v>61812</v>
+        <v>61165</v>
       </c>
       <c r="H176">
-        <v>32647</v>
+        <v>32163</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7925</v>
+        <v>7476</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>34925</v>
+        <v>34476</v>
       </c>
       <c r="G177">
-        <v>50292</v>
+        <v>49645</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21998</v>
+        <v>21806</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41875</v>
+        <v>41798</v>
       </c>
       <c r="G179">
-        <v>60300</v>
+        <v>60189</v>
       </c>
       <c r="H179">
-        <v>19877</v>
+        <v>19992</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>46141</v>
+        <v>45875</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65250</v>
+        <v>65143</v>
       </c>
       <c r="G181">
-        <v>93960</v>
+        <v>93806</v>
       </c>
       <c r="H181">
-        <v>19109</v>
+        <v>19268</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>68315</v>
+        <v>67809</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86651</v>
+        <v>86559</v>
       </c>
       <c r="G182">
-        <v>124777</v>
+        <v>124645</v>
       </c>
       <c r="H182">
-        <v>18336</v>
+        <v>18750</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10262</v>
+        <v>10170</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37262</v>
+        <v>37170</v>
       </c>
       <c r="G183">
-        <v>53657</v>
+        <v>53525</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>71549</v>
+        <v>60715</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>80262</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>115577</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>19547</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>76352</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>91352</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>131547</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>90008</v>
+        <v>80162</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>110793</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>159542</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>30631</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>81342</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>96342</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>138732</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,16 +8738,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>142601</v>
+        <v>141978</v>
       </c>
       <c r="E190">
         <v>157342</v>
       </c>
       <c r="F190">
-        <v>157601</v>
+        <v>156978</v>
       </c>
       <c r="G190">
-        <v>226945</v>
+        <v>226048</v>
       </c>
       <c r="H190">
         <v>15000</v>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>171754</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>186754</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>268926</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>6724</v>
+        <v>7285</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>28214</v>
+        <v>27653</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11831</v>
+        <v>11748</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38831</v>
+        <v>38748</v>
       </c>
       <c r="G196">
-        <v>55917</v>
+        <v>55797</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51984</v>
+        <v>51598</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17426</v>
+        <v>17812</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,16 +9128,16 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>75375</v>
+        <v>74743</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>90375</v>
+        <v>89743</v>
       </c>
       <c r="G199">
-        <v>130140</v>
+        <v>129230</v>
       </c>
       <c r="H199">
         <v>15000</v>
@@ -9172,16 +9172,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>57028</v>
+        <v>56539</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>72028</v>
+        <v>71539</v>
       </c>
       <c r="G200">
-        <v>103720</v>
+        <v>103016</v>
       </c>
       <c r="H200">
         <v>15000</v>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36935</v>
+        <v>36678</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63935</v>
+        <v>63678</v>
       </c>
       <c r="G202">
-        <v>92066</v>
+        <v>91696</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27649</v>
+        <v>27449</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54649</v>
+        <v>54449</v>
       </c>
       <c r="G204">
-        <v>78695</v>
+        <v>78407</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>102448</v>
+        <v>102000</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>117448</v>
+        <v>117159</v>
       </c>
       <c r="G206">
-        <v>169125</v>
+        <v>168709</v>
       </c>
       <c r="H206">
-        <v>15000</v>
+        <v>15159</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>63191</v>
+        <v>62469</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>81810</v>
+        <v>81521</v>
       </c>
       <c r="G207">
-        <v>117806</v>
+        <v>117390</v>
       </c>
       <c r="H207">
-        <v>18619</v>
+        <v>19052</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>145675</v>
+        <v>145038</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>180675</v>
+        <v>180038</v>
       </c>
       <c r="G208">
-        <v>260172</v>
+        <v>259255</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,16 +9567,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>145339</v>
+        <v>144098</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>160339</v>
+        <v>159098</v>
       </c>
       <c r="G209">
-        <v>230888</v>
+        <v>229101</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9611,16 +9611,16 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>188902</v>
+        <v>188076</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>203902</v>
+        <v>203076</v>
       </c>
       <c r="G210">
-        <v>293619</v>
+        <v>292429</v>
       </c>
       <c r="H210">
         <v>15000</v>
@@ -9654,16 +9654,16 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>187253</v>
+        <v>185685</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>202253</v>
+        <v>200685</v>
       </c>
       <c r="G211">
-        <v>291244</v>
+        <v>288986</v>
       </c>
       <c r="H211">
         <v>15000</v>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>289765</v>
+        <v>288498</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>304765</v>
+        <v>304371</v>
       </c>
       <c r="G212">
-        <v>438862</v>
+        <v>438294</v>
       </c>
       <c r="H212">
-        <v>15000</v>
+        <v>15873</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>225437</v>
+        <v>224451</v>
       </c>
       <c r="E213">
         <v>370241</v>
       </c>
       <c r="F213">
-        <v>240569</v>
+        <v>240175</v>
       </c>
       <c r="G213">
-        <v>346419</v>
+        <v>345852</v>
       </c>
       <c r="H213">
-        <v>15132</v>
+        <v>15724</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>35014</v>
+        <v>34558</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>60255</v>
+        <v>56251</v>
       </c>
       <c r="G214">
-        <v>86767</v>
+        <v>81001</v>
       </c>
       <c r="H214">
-        <v>25241</v>
+        <v>21693</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,16 +9829,16 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>37255</v>
+        <v>33251</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>52255</v>
+        <v>48251</v>
       </c>
       <c r="G215">
-        <v>75247</v>
+        <v>69481</v>
       </c>
       <c r="H215">
         <v>15000</v>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>16434</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>36733</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>52896</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>20299</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>67786</v>
+        <v>16434</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>82786</v>
+        <v>36733</v>
       </c>
       <c r="G218">
-        <v>119212</v>
+        <v>52896</v>
       </c>
       <c r="H218">
-        <v>15000</v>
+        <v>20299</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12728</v>
+        <v>12624</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>39728</v>
+        <v>44612</v>
       </c>
       <c r="G220">
-        <v>57208</v>
+        <v>64241</v>
       </c>
       <c r="H220">
-        <v>27000</v>
+        <v>31988</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,19 +10094,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>9612</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>36612</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>52721</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10137,19 +10137,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>23663</v>
+        <v>22459</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>58663</v>
+        <v>49459</v>
       </c>
       <c r="G222">
-        <v>84475</v>
+        <v>71221</v>
       </c>
       <c r="H222">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10183,19 +10183,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>53826</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>111059</v>
       </c>
       <c r="F223">
-        <v>70843</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>102014</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>17017</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>17387</v>
+        <v>17247</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46143</v>
+        <v>46015</v>
       </c>
       <c r="G224">
-        <v>66446</v>
+        <v>66262</v>
       </c>
       <c r="H224">
-        <v>28756</v>
+        <v>28768</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11143</v>
+        <v>11015</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38143</v>
+        <v>38015</v>
       </c>
       <c r="G225">
-        <v>54926</v>
+        <v>54742</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26641</v>
+        <v>26460</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61641</v>
+        <v>61460</v>
       </c>
       <c r="G226">
-        <v>88763</v>
+        <v>88502</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,16 +10362,16 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38568</v>
+        <v>38399</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>65568</v>
+        <v>65399</v>
       </c>
       <c r="G227">
-        <v>94418</v>
+        <v>94175</v>
       </c>
       <c r="H227">
         <v>27000</v>
@@ -10406,19 +10406,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>35894</v>
+        <v>36264</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>62894</v>
+        <v>71264</v>
       </c>
       <c r="G228">
-        <v>90567</v>
+        <v>102620</v>
       </c>
       <c r="H228">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10452,19 +10452,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>36152</v>
       </c>
       <c r="E229">
         <v>185111</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>63152</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>90939</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15770</v>
+        <v>15302</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42954</v>
+        <v>42777</v>
       </c>
       <c r="G230">
-        <v>61854</v>
+        <v>61599</v>
       </c>
       <c r="H230">
-        <v>27184</v>
+        <v>27475</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>10118</v>
+        <v>9676</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>33144</v>
+        <v>32967</v>
       </c>
       <c r="G231">
-        <v>47727</v>
+        <v>47472</v>
       </c>
       <c r="H231">
-        <v>23026</v>
+        <v>23291</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>23448</v>
       </c>
       <c r="E233">
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>38448</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>55365</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>41699</v>
       </c>
       <c r="E235">
         <v>111059</v>
       </c>
       <c r="F235">
-        <v>0</v>
+        <v>65992</v>
       </c>
       <c r="G235">
-        <v>0</v>
+        <v>95028</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>24293</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>86012</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>112598</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>162141</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>26586</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>26929</v>
+        <v>27927</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>61484</v>
+        <v>61428</v>
       </c>
       <c r="G238">
-        <v>88537</v>
+        <v>88456</v>
       </c>
       <c r="H238">
-        <v>34555</v>
+        <v>33501</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>32036</v>
+        <v>31896</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>53464</v>
+        <v>53408</v>
       </c>
       <c r="G239">
-        <v>76988</v>
+        <v>76908</v>
       </c>
       <c r="H239">
-        <v>21428</v>
+        <v>21512</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,7 +10931,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>47246</v>
+        <v>46848</v>
       </c>
       <c r="E240">
         <v>103654</v>
@@ -10943,7 +10943,7 @@
         <v>111947</v>
       </c>
       <c r="H240">
-        <v>30495</v>
+        <v>30893</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,16 +10977,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>84757</v>
+        <v>84386</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>99757</v>
+        <v>99386</v>
       </c>
       <c r="G241">
-        <v>143650</v>
+        <v>143116</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>110241</v>
       </c>
       <c r="E243">
         <v>133275</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>125241</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>180347</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64584</v>
+        <v>64127</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79584</v>
+        <v>79388</v>
       </c>
       <c r="G244">
-        <v>114601</v>
+        <v>114319</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>15261</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,16 +11155,16 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>44780</v>
+        <v>44584</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>59780</v>
+        <v>59584</v>
       </c>
       <c r="G245">
-        <v>86083</v>
+        <v>85801</v>
       </c>
       <c r="H245">
         <v>15000</v>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>76192</v>
+        <v>75858</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>91192</v>
+        <v>108923</v>
       </c>
       <c r="G246">
-        <v>131316</v>
+        <v>156849</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>33065</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>79716</v>
       </c>
       <c r="E247">
         <v>98119</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>94716</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>136391</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>17003</v>
+        <v>16833</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42532</v>
+        <v>42492</v>
       </c>
       <c r="G248">
-        <v>61246</v>
+        <v>61188</v>
       </c>
       <c r="H248">
-        <v>25529</v>
+        <v>25659</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11783</v>
+        <v>11684</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34532</v>
+        <v>34492</v>
       </c>
       <c r="G249">
-        <v>49726</v>
+        <v>49668</v>
       </c>
       <c r="H249">
-        <v>22749</v>
+        <v>22808</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>31115</v>
       </c>
       <c r="E250">
         <v>74033</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>51761</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>74536</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>20646</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16714</v>
+        <v>16482</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>43714</v>
+        <v>43482</v>
       </c>
       <c r="G253">
-        <v>62948</v>
+        <v>62614</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11596,19 +11596,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>22970</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>49970</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>71957</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -11639,19 +11639,19 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9638</v>
+        <v>9612</v>
       </c>
       <c r="E256">
         <v>53688</v>
       </c>
       <c r="F256">
-        <v>34938</v>
+        <v>40266</v>
       </c>
       <c r="G256">
-        <v>50311</v>
+        <v>57983</v>
       </c>
       <c r="H256">
-        <v>25300</v>
+        <v>30654</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>14888</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>32893</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>47366</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>18005</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12360</v>
+        <v>12322</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39360</v>
+        <v>39322</v>
       </c>
       <c r="G258">
-        <v>56678</v>
+        <v>56624</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8918</v>
+        <v>8847</v>
       </c>
       <c r="E260">
         <v>53688</v>
       </c>
       <c r="F260">
-        <v>39376</v>
+        <v>39325</v>
       </c>
       <c r="G260">
-        <v>56701</v>
+        <v>56628</v>
       </c>
       <c r="H260">
-        <v>30458</v>
+        <v>30478</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>11095</v>
+        <v>10967</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>31376</v>
+        <v>31325</v>
       </c>
       <c r="G261">
-        <v>45181</v>
+        <v>45108</v>
       </c>
       <c r="H261">
-        <v>20281</v>
+        <v>20358</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12824</v>
+        <v>12465</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>35289</v>
+        <v>39127</v>
       </c>
       <c r="G262">
-        <v>50816</v>
+        <v>56343</v>
       </c>
       <c r="H262">
-        <v>22465</v>
+        <v>26662</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>10473</v>
       </c>
       <c r="E263">
         <v>53688</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>31127</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>44823</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>20654</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>19372</v>
+        <v>19670</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>51880</v>
+        <v>51837</v>
       </c>
       <c r="G264">
-        <v>74707</v>
+        <v>74645</v>
       </c>
       <c r="H264">
-        <v>32508</v>
+        <v>32167</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24303</v>
+        <v>24197</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>43880</v>
+        <v>43837</v>
       </c>
       <c r="G265">
-        <v>63187</v>
+        <v>63125</v>
       </c>
       <c r="H265">
-        <v>19577</v>
+        <v>19640</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,19 +12078,19 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34582</v>
+        <v>34335</v>
       </c>
       <c r="E266">
         <v>72201</v>
       </c>
       <c r="F266">
-        <v>52323</v>
+        <v>54151</v>
       </c>
       <c r="G266">
-        <v>75345</v>
+        <v>77977</v>
       </c>
       <c r="H266">
-        <v>17741</v>
+        <v>19816</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>30955</v>
       </c>
       <c r="E267">
         <v>72201</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>46541</v>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>67019</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>15586</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10214</v>
+        <v>10202</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>25214</v>
+        <v>39546</v>
       </c>
       <c r="G268">
-        <v>36308</v>
+        <v>56946</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>29344</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,19 +12211,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>16546</v>
       </c>
       <c r="E269">
         <v>27770</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>31546</v>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>45426</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12264</v>
+        <v>12162</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>39264</v>
+        <v>39162</v>
       </c>
       <c r="G270">
-        <v>56540</v>
+        <v>56393</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>63512</v>
+        <v>62867</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>78512</v>
+        <v>77867</v>
       </c>
       <c r="G272">
-        <v>113057</v>
+        <v>112128</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>40376</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>0</v>
+        <v>60417</v>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>20041</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>69435</v>
+        <v>74583</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>84435</v>
+        <v>0</v>
       </c>
       <c r="G274">
-        <v>121586</v>
+        <v>0</v>
       </c>
       <c r="H274">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>77771</v>
       </c>
       <c r="E275">
         <v>111059</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>92771</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>133590</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11239</v>
+        <v>11158</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>37871</v>
+        <v>37769</v>
       </c>
       <c r="G276">
-        <v>54534</v>
+        <v>54387</v>
       </c>
       <c r="H276">
-        <v>26632</v>
+        <v>26611</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>7333</v>
+        <v>7077</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>29871</v>
+        <v>29769</v>
       </c>
       <c r="G277">
-        <v>43014</v>
+        <v>42867</v>
       </c>
       <c r="H277">
-        <v>22538</v>
+        <v>22692</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20301</v>
+        <v>20148</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>51880</v>
+        <v>51837</v>
       </c>
       <c r="G278">
-        <v>74707</v>
+        <v>74645</v>
       </c>
       <c r="H278">
-        <v>31579</v>
+        <v>31689</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24303</v>
+        <v>24197</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>43880</v>
+        <v>43837</v>
       </c>
       <c r="G279">
-        <v>63187</v>
+        <v>63125</v>
       </c>
       <c r="H279">
-        <v>19577</v>
+        <v>19640</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11799</v>
+        <v>11700</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23139</v>
+        <v>23238</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,16 +12826,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17819</v>
+        <v>17662</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32819</v>
+        <v>32662</v>
       </c>
       <c r="G283">
-        <v>47259</v>
+        <v>47033</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>50191</v>
+        <v>20818</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>65191</v>
+        <v>35980</v>
       </c>
       <c r="G285">
-        <v>93875</v>
+        <v>51811</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>15162</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>58997</v>
+        <v>24197</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>73997</v>
+        <v>41664</v>
       </c>
       <c r="G287">
-        <v>106556</v>
+        <v>59996</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>17467</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>33765</v>
+        <v>33617</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55851</v>
+        <v>55732</v>
       </c>
       <c r="G288">
-        <v>80425</v>
+        <v>80254</v>
       </c>
       <c r="H288">
-        <v>22086</v>
+        <v>22115</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23935</v>
+        <v>23639</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39393</v>
+        <v>39274</v>
       </c>
       <c r="G289">
-        <v>56726</v>
+        <v>56555</v>
       </c>
       <c r="H289">
-        <v>15458</v>
+        <v>15635</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>44940</v>
+        <v>44616</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>62161</v>
+        <v>61992</v>
       </c>
       <c r="G292">
-        <v>89512</v>
+        <v>89268</v>
       </c>
       <c r="H292">
-        <v>17221</v>
+        <v>17376</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23695</v>
+        <v>23272</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39297</v>
+        <v>39128</v>
       </c>
       <c r="G293">
-        <v>56588</v>
+        <v>56344</v>
       </c>
       <c r="H293">
-        <v>15602</v>
+        <v>15856</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13310,19 +13310,19 @@
         <v>15</v>
       </c>
       <c r="D294">
-        <v>87479</v>
+        <v>0</v>
       </c>
       <c r="E294">
         <v>68480</v>
       </c>
       <c r="F294">
-        <v>102479</v>
+        <v>0</v>
       </c>
       <c r="G294">
-        <v>147570</v>
+        <v>0</v>
       </c>
       <c r="H294">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I294" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>23743</v>
+        <v>23639</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>42204</v>
+        <v>42163</v>
       </c>
       <c r="G295">
-        <v>60774</v>
+        <v>60715</v>
       </c>
       <c r="H295">
-        <v>18461</v>
+        <v>18524</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,16 +13399,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>63063</v>
+        <v>62788</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>78063</v>
+        <v>77788</v>
       </c>
       <c r="G296">
-        <v>112411</v>
+        <v>112015</v>
       </c>
       <c r="H296">
         <v>15000</v>
@@ -13486,16 +13486,16 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>75071</v>
+        <v>73627</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>90071</v>
+        <v>88627</v>
       </c>
       <c r="G298">
-        <v>129702</v>
+        <v>127623</v>
       </c>
       <c r="H298">
         <v>15000</v>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>70892</v>
+        <v>70264</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>88506</v>
+        <v>88447</v>
       </c>
       <c r="G300">
-        <v>127449</v>
+        <v>127364</v>
       </c>
       <c r="H300">
-        <v>17614</v>
+        <v>18183</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33861</v>
+        <v>33713</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>55637</v>
+        <v>55578</v>
       </c>
       <c r="G301">
-        <v>80117</v>
+        <v>80032</v>
       </c>
       <c r="H301">
-        <v>21776</v>
+        <v>21865</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>11927</v>
+        <v>10935</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>38927</v>
+        <v>37935</v>
       </c>
       <c r="G303">
-        <v>56055</v>
+        <v>54626</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13792,19 +13792,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>105570</v>
+        <v>25600</v>
       </c>
       <c r="E305">
         <v>166598</v>
       </c>
       <c r="F305">
-        <v>120570</v>
+        <v>52600</v>
       </c>
       <c r="G305">
-        <v>173621</v>
+        <v>75744</v>
       </c>
       <c r="H305">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>52513</v>
+        <v>52076</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>80072</v>
+        <v>79901</v>
       </c>
       <c r="G306">
-        <v>115304</v>
+        <v>115057</v>
       </c>
       <c r="H306">
-        <v>27559</v>
+        <v>27825</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50704</v>
+        <v>50275</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69594</v>
+        <v>69423</v>
       </c>
       <c r="G307">
-        <v>100215</v>
+        <v>99969</v>
       </c>
       <c r="H307">
-        <v>18890</v>
+        <v>19148</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69644</v>
+        <v>69132</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>27535</v>
+        <v>28047</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,16 +13970,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>78209</v>
+        <v>77867</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>93209</v>
+        <v>92867</v>
       </c>
       <c r="G309">
-        <v>134221</v>
+        <v>133728</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24816</v>
+        <v>24245</v>
       </c>
       <c r="E310">
         <v>55520</v>
@@ -14026,7 +14026,7 @@
         <v>59962</v>
       </c>
       <c r="H310">
-        <v>16824</v>
+        <v>17395</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,16 +14058,16 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>37624</v>
+        <v>37459</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>52624</v>
+        <v>52459</v>
       </c>
       <c r="G311">
-        <v>75779</v>
+        <v>75541</v>
       </c>
       <c r="H311">
         <v>15000</v>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>66490</v>
+        <v>66454</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>90473</v>
+        <v>90194</v>
       </c>
       <c r="G312">
-        <v>130281</v>
+        <v>129879</v>
       </c>
       <c r="H312">
-        <v>23983</v>
+        <v>23740</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,16 +14146,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63672</v>
+        <v>63393</v>
       </c>
       <c r="E313">
         <v>83309</v>
       </c>
       <c r="F313">
-        <v>78672</v>
+        <v>78393</v>
       </c>
       <c r="G313">
-        <v>113288</v>
+        <v>112886</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>20925</v>
+        <v>22316</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>35925</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>51732</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32644</v>
+        <v>32502</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>63021</v>
+        <v>49604</v>
       </c>
       <c r="G316">
-        <v>90750</v>
+        <v>71430</v>
       </c>
       <c r="H316">
-        <v>30377</v>
+        <v>17102</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>39801</v>
+        <v>26604</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>41604</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>59910</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>12136</v>
+        <v>12083</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>21174</v>
+        <v>21227</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,16 +14412,16 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29586</v>
+        <v>29330</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44586</v>
+        <v>44330</v>
       </c>
       <c r="G319">
-        <v>64204</v>
+        <v>63835</v>
       </c>
       <c r="H319">
         <v>15000</v>
@@ -14456,19 +14456,19 @@
         <v>15</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>50498</v>
       </c>
       <c r="E320">
         <v>111059</v>
       </c>
       <c r="F320">
-        <v>0</v>
+        <v>76176</v>
       </c>
       <c r="G320">
-        <v>0</v>
+        <v>109693</v>
       </c>
       <c r="H320">
-        <v>0</v>
+        <v>25678</v>
       </c>
       <c r="I320" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>38504</v>
+        <v>38336</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>64714</v>
+        <v>64647</v>
       </c>
       <c r="G321">
-        <v>93188</v>
+        <v>93092</v>
       </c>
       <c r="H321">
-        <v>26210</v>
+        <v>26311</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>59157</v>
+        <v>59153</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>74157</v>
+        <v>90812</v>
       </c>
       <c r="G324">
-        <v>106786</v>
+        <v>130769</v>
       </c>
       <c r="H324">
-        <v>15000</v>
+        <v>31659</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>63967</v>
       </c>
       <c r="E325">
         <v>74033</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>78967</v>
       </c>
       <c r="G325">
-        <v>0</v>
+        <v>113712</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9446</v>
+        <v>9405</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>35041</v>
+        <v>35025</v>
       </c>
       <c r="G327">
-        <v>50459</v>
+        <v>50436</v>
       </c>
       <c r="H327">
-        <v>25595</v>
+        <v>25620</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>17040</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>38079</v>
       </c>
       <c r="G329">
-        <v>0</v>
+        <v>54834</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>21039</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>22110</v>
+        <v>21949</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>49110</v>
+        <v>48949</v>
       </c>
       <c r="G330">
-        <v>70718</v>
+        <v>70487</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,19 +14979,19 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43947</v>
+        <v>43628</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>70947</v>
+        <v>78628</v>
       </c>
       <c r="G332">
-        <v>102164</v>
+        <v>113224</v>
       </c>
       <c r="H332">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I332" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>0</v>
+        <v>83302</v>
       </c>
       <c r="E333">
         <v>111059</v>
       </c>
       <c r="F333">
-        <v>0</v>
+        <v>98302</v>
       </c>
       <c r="G333">
-        <v>0</v>
+        <v>141555</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,19 +15067,19 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32084</v>
+        <v>32581</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>59084</v>
+        <v>67581</v>
       </c>
       <c r="G334">
-        <v>85081</v>
+        <v>97317</v>
       </c>
       <c r="H334">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I334" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>49414</v>
       </c>
       <c r="E335">
         <v>111059</v>
       </c>
       <c r="F335">
-        <v>0</v>
+        <v>69078</v>
       </c>
       <c r="G335">
-        <v>0</v>
+        <v>99472</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>19664</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>190103</v>
+        <v>188761</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>205103</v>
+        <v>204469</v>
       </c>
       <c r="G336">
-        <v>295348</v>
+        <v>294435</v>
       </c>
       <c r="H336">
-        <v>15000</v>
+        <v>15708</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,16 +15199,16 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>144987</v>
+        <v>144353</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>159987</v>
+        <v>159353</v>
       </c>
       <c r="G337">
-        <v>230381</v>
+        <v>229468</v>
       </c>
       <c r="H337">
         <v>15000</v>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>62839</v>
+        <v>57623</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89443</v>
+        <v>89259</v>
       </c>
       <c r="G338">
-        <v>128798</v>
+        <v>128533</v>
       </c>
       <c r="H338">
-        <v>26604</v>
+        <v>31636</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,16 +15287,16 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>42074</v>
+        <v>41890</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>69074</v>
+        <v>68890</v>
       </c>
       <c r="G339">
-        <v>99467</v>
+        <v>99202</v>
       </c>
       <c r="H339">
         <v>27000</v>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>109986</v>
       </c>
       <c r="E341">
         <v>185111</v>
       </c>
       <c r="F341">
-        <v>0</v>
+        <v>124986</v>
       </c>
       <c r="G341">
-        <v>0</v>
+        <v>179980</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,19 +15415,19 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>104513</v>
+        <v>104056</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>131513</v>
+        <v>139056</v>
       </c>
       <c r="G342">
-        <v>189379</v>
+        <v>200241</v>
       </c>
       <c r="H342">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I342" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>144369</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>0</v>
+        <v>159369</v>
       </c>
       <c r="G343">
-        <v>0</v>
+        <v>229491</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71156</v>
+        <v>71015</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>86675</v>
+        <v>86015</v>
       </c>
       <c r="G2">
-        <v>124812</v>
+        <v>123862</v>
       </c>
       <c r="H2">
-        <v>15519</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,16 +548,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>47581</v>
+        <v>45543</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>62581</v>
+        <v>60543</v>
       </c>
       <c r="G3">
-        <v>90117</v>
+        <v>87182</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94445</v>
+        <v>94538</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>109445</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>157601</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>66534</v>
+        <v>67579</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>81534</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>117409</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7141</v>
+        <v>7159</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30509</v>
+        <v>30516</v>
       </c>
       <c r="G7">
-        <v>43933</v>
+        <v>43943</v>
       </c>
       <c r="H7">
-        <v>23368</v>
+        <v>23357</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39372</v>
+        <v>39503</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55064</v>
+        <v>55525</v>
       </c>
       <c r="G8">
-        <v>79292</v>
+        <v>79956</v>
       </c>
       <c r="H8">
-        <v>15692</v>
+        <v>16022</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>39662</v>
       </c>
       <c r="E9">
         <v>74033</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>54662</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>78713</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56412</v>
+        <v>56553</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78541</v>
+        <v>78598</v>
       </c>
       <c r="G10">
-        <v>113099</v>
+        <v>113181</v>
       </c>
       <c r="H10">
-        <v>22129</v>
+        <v>22045</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>75090</v>
       </c>
       <c r="E11">
         <v>111059</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>90090</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>129730</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>84354</v>
+        <v>84646</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>101738</v>
+        <v>101020</v>
       </c>
       <c r="G12">
-        <v>146503</v>
+        <v>145469</v>
       </c>
       <c r="H12">
-        <v>17384</v>
+        <v>16374</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>13390</v>
+        <v>12672</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>40390</v>
+        <v>39672</v>
       </c>
       <c r="G13">
-        <v>58162</v>
+        <v>57128</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>26588</v>
+        <v>26303</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45508</v>
+        <v>45394</v>
       </c>
       <c r="G15">
-        <v>65532</v>
+        <v>65367</v>
       </c>
       <c r="H15">
-        <v>18920</v>
+        <v>19091</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,19 +1336,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54244</v>
+        <v>54428</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>69428</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>99976</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1425,19 +1425,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96039</v>
+        <v>96280</v>
       </c>
       <c r="E23">
         <v>133275</v>
       </c>
       <c r="F23">
-        <v>111039</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>159896</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21121</v>
+        <v>24034</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>39711</v>
+        <v>40877</v>
       </c>
       <c r="G27">
-        <v>57184</v>
+        <v>58863</v>
       </c>
       <c r="H27">
-        <v>18590</v>
+        <v>16843</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75587</v>
+        <v>75697</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>94542</v>
+        <v>94586</v>
       </c>
       <c r="G28">
-        <v>136140</v>
+        <v>136204</v>
       </c>
       <c r="H28">
-        <v>18955</v>
+        <v>18889</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>33474</v>
+        <v>30010</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>60474</v>
+        <v>57010</v>
       </c>
       <c r="G29">
-        <v>87083</v>
+        <v>82094</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>119167</v>
+        <v>122407</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>136967</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>197232</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>17800</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,16 +1776,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72384</v>
+        <v>72565</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>99384</v>
+        <v>99565</v>
       </c>
       <c r="G31">
-        <v>143113</v>
+        <v>143374</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60715</v>
+        <v>60868</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80731</v>
+        <v>80838</v>
       </c>
       <c r="G32">
-        <v>116253</v>
+        <v>116407</v>
       </c>
       <c r="H32">
-        <v>20016</v>
+        <v>19970</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36200</v>
+        <v>36307</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63200</v>
+        <v>63307</v>
       </c>
       <c r="G33">
-        <v>91008</v>
+        <v>91162</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,19 +1956,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>83318</v>
+        <v>84071</v>
       </c>
       <c r="E35">
         <v>129572</v>
       </c>
       <c r="F35">
-        <v>98318</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>141578</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>48569</v>
+        <v>49314</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>75569</v>
+        <v>76314</v>
       </c>
       <c r="G36">
-        <v>108819</v>
+        <v>109892</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,16 +2046,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35498</v>
+        <v>35587</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>62498</v>
+        <v>62587</v>
       </c>
       <c r="G37">
-        <v>89997</v>
+        <v>90125</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>66996</v>
+        <v>67547</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>93996</v>
+        <v>94547</v>
       </c>
       <c r="G38">
-        <v>135354</v>
+        <v>136148</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>62262</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>89262</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>128537</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,19 +2177,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>87718</v>
+        <v>108504</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>114718</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>165194</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>88531</v>
+        <v>88753</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>113606</v>
+        <v>113694</v>
       </c>
       <c r="G41">
-        <v>163593</v>
+        <v>163719</v>
       </c>
       <c r="H41">
-        <v>25075</v>
+        <v>24941</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31529</v>
+        <v>31640</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58529</v>
+        <v>58640</v>
       </c>
       <c r="G43">
-        <v>84282</v>
+        <v>84442</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,16 +2393,16 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>80194</v>
+        <v>79532</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>107194</v>
+        <v>106532</v>
       </c>
       <c r="G45">
-        <v>154359</v>
+        <v>153406</v>
       </c>
       <c r="H45">
         <v>27000</v>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>16673</v>
+        <v>16715</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>43673</v>
+        <v>43715</v>
       </c>
       <c r="G47">
-        <v>62889</v>
+        <v>62950</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>34733</v>
+        <v>34820</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>57748</v>
+        <v>57833</v>
       </c>
       <c r="G50">
-        <v>83157</v>
+        <v>83280</v>
       </c>
       <c r="H50">
-        <v>23015</v>
+        <v>23013</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>34112</v>
+        <v>34197</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>49112</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>70721</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54180</v>
+        <v>54316</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>69180</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>99619</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>58962</v>
+        <v>59110</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>73962</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>106505</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48665</v>
+        <v>48611</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>82318</v>
+        <v>82478</v>
       </c>
       <c r="G54">
-        <v>118538</v>
+        <v>118768</v>
       </c>
       <c r="H54">
-        <v>33653</v>
+        <v>33867</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44520</v>
+        <v>44680</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71520</v>
+        <v>71680</v>
       </c>
       <c r="G55">
-        <v>102989</v>
+        <v>103219</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53383</v>
+        <v>53501</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>80383</v>
+        <v>80501</v>
       </c>
       <c r="G56">
-        <v>115752</v>
+        <v>115921</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>65721</v>
+        <v>65949</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90041</v>
+        <v>90133</v>
       </c>
       <c r="G57">
-        <v>129659</v>
+        <v>129792</v>
       </c>
       <c r="H57">
-        <v>24320</v>
+        <v>24184</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>17167</v>
+        <v>17210</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38646</v>
+        <v>38652</v>
       </c>
       <c r="G58">
-        <v>55650</v>
+        <v>55659</v>
       </c>
       <c r="H58">
-        <v>21479</v>
+        <v>21442</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6201</v>
+        <v>6216</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22913</v>
+        <v>22919</v>
       </c>
       <c r="G59">
-        <v>32995</v>
+        <v>33003</v>
       </c>
       <c r="H59">
-        <v>16712</v>
+        <v>16703</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>23623</v>
+        <v>23698</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>48520</v>
+        <v>48584</v>
       </c>
       <c r="G60">
-        <v>69869</v>
+        <v>69961</v>
       </c>
       <c r="H60">
-        <v>24897</v>
+        <v>24886</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,19 +3102,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25520</v>
+        <v>25584</v>
       </c>
       <c r="E61">
         <v>49967</v>
       </c>
       <c r="F61">
-        <v>40520</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>58349</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13836</v>
+        <v>13759</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>40836</v>
+        <v>40759</v>
       </c>
       <c r="G63">
-        <v>58804</v>
+        <v>58693</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>33904</v>
+        <v>34021</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>60904</v>
+        <v>61021</v>
       </c>
       <c r="G65">
-        <v>87702</v>
+        <v>87870</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25823</v>
+        <v>25840</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60481</v>
+        <v>60532</v>
       </c>
       <c r="G66">
-        <v>87093</v>
+        <v>87166</v>
       </c>
       <c r="H66">
-        <v>34658</v>
+        <v>34692</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20435</v>
+        <v>20486</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47435</v>
+        <v>47486</v>
       </c>
       <c r="G67">
-        <v>68306</v>
+        <v>68380</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47948</v>
+        <v>47988</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>74948</v>
+        <v>75017</v>
       </c>
       <c r="G68">
-        <v>107925</v>
+        <v>108024</v>
       </c>
       <c r="H68">
-        <v>27000</v>
+        <v>27029</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3452,16 +3452,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27672</v>
+        <v>27741</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>54672</v>
+        <v>54741</v>
       </c>
       <c r="G69">
-        <v>78728</v>
+        <v>78827</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110353</v>
+        <v>110438</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>125353</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>180508</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52554</v>
+        <v>52686</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>77555</v>
+        <v>77608</v>
       </c>
       <c r="G71">
-        <v>111679</v>
+        <v>111756</v>
       </c>
       <c r="H71">
-        <v>25001</v>
+        <v>24922</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6790</v>
+        <v>6776</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21790</v>
+        <v>21776</v>
       </c>
       <c r="G73">
-        <v>31378</v>
+        <v>31357</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70279</v>
+        <v>70456</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>85279</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>122802</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>87718</v>
+        <v>88002</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>120809</v>
+        <v>120886</v>
       </c>
       <c r="G76">
-        <v>173965</v>
+        <v>174076</v>
       </c>
       <c r="H76">
-        <v>33091</v>
+        <v>32884</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>57145</v>
+        <v>57336</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>79391</v>
+        <v>79468</v>
       </c>
       <c r="G77">
-        <v>114323</v>
+        <v>114434</v>
       </c>
       <c r="H77">
-        <v>22246</v>
+        <v>22132</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>19335</v>
+        <v>19528</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>46335</v>
+        <v>46528</v>
       </c>
       <c r="G81">
-        <v>66722</v>
+        <v>67000</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>86761</v>
+        <v>87043</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>101761</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>146536</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>45541</v>
+        <v>45383</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>67184</v>
+        <v>67325</v>
       </c>
       <c r="G84">
-        <v>96745</v>
+        <v>96948</v>
       </c>
       <c r="H84">
-        <v>21643</v>
+        <v>21942</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>43373</v>
+        <v>43514</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>58373</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>84057</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8942</v>
+        <v>8949</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38570</v>
+        <v>38573</v>
       </c>
       <c r="G90">
-        <v>55541</v>
+        <v>55545</v>
       </c>
       <c r="H90">
-        <v>29628</v>
+        <v>29624</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3682</v>
+        <v>3691</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30570</v>
+        <v>30573</v>
       </c>
       <c r="G91">
-        <v>44021</v>
+        <v>44025</v>
       </c>
       <c r="H91">
-        <v>26888</v>
+        <v>26882</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>7763</v>
+        <v>7798</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>22763</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>32779</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63314</v>
+        <v>63521</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>79164</v>
+        <v>79199</v>
       </c>
       <c r="G96">
-        <v>113996</v>
+        <v>114047</v>
       </c>
       <c r="H96">
-        <v>15850</v>
+        <v>15678</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34414</v>
+        <v>34501</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52249</v>
+        <v>52284</v>
       </c>
       <c r="G97">
-        <v>75239</v>
+        <v>75289</v>
       </c>
       <c r="H97">
-        <v>17835</v>
+        <v>17783</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>78903</v>
+        <v>79165</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>94532</v>
+        <v>94165</v>
       </c>
       <c r="G98">
-        <v>136126</v>
+        <v>135598</v>
       </c>
       <c r="H98">
-        <v>15629</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>43692</v>
+        <v>41005</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>61014</v>
+        <v>59939</v>
       </c>
       <c r="G99">
-        <v>87860</v>
+        <v>86312</v>
       </c>
       <c r="H99">
-        <v>17322</v>
+        <v>18934</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,7 +4809,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61018</v>
+        <v>61203</v>
       </c>
       <c r="E100">
         <v>107912</v>
@@ -4821,7 +4821,7 @@
         <v>116545</v>
       </c>
       <c r="H100">
-        <v>19916</v>
+        <v>19731</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,19 +4855,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63282</v>
+        <v>63441</v>
       </c>
       <c r="E101">
         <v>107912</v>
       </c>
       <c r="F101">
-        <v>78282</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>112726</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5027,19 +5027,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71602</v>
+        <v>71782</v>
       </c>
       <c r="E105">
         <v>129572</v>
       </c>
       <c r="F105">
-        <v>86602</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>124707</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>75138</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>102138</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>147079</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6153</v>
+        <v>6056</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33153</v>
+        <v>33056</v>
       </c>
       <c r="G109">
-        <v>47740</v>
+        <v>47601</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15015</v>
+        <v>15069</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42015</v>
+        <v>42069</v>
       </c>
       <c r="G111">
-        <v>60502</v>
+        <v>60579</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51040</v>
+        <v>51216</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>76949</v>
+        <v>77020</v>
       </c>
       <c r="G113">
-        <v>110807</v>
+        <v>110909</v>
       </c>
       <c r="H113">
-        <v>25909</v>
+        <v>25804</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>98525</v>
+        <v>99731</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>117603</v>
+        <v>118086</v>
       </c>
       <c r="G115">
-        <v>169348</v>
+        <v>170044</v>
       </c>
       <c r="H115">
-        <v>19078</v>
+        <v>18355</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>79939</v>
+        <v>80220</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>95199</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>137087</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15260</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>49956</v>
+        <v>50129</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>64956</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>93537</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>85821</v>
+        <v>86036</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>100821</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>145182</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,19 +5803,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>110831</v>
+        <v>111109</v>
       </c>
       <c r="E123">
         <v>148085</v>
       </c>
       <c r="F123">
-        <v>125831</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>181197</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5846,19 +5846,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>60205</v>
+        <v>46118</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>61118</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>88010</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35403</v>
+        <v>35524</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>50403</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>72580</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,19 +5935,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>86235</v>
+        <v>63648</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>78648</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>113253</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5980,19 +5980,19 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>52554</v>
+        <v>52686</v>
       </c>
       <c r="E127">
         <v>81439</v>
       </c>
       <c r="F127">
-        <v>67554</v>
+        <v>0</v>
       </c>
       <c r="G127">
-        <v>97278</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I127" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>39151</v>
       </c>
       <c r="E128">
         <v>92546</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>63306</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>91161</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>24155</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>32310</v>
+        <v>32391</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>55017</v>
+        <v>55049</v>
       </c>
       <c r="G129">
-        <v>79224</v>
+        <v>79271</v>
       </c>
       <c r="H129">
-        <v>22707</v>
+        <v>22658</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>13836</v>
+        <v>12720</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33144</v>
+        <v>33149</v>
       </c>
       <c r="G130">
-        <v>47727</v>
+        <v>47735</v>
       </c>
       <c r="H130">
-        <v>19308</v>
+        <v>20429</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4559</v>
+        <v>4570</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25144</v>
+        <v>25149</v>
       </c>
       <c r="G131">
-        <v>36207</v>
+        <v>36215</v>
       </c>
       <c r="H131">
-        <v>20585</v>
+        <v>20579</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>28612</v>
+        <v>27661</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>44095</v>
+        <v>43715</v>
       </c>
       <c r="G132">
-        <v>63497</v>
+        <v>62950</v>
       </c>
       <c r="H132">
-        <v>15483</v>
+        <v>16054</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17263</v>
+        <v>17322</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36573</v>
+        <v>36596</v>
       </c>
       <c r="G135">
-        <v>52665</v>
+        <v>52698</v>
       </c>
       <c r="H135">
-        <v>19310</v>
+        <v>19274</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>27943</v>
+        <v>28045</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46664</v>
+        <v>46705</v>
       </c>
       <c r="G137">
-        <v>67196</v>
+        <v>67255</v>
       </c>
       <c r="H137">
-        <v>18721</v>
+        <v>18660</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>26986</v>
+        <v>26958</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>53913</v>
+        <v>53902</v>
       </c>
       <c r="G139">
-        <v>77635</v>
+        <v>77619</v>
       </c>
       <c r="H139">
-        <v>26927</v>
+        <v>26944</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>57958</v>
+        <v>56202</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>71202</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>102531</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77309</v>
+        <v>77583</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>92309</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>132925</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>86841</v>
+        <v>87139</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>101841</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>146651</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86251</v>
+        <v>86468</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>101251</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>145801</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122403</v>
+        <v>122710</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>137403</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>197860</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38160</v>
+        <v>38288</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62910</v>
+        <v>62961</v>
       </c>
       <c r="G150">
-        <v>90590</v>
+        <v>90664</v>
       </c>
       <c r="H150">
-        <v>24750</v>
+        <v>24673</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>24133</v>
+        <v>23427</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>59133</v>
+        <v>58427</v>
       </c>
       <c r="G152">
-        <v>85152</v>
+        <v>84135</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29553</v>
+        <v>29643</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>53914</v>
+        <v>53950</v>
       </c>
       <c r="G153">
-        <v>77636</v>
+        <v>77688</v>
       </c>
       <c r="H153">
-        <v>24361</v>
+        <v>24307</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48537</v>
+        <v>48707</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20873</v>
+        <v>20703</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>75556</v>
+        <v>76113</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>90556</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>130401</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65226</v>
+        <v>65454</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>80226</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>115525</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>39037</v>
+        <v>39135</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65489</v>
+        <v>65642</v>
       </c>
       <c r="G158">
-        <v>94304</v>
+        <v>94524</v>
       </c>
       <c r="H158">
-        <v>26452</v>
+        <v>26507</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>41890</v>
+        <v>42043</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>56890</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>81922</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>18538</v>
+        <v>18313</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>35068</v>
+        <v>34978</v>
       </c>
       <c r="G161">
-        <v>50498</v>
+        <v>50368</v>
       </c>
       <c r="H161">
-        <v>16530</v>
+        <v>16665</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>55918</v>
+        <v>56106</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>70918</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>102122</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70678</v>
+        <v>70855</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>85678</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>123376</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54180</v>
+        <v>54316</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>69180</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>99619</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33873</v>
+        <v>33989</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>48873</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70377</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,16 +7769,16 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>5196</v>
+        <v>5209</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>40196</v>
+        <v>40209</v>
       </c>
       <c r="G168">
-        <v>57882</v>
+        <v>57901</v>
       </c>
       <c r="H168">
         <v>35000</v>
@@ -7815,19 +7815,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74121</v>
+        <v>74307</v>
       </c>
       <c r="E169">
         <v>74033</v>
       </c>
       <c r="F169">
-        <v>89121</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>128334</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7902,19 +7902,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>15239</v>
+        <v>16076</v>
       </c>
       <c r="E171">
         <v>27751</v>
       </c>
       <c r="F171">
-        <v>30239</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>43544</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7988,19 +7988,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>31386</v>
+        <v>28460</v>
       </c>
       <c r="E173">
         <v>85141</v>
       </c>
       <c r="F173">
-        <v>51760</v>
+        <v>50589</v>
       </c>
       <c r="G173">
-        <v>74534</v>
+        <v>72848</v>
       </c>
       <c r="H173">
-        <v>20374</v>
+        <v>22129</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8032,19 +8032,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>7508</v>
+        <v>7527</v>
       </c>
       <c r="E174">
         <v>55539</v>
       </c>
       <c r="F174">
-        <v>37770</v>
+        <v>37782</v>
       </c>
       <c r="G174">
-        <v>54389</v>
+        <v>54406</v>
       </c>
       <c r="H174">
-        <v>30262</v>
+        <v>30255</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>5276</v>
+        <v>5305</v>
       </c>
       <c r="E175">
         <v>55539</v>
       </c>
       <c r="F175">
-        <v>29770</v>
+        <v>29782</v>
       </c>
       <c r="G175">
-        <v>42869</v>
+        <v>42886</v>
       </c>
       <c r="H175">
-        <v>24494</v>
+        <v>24477</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>10313</v>
+        <v>10211</v>
       </c>
       <c r="E176">
         <v>74033</v>
       </c>
       <c r="F176">
-        <v>42476</v>
+        <v>42495</v>
       </c>
       <c r="G176">
-        <v>61165</v>
+        <v>61193</v>
       </c>
       <c r="H176">
-        <v>32163</v>
+        <v>32284</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8168,16 +8168,16 @@
         <v>17</v>
       </c>
       <c r="D177">
-        <v>7476</v>
+        <v>7495</v>
       </c>
       <c r="E177">
         <v>74033</v>
       </c>
       <c r="F177">
-        <v>34476</v>
+        <v>34495</v>
       </c>
       <c r="G177">
-        <v>49645</v>
+        <v>49673</v>
       </c>
       <c r="H177">
         <v>27000</v>
@@ -8256,19 +8256,19 @@
         <v>17</v>
       </c>
       <c r="D179">
-        <v>21806</v>
+        <v>21381</v>
       </c>
       <c r="E179">
         <v>69424</v>
       </c>
       <c r="F179">
-        <v>41798</v>
+        <v>41628</v>
       </c>
       <c r="G179">
-        <v>60189</v>
+        <v>59944</v>
       </c>
       <c r="H179">
-        <v>19992</v>
+        <v>20247</v>
       </c>
       <c r="I179" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8343,19 +8343,19 @@
         <v>17</v>
       </c>
       <c r="D181">
-        <v>45875</v>
+        <v>46022</v>
       </c>
       <c r="E181">
         <v>104598</v>
       </c>
       <c r="F181">
-        <v>65143</v>
+        <v>65202</v>
       </c>
       <c r="G181">
-        <v>93806</v>
+        <v>93891</v>
       </c>
       <c r="H181">
-        <v>19268</v>
+        <v>19180</v>
       </c>
       <c r="I181" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>67809</v>
+        <v>67915</v>
       </c>
       <c r="E182">
         <v>74033</v>
       </c>
       <c r="F182">
-        <v>86559</v>
+        <v>86520</v>
       </c>
       <c r="G182">
-        <v>124645</v>
+        <v>124589</v>
       </c>
       <c r="H182">
-        <v>18750</v>
+        <v>18605</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8432,16 +8432,16 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>10170</v>
+        <v>10131</v>
       </c>
       <c r="E183">
         <v>74033</v>
       </c>
       <c r="F183">
-        <v>37170</v>
+        <v>37131</v>
       </c>
       <c r="G183">
-        <v>53525</v>
+        <v>53469</v>
       </c>
       <c r="H183">
         <v>27000</v>
@@ -8476,19 +8476,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>60715</v>
+        <v>60868</v>
       </c>
       <c r="E184">
         <v>111059</v>
       </c>
       <c r="F184">
-        <v>80262</v>
+        <v>83294</v>
       </c>
       <c r="G184">
-        <v>115577</v>
+        <v>119943</v>
       </c>
       <c r="H184">
-        <v>19547</v>
+        <v>22426</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8522,19 +8522,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>66573</v>
       </c>
       <c r="E185">
         <v>111059</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>81573</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>117465</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8565,19 +8565,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>80162</v>
+        <v>80363</v>
       </c>
       <c r="E186">
         <v>148085</v>
       </c>
       <c r="F186">
-        <v>110793</v>
+        <v>111028</v>
       </c>
       <c r="G186">
-        <v>159542</v>
+        <v>159880</v>
       </c>
       <c r="H186">
-        <v>30631</v>
+        <v>30665</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8611,19 +8611,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>81342</v>
+        <v>81546</v>
       </c>
       <c r="E187">
         <v>148085</v>
       </c>
       <c r="F187">
-        <v>96342</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>138732</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8738,19 +8738,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>141978</v>
+        <v>142334</v>
       </c>
       <c r="E190">
         <v>157342</v>
       </c>
       <c r="F190">
-        <v>156978</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>226048</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>171754</v>
+        <v>172185</v>
       </c>
       <c r="E192">
         <v>185111</v>
       </c>
       <c r="F192">
-        <v>186754</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>268926</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3787240/MARVEL_Tkon_Fighting_Souls/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8908,7 +8908,7 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>7285</v>
+        <v>7479</v>
       </c>
       <c r="E194">
         <v>53688</v>
@@ -8920,7 +8920,7 @@
         <v>50311</v>
       </c>
       <c r="H194">
-        <v>27653</v>
+        <v>27459</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/493840/Marvel_vs_Capcom_Infinite/","Abrir Steam")</f>
@@ -8995,16 +8995,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>11748</v>
+        <v>11761</v>
       </c>
       <c r="E196">
         <v>83309</v>
       </c>
       <c r="F196">
-        <v>38748</v>
+        <v>38761</v>
       </c>
       <c r="G196">
-        <v>55797</v>
+        <v>55816</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9083,7 +9083,7 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>51598</v>
+        <v>51663</v>
       </c>
       <c r="E198">
         <v>92546</v>
@@ -9095,7 +9095,7 @@
         <v>99950</v>
       </c>
       <c r="H198">
-        <v>17812</v>
+        <v>17747</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9128,19 +9128,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>74743</v>
+        <v>74994</v>
       </c>
       <c r="E199">
         <v>92546</v>
       </c>
       <c r="F199">
-        <v>89743</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>129230</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9172,19 +9172,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>56539</v>
+        <v>56729</v>
       </c>
       <c r="E200">
         <v>92546</v>
       </c>
       <c r="F200">
-        <v>71539</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>103016</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -9259,16 +9259,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>36678</v>
+        <v>36706</v>
       </c>
       <c r="E202">
         <v>111059</v>
       </c>
       <c r="F202">
-        <v>63678</v>
+        <v>63706</v>
       </c>
       <c r="G202">
-        <v>91696</v>
+        <v>91737</v>
       </c>
       <c r="H202">
         <v>27000</v>
@@ -9348,16 +9348,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>27449</v>
+        <v>27486</v>
       </c>
       <c r="E204">
         <v>92546</v>
       </c>
       <c r="F204">
-        <v>54449</v>
+        <v>54486</v>
       </c>
       <c r="G204">
-        <v>78407</v>
+        <v>78460</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9437,19 +9437,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>102000</v>
+        <v>102256</v>
       </c>
       <c r="E206">
         <v>129572</v>
       </c>
       <c r="F206">
-        <v>117159</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>168709</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>15159</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9480,19 +9480,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>62469</v>
+        <v>62498</v>
       </c>
       <c r="E207">
         <v>129572</v>
       </c>
       <c r="F207">
-        <v>81521</v>
+        <v>81532</v>
       </c>
       <c r="G207">
-        <v>117390</v>
+        <v>117406</v>
       </c>
       <c r="H207">
-        <v>19052</v>
+        <v>19034</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9524,16 +9524,16 @@
         <v>15</v>
       </c>
       <c r="D208">
-        <v>145038</v>
+        <v>145402</v>
       </c>
       <c r="E208">
         <v>185111</v>
       </c>
       <c r="F208">
-        <v>180038</v>
+        <v>180402</v>
       </c>
       <c r="G208">
-        <v>259255</v>
+        <v>259779</v>
       </c>
       <c r="H208">
         <v>35000</v>
@@ -9567,19 +9567,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>144098</v>
+        <v>144907</v>
       </c>
       <c r="E209">
         <v>185111</v>
       </c>
       <c r="F209">
-        <v>159098</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>229101</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9611,19 +9611,19 @@
         <v>15</v>
       </c>
       <c r="D210">
-        <v>188076</v>
+        <v>188548</v>
       </c>
       <c r="E210">
         <v>240650</v>
       </c>
       <c r="F210">
-        <v>203076</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>292429</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I210" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9654,19 +9654,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>185685</v>
+        <v>186311</v>
       </c>
       <c r="E211">
         <v>185111</v>
       </c>
       <c r="F211">
-        <v>200685</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>288986</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9698,19 +9698,19 @@
         <v>15</v>
       </c>
       <c r="D212">
-        <v>288498</v>
+        <v>289222</v>
       </c>
       <c r="E212">
         <v>370241</v>
       </c>
       <c r="F212">
-        <v>304371</v>
+        <v>304596</v>
       </c>
       <c r="G212">
-        <v>438294</v>
+        <v>438618</v>
       </c>
       <c r="H212">
-        <v>15873</v>
+        <v>15374</v>
       </c>
       <c r="I212" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9741,19 +9741,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>224451</v>
+        <v>225014</v>
       </c>
       <c r="E213">
         <v>370241</v>
       </c>
       <c r="F213">
-        <v>240175</v>
+        <v>240400</v>
       </c>
       <c r="G213">
-        <v>345852</v>
+        <v>346176</v>
       </c>
       <c r="H213">
-        <v>15724</v>
+        <v>15386</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -9784,19 +9784,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>34558</v>
+        <v>34581</v>
       </c>
       <c r="E214">
         <v>53688</v>
       </c>
       <c r="F214">
-        <v>56251</v>
+        <v>57485</v>
       </c>
       <c r="G214">
-        <v>81001</v>
+        <v>82778</v>
       </c>
       <c r="H214">
-        <v>21693</v>
+        <v>22904</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9829,19 +9829,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>33251</v>
+        <v>34485</v>
       </c>
       <c r="E215">
         <v>53688</v>
       </c>
       <c r="F215">
-        <v>48251</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>69481</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9873,19 +9873,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>16434</v>
+        <v>16475</v>
       </c>
       <c r="E216">
         <v>53688</v>
       </c>
       <c r="F216">
-        <v>36733</v>
+        <v>36750</v>
       </c>
       <c r="G216">
-        <v>52896</v>
+        <v>52920</v>
       </c>
       <c r="H216">
-        <v>20299</v>
+        <v>20275</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9961,19 +9961,19 @@
         <v>15</v>
       </c>
       <c r="D218">
-        <v>16434</v>
+        <v>16475</v>
       </c>
       <c r="E218">
         <v>53688</v>
       </c>
       <c r="F218">
-        <v>36733</v>
+        <v>36750</v>
       </c>
       <c r="G218">
-        <v>52896</v>
+        <v>52920</v>
       </c>
       <c r="H218">
-        <v>20299</v>
+        <v>20275</v>
       </c>
       <c r="I218" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10048,19 +10048,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>12624</v>
+        <v>12640</v>
       </c>
       <c r="E220">
         <v>74033</v>
       </c>
       <c r="F220">
-        <v>44612</v>
+        <v>44636</v>
       </c>
       <c r="G220">
-        <v>64241</v>
+        <v>64276</v>
       </c>
       <c r="H220">
-        <v>31988</v>
+        <v>31996</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10094,16 +10094,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>9612</v>
+        <v>9636</v>
       </c>
       <c r="E221">
         <v>74033</v>
       </c>
       <c r="F221">
-        <v>36612</v>
+        <v>36636</v>
       </c>
       <c r="G221">
-        <v>52721</v>
+        <v>52756</v>
       </c>
       <c r="H221">
         <v>27000</v>
@@ -10137,16 +10137,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>22459</v>
+        <v>22516</v>
       </c>
       <c r="E222">
         <v>111059</v>
       </c>
       <c r="F222">
-        <v>49459</v>
+        <v>49516</v>
       </c>
       <c r="G222">
-        <v>71221</v>
+        <v>71303</v>
       </c>
       <c r="H222">
         <v>27000</v>
@@ -10226,19 +10226,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>17247</v>
+        <v>17402</v>
       </c>
       <c r="E224">
         <v>129572</v>
       </c>
       <c r="F224">
-        <v>46015</v>
+        <v>46186</v>
       </c>
       <c r="G224">
-        <v>66262</v>
+        <v>66508</v>
       </c>
       <c r="H224">
-        <v>28768</v>
+        <v>28784</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -10272,16 +10272,16 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>11015</v>
+        <v>11186</v>
       </c>
       <c r="E225">
         <v>129572</v>
       </c>
       <c r="F225">
-        <v>38015</v>
+        <v>38186</v>
       </c>
       <c r="G225">
-        <v>54742</v>
+        <v>54988</v>
       </c>
       <c r="H225">
         <v>27000</v>
@@ -10316,16 +10316,16 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>26460</v>
+        <v>26479</v>
       </c>
       <c r="E226">
         <v>148085</v>
       </c>
       <c r="F226">
-        <v>61460</v>
+        <v>61479</v>
       </c>
       <c r="G226">
-        <v>88502</v>
+        <v>88530</v>
       </c>
       <c r="H226">
         <v>35000</v>
@@ -10362,16 +10362,16 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>38399</v>
+        <v>38496</v>
       </c>
       <c r="E227">
         <v>148085</v>
       </c>
       <c r="F227">
-        <v>65399</v>
+        <v>65496</v>
       </c>
       <c r="G227">
-        <v>94175</v>
+        <v>94314</v>
       </c>
       <c r="H227">
         <v>27000</v>
@@ -10406,16 +10406,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>36264</v>
+        <v>36546</v>
       </c>
       <c r="E228">
         <v>185111</v>
       </c>
       <c r="F228">
-        <v>71264</v>
+        <v>71546</v>
       </c>
       <c r="G228">
-        <v>102620</v>
+        <v>103026</v>
       </c>
       <c r="H228">
         <v>35000</v>
@@ -10452,16 +10452,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>36152</v>
+        <v>36243</v>
       </c>
       <c r="E229">
         <v>185111</v>
       </c>
       <c r="F229">
-        <v>63152</v>
+        <v>63243</v>
       </c>
       <c r="G229">
-        <v>90939</v>
+        <v>91070</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10495,19 +10495,19 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>15302</v>
+        <v>15373</v>
       </c>
       <c r="E230">
         <v>59223</v>
       </c>
       <c r="F230">
-        <v>42777</v>
+        <v>42870</v>
       </c>
       <c r="G230">
-        <v>61599</v>
+        <v>61733</v>
       </c>
       <c r="H230">
-        <v>27475</v>
+        <v>27497</v>
       </c>
       <c r="I230" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10541,19 +10541,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>9676</v>
+        <v>9908</v>
       </c>
       <c r="E231">
         <v>59223</v>
       </c>
       <c r="F231">
-        <v>32967</v>
+        <v>33060</v>
       </c>
       <c r="G231">
-        <v>47472</v>
+        <v>47606</v>
       </c>
       <c r="H231">
-        <v>23291</v>
+        <v>23152</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10628,19 +10628,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>23448</v>
+        <v>23507</v>
       </c>
       <c r="E233">
         <v>55520</v>
       </c>
       <c r="F233">
-        <v>38448</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>55365</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10714,19 +10714,19 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>41699</v>
+        <v>41804</v>
       </c>
       <c r="E235">
         <v>111059</v>
       </c>
       <c r="F235">
-        <v>65992</v>
+        <v>66034</v>
       </c>
       <c r="G235">
-        <v>95028</v>
+        <v>95089</v>
       </c>
       <c r="H235">
-        <v>24293</v>
+        <v>24230</v>
       </c>
       <c r="I235" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10799,19 +10799,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>86012</v>
+        <v>86228</v>
       </c>
       <c r="E237">
         <v>185111</v>
       </c>
       <c r="F237">
-        <v>112598</v>
+        <v>112684</v>
       </c>
       <c r="G237">
-        <v>162141</v>
+        <v>162265</v>
       </c>
       <c r="H237">
-        <v>26586</v>
+        <v>26456</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10842,19 +10842,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>27927</v>
+        <v>27965</v>
       </c>
       <c r="E238">
         <v>88844</v>
       </c>
       <c r="F238">
-        <v>61428</v>
+        <v>61460</v>
       </c>
       <c r="G238">
-        <v>88456</v>
+        <v>88502</v>
       </c>
       <c r="H238">
-        <v>33501</v>
+        <v>33495</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10888,19 +10888,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>31896</v>
+        <v>31976</v>
       </c>
       <c r="E239">
         <v>88844</v>
       </c>
       <c r="F239">
-        <v>53408</v>
+        <v>53440</v>
       </c>
       <c r="G239">
-        <v>76908</v>
+        <v>76954</v>
       </c>
       <c r="H239">
-        <v>21512</v>
+        <v>21464</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10931,7 +10931,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>46848</v>
+        <v>46997</v>
       </c>
       <c r="E240">
         <v>103654</v>
@@ -10943,7 +10943,7 @@
         <v>111947</v>
       </c>
       <c r="H240">
-        <v>30893</v>
+        <v>30744</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10977,19 +10977,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>84386</v>
+        <v>84598</v>
       </c>
       <c r="E241">
         <v>103654</v>
       </c>
       <c r="F241">
-        <v>99386</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>143116</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11066,19 +11066,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>110241</v>
+        <v>110518</v>
       </c>
       <c r="E243">
         <v>133275</v>
       </c>
       <c r="F243">
-        <v>125241</v>
+        <v>0</v>
       </c>
       <c r="G243">
-        <v>180347</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -11109,19 +11109,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>64127</v>
+        <v>64192</v>
       </c>
       <c r="E244">
         <v>83309</v>
       </c>
       <c r="F244">
-        <v>79388</v>
+        <v>79500</v>
       </c>
       <c r="G244">
-        <v>114319</v>
+        <v>114480</v>
       </c>
       <c r="H244">
-        <v>15261</v>
+        <v>15308</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11155,19 +11155,19 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>44584</v>
+        <v>44696</v>
       </c>
       <c r="E245">
         <v>83309</v>
       </c>
       <c r="F245">
-        <v>59584</v>
+        <v>0</v>
       </c>
       <c r="G245">
-        <v>85801</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I245" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11199,19 +11199,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>75858</v>
+        <v>76049</v>
       </c>
       <c r="E246">
         <v>98119</v>
       </c>
       <c r="F246">
-        <v>108923</v>
+        <v>109153</v>
       </c>
       <c r="G246">
-        <v>156849</v>
+        <v>157180</v>
       </c>
       <c r="H246">
-        <v>33065</v>
+        <v>33104</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11245,19 +11245,19 @@
         <v>17</v>
       </c>
       <c r="D247">
-        <v>79716</v>
+        <v>79916</v>
       </c>
       <c r="E247">
         <v>98119</v>
       </c>
       <c r="F247">
-        <v>94716</v>
+        <v>0</v>
       </c>
       <c r="G247">
-        <v>136391</v>
+        <v>0</v>
       </c>
       <c r="H247">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I247" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -11289,19 +11289,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>16833</v>
+        <v>16891</v>
       </c>
       <c r="E248">
         <v>61074</v>
       </c>
       <c r="F248">
-        <v>42492</v>
+        <v>42510</v>
       </c>
       <c r="G248">
-        <v>61188</v>
+        <v>61214</v>
       </c>
       <c r="H248">
-        <v>25659</v>
+        <v>25619</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11335,19 +11335,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>11684</v>
+        <v>11729</v>
       </c>
       <c r="E249">
         <v>61074</v>
       </c>
       <c r="F249">
-        <v>34492</v>
+        <v>34510</v>
       </c>
       <c r="G249">
-        <v>49668</v>
+        <v>49694</v>
       </c>
       <c r="H249">
-        <v>22808</v>
+        <v>22781</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11379,19 +11379,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>31115</v>
+        <v>31193</v>
       </c>
       <c r="E250">
         <v>74033</v>
       </c>
       <c r="F250">
-        <v>51761</v>
+        <v>51792</v>
       </c>
       <c r="G250">
-        <v>74536</v>
+        <v>74580</v>
       </c>
       <c r="H250">
-        <v>20646</v>
+        <v>20599</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -11511,16 +11511,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>16482</v>
+        <v>16523</v>
       </c>
       <c r="E253">
         <v>111059</v>
       </c>
       <c r="F253">
-        <v>43482</v>
+        <v>43523</v>
       </c>
       <c r="G253">
-        <v>62614</v>
+        <v>62673</v>
       </c>
       <c r="H253">
         <v>27000</v>
@@ -11596,16 +11596,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>22970</v>
+        <v>23027</v>
       </c>
       <c r="E255">
         <v>185111</v>
       </c>
       <c r="F255">
-        <v>49970</v>
+        <v>50027</v>
       </c>
       <c r="G255">
-        <v>71957</v>
+        <v>72039</v>
       </c>
       <c r="H255">
         <v>27000</v>
@@ -11639,7 +11639,7 @@
         <v>15</v>
       </c>
       <c r="D256">
-        <v>9612</v>
+        <v>9620</v>
       </c>
       <c r="E256">
         <v>53688</v>
@@ -11651,7 +11651,7 @@
         <v>57983</v>
       </c>
       <c r="H256">
-        <v>30654</v>
+        <v>30646</v>
       </c>
       <c r="I256" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11684,19 +11684,19 @@
         <v>17</v>
       </c>
       <c r="D257">
-        <v>14888</v>
+        <v>14925</v>
       </c>
       <c r="E257">
         <v>53688</v>
       </c>
       <c r="F257">
-        <v>32893</v>
+        <v>32908</v>
       </c>
       <c r="G257">
-        <v>47366</v>
+        <v>47388</v>
       </c>
       <c r="H257">
-        <v>18005</v>
+        <v>17983</v>
       </c>
       <c r="I257" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11727,16 +11727,16 @@
         <v>15</v>
       </c>
       <c r="D258">
-        <v>12322</v>
+        <v>12321</v>
       </c>
       <c r="E258">
         <v>72201</v>
       </c>
       <c r="F258">
-        <v>39322</v>
+        <v>39321</v>
       </c>
       <c r="G258">
-        <v>56624</v>
+        <v>56622</v>
       </c>
       <c r="H258">
         <v>27000</v>
@@ -11814,19 +11814,19 @@
         <v>15</v>
       </c>
       <c r="D260">
-        <v>8847</v>
+        <v>8853</v>
       </c>
       <c r="E260">
         <v>53688</v>
       </c>
       <c r="F260">
-        <v>39325</v>
+        <v>40266</v>
       </c>
       <c r="G260">
-        <v>56628</v>
+        <v>57983</v>
       </c>
       <c r="H260">
-        <v>30478</v>
+        <v>31413</v>
       </c>
       <c r="I260" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11859,19 +11859,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>10967</v>
+        <v>16619</v>
       </c>
       <c r="E261">
         <v>53688</v>
       </c>
       <c r="F261">
-        <v>31325</v>
+        <v>0</v>
       </c>
       <c r="G261">
-        <v>45108</v>
+        <v>0</v>
       </c>
       <c r="H261">
-        <v>20358</v>
+        <v>0</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11903,19 +11903,19 @@
         <v>15</v>
       </c>
       <c r="D262">
-        <v>12465</v>
+        <v>12656</v>
       </c>
       <c r="E262">
         <v>53688</v>
       </c>
       <c r="F262">
-        <v>39127</v>
+        <v>39138</v>
       </c>
       <c r="G262">
-        <v>56343</v>
+        <v>56359</v>
       </c>
       <c r="H262">
-        <v>26662</v>
+        <v>26482</v>
       </c>
       <c r="I262" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>10473</v>
+        <v>10499</v>
       </c>
       <c r="E263">
         <v>53688</v>
       </c>
       <c r="F263">
-        <v>31127</v>
+        <v>31138</v>
       </c>
       <c r="G263">
-        <v>44823</v>
+        <v>44839</v>
       </c>
       <c r="H263">
-        <v>20654</v>
+        <v>20639</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11991,19 +11991,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>19670</v>
+        <v>19576</v>
       </c>
       <c r="E264">
         <v>72201</v>
       </c>
       <c r="F264">
-        <v>51837</v>
+        <v>51862</v>
       </c>
       <c r="G264">
-        <v>74645</v>
+        <v>74681</v>
       </c>
       <c r="H264">
-        <v>32167</v>
+        <v>32286</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12035,19 +12035,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24197</v>
+        <v>24258</v>
       </c>
       <c r="E265">
         <v>72201</v>
       </c>
       <c r="F265">
-        <v>43837</v>
+        <v>43862</v>
       </c>
       <c r="G265">
-        <v>63125</v>
+        <v>63161</v>
       </c>
       <c r="H265">
-        <v>19640</v>
+        <v>19604</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -12078,7 +12078,7 @@
         <v>15</v>
       </c>
       <c r="D266">
-        <v>34335</v>
+        <v>34357</v>
       </c>
       <c r="E266">
         <v>72201</v>
@@ -12090,7 +12090,7 @@
         <v>77977</v>
       </c>
       <c r="H266">
-        <v>19816</v>
+        <v>19794</v>
       </c>
       <c r="I266" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12123,19 +12123,19 @@
         <v>17</v>
       </c>
       <c r="D267">
-        <v>30955</v>
+        <v>31033</v>
       </c>
       <c r="E267">
         <v>72201</v>
       </c>
       <c r="F267">
-        <v>46541</v>
+        <v>46572</v>
       </c>
       <c r="G267">
-        <v>67019</v>
+        <v>67064</v>
       </c>
       <c r="H267">
-        <v>15586</v>
+        <v>15539</v>
       </c>
       <c r="I267" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12166,19 +12166,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>10202</v>
+        <v>10179</v>
       </c>
       <c r="E268">
         <v>27770</v>
       </c>
       <c r="F268">
-        <v>39546</v>
+        <v>39587</v>
       </c>
       <c r="G268">
-        <v>56946</v>
+        <v>57005</v>
       </c>
       <c r="H268">
-        <v>29344</v>
+        <v>29408</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12211,19 +12211,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>16546</v>
+        <v>16587</v>
       </c>
       <c r="E269">
         <v>27770</v>
       </c>
       <c r="F269">
-        <v>31546</v>
+        <v>0</v>
       </c>
       <c r="G269">
-        <v>45426</v>
+        <v>0</v>
       </c>
       <c r="H269">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -12254,16 +12254,16 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>12162</v>
+        <v>12161</v>
       </c>
       <c r="E270">
         <v>83309</v>
       </c>
       <c r="F270">
-        <v>39162</v>
+        <v>39161</v>
       </c>
       <c r="G270">
-        <v>56393</v>
+        <v>56392</v>
       </c>
       <c r="H270">
         <v>27000</v>
@@ -12341,16 +12341,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62867</v>
+        <v>62722</v>
       </c>
       <c r="E272">
         <v>98119</v>
       </c>
       <c r="F272">
-        <v>77867</v>
+        <v>77722</v>
       </c>
       <c r="G272">
-        <v>112128</v>
+        <v>111920</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12387,19 +12387,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>40376</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>98119</v>
       </c>
       <c r="F273">
-        <v>60417</v>
+        <v>0</v>
       </c>
       <c r="G273">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>20041</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12430,19 +12430,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>74583</v>
+        <v>74339</v>
       </c>
       <c r="E274">
         <v>111059</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>106911</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>153952</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>32572</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12476,19 +12476,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>77771</v>
+        <v>77966</v>
       </c>
       <c r="E275">
         <v>111059</v>
       </c>
       <c r="F275">
-        <v>92771</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>133590</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -12519,19 +12519,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>11158</v>
+        <v>11170</v>
       </c>
       <c r="E276">
         <v>53688</v>
       </c>
       <c r="F276">
-        <v>37769</v>
+        <v>37776</v>
       </c>
       <c r="G276">
-        <v>54387</v>
+        <v>54397</v>
       </c>
       <c r="H276">
-        <v>26611</v>
+        <v>26606</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12565,19 +12565,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>7077</v>
+        <v>7095</v>
       </c>
       <c r="E277">
         <v>53688</v>
       </c>
       <c r="F277">
-        <v>29769</v>
+        <v>29776</v>
       </c>
       <c r="G277">
-        <v>42867</v>
+        <v>42877</v>
       </c>
       <c r="H277">
-        <v>22692</v>
+        <v>22681</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12608,19 +12608,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>20148</v>
+        <v>20055</v>
       </c>
       <c r="E278">
         <v>72201</v>
       </c>
       <c r="F278">
-        <v>51837</v>
+        <v>46513</v>
       </c>
       <c r="G278">
-        <v>74645</v>
+        <v>66979</v>
       </c>
       <c r="H278">
-        <v>31689</v>
+        <v>26458</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12654,19 +12654,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>24197</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>72201</v>
       </c>
       <c r="F279">
-        <v>43837</v>
+        <v>0</v>
       </c>
       <c r="G279">
-        <v>63125</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>19640</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -12697,7 +12697,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>11700</v>
+        <v>11745</v>
       </c>
       <c r="E280">
         <v>53688</v>
@@ -12709,7 +12709,7 @@
         <v>50311</v>
       </c>
       <c r="H280">
-        <v>23238</v>
+        <v>23193</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12826,19 +12826,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>17662</v>
+        <v>17722</v>
       </c>
       <c r="E283">
         <v>44413</v>
       </c>
       <c r="F283">
-        <v>32662</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>47033</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12912,19 +12912,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>20818</v>
+        <v>17946</v>
       </c>
       <c r="E285">
         <v>55520</v>
       </c>
       <c r="F285">
-        <v>35980</v>
+        <v>34831</v>
       </c>
       <c r="G285">
-        <v>51811</v>
+        <v>50157</v>
       </c>
       <c r="H285">
-        <v>15162</v>
+        <v>16885</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -12998,19 +12998,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>24197</v>
+        <v>21062</v>
       </c>
       <c r="E287">
         <v>66628</v>
       </c>
       <c r="F287">
-        <v>41664</v>
+        <v>40410</v>
       </c>
       <c r="G287">
-        <v>59996</v>
+        <v>58190</v>
       </c>
       <c r="H287">
-        <v>17467</v>
+        <v>19348</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -13042,19 +13042,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>33617</v>
+        <v>33702</v>
       </c>
       <c r="E288">
         <v>61074</v>
       </c>
       <c r="F288">
-        <v>55732</v>
+        <v>55769</v>
       </c>
       <c r="G288">
-        <v>80254</v>
+        <v>80307</v>
       </c>
       <c r="H288">
-        <v>22115</v>
+        <v>22067</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13088,19 +13088,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>23639</v>
+        <v>23730</v>
       </c>
       <c r="E289">
         <v>61074</v>
       </c>
       <c r="F289">
-        <v>39274</v>
+        <v>39311</v>
       </c>
       <c r="G289">
-        <v>56555</v>
+        <v>56608</v>
       </c>
       <c r="H289">
-        <v>15635</v>
+        <v>15581</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -13221,19 +13221,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>44616</v>
+        <v>44664</v>
       </c>
       <c r="E292">
         <v>61074</v>
       </c>
       <c r="F292">
-        <v>61992</v>
+        <v>61983</v>
       </c>
       <c r="G292">
-        <v>89268</v>
+        <v>89256</v>
       </c>
       <c r="H292">
-        <v>17376</v>
+        <v>17319</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13266,19 +13266,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>23272</v>
+        <v>23251</v>
       </c>
       <c r="E293">
         <v>61074</v>
       </c>
       <c r="F293">
-        <v>39128</v>
+        <v>39119</v>
       </c>
       <c r="G293">
-        <v>56344</v>
+        <v>56331</v>
       </c>
       <c r="H293">
-        <v>15856</v>
+        <v>15868</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13355,19 +13355,19 @@
         <v>17</v>
       </c>
       <c r="D295">
-        <v>23639</v>
+        <v>23698</v>
       </c>
       <c r="E295">
         <v>68480</v>
       </c>
       <c r="F295">
-        <v>42163</v>
+        <v>42186</v>
       </c>
       <c r="G295">
-        <v>60715</v>
+        <v>60748</v>
       </c>
       <c r="H295">
-        <v>18524</v>
+        <v>18488</v>
       </c>
       <c r="I295" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -13399,19 +13399,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>62788</v>
+        <v>62945</v>
       </c>
       <c r="E296">
         <v>78662</v>
       </c>
       <c r="F296">
-        <v>77788</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>112015</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13486,19 +13486,19 @@
         <v>15</v>
       </c>
       <c r="D298">
-        <v>73627</v>
+        <v>73812</v>
       </c>
       <c r="E298">
         <v>94398</v>
       </c>
       <c r="F298">
-        <v>88627</v>
+        <v>0</v>
       </c>
       <c r="G298">
-        <v>127623</v>
+        <v>0</v>
       </c>
       <c r="H298">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I298" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1636440/SILENT_HILL_Townfall/","Abrir Steam")</f>
@@ -13572,19 +13572,19 @@
         <v>15</v>
       </c>
       <c r="D300">
-        <v>70264</v>
+        <v>70328</v>
       </c>
       <c r="E300">
         <v>92546</v>
       </c>
       <c r="F300">
-        <v>88447</v>
+        <v>88468</v>
       </c>
       <c r="G300">
-        <v>127364</v>
+        <v>127394</v>
       </c>
       <c r="H300">
-        <v>18183</v>
+        <v>18140</v>
       </c>
       <c r="I300" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13617,19 +13617,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>33713</v>
+        <v>33766</v>
       </c>
       <c r="E301">
         <v>92546</v>
       </c>
       <c r="F301">
-        <v>55578</v>
+        <v>55599</v>
       </c>
       <c r="G301">
-        <v>80032</v>
+        <v>80063</v>
       </c>
       <c r="H301">
-        <v>21865</v>
+        <v>21833</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13704,16 +13704,16 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>10935</v>
+        <v>11554</v>
       </c>
       <c r="E303">
         <v>129572</v>
       </c>
       <c r="F303">
-        <v>37935</v>
+        <v>38554</v>
       </c>
       <c r="G303">
-        <v>54626</v>
+        <v>55518</v>
       </c>
       <c r="H303">
         <v>27000</v>
@@ -13792,16 +13792,16 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>25600</v>
+        <v>25664</v>
       </c>
       <c r="E305">
         <v>166598</v>
       </c>
       <c r="F305">
-        <v>52600</v>
+        <v>52664</v>
       </c>
       <c r="G305">
-        <v>75744</v>
+        <v>75836</v>
       </c>
       <c r="H305">
         <v>27000</v>
@@ -13835,19 +13835,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>52076</v>
+        <v>52207</v>
       </c>
       <c r="E306">
         <v>111059</v>
       </c>
       <c r="F306">
-        <v>79901</v>
+        <v>79964</v>
       </c>
       <c r="G306">
-        <v>115057</v>
+        <v>115148</v>
       </c>
       <c r="H306">
-        <v>27825</v>
+        <v>27757</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13881,19 +13881,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>50275</v>
+        <v>50433</v>
       </c>
       <c r="E307">
         <v>111059</v>
       </c>
       <c r="F307">
-        <v>69423</v>
+        <v>69486</v>
       </c>
       <c r="G307">
-        <v>99969</v>
+        <v>100060</v>
       </c>
       <c r="H307">
-        <v>19148</v>
+        <v>19053</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13924,7 +13924,7 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>69132</v>
+        <v>69193</v>
       </c>
       <c r="E308">
         <v>129572</v>
@@ -13936,7 +13936,7 @@
         <v>139938</v>
       </c>
       <c r="H308">
-        <v>28047</v>
+        <v>27986</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -13970,19 +13970,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>77867</v>
+        <v>105836</v>
       </c>
       <c r="E309">
         <v>129572</v>
       </c>
       <c r="F309">
-        <v>92867</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>133728</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -14014,7 +14014,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>24245</v>
+        <v>24561</v>
       </c>
       <c r="E310">
         <v>55520</v>
@@ -14026,7 +14026,7 @@
         <v>59962</v>
       </c>
       <c r="H310">
-        <v>17395</v>
+        <v>17079</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14058,19 +14058,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>37459</v>
+        <v>37553</v>
       </c>
       <c r="E311">
         <v>55520</v>
       </c>
       <c r="F311">
-        <v>52459</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>75541</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14101,19 +14101,19 @@
         <v>15</v>
       </c>
       <c r="D312">
-        <v>66454</v>
+        <v>66653</v>
       </c>
       <c r="E312">
         <v>83309</v>
       </c>
       <c r="F312">
-        <v>90194</v>
+        <v>90353</v>
       </c>
       <c r="G312">
-        <v>129879</v>
+        <v>130108</v>
       </c>
       <c r="H312">
-        <v>23740</v>
+        <v>23700</v>
       </c>
       <c r="I312" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14146,19 +14146,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>63393</v>
+        <v>63552</v>
       </c>
       <c r="E313">
         <v>83309</v>
       </c>
       <c r="F313">
-        <v>78393</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>112886</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -14232,19 +14232,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>22316</v>
+        <v>22196</v>
       </c>
       <c r="E315">
         <v>38859</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>37196</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>53562</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -14276,19 +14276,19 @@
         <v>15</v>
       </c>
       <c r="D316">
-        <v>32502</v>
+        <v>32583</v>
       </c>
       <c r="E316">
         <v>59223</v>
       </c>
       <c r="F316">
-        <v>49604</v>
+        <v>62788</v>
       </c>
       <c r="G316">
-        <v>71430</v>
+        <v>90415</v>
       </c>
       <c r="H316">
-        <v>17102</v>
+        <v>30205</v>
       </c>
       <c r="I316" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14322,19 +14322,19 @@
         <v>17</v>
       </c>
       <c r="D317">
-        <v>26604</v>
+        <v>39598</v>
       </c>
       <c r="E317">
         <v>59223</v>
       </c>
       <c r="F317">
-        <v>41604</v>
+        <v>0</v>
       </c>
       <c r="G317">
-        <v>59910</v>
+        <v>0</v>
       </c>
       <c r="H317">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I317" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14366,7 +14366,7 @@
         <v>15</v>
       </c>
       <c r="D318">
-        <v>12083</v>
+        <v>12113</v>
       </c>
       <c r="E318">
         <v>44413</v>
@@ -14378,7 +14378,7 @@
         <v>47966</v>
       </c>
       <c r="H318">
-        <v>21227</v>
+        <v>21197</v>
       </c>
       <c r="I318" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14412,19 +14412,19 @@
         <v>17</v>
       </c>
       <c r="D319">
-        <v>29330</v>
+        <v>29435</v>
       </c>
       <c r="E319">
         <v>44413</v>
       </c>
       <c r="F319">
-        <v>44330</v>
+        <v>0</v>
       </c>
       <c r="G319">
-        <v>63835</v>
+        <v>0</v>
       </c>
       <c r="H319">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I319" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -14456,19 +14456,19 @@
         <v>15</v>
       </c>
       <c r="D320">
-        <v>50498</v>
+        <v>50625</v>
       </c>
       <c r="E320">
         <v>111059</v>
       </c>
       <c r="F320">
-        <v>76176</v>
+        <v>76226</v>
       </c>
       <c r="G320">
-        <v>109693</v>
+        <v>109765</v>
       </c>
       <c r="H320">
-        <v>25678</v>
+        <v>25601</v>
       </c>
       <c r="I320" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14502,19 +14502,19 @@
         <v>17</v>
       </c>
       <c r="D321">
-        <v>38336</v>
+        <v>38432</v>
       </c>
       <c r="E321">
         <v>111059</v>
       </c>
       <c r="F321">
-        <v>64647</v>
+        <v>64686</v>
       </c>
       <c r="G321">
-        <v>93092</v>
+        <v>93148</v>
       </c>
       <c r="H321">
-        <v>26311</v>
+        <v>26254</v>
       </c>
       <c r="I321" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -14632,19 +14632,19 @@
         <v>15</v>
       </c>
       <c r="D324">
-        <v>59153</v>
+        <v>0</v>
       </c>
       <c r="E324">
         <v>74033</v>
       </c>
       <c r="F324">
-        <v>90812</v>
+        <v>0</v>
       </c>
       <c r="G324">
-        <v>130769</v>
+        <v>0</v>
       </c>
       <c r="H324">
-        <v>31659</v>
+        <v>0</v>
       </c>
       <c r="I324" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14678,19 +14678,19 @@
         <v>17</v>
       </c>
       <c r="D325">
-        <v>63967</v>
+        <v>0</v>
       </c>
       <c r="E325">
         <v>74033</v>
       </c>
       <c r="F325">
-        <v>78967</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>113712</v>
+        <v>0</v>
       </c>
       <c r="H325">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I325" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -14763,19 +14763,19 @@
         <v>17</v>
       </c>
       <c r="D327">
-        <v>9405</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>64777</v>
       </c>
       <c r="F327">
-        <v>35025</v>
+        <v>0</v>
       </c>
       <c r="G327">
-        <v>50436</v>
+        <v>0</v>
       </c>
       <c r="H327">
-        <v>25620</v>
+        <v>0</v>
       </c>
       <c r="I327" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14848,19 +14848,19 @@
         <v>17</v>
       </c>
       <c r="D329">
-        <v>17040</v>
+        <v>17083</v>
       </c>
       <c r="E329">
         <v>64777</v>
       </c>
       <c r="F329">
-        <v>38079</v>
+        <v>38096</v>
       </c>
       <c r="G329">
-        <v>54834</v>
+        <v>54858</v>
       </c>
       <c r="H329">
-        <v>21039</v>
+        <v>21013</v>
       </c>
       <c r="I329" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -14891,16 +14891,16 @@
         <v>15</v>
       </c>
       <c r="D330">
-        <v>21949</v>
+        <v>22084</v>
       </c>
       <c r="E330">
         <v>92546</v>
       </c>
       <c r="F330">
-        <v>48949</v>
+        <v>49084</v>
       </c>
       <c r="G330">
-        <v>70487</v>
+        <v>70681</v>
       </c>
       <c r="H330">
         <v>27000</v>
@@ -14979,16 +14979,16 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>43628</v>
+        <v>43673</v>
       </c>
       <c r="E332">
         <v>111059</v>
       </c>
       <c r="F332">
-        <v>78628</v>
+        <v>78673</v>
       </c>
       <c r="G332">
-        <v>113224</v>
+        <v>113289</v>
       </c>
       <c r="H332">
         <v>35000</v>
@@ -15024,19 +15024,19 @@
         <v>17</v>
       </c>
       <c r="D333">
-        <v>83302</v>
+        <v>83511</v>
       </c>
       <c r="E333">
         <v>111059</v>
       </c>
       <c r="F333">
-        <v>98302</v>
+        <v>0</v>
       </c>
       <c r="G333">
-        <v>141555</v>
+        <v>0</v>
       </c>
       <c r="H333">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I333" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -15067,16 +15067,16 @@
         <v>15</v>
       </c>
       <c r="D334">
-        <v>32581</v>
+        <v>32695</v>
       </c>
       <c r="E334">
         <v>111059</v>
       </c>
       <c r="F334">
-        <v>67581</v>
+        <v>67695</v>
       </c>
       <c r="G334">
-        <v>97317</v>
+        <v>97481</v>
       </c>
       <c r="H334">
         <v>35000</v>
@@ -15112,19 +15112,19 @@
         <v>17</v>
       </c>
       <c r="D335">
-        <v>49414</v>
+        <v>49538</v>
       </c>
       <c r="E335">
         <v>111059</v>
       </c>
       <c r="F335">
-        <v>69078</v>
+        <v>69128</v>
       </c>
       <c r="G335">
-        <v>99472</v>
+        <v>99544</v>
       </c>
       <c r="H335">
-        <v>19664</v>
+        <v>19590</v>
       </c>
       <c r="I335" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15155,19 +15155,19 @@
         <v>15</v>
       </c>
       <c r="D336">
-        <v>188761</v>
+        <v>189491</v>
       </c>
       <c r="E336">
         <v>240650</v>
       </c>
       <c r="F336">
-        <v>204469</v>
+        <v>0</v>
       </c>
       <c r="G336">
-        <v>294435</v>
+        <v>0</v>
       </c>
       <c r="H336">
-        <v>15708</v>
+        <v>0</v>
       </c>
       <c r="I336" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15199,19 +15199,19 @@
         <v>17</v>
       </c>
       <c r="D337">
-        <v>144353</v>
+        <v>144715</v>
       </c>
       <c r="E337">
         <v>240650</v>
       </c>
       <c r="F337">
-        <v>159353</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>229468</v>
+        <v>0</v>
       </c>
       <c r="H337">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I337" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -15243,19 +15243,19 @@
         <v>15</v>
       </c>
       <c r="D338">
-        <v>57623</v>
+        <v>61395</v>
       </c>
       <c r="E338">
         <v>129572</v>
       </c>
       <c r="F338">
-        <v>89259</v>
+        <v>89364</v>
       </c>
       <c r="G338">
-        <v>128533</v>
+        <v>128684</v>
       </c>
       <c r="H338">
-        <v>31636</v>
+        <v>27969</v>
       </c>
       <c r="I338" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15287,16 +15287,16 @@
         <v>17</v>
       </c>
       <c r="D339">
-        <v>41890</v>
+        <v>41995</v>
       </c>
       <c r="E339">
         <v>129572</v>
       </c>
       <c r="F339">
-        <v>68890</v>
+        <v>68995</v>
       </c>
       <c r="G339">
-        <v>99202</v>
+        <v>99353</v>
       </c>
       <c r="H339">
         <v>27000</v>
@@ -15372,19 +15372,19 @@
         <v>17</v>
       </c>
       <c r="D341">
-        <v>109986</v>
+        <v>110262</v>
       </c>
       <c r="E341">
         <v>185111</v>
       </c>
       <c r="F341">
-        <v>124986</v>
+        <v>0</v>
       </c>
       <c r="G341">
-        <v>179980</v>
+        <v>0</v>
       </c>
       <c r="H341">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I341" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -15415,16 +15415,16 @@
         <v>15</v>
       </c>
       <c r="D342">
-        <v>104056</v>
+        <v>104317</v>
       </c>
       <c r="E342">
         <v>240650</v>
       </c>
       <c r="F342">
-        <v>139056</v>
+        <v>139317</v>
       </c>
       <c r="G342">
-        <v>200241</v>
+        <v>200616</v>
       </c>
       <c r="H342">
         <v>35000</v>
@@ -15458,19 +15458,19 @@
         <v>17</v>
       </c>
       <c r="D343">
-        <v>144369</v>
+        <v>144731</v>
       </c>
       <c r="E343">
         <v>240650</v>
       </c>
       <c r="F343">
-        <v>159369</v>
+        <v>0</v>
       </c>
       <c r="G343">
-        <v>229491</v>
+        <v>0</v>
       </c>
       <c r="H343">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I343" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -502,19 +502,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71015</v>
+        <v>70582</v>
       </c>
       <c r="E2">
         <v>74033</v>
       </c>
       <c r="F2">
-        <v>86015</v>
+        <v>88005</v>
       </c>
       <c r="G2">
-        <v>123862</v>
+        <v>126727</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>17423</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -548,19 +548,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>45543</v>
+        <v>47533</v>
       </c>
       <c r="E3">
         <v>74033</v>
       </c>
       <c r="F3">
-        <v>60543</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>87182</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -592,19 +592,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>94538</v>
+        <v>93934</v>
       </c>
       <c r="E4">
         <v>85141</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>108934</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>156865</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -638,19 +638,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>67579</v>
+        <v>70965</v>
       </c>
       <c r="E5">
         <v>85141</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>85965</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>123790</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -724,19 +724,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>7159</v>
+        <v>8082</v>
       </c>
       <c r="E7">
         <v>55520</v>
       </c>
       <c r="F7">
-        <v>30516</v>
+        <v>30886</v>
       </c>
       <c r="G7">
-        <v>43943</v>
+        <v>44476</v>
       </c>
       <c r="H7">
-        <v>23357</v>
+        <v>22804</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -768,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>39503</v>
+        <v>37921</v>
       </c>
       <c r="E8">
         <v>74033</v>
       </c>
       <c r="F8">
-        <v>55525</v>
+        <v>54483</v>
       </c>
       <c r="G8">
-        <v>79956</v>
+        <v>78456</v>
       </c>
       <c r="H8">
-        <v>16022</v>
+        <v>16562</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -814,19 +814,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>39662</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>74033</v>
       </c>
       <c r="F9">
-        <v>54662</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>78713</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -857,19 +857,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>56553</v>
+        <v>56412</v>
       </c>
       <c r="E10">
         <v>111059</v>
       </c>
       <c r="F10">
-        <v>78598</v>
+        <v>78541</v>
       </c>
       <c r="G10">
-        <v>113181</v>
+        <v>113099</v>
       </c>
       <c r="H10">
-        <v>22045</v>
+        <v>22129</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -903,19 +903,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>75090</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>111059</v>
       </c>
       <c r="F11">
-        <v>90090</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>129730</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -946,19 +946,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>84646</v>
+        <v>84339</v>
       </c>
       <c r="E12">
         <v>83290</v>
       </c>
       <c r="F12">
-        <v>101020</v>
+        <v>101419</v>
       </c>
       <c r="G12">
-        <v>145469</v>
+        <v>146043</v>
       </c>
       <c r="H12">
-        <v>16374</v>
+        <v>17080</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -991,16 +991,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>12672</v>
+        <v>13071</v>
       </c>
       <c r="E13">
         <v>83290</v>
       </c>
       <c r="F13">
-        <v>39672</v>
+        <v>40071</v>
       </c>
       <c r="G13">
-        <v>57128</v>
+        <v>57702</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>26303</v>
+        <v>26205</v>
       </c>
       <c r="E15">
         <v>74033</v>
       </c>
       <c r="F15">
-        <v>45394</v>
+        <v>45355</v>
       </c>
       <c r="G15">
-        <v>65367</v>
+        <v>65311</v>
       </c>
       <c r="H15">
-        <v>19091</v>
+        <v>19150</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1336,16 +1336,16 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>54428</v>
+        <v>54228</v>
       </c>
       <c r="E21">
         <v>103654</v>
       </c>
       <c r="F21">
-        <v>69428</v>
+        <v>69228</v>
       </c>
       <c r="G21">
-        <v>99976</v>
+        <v>99688</v>
       </c>
       <c r="H21">
         <v>15000</v>
@@ -1425,7 +1425,7 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>96280</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>133275</v>
@@ -1596,19 +1596,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>24034</v>
+        <v>23958</v>
       </c>
       <c r="E27">
         <v>64777</v>
       </c>
       <c r="F27">
-        <v>40877</v>
+        <v>40846</v>
       </c>
       <c r="G27">
-        <v>58863</v>
+        <v>58818</v>
       </c>
       <c r="H27">
-        <v>16843</v>
+        <v>16888</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1640,19 +1640,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75697</v>
+        <v>75301</v>
       </c>
       <c r="E28">
         <v>129572</v>
       </c>
       <c r="F28">
-        <v>94586</v>
+        <v>97179</v>
       </c>
       <c r="G28">
-        <v>136204</v>
+        <v>139938</v>
       </c>
       <c r="H28">
-        <v>18889</v>
+        <v>21878</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1686,16 +1686,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>30010</v>
+        <v>36630</v>
       </c>
       <c r="E29">
         <v>129572</v>
       </c>
       <c r="F29">
-        <v>57010</v>
+        <v>63630</v>
       </c>
       <c r="G29">
-        <v>82094</v>
+        <v>91627</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1730,19 +1730,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>122407</v>
+        <v>118562</v>
       </c>
       <c r="E30">
         <v>185111</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>136725</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>196884</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>18163</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1776,19 +1776,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>72565</v>
+        <v>96676</v>
       </c>
       <c r="E31">
         <v>185111</v>
       </c>
       <c r="F31">
-        <v>99565</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>143374</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1820,19 +1820,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>60868</v>
+        <v>60715</v>
       </c>
       <c r="E32">
         <v>111059</v>
       </c>
       <c r="F32">
-        <v>80838</v>
+        <v>80715</v>
       </c>
       <c r="G32">
-        <v>116407</v>
+        <v>116230</v>
       </c>
       <c r="H32">
-        <v>19970</v>
+        <v>20000</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1866,16 +1866,16 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>36307</v>
+        <v>36184</v>
       </c>
       <c r="E33">
         <v>111059</v>
       </c>
       <c r="F33">
-        <v>63307</v>
+        <v>63184</v>
       </c>
       <c r="G33">
-        <v>91162</v>
+        <v>90985</v>
       </c>
       <c r="H33">
         <v>27000</v>
@@ -1956,7 +1956,7 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>84071</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>129572</v>
@@ -2000,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>49314</v>
+        <v>49605</v>
       </c>
       <c r="E36">
         <v>129572</v>
       </c>
       <c r="F36">
-        <v>76314</v>
+        <v>76605</v>
       </c>
       <c r="G36">
-        <v>109892</v>
+        <v>110311</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2046,19 +2046,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35587</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>129572</v>
       </c>
       <c r="F37">
-        <v>62587</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>90125</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2089,16 +2089,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>67547</v>
+        <v>67347</v>
       </c>
       <c r="E38">
         <v>185111</v>
       </c>
       <c r="F38">
-        <v>94547</v>
+        <v>94347</v>
       </c>
       <c r="G38">
-        <v>136148</v>
+        <v>135860</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2134,19 +2134,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>62038</v>
       </c>
       <c r="E39">
         <v>185111</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>89038</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>128215</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2177,19 +2177,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>108504</v>
+        <v>108121</v>
       </c>
       <c r="E40">
         <v>240650</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>135121</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>194574</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2222,19 +2222,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>88753</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>185111</v>
       </c>
       <c r="F41">
-        <v>113694</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>163719</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>24941</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2307,16 +2307,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>31640</v>
+        <v>31529</v>
       </c>
       <c r="E43">
         <v>129572</v>
       </c>
       <c r="F43">
-        <v>58640</v>
+        <v>58529</v>
       </c>
       <c r="G43">
-        <v>84442</v>
+        <v>84282</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>79532</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>185111</v>
       </c>
       <c r="F45">
-        <v>106532</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>153406</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2478,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>16715</v>
+        <v>19463</v>
       </c>
       <c r="E47">
         <v>111059</v>
       </c>
       <c r="F47">
-        <v>43715</v>
+        <v>46463</v>
       </c>
       <c r="G47">
-        <v>62950</v>
+        <v>66907</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2608,19 +2608,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>34820</v>
+        <v>43054</v>
       </c>
       <c r="E50">
         <v>64777</v>
       </c>
       <c r="F50">
-        <v>57833</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>83280</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>23013</v>
+        <v>0</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2654,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>34197</v>
+        <v>33984</v>
       </c>
       <c r="E51">
         <v>64777</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>48984</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>70537</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2698,19 +2698,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>54316</v>
+        <v>54180</v>
       </c>
       <c r="E52">
         <v>77736</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>69180</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>99619</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2744,19 +2744,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>59110</v>
+        <v>67522</v>
       </c>
       <c r="E53">
         <v>77736</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>82522</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>118832</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48611</v>
+        <v>48745</v>
       </c>
       <c r="E54">
         <v>129572</v>
       </c>
       <c r="F54">
-        <v>82478</v>
+        <v>82318</v>
       </c>
       <c r="G54">
-        <v>118768</v>
+        <v>118538</v>
       </c>
       <c r="H54">
-        <v>33867</v>
+        <v>33573</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2834,16 +2834,16 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>44680</v>
+        <v>44520</v>
       </c>
       <c r="E55">
         <v>129572</v>
       </c>
       <c r="F55">
-        <v>71680</v>
+        <v>71520</v>
       </c>
       <c r="G55">
-        <v>103219</v>
+        <v>102989</v>
       </c>
       <c r="H55">
         <v>27000</v>
@@ -2878,16 +2878,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53501</v>
+        <v>53351</v>
       </c>
       <c r="E56">
         <v>148085</v>
       </c>
       <c r="F56">
-        <v>80501</v>
+        <v>80351</v>
       </c>
       <c r="G56">
-        <v>115921</v>
+        <v>115705</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2924,19 +2924,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>65949</v>
+        <v>65705</v>
       </c>
       <c r="E57">
         <v>148085</v>
       </c>
       <c r="F57">
-        <v>90133</v>
+        <v>90035</v>
       </c>
       <c r="G57">
-        <v>129792</v>
+        <v>129650</v>
       </c>
       <c r="H57">
-        <v>24184</v>
+        <v>24330</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>17210</v>
+        <v>16928</v>
       </c>
       <c r="E58">
         <v>37007</v>
       </c>
       <c r="F58">
-        <v>38652</v>
+        <v>38646</v>
       </c>
       <c r="G58">
-        <v>55659</v>
+        <v>55650</v>
       </c>
       <c r="H58">
-        <v>21442</v>
+        <v>21718</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3013,19 +3013,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6216</v>
+        <v>6201</v>
       </c>
       <c r="E59">
         <v>37007</v>
       </c>
       <c r="F59">
-        <v>22919</v>
+        <v>22913</v>
       </c>
       <c r="G59">
-        <v>33003</v>
+        <v>32995</v>
       </c>
       <c r="H59">
-        <v>16703</v>
+        <v>16712</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3057,19 +3057,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>23698</v>
+        <v>24085</v>
       </c>
       <c r="E60">
         <v>49967</v>
       </c>
       <c r="F60">
-        <v>48584</v>
+        <v>39085</v>
       </c>
       <c r="G60">
-        <v>69961</v>
+        <v>56282</v>
       </c>
       <c r="H60">
-        <v>24886</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3102,7 +3102,7 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25584</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>49967</v>
@@ -3187,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13759</v>
+        <v>13677</v>
       </c>
       <c r="E63">
         <v>83290</v>
       </c>
       <c r="F63">
-        <v>40759</v>
+        <v>40677</v>
       </c>
       <c r="G63">
-        <v>58693</v>
+        <v>58575</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3273,16 +3273,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>34021</v>
+        <v>33904</v>
       </c>
       <c r="E65">
         <v>124926</v>
       </c>
       <c r="F65">
-        <v>61021</v>
+        <v>60904</v>
       </c>
       <c r="G65">
-        <v>87870</v>
+        <v>87702</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3317,19 +3317,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25840</v>
+        <v>25743</v>
       </c>
       <c r="E66">
         <v>92546</v>
       </c>
       <c r="F66">
-        <v>60532</v>
+        <v>60465</v>
       </c>
       <c r="G66">
-        <v>87166</v>
+        <v>87070</v>
       </c>
       <c r="H66">
-        <v>34692</v>
+        <v>34722</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3362,16 +3362,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>20486</v>
+        <v>20419</v>
       </c>
       <c r="E67">
         <v>92546</v>
       </c>
       <c r="F67">
-        <v>47486</v>
+        <v>47419</v>
       </c>
       <c r="G67">
-        <v>68380</v>
+        <v>68283</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>47988</v>
+        <v>47836</v>
       </c>
       <c r="E68">
         <v>111059</v>
       </c>
       <c r="F68">
-        <v>75017</v>
+        <v>74836</v>
       </c>
       <c r="G68">
-        <v>108024</v>
+        <v>107764</v>
       </c>
       <c r="H68">
-        <v>27029</v>
+        <v>27000</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3452,19 +3452,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27741</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>111059</v>
       </c>
       <c r="F69">
-        <v>54741</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>78827</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3495,19 +3495,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>110438</v>
+        <v>115900</v>
       </c>
       <c r="E70">
         <v>129572</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>130900</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>188496</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3539,19 +3539,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>52686</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>129572</v>
       </c>
       <c r="F71">
-        <v>77608</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>111756</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>24922</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3626,16 +3626,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6776</v>
+        <v>6743</v>
       </c>
       <c r="E73">
         <v>27751</v>
       </c>
       <c r="F73">
-        <v>21776</v>
+        <v>21743</v>
       </c>
       <c r="G73">
-        <v>31357</v>
+        <v>31310</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3712,19 +3712,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70456</v>
+        <v>70024</v>
       </c>
       <c r="E75">
         <v>97175</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85024</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>122435</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3755,19 +3755,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>88002</v>
+        <v>87686</v>
       </c>
       <c r="E76">
         <v>129572</v>
       </c>
       <c r="F76">
-        <v>120886</v>
+        <v>120803</v>
       </c>
       <c r="G76">
-        <v>174076</v>
+        <v>173956</v>
       </c>
       <c r="H76">
-        <v>32884</v>
+        <v>33117</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3800,19 +3800,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>57336</v>
+        <v>57129</v>
       </c>
       <c r="E77">
         <v>129572</v>
       </c>
       <c r="F77">
-        <v>79468</v>
+        <v>79385</v>
       </c>
       <c r="G77">
-        <v>114434</v>
+        <v>114314</v>
       </c>
       <c r="H77">
-        <v>22132</v>
+        <v>22256</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3974,16 +3974,16 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>19528</v>
+        <v>19383</v>
       </c>
       <c r="E81">
         <v>92546</v>
       </c>
       <c r="F81">
-        <v>46528</v>
+        <v>46383</v>
       </c>
       <c r="G81">
-        <v>67000</v>
+        <v>66792</v>
       </c>
       <c r="H81">
         <v>27000</v>
@@ -4060,19 +4060,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>87043</v>
+        <v>86730</v>
       </c>
       <c r="E83">
         <v>129572</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>101730</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>146491</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4104,19 +4104,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>45383</v>
+        <v>44823</v>
       </c>
       <c r="E84">
         <v>74033</v>
       </c>
       <c r="F84">
-        <v>67325</v>
+        <v>67111</v>
       </c>
       <c r="G84">
-        <v>96948</v>
+        <v>96640</v>
       </c>
       <c r="H84">
-        <v>21942</v>
+        <v>22288</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4148,19 +4148,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>43514</v>
+        <v>43357</v>
       </c>
       <c r="E85">
         <v>74033</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>58357</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>84034</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4367,19 +4367,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>8949</v>
+        <v>8926</v>
       </c>
       <c r="E90">
         <v>59223</v>
       </c>
       <c r="F90">
-        <v>38573</v>
+        <v>38570</v>
       </c>
       <c r="G90">
-        <v>55545</v>
+        <v>55541</v>
       </c>
       <c r="H90">
-        <v>29624</v>
+        <v>29644</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4413,19 +4413,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3691</v>
+        <v>3682</v>
       </c>
       <c r="E91">
         <v>59223</v>
       </c>
       <c r="F91">
-        <v>30573</v>
+        <v>30570</v>
       </c>
       <c r="G91">
-        <v>44025</v>
+        <v>44021</v>
       </c>
       <c r="H91">
-        <v>26882</v>
+        <v>26888</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4499,19 +4499,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>7798</v>
+        <v>7763</v>
       </c>
       <c r="E93">
         <v>27751</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>22763</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>32779</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4629,19 +4629,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>63521</v>
+        <v>45572</v>
       </c>
       <c r="E96">
         <v>83290</v>
       </c>
       <c r="F96">
-        <v>79199</v>
+        <v>62468</v>
       </c>
       <c r="G96">
-        <v>114047</v>
+        <v>89954</v>
       </c>
       <c r="H96">
-        <v>15678</v>
+        <v>16896</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4675,19 +4675,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>34501</v>
+        <v>34383</v>
       </c>
       <c r="E97">
         <v>83290</v>
       </c>
       <c r="F97">
-        <v>52284</v>
+        <v>52237</v>
       </c>
       <c r="G97">
-        <v>75289</v>
+        <v>75221</v>
       </c>
       <c r="H97">
-        <v>17783</v>
+        <v>17854</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4719,19 +4719,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79165</v>
+        <v>49876</v>
       </c>
       <c r="E98">
         <v>96249</v>
       </c>
       <c r="F98">
-        <v>94165</v>
+        <v>72187</v>
       </c>
       <c r="G98">
-        <v>135598</v>
+        <v>103949</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>22311</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4765,19 +4765,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>41005</v>
+        <v>40854</v>
       </c>
       <c r="E99">
         <v>96249</v>
       </c>
       <c r="F99">
-        <v>59939</v>
+        <v>59879</v>
       </c>
       <c r="G99">
-        <v>86312</v>
+        <v>86226</v>
       </c>
       <c r="H99">
-        <v>18934</v>
+        <v>19025</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4809,19 +4809,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61203</v>
+        <v>60875</v>
       </c>
       <c r="E100">
         <v>107912</v>
       </c>
       <c r="F100">
-        <v>80934</v>
+        <v>78910</v>
       </c>
       <c r="G100">
-        <v>116545</v>
+        <v>113630</v>
       </c>
       <c r="H100">
-        <v>19731</v>
+        <v>18035</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4855,7 +4855,7 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>63441</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>107912</v>
@@ -5027,7 +5027,7 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>71782</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>129572</v>
@@ -5112,19 +5112,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>75138</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>185111</v>
       </c>
       <c r="F107">
-        <v>102138</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>147079</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5197,16 +5197,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>6056</v>
+        <v>6137</v>
       </c>
       <c r="E109">
         <v>129572</v>
       </c>
       <c r="F109">
-        <v>33056</v>
+        <v>33137</v>
       </c>
       <c r="G109">
-        <v>47601</v>
+        <v>47717</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5284,16 +5284,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>15069</v>
+        <v>15015</v>
       </c>
       <c r="E111">
         <v>166598</v>
       </c>
       <c r="F111">
-        <v>42069</v>
+        <v>42015</v>
       </c>
       <c r="G111">
-        <v>60579</v>
+        <v>60502</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5370,19 +5370,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>51216</v>
+        <v>50865</v>
       </c>
       <c r="E113">
         <v>129572</v>
       </c>
       <c r="F113">
-        <v>77020</v>
+        <v>76879</v>
       </c>
       <c r="G113">
-        <v>110909</v>
+        <v>110706</v>
       </c>
       <c r="H113">
-        <v>25804</v>
+        <v>26014</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5456,19 +5456,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>99731</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>185111</v>
       </c>
       <c r="F115">
-        <v>118086</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>170044</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>18355</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4080220/EA_SPORTS_FC_27/","Abrir Steam")</f>
@@ -5584,19 +5584,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>80220</v>
+        <v>79923</v>
       </c>
       <c r="E118">
         <v>88844</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>94923</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>136689</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5629,19 +5629,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>50129</v>
+        <v>49940</v>
       </c>
       <c r="E119">
         <v>88844</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>64940</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>93514</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5716,19 +5716,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>86036</v>
+        <v>101665</v>
       </c>
       <c r="E121">
         <v>118465</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>116665</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>167998</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5760,19 +5760,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>207124</v>
       </c>
       <c r="E122">
         <v>148085</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>222124</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>319859</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5803,7 +5803,7 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>111109</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>148085</v>
@@ -5846,16 +5846,16 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>46118</v>
+        <v>45987</v>
       </c>
       <c r="E124">
         <v>59223</v>
       </c>
       <c r="F124">
-        <v>61118</v>
+        <v>60987</v>
       </c>
       <c r="G124">
-        <v>88010</v>
+        <v>87821</v>
       </c>
       <c r="H124">
         <v>15000</v>
@@ -5891,19 +5891,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>35524</v>
+        <v>35387</v>
       </c>
       <c r="E125">
         <v>59223</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>50387</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>72557</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5935,16 +5935,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>63648</v>
+        <v>63457</v>
       </c>
       <c r="E126">
         <v>81439</v>
       </c>
       <c r="F126">
-        <v>78648</v>
+        <v>78457</v>
       </c>
       <c r="G126">
-        <v>113253</v>
+        <v>112978</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -5980,7 +5980,7 @@
         <v>17</v>
       </c>
       <c r="D127">
-        <v>52686</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>81439</v>
@@ -6023,19 +6023,19 @@
         <v>15</v>
       </c>
       <c r="D128">
-        <v>39151</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>92546</v>
       </c>
       <c r="F128">
-        <v>63306</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>91161</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>24155</v>
+        <v>0</v>
       </c>
       <c r="I128" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6066,19 +6066,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>32391</v>
+        <v>32183</v>
       </c>
       <c r="E129">
         <v>92546</v>
       </c>
       <c r="F129">
-        <v>55049</v>
+        <v>54966</v>
       </c>
       <c r="G129">
-        <v>79271</v>
+        <v>79151</v>
       </c>
       <c r="H129">
-        <v>22658</v>
+        <v>22783</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6110,19 +6110,19 @@
         <v>15</v>
       </c>
       <c r="D130">
-        <v>12720</v>
+        <v>12672</v>
       </c>
       <c r="E130">
         <v>44413</v>
       </c>
       <c r="F130">
-        <v>33149</v>
+        <v>33138</v>
       </c>
       <c r="G130">
-        <v>47735</v>
+        <v>47719</v>
       </c>
       <c r="H130">
-        <v>20429</v>
+        <v>20466</v>
       </c>
       <c r="I130" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6156,19 +6156,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>4570</v>
+        <v>4543</v>
       </c>
       <c r="E131">
         <v>44413</v>
       </c>
       <c r="F131">
-        <v>25149</v>
+        <v>25138</v>
       </c>
       <c r="G131">
-        <v>36215</v>
+        <v>36199</v>
       </c>
       <c r="H131">
-        <v>20579</v>
+        <v>20595</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6200,19 +6200,19 @@
         <v>15</v>
       </c>
       <c r="D132">
-        <v>27661</v>
+        <v>27576</v>
       </c>
       <c r="E132">
         <v>59223</v>
       </c>
       <c r="F132">
-        <v>43715</v>
+        <v>43681</v>
       </c>
       <c r="G132">
-        <v>62950</v>
+        <v>62901</v>
       </c>
       <c r="H132">
-        <v>16054</v>
+        <v>16105</v>
       </c>
       <c r="I132" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6332,19 +6332,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>17322</v>
+        <v>17247</v>
       </c>
       <c r="E135">
         <v>60686</v>
       </c>
       <c r="F135">
-        <v>36596</v>
+        <v>36566</v>
       </c>
       <c r="G135">
-        <v>52698</v>
+        <v>52655</v>
       </c>
       <c r="H135">
-        <v>19274</v>
+        <v>19319</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6418,19 +6418,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>28045</v>
+        <v>27943</v>
       </c>
       <c r="E137">
         <v>75607</v>
       </c>
       <c r="F137">
-        <v>46705</v>
+        <v>46664</v>
       </c>
       <c r="G137">
-        <v>67255</v>
+        <v>67196</v>
       </c>
       <c r="H137">
-        <v>18660</v>
+        <v>18721</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6505,19 +6505,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>26958</v>
+        <v>26668</v>
       </c>
       <c r="E139">
         <v>95175</v>
       </c>
       <c r="F139">
-        <v>53902</v>
+        <v>53668</v>
       </c>
       <c r="G139">
-        <v>77619</v>
+        <v>77282</v>
       </c>
       <c r="H139">
-        <v>26944</v>
+        <v>27000</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6591,19 +6591,19 @@
         <v>17</v>
       </c>
       <c r="D141">
-        <v>56202</v>
+        <v>57942</v>
       </c>
       <c r="E141">
         <v>90695</v>
       </c>
       <c r="F141">
-        <v>71202</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>102531</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6677,19 +6677,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>77583</v>
+        <v>77293</v>
       </c>
       <c r="E143">
         <v>129572</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>92293</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>132902</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6763,19 +6763,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>87139</v>
+        <v>86825</v>
       </c>
       <c r="E145">
         <v>155491</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>101825</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>146628</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6849,19 +6849,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>86468</v>
+        <v>85948</v>
       </c>
       <c r="E147">
         <v>90695</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>100948</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>145365</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6935,19 +6935,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>122710</v>
+        <v>126340</v>
       </c>
       <c r="E149">
         <v>129572</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>141340</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>203530</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3010850/Gears_of_War_EDay/","Abrir Steam")</f>
@@ -6979,19 +6979,19 @@
         <v>15</v>
       </c>
       <c r="D150">
-        <v>38288</v>
+        <v>38144</v>
       </c>
       <c r="E150">
         <v>92546</v>
       </c>
       <c r="F150">
-        <v>62961</v>
+        <v>62904</v>
       </c>
       <c r="G150">
-        <v>90664</v>
+        <v>90582</v>
       </c>
       <c r="H150">
-        <v>24673</v>
+        <v>24760</v>
       </c>
       <c r="I150" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -7067,16 +7067,16 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>23427</v>
+        <v>24707</v>
       </c>
       <c r="E152">
         <v>92546</v>
       </c>
       <c r="F152">
-        <v>58427</v>
+        <v>59707</v>
       </c>
       <c r="G152">
-        <v>84135</v>
+        <v>85978</v>
       </c>
       <c r="H152">
         <v>35000</v>
@@ -7111,19 +7111,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>29643</v>
+        <v>29537</v>
       </c>
       <c r="E153">
         <v>92546</v>
       </c>
       <c r="F153">
-        <v>53950</v>
+        <v>53908</v>
       </c>
       <c r="G153">
-        <v>77688</v>
+        <v>77628</v>
       </c>
       <c r="H153">
-        <v>24307</v>
+        <v>24371</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -7155,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>48707</v>
+        <v>48521</v>
       </c>
       <c r="E154">
         <v>92546</v>
@@ -7167,7 +7167,7 @@
         <v>99950</v>
       </c>
       <c r="H154">
-        <v>20703</v>
+        <v>20889</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7200,19 +7200,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>76113</v>
+        <v>75843</v>
       </c>
       <c r="E155">
         <v>92546</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>90843</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>130814</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7244,19 +7244,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>65454</v>
+        <v>65211</v>
       </c>
       <c r="E156">
         <v>92546</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>80211</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>115504</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7332,19 +7332,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>39135</v>
+        <v>39037</v>
       </c>
       <c r="E158">
         <v>62926</v>
       </c>
       <c r="F158">
-        <v>65642</v>
+        <v>65424</v>
       </c>
       <c r="G158">
-        <v>94524</v>
+        <v>94211</v>
       </c>
       <c r="H158">
-        <v>26507</v>
+        <v>26387</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7378,19 +7378,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>42043</v>
+        <v>41890</v>
       </c>
       <c r="E159">
         <v>62926</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>56890</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>81922</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7463,19 +7463,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>18313</v>
+        <v>18203</v>
       </c>
       <c r="E161">
         <v>55520</v>
       </c>
       <c r="F161">
-        <v>34978</v>
+        <v>34934</v>
       </c>
       <c r="G161">
-        <v>50368</v>
+        <v>50305</v>
       </c>
       <c r="H161">
-        <v>16665</v>
+        <v>16731</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7549,19 +7549,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>56106</v>
+        <v>55902</v>
       </c>
       <c r="E163">
         <v>74033</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>70902</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>102099</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>70855</v>
+        <v>70423</v>
       </c>
       <c r="E165">
         <v>111059</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>85423</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>123009</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2806050/Halo_Campaign_Evolved/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>54316</v>
+        <v>54180</v>
       </c>
       <c r="E166">
         <v>74033</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>69180</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>99619</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7725,19 +7725,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>33989</v>
+        <v>43213</v>
       </c>
       <c r="E167">
         <v>74033</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>58213</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>83827</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7769,19 +7769,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>5209</v>
+        <v>62788</v>
       </c>
       <c r="E168">
         <v>74033</v>
       </c>
       <c r="F168">
-        <v>40209</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>57901</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7815,7 +7815,7 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>74307</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>74033</v>
@@ -7902,19 +7902,19 @@
         <v>17</v>
     